--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Sales_Record" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rate" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="REPORT (EN)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="REPORT (TH)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ทีมขาย" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Rate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="REPORT (EN)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="REPORT (TH)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;฿&quot;"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,8 +162,13 @@
       <color rgb="008A5A12"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006A7682"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -249,8 +255,13 @@
         <fgColor rgb="00FCEFD8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5F8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -333,11 +344,101 @@
         <color rgb="009AA7B2"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="009AA7B2"/>
+      </right>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C4CDD5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="009AA7B2"/>
+      </right>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C4CDD5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C4CDD5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C4CDD5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C4CDD5"/>
+      </right>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="009AA7B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C4CDD5"/>
+      </right>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="009AA7B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -534,6 +635,42 @@
     <xf numFmtId="1" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1011,20 +1148,17 @@
           <t>รวม</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>MIZTEEN</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
-        <is>
-          <t>OLIVE</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
+      <c r="L5" s="11">
+        <f>'ทีมขาย'!A6</f>
+        <v/>
+      </c>
+      <c r="M5" s="11">
+        <f>'ทีมขาย'!A7</f>
+        <v/>
+      </c>
+      <c r="N5" s="11">
+        <f>'ทีมขาย'!A8</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -1065,15 +1199,15 @@
         <v/>
       </c>
       <c r="L6" s="13">
-        <f>SUMIF(K13:K52,"MIZTEEN",M13:M52)</f>
+        <f>SUMIF($K$13:$K$52,L5,$M$13:$M$52)</f>
         <v/>
       </c>
       <c r="M6" s="13">
-        <f>SUMIF(K13:K52,"OLIVE",M13:M52)</f>
+        <f>SUMIF($K$13:$K$52,M5,$M$13:$M$52)</f>
         <v/>
       </c>
       <c r="N6" s="13">
-        <f>SUMIF(K13:K52,"SUPPORT",M13:M52)</f>
+        <f>SUMIF($K$13:$K$52,N5,$M$13:$M$52)</f>
         <v/>
       </c>
     </row>
@@ -1104,6 +1238,8 @@
           <t>จำนวนดีลทั้งหมด</t>
         </is>
       </c>
+      <c r="H7" s="70" t="n"/>
+      <c r="I7" s="18" t="n"/>
       <c r="K7" s="17" t="inlineStr">
         <is>
           <t>จ่ายแล้ว</t>
@@ -1115,6 +1251,7 @@
           <t>ค้างจ่าย</t>
         </is>
       </c>
+      <c r="N7" s="18" t="n"/>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="14">
@@ -1125,14 +1262,18 @@
         <f>COUNTA(B13:B52)</f>
         <v/>
       </c>
+      <c r="H8" s="70" t="n"/>
+      <c r="I8" s="18" t="n"/>
       <c r="K8" s="12">
         <f>SUMIF(N13:N52,"จ่ายแล้ว",M13:M52)</f>
         <v/>
       </c>
+      <c r="L8" s="18" t="n"/>
       <c r="M8" s="20">
         <f>SUM(M13:M52)-SUMIF(N13:N52,"จ่ายแล้ว",M13:M52)</f>
         <v/>
       </c>
+      <c r="N8" s="18" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
@@ -1140,6 +1281,8 @@
           <t>บันทึก</t>
         </is>
       </c>
+      <c r="B11" s="71" t="n"/>
+      <c r="C11" s="72" t="n"/>
       <c r="D11" s="22" t="inlineStr">
         <is>
           <t>ลูกค้า</t>
@@ -1150,6 +1293,7 @@
           <t>ธุรกรรม</t>
         </is>
       </c>
+      <c r="F11" s="72" t="n"/>
       <c r="G11" s="22" t="inlineStr">
         <is>
           <t>บริการ</t>
@@ -1160,11 +1304,15 @@
           <t>รายได้ (THB)</t>
         </is>
       </c>
+      <c r="I11" s="71" t="n"/>
+      <c r="J11" s="72" t="n"/>
       <c r="K11" s="25" t="inlineStr">
         <is>
           <t>ค่าคอมมิชชั่น</t>
         </is>
       </c>
+      <c r="L11" s="71" t="n"/>
+      <c r="M11" s="72" t="n"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t>สถานะ</t>
@@ -1268,7 +1416,7 @@
       </c>
       <c r="K13" s="31" t="n"/>
       <c r="L13" s="35">
-        <f>IF(G13="","",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G13="","",IF(K13="",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K13,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M13" s="36">
@@ -1302,7 +1450,7 @@
       </c>
       <c r="K14" s="37" t="n"/>
       <c r="L14" s="41">
-        <f>IF(G14="","",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G14="","",IF(K14="",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K14,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M14" s="42">
@@ -1336,7 +1484,7 @@
       </c>
       <c r="K15" s="31" t="n"/>
       <c r="L15" s="35">
-        <f>IF(G15="","",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G15="","",IF(K15="",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K15,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M15" s="36">
@@ -1370,7 +1518,7 @@
       </c>
       <c r="K16" s="37" t="n"/>
       <c r="L16" s="41">
-        <f>IF(G16="","",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G16="","",IF(K16="",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K16,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M16" s="42">
@@ -1404,7 +1552,7 @@
       </c>
       <c r="K17" s="31" t="n"/>
       <c r="L17" s="35">
-        <f>IF(G17="","",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G17="","",IF(K17="",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K17,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M17" s="36">
@@ -1438,7 +1586,7 @@
       </c>
       <c r="K18" s="37" t="n"/>
       <c r="L18" s="41">
-        <f>IF(G18="","",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G18="","",IF(K18="",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K18,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M18" s="42">
@@ -1472,7 +1620,7 @@
       </c>
       <c r="K19" s="31" t="n"/>
       <c r="L19" s="35">
-        <f>IF(G19="","",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G19="","",IF(K19="",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K19,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M19" s="36">
@@ -1506,7 +1654,7 @@
       </c>
       <c r="K20" s="37" t="n"/>
       <c r="L20" s="41">
-        <f>IF(G20="","",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G20="","",IF(K20="",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K20,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M20" s="42">
@@ -1540,7 +1688,7 @@
       </c>
       <c r="K21" s="31" t="n"/>
       <c r="L21" s="35">
-        <f>IF(G21="","",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G21="","",IF(K21="",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K21,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M21" s="36">
@@ -1574,7 +1722,7 @@
       </c>
       <c r="K22" s="37" t="n"/>
       <c r="L22" s="41">
-        <f>IF(G22="","",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G22="","",IF(K22="",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K22,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M22" s="42">
@@ -1608,7 +1756,7 @@
       </c>
       <c r="K23" s="31" t="n"/>
       <c r="L23" s="35">
-        <f>IF(G23="","",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G23="","",IF(K23="",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K23,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M23" s="36">
@@ -1642,7 +1790,7 @@
       </c>
       <c r="K24" s="37" t="n"/>
       <c r="L24" s="41">
-        <f>IF(G24="","",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G24="","",IF(K24="",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K24,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M24" s="42">
@@ -1676,7 +1824,7 @@
       </c>
       <c r="K25" s="31" t="n"/>
       <c r="L25" s="35">
-        <f>IF(G25="","",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G25="","",IF(K25="",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K25,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M25" s="36">
@@ -1710,7 +1858,7 @@
       </c>
       <c r="K26" s="37" t="n"/>
       <c r="L26" s="41">
-        <f>IF(G26="","",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G26="","",IF(K26="",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K26,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M26" s="42">
@@ -1744,7 +1892,7 @@
       </c>
       <c r="K27" s="31" t="n"/>
       <c r="L27" s="35">
-        <f>IF(G27="","",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G27="","",IF(K27="",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K27,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M27" s="36">
@@ -1778,7 +1926,7 @@
       </c>
       <c r="K28" s="37" t="n"/>
       <c r="L28" s="41">
-        <f>IF(G28="","",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G28="","",IF(K28="",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K28,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M28" s="42">
@@ -1812,7 +1960,7 @@
       </c>
       <c r="K29" s="31" t="n"/>
       <c r="L29" s="35">
-        <f>IF(G29="","",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G29="","",IF(K29="",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K29,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M29" s="36">
@@ -1846,7 +1994,7 @@
       </c>
       <c r="K30" s="37" t="n"/>
       <c r="L30" s="41">
-        <f>IF(G30="","",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G30="","",IF(K30="",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K30,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M30" s="42">
@@ -1880,7 +2028,7 @@
       </c>
       <c r="K31" s="31" t="n"/>
       <c r="L31" s="35">
-        <f>IF(G31="","",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G31="","",IF(K31="",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K31,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M31" s="36">
@@ -1914,7 +2062,7 @@
       </c>
       <c r="K32" s="37" t="n"/>
       <c r="L32" s="41">
-        <f>IF(G32="","",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G32="","",IF(K32="",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K32,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M32" s="42">
@@ -1948,7 +2096,7 @@
       </c>
       <c r="K33" s="31" t="n"/>
       <c r="L33" s="35">
-        <f>IF(G33="","",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G33="","",IF(K33="",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K33,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M33" s="36">
@@ -1982,7 +2130,7 @@
       </c>
       <c r="K34" s="37" t="n"/>
       <c r="L34" s="41">
-        <f>IF(G34="","",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G34="","",IF(K34="",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K34,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M34" s="42">
@@ -2016,7 +2164,7 @@
       </c>
       <c r="K35" s="31" t="n"/>
       <c r="L35" s="35">
-        <f>IF(G35="","",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G35="","",IF(K35="",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K35,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M35" s="36">
@@ -2050,7 +2198,7 @@
       </c>
       <c r="K36" s="37" t="n"/>
       <c r="L36" s="41">
-        <f>IF(G36="","",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G36="","",IF(K36="",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K36,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M36" s="42">
@@ -2084,7 +2232,7 @@
       </c>
       <c r="K37" s="31" t="n"/>
       <c r="L37" s="35">
-        <f>IF(G37="","",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G37="","",IF(K37="",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K37,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M37" s="36">
@@ -2118,7 +2266,7 @@
       </c>
       <c r="K38" s="37" t="n"/>
       <c r="L38" s="41">
-        <f>IF(G38="","",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G38="","",IF(K38="",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K38,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M38" s="42">
@@ -2152,7 +2300,7 @@
       </c>
       <c r="K39" s="31" t="n"/>
       <c r="L39" s="35">
-        <f>IF(G39="","",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G39="","",IF(K39="",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K39,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M39" s="36">
@@ -2186,7 +2334,7 @@
       </c>
       <c r="K40" s="37" t="n"/>
       <c r="L40" s="41">
-        <f>IF(G40="","",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G40="","",IF(K40="",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K40,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M40" s="42">
@@ -2220,7 +2368,7 @@
       </c>
       <c r="K41" s="31" t="n"/>
       <c r="L41" s="35">
-        <f>IF(G41="","",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G41="","",IF(K41="",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K41,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M41" s="36">
@@ -2254,7 +2402,7 @@
       </c>
       <c r="K42" s="37" t="n"/>
       <c r="L42" s="41">
-        <f>IF(G42="","",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G42="","",IF(K42="",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K42,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M42" s="42">
@@ -2288,7 +2436,7 @@
       </c>
       <c r="K43" s="31" t="n"/>
       <c r="L43" s="35">
-        <f>IF(G43="","",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G43="","",IF(K43="",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K43,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M43" s="36">
@@ -2322,7 +2470,7 @@
       </c>
       <c r="K44" s="37" t="n"/>
       <c r="L44" s="41">
-        <f>IF(G44="","",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G44="","",IF(K44="",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K44,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M44" s="42">
@@ -2356,7 +2504,7 @@
       </c>
       <c r="K45" s="31" t="n"/>
       <c r="L45" s="35">
-        <f>IF(G45="","",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G45="","",IF(K45="",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K45,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M45" s="36">
@@ -2390,7 +2538,7 @@
       </c>
       <c r="K46" s="37" t="n"/>
       <c r="L46" s="41">
-        <f>IF(G46="","",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G46="","",IF(K46="",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K46,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M46" s="42">
@@ -2424,7 +2572,7 @@
       </c>
       <c r="K47" s="31" t="n"/>
       <c r="L47" s="35">
-        <f>IF(G47="","",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G47="","",IF(K47="",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K47,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M47" s="36">
@@ -2458,7 +2606,7 @@
       </c>
       <c r="K48" s="37" t="n"/>
       <c r="L48" s="41">
-        <f>IF(G48="","",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G48="","",IF(K48="",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K48,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M48" s="42">
@@ -2492,7 +2640,7 @@
       </c>
       <c r="K49" s="31" t="n"/>
       <c r="L49" s="35">
-        <f>IF(G49="","",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G49="","",IF(K49="",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K49,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M49" s="36">
@@ -2526,7 +2674,7 @@
       </c>
       <c r="K50" s="37" t="n"/>
       <c r="L50" s="41">
-        <f>IF(G50="","",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G50="","",IF(K50="",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K50,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M50" s="42">
@@ -2560,7 +2708,7 @@
       </c>
       <c r="K51" s="31" t="n"/>
       <c r="L51" s="35">
-        <f>IF(G51="","",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G51="","",IF(K51="",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K51,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M51" s="36">
@@ -2594,7 +2742,7 @@
       </c>
       <c r="K52" s="37" t="n"/>
       <c r="L52" s="41">
-        <f>IF(G52="","",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$D$7,4,FALSE)),""))</f>
+        <f>IF(G52="","",IF(K52="",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K52,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
         <v/>
       </c>
       <c r="M52" s="42">
@@ -2610,23 +2758,23 @@
       <c r="D53" s="43" t="n"/>
       <c r="E53" s="43" t="n"/>
       <c r="F53" s="43" t="n"/>
-      <c r="G53" s="44" t="inlineStr">
+      <c r="G53" s="80" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="H53" s="45">
+      <c r="H53" s="83">
         <f>SUM(H13:H52)</f>
         <v/>
       </c>
       <c r="I53" s="43" t="n"/>
-      <c r="J53" s="45">
+      <c r="J53" s="83">
         <f>SUM(J13:J52)</f>
         <v/>
       </c>
       <c r="K53" s="43" t="n"/>
       <c r="L53" s="43" t="n"/>
-      <c r="M53" s="45">
+      <c r="M53" s="83">
         <f>SUM(M13:M52)</f>
         <v/>
       </c>
@@ -2666,11 +2814,11 @@
     <dataValidation sqref="G13:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Starter,Plus,Premium,Enterprise"</formula1>
     </dataValidation>
-    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"MIZTEEN,OLIVE,SUPPORT"</formula1>
-    </dataValidation>
     <dataValidation sqref="N13:N52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"รอจ่าย,จ่ายแล้ว"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'ทีมขาย'!$A$6:$A$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2678,6 +2826,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EASY
+CRM</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>TEAM &amp; COMMISSION RATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>ทีมขายและอัตราค่าคอมส่วนตัว · แก้รายชื่อ/เปอร์เซ็นต์ได้ที่นี่</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="73" t="inlineStr">
+        <is>
+          <t>เพิ่ม/แก้รายชื่อได้เลย · ใส่ % ส่วนตัว (เช่น 12%) เพื่อใช้แทนเรตแพ็กเกจ · เว้นว่าง = คิดตามเรตแพ็กเกจ (แท็บ Rate) · ชื่อในนี้จะกลายเป็นดรอปดาวน์ Sales ในแท็บ Sales_Record อัตโนมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>ชื่อ Sales</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>ตำแหน่ง / บทบาท</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>% ค่าคอมส่วนตัว
+(เว้นว่าง = ตามแพ็กเกจ)</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>จำนวนดีล</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>ค่าคอมรวม (THB)</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>จ่ายแล้ว (THB)</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="inlineStr">
+        <is>
+          <t>ค้างจ่าย (THB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="74" t="inlineStr">
+        <is>
+          <t>MIZTEEN</t>
+        </is>
+      </c>
+      <c r="B6" s="75" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="C6" s="76" t="n"/>
+      <c r="D6" s="77">
+        <f>IF($A6="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E6" s="78">
+        <f>IF($A6="","",SUMIF(Sales_Record!$K$13:$K$52,$A6,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F6" s="79">
+        <f>IF($A6="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G6" s="79">
+        <f>IF($A6="","",E6-F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="74" t="inlineStr">
+        <is>
+          <t>OLIVE</t>
+        </is>
+      </c>
+      <c r="B7" s="75" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="C7" s="76" t="n"/>
+      <c r="D7" s="77">
+        <f>IF($A7="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E7" s="78">
+        <f>IF($A7="","",SUMIF(Sales_Record!$K$13:$K$52,$A7,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F7" s="79">
+        <f>IF($A7="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="79">
+        <f>IF($A7="","",E7-F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="74" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="B8" s="75" t="inlineStr">
+        <is>
+          <t>Support / Sales</t>
+        </is>
+      </c>
+      <c r="C8" s="76" t="n"/>
+      <c r="D8" s="77">
+        <f>IF($A8="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E8" s="78">
+        <f>IF($A8="","",SUMIF(Sales_Record!$K$13:$K$52,$A8,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F8" s="79">
+        <f>IF($A8="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A8,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="79">
+        <f>IF($A8="","",E8-F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr"/>
+      <c r="B9" s="75" t="inlineStr"/>
+      <c r="C9" s="76" t="n"/>
+      <c r="D9" s="77">
+        <f>IF($A9="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E9" s="78">
+        <f>IF($A9="","",SUMIF(Sales_Record!$K$13:$K$52,$A9,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F9" s="79">
+        <f>IF($A9="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A9,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="79">
+        <f>IF($A9="","",E9-F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="74" t="inlineStr"/>
+      <c r="B10" s="75" t="inlineStr"/>
+      <c r="C10" s="76" t="n"/>
+      <c r="D10" s="77">
+        <f>IF($A10="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E10" s="78">
+        <f>IF($A10="","",SUMIF(Sales_Record!$K$13:$K$52,$A10,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F10" s="79">
+        <f>IF($A10="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A10,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="79">
+        <f>IF($A10="","",E10-F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="74" t="inlineStr"/>
+      <c r="B11" s="75" t="inlineStr"/>
+      <c r="C11" s="76" t="n"/>
+      <c r="D11" s="77">
+        <f>IF($A11="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E11" s="78">
+        <f>IF($A11="","",SUMIF(Sales_Record!$K$13:$K$52,$A11,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F11" s="79">
+        <f>IF($A11="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A11,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="79">
+        <f>IF($A11="","",E11-F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="74" t="inlineStr"/>
+      <c r="B12" s="75" t="inlineStr"/>
+      <c r="C12" s="76" t="n"/>
+      <c r="D12" s="77">
+        <f>IF($A12="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="78">
+        <f>IF($A12="","",SUMIF(Sales_Record!$K$13:$K$52,$A12,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F12" s="79">
+        <f>IF($A12="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A12,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="79">
+        <f>IF($A12="","",E12-F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="74" t="inlineStr"/>
+      <c r="B13" s="75" t="inlineStr"/>
+      <c r="C13" s="76" t="n"/>
+      <c r="D13" s="77">
+        <f>IF($A13="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="78">
+        <f>IF($A13="","",SUMIF(Sales_Record!$K$13:$K$52,$A13,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F13" s="79">
+        <f>IF($A13="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A13,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="79">
+        <f>IF($A13="","",E13-F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="74" t="inlineStr"/>
+      <c r="B14" s="75" t="inlineStr"/>
+      <c r="C14" s="76" t="n"/>
+      <c r="D14" s="77">
+        <f>IF($A14="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="78">
+        <f>IF($A14="","",SUMIF(Sales_Record!$K$13:$K$52,$A14,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F14" s="79">
+        <f>IF($A14="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A14,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="79">
+        <f>IF($A14="","",E14-F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="74" t="inlineStr"/>
+      <c r="B15" s="75" t="inlineStr"/>
+      <c r="C15" s="76" t="n"/>
+      <c r="D15" s="77">
+        <f>IF($A15="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="78">
+        <f>IF($A15="","",SUMIF(Sales_Record!$K$13:$K$52,$A15,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F15" s="79">
+        <f>IF($A15="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A15,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="79">
+        <f>IF($A15="","",E15-F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="74" t="inlineStr"/>
+      <c r="B16" s="75" t="inlineStr"/>
+      <c r="C16" s="76" t="n"/>
+      <c r="D16" s="77">
+        <f>IF($A16="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="78">
+        <f>IF($A16="","",SUMIF(Sales_Record!$K$13:$K$52,$A16,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F16" s="79">
+        <f>IF($A16="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A16,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="79">
+        <f>IF($A16="","",E16-F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="74" t="inlineStr"/>
+      <c r="B17" s="75" t="inlineStr"/>
+      <c r="C17" s="76" t="n"/>
+      <c r="D17" s="77">
+        <f>IF($A17="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E17" s="78">
+        <f>IF($A17="","",SUMIF(Sales_Record!$K$13:$K$52,$A17,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F17" s="79">
+        <f>IF($A17="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A17,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G17" s="79">
+        <f>IF($A17="","",E17-F17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="74" t="inlineStr"/>
+      <c r="B18" s="75" t="inlineStr"/>
+      <c r="C18" s="76" t="n"/>
+      <c r="D18" s="77">
+        <f>IF($A18="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="78">
+        <f>IF($A18="","",SUMIF(Sales_Record!$K$13:$K$52,$A18,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F18" s="79">
+        <f>IF($A18="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A18,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="79">
+        <f>IF($A18="","",E18-F18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="74" t="inlineStr"/>
+      <c r="B19" s="75" t="inlineStr"/>
+      <c r="C19" s="76" t="n"/>
+      <c r="D19" s="77">
+        <f>IF($A19="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="78">
+        <f>IF($A19="","",SUMIF(Sales_Record!$K$13:$K$52,$A19,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F19" s="79">
+        <f>IF($A19="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A19,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="79">
+        <f>IF($A19="","",E19-F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="74" t="inlineStr"/>
+      <c r="B20" s="75" t="inlineStr"/>
+      <c r="C20" s="76" t="n"/>
+      <c r="D20" s="77">
+        <f>IF($A20="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A20,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="78">
+        <f>IF($A20="","",SUMIF(Sales_Record!$K$13:$K$52,$A20,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F20" s="79">
+        <f>IF($A20="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A20,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="79">
+        <f>IF($A20="","",E20-F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>รวมทั้งทีม</t>
+        </is>
+      </c>
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="85" t="n"/>
+      <c r="D21" s="82">
+        <f>SUM(D6:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="83">
+        <f>SUM(E6:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="83">
+        <f>SUM(F6:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="83">
+        <f>E21-F21</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A1:B2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2741,7 +3348,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="74" t="inlineStr">
         <is>
           <t>Starter</t>
         </is>
@@ -2789,7 +3396,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="74" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
@@ -2878,13 +3485,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G8"/>
+  <dimension ref="B1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2943,110 +3550,419 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="61" t="inlineStr">
-        <is>
-          <t>MIZTEEN</t>
-        </is>
+      <c r="B5" s="61">
+        <f>IF('ทีมขาย'!A6="","",'ทีมขาย'!A6)</f>
+        <v/>
       </c>
       <c r="C5" s="62">
-        <f>COUNTIFS(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$B$13:$B$52,"&lt;&gt;")</f>
+        <f>IF($B5="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="D5" s="63">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$J$13:$J$52)</f>
+        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$J$13:$J$52))</f>
         <v/>
       </c>
       <c r="E5" s="64">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$M$13:$M$52)</f>
+        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$M$13:$M$52))</f>
         <v/>
       </c>
       <c r="F5" s="63">
-        <f>SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B5,Sales_Record!$N$13:$N$52,"จ่ายแล้ว")</f>
+        <f>IF($B5="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B5,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
         <v/>
       </c>
       <c r="G5" s="63">
-        <f>E5-F5</f>
+        <f>IF($B5="","",E5-F5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="65" t="inlineStr">
-        <is>
-          <t>OLIVE</t>
-        </is>
-      </c>
-      <c r="C6" s="66">
-        <f>COUNTIFS(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$B$13:$B$52,"&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="D6" s="67">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$J$13:$J$52)</f>
-        <v/>
-      </c>
-      <c r="E6" s="68">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$M$13:$M$52)</f>
-        <v/>
-      </c>
-      <c r="F6" s="67">
-        <f>SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว")</f>
-        <v/>
-      </c>
-      <c r="G6" s="67">
-        <f>E6-F6</f>
+      <c r="B6" s="61">
+        <f>IF('ทีมขาย'!A7="","",'ทีมขาย'!A7)</f>
+        <v/>
+      </c>
+      <c r="C6" s="62">
+        <f>IF($B6="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D6" s="63">
+        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E6" s="64">
+        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F6" s="63">
+        <f>IF($B6="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G6" s="63">
+        <f>IF($B6="","",E6-F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="61" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
+      <c r="B7" s="61">
+        <f>IF('ทีมขาย'!A8="","",'ทีมขาย'!A8)</f>
+        <v/>
       </c>
       <c r="C7" s="62">
-        <f>COUNTIFS(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$B$13:$B$52,"&lt;&gt;")</f>
+        <f>IF($B7="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="D7" s="63">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$J$13:$J$52)</f>
+        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$J$13:$J$52))</f>
         <v/>
       </c>
       <c r="E7" s="64">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$M$13:$M$52)</f>
+        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$M$13:$M$52))</f>
         <v/>
       </c>
       <c r="F7" s="63">
-        <f>SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว")</f>
+        <f>IF($B7="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
         <v/>
       </c>
       <c r="G7" s="63">
-        <f>E7-F7</f>
+        <f>IF($B7="","",E7-F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="61">
+        <f>IF('ทีมขาย'!A9="","",'ทีมขาย'!A9)</f>
+        <v/>
+      </c>
+      <c r="C8" s="62">
+        <f>IF($B8="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D8" s="63">
+        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E8" s="64">
+        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F8" s="63">
+        <f>IF($B8="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B8,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="63">
+        <f>IF($B8="","",E8-F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="61">
+        <f>IF('ทีมขาย'!A10="","",'ทีมขาย'!A10)</f>
+        <v/>
+      </c>
+      <c r="C9" s="62">
+        <f>IF($B9="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D9" s="63">
+        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E9" s="64">
+        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F9" s="63">
+        <f>IF($B9="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B9,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="63">
+        <f>IF($B9="","",E9-F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="61">
+        <f>IF('ทีมขาย'!A11="","",'ทีมขาย'!A11)</f>
+        <v/>
+      </c>
+      <c r="C10" s="62">
+        <f>IF($B10="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D10" s="63">
+        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E10" s="64">
+        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F10" s="63">
+        <f>IF($B10="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B10,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="63">
+        <f>IF($B10="","",E10-F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="61">
+        <f>IF('ทีมขาย'!A12="","",'ทีมขาย'!A12)</f>
+        <v/>
+      </c>
+      <c r="C11" s="62">
+        <f>IF($B11="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D11" s="63">
+        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E11" s="64">
+        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F11" s="63">
+        <f>IF($B11="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B11,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="63">
+        <f>IF($B11="","",E11-F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="61">
+        <f>IF('ทีมขาย'!A13="","",'ทีมขาย'!A13)</f>
+        <v/>
+      </c>
+      <c r="C12" s="62">
+        <f>IF($B12="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="63">
+        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E12" s="64">
+        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F12" s="63">
+        <f>IF($B12="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B12,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="63">
+        <f>IF($B12="","",E12-F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="61">
+        <f>IF('ทีมขาย'!A14="","",'ทีมขาย'!A14)</f>
+        <v/>
+      </c>
+      <c r="C13" s="62">
+        <f>IF($B13="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D13" s="63">
+        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E13" s="64">
+        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F13" s="63">
+        <f>IF($B13="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B13,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="63">
+        <f>IF($B13="","",E13-F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="61">
+        <f>IF('ทีมขาย'!A15="","",'ทีมขาย'!A15)</f>
+        <v/>
+      </c>
+      <c r="C14" s="62">
+        <f>IF($B14="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="63">
+        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E14" s="64">
+        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F14" s="63">
+        <f>IF($B14="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B14,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="63">
+        <f>IF($B14="","",E14-F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="61">
+        <f>IF('ทีมขาย'!A16="","",'ทีมขาย'!A16)</f>
+        <v/>
+      </c>
+      <c r="C15" s="62">
+        <f>IF($B15="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="63">
+        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E15" s="64">
+        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F15" s="63">
+        <f>IF($B15="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B15,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="63">
+        <f>IF($B15="","",E15-F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="61">
+        <f>IF('ทีมขาย'!A17="","",'ทีมขาย'!A17)</f>
+        <v/>
+      </c>
+      <c r="C16" s="62">
+        <f>IF($B16="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D16" s="63">
+        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E16" s="64">
+        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F16" s="63">
+        <f>IF($B16="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B16,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="63">
+        <f>IF($B16="","",E16-F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="61">
+        <f>IF('ทีมขาย'!A18="","",'ทีมขาย'!A18)</f>
+        <v/>
+      </c>
+      <c r="C17" s="62">
+        <f>IF($B17="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D17" s="63">
+        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E17" s="64">
+        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F17" s="63">
+        <f>IF($B17="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B17,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G17" s="63">
+        <f>IF($B17="","",E17-F17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="61">
+        <f>IF('ทีมขาย'!A19="","",'ทีมขาย'!A19)</f>
+        <v/>
+      </c>
+      <c r="C18" s="62">
+        <f>IF($B18="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D18" s="63">
+        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E18" s="64">
+        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F18" s="63">
+        <f>IF($B18="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B18,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="63">
+        <f>IF($B18="","",E18-F18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="61">
+        <f>IF('ทีมขาย'!A20="","",'ทีมขาย'!A20)</f>
+        <v/>
+      </c>
+      <c r="C19" s="62">
+        <f>IF($B19="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D19" s="63">
+        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E19" s="64">
+        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F19" s="63">
+        <f>IF($B19="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B19,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="63">
+        <f>IF($B19="","",E19-F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C8" s="69">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="45">
-        <f>SUM(D5:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="45">
-        <f>SUM(E5:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="45">
-        <f>SUM(F5:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="45">
-        <f>SUM(G5:G7)</f>
+      <c r="C20" s="69">
+        <f>SUM(C5:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="83">
+        <f>SUM(D5:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="83">
+        <f>SUM(E5:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="83">
+        <f>SUM(F5:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="83">
+        <f>E20-F20</f>
         <v/>
       </c>
     </row>
@@ -3059,13 +3975,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G8"/>
+  <dimension ref="B1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3124,110 +4040,419 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="61" t="inlineStr">
-        <is>
-          <t>MIZTEEN</t>
-        </is>
+      <c r="B5" s="61">
+        <f>IF('ทีมขาย'!A6="","",'ทีมขาย'!A6)</f>
+        <v/>
       </c>
       <c r="C5" s="62">
-        <f>COUNTIFS(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$B$13:$B$52,"&lt;&gt;")</f>
+        <f>IF($B5="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="D5" s="63">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$J$13:$J$52)</f>
+        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$J$13:$J$52))</f>
         <v/>
       </c>
       <c r="E5" s="64">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$M$13:$M$52)</f>
+        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$M$13:$M$52))</f>
         <v/>
       </c>
       <c r="F5" s="63">
-        <f>SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B5,Sales_Record!$N$13:$N$52,"จ่ายแล้ว")</f>
+        <f>IF($B5="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B5,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
         <v/>
       </c>
       <c r="G5" s="63">
-        <f>E5-F5</f>
+        <f>IF($B5="","",E5-F5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="65" t="inlineStr">
-        <is>
-          <t>OLIVE</t>
-        </is>
-      </c>
-      <c r="C6" s="66">
-        <f>COUNTIFS(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$B$13:$B$52,"&lt;&gt;")</f>
-        <v/>
-      </c>
-      <c r="D6" s="67">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$J$13:$J$52)</f>
-        <v/>
-      </c>
-      <c r="E6" s="68">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$M$13:$M$52)</f>
-        <v/>
-      </c>
-      <c r="F6" s="67">
-        <f>SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว")</f>
-        <v/>
-      </c>
-      <c r="G6" s="67">
-        <f>E6-F6</f>
+      <c r="B6" s="61">
+        <f>IF('ทีมขาย'!A7="","",'ทีมขาย'!A7)</f>
+        <v/>
+      </c>
+      <c r="C6" s="62">
+        <f>IF($B6="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D6" s="63">
+        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E6" s="64">
+        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F6" s="63">
+        <f>IF($B6="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G6" s="63">
+        <f>IF($B6="","",E6-F6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="61" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
+      <c r="B7" s="61">
+        <f>IF('ทีมขาย'!A8="","",'ทีมขาย'!A8)</f>
+        <v/>
       </c>
       <c r="C7" s="62">
-        <f>COUNTIFS(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$B$13:$B$52,"&lt;&gt;")</f>
+        <f>IF($B7="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="D7" s="63">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$J$13:$J$52)</f>
+        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$J$13:$J$52))</f>
         <v/>
       </c>
       <c r="E7" s="64">
-        <f>SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$M$13:$M$52)</f>
+        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$M$13:$M$52))</f>
         <v/>
       </c>
       <c r="F7" s="63">
-        <f>SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว")</f>
+        <f>IF($B7="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
         <v/>
       </c>
       <c r="G7" s="63">
-        <f>E7-F7</f>
+        <f>IF($B7="","",E7-F7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="44" t="inlineStr">
+      <c r="B8" s="61">
+        <f>IF('ทีมขาย'!A9="","",'ทีมขาย'!A9)</f>
+        <v/>
+      </c>
+      <c r="C8" s="62">
+        <f>IF($B8="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D8" s="63">
+        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E8" s="64">
+        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F8" s="63">
+        <f>IF($B8="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B8,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="63">
+        <f>IF($B8="","",E8-F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="61">
+        <f>IF('ทีมขาย'!A10="","",'ทีมขาย'!A10)</f>
+        <v/>
+      </c>
+      <c r="C9" s="62">
+        <f>IF($B9="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D9" s="63">
+        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E9" s="64">
+        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F9" s="63">
+        <f>IF($B9="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B9,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="63">
+        <f>IF($B9="","",E9-F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="61">
+        <f>IF('ทีมขาย'!A11="","",'ทีมขาย'!A11)</f>
+        <v/>
+      </c>
+      <c r="C10" s="62">
+        <f>IF($B10="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D10" s="63">
+        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E10" s="64">
+        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F10" s="63">
+        <f>IF($B10="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B10,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="63">
+        <f>IF($B10="","",E10-F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="61">
+        <f>IF('ทีมขาย'!A12="","",'ทีมขาย'!A12)</f>
+        <v/>
+      </c>
+      <c r="C11" s="62">
+        <f>IF($B11="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D11" s="63">
+        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E11" s="64">
+        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F11" s="63">
+        <f>IF($B11="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B11,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="63">
+        <f>IF($B11="","",E11-F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="61">
+        <f>IF('ทีมขาย'!A13="","",'ทีมขาย'!A13)</f>
+        <v/>
+      </c>
+      <c r="C12" s="62">
+        <f>IF($B12="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D12" s="63">
+        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E12" s="64">
+        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F12" s="63">
+        <f>IF($B12="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B12,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="63">
+        <f>IF($B12="","",E12-F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="61">
+        <f>IF('ทีมขาย'!A14="","",'ทีมขาย'!A14)</f>
+        <v/>
+      </c>
+      <c r="C13" s="62">
+        <f>IF($B13="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D13" s="63">
+        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E13" s="64">
+        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F13" s="63">
+        <f>IF($B13="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B13,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="63">
+        <f>IF($B13="","",E13-F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="61">
+        <f>IF('ทีมขาย'!A15="","",'ทีมขาย'!A15)</f>
+        <v/>
+      </c>
+      <c r="C14" s="62">
+        <f>IF($B14="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="63">
+        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E14" s="64">
+        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F14" s="63">
+        <f>IF($B14="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B14,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="63">
+        <f>IF($B14="","",E14-F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="61">
+        <f>IF('ทีมขาย'!A16="","",'ทีมขาย'!A16)</f>
+        <v/>
+      </c>
+      <c r="C15" s="62">
+        <f>IF($B15="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D15" s="63">
+        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E15" s="64">
+        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F15" s="63">
+        <f>IF($B15="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B15,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="63">
+        <f>IF($B15="","",E15-F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="61">
+        <f>IF('ทีมขาย'!A17="","",'ทีมขาย'!A17)</f>
+        <v/>
+      </c>
+      <c r="C16" s="62">
+        <f>IF($B16="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D16" s="63">
+        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E16" s="64">
+        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F16" s="63">
+        <f>IF($B16="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B16,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="63">
+        <f>IF($B16="","",E16-F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="61">
+        <f>IF('ทีมขาย'!A18="","",'ทีมขาย'!A18)</f>
+        <v/>
+      </c>
+      <c r="C17" s="62">
+        <f>IF($B17="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D17" s="63">
+        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E17" s="64">
+        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F17" s="63">
+        <f>IF($B17="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B17,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G17" s="63">
+        <f>IF($B17="","",E17-F17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="61">
+        <f>IF('ทีมขาย'!A19="","",'ทีมขาย'!A19)</f>
+        <v/>
+      </c>
+      <c r="C18" s="62">
+        <f>IF($B18="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D18" s="63">
+        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E18" s="64">
+        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F18" s="63">
+        <f>IF($B18="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B18,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="63">
+        <f>IF($B18="","",E18-F18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="61">
+        <f>IF('ทีมขาย'!A20="","",'ทีมขาย'!A20)</f>
+        <v/>
+      </c>
+      <c r="C19" s="62">
+        <f>IF($B19="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="D19" s="63">
+        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="E19" s="64">
+        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$M$13:$M$52))</f>
+        <v/>
+      </c>
+      <c r="F19" s="63">
+        <f>IF($B19="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B19,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="63">
+        <f>IF($B19="","",E19-F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>รวมทั้งทีม</t>
         </is>
       </c>
-      <c r="C8" s="69">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="45">
-        <f>SUM(D5:D7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="45">
-        <f>SUM(E5:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="45">
-        <f>SUM(F5:F7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="45">
-        <f>SUM(G5:G7)</f>
+      <c r="C20" s="69">
+        <f>SUM(C5:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="83">
+        <f>SUM(D5:D19)</f>
+        <v/>
+      </c>
+      <c r="E20" s="83">
+        <f>SUM(E5:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="83">
+        <f>SUM(F5:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="83">
+        <f>E20-F20</f>
         <v/>
       </c>
     </row>

--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;฿&quot;"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,20 @@
       <color rgb="006A7682"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E5E5D"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -260,8 +272,13 @@
         <fgColor rgb="00F2F5F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -434,11 +451,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="009AA7B2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C4CDD5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="009AA7B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C4CDD5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -671,6 +717,53 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1036,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1049,10 +1142,11 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1067,7 +1161,7 @@
           <t>SALES RECORD &amp; COMMISSION SYSTEM 2026</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>ปีงบประมาณ 2026</t>
         </is>
@@ -1079,12 +1173,13 @@
           <t>ระบบบันทึกการขายและคำนวณค่าคอมมิชชั่น · EasyCRM (บริษัท อีซี่สลิป จำกัด)</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>อัปเดตอัตโนมัติจากตารางด้านล่าง</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1096,7 +1191,7 @@
           <t>สรุปรายได้ (THB)</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>สรุปค่าคอมรายคน (THB)</t>
         </is>
@@ -1143,20 +1238,20 @@
           <t>สุทธิ</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="L5" s="11">
+      <c r="M5" s="11">
         <f>'ทีมขาย'!A6</f>
         <v/>
       </c>
-      <c r="M5" s="11">
+      <c r="N5" s="11">
         <f>'ทีมขาย'!A7</f>
         <v/>
       </c>
-      <c r="N5" s="11">
+      <c r="O5" s="11">
         <f>'ทีมขาย'!A8</f>
         <v/>
       </c>
@@ -1194,20 +1289,20 @@
         <f>SUM(J13:J52)</f>
         <v/>
       </c>
-      <c r="K6" s="14">
-        <f>SUM(M13:M52)</f>
-        <v/>
-      </c>
-      <c r="L6" s="13">
-        <f>SUMIF($K$13:$K$52,L5,$M$13:$M$52)</f>
+      <c r="L6" s="14">
+        <f>SUM(N13:N52)</f>
         <v/>
       </c>
       <c r="M6" s="13">
-        <f>SUMIF($K$13:$K$52,M5,$M$13:$M$52)</f>
+        <f>'ทีมขาย'!G6</f>
         <v/>
       </c>
       <c r="N6" s="13">
-        <f>SUMIF($K$13:$K$52,N5,$M$13:$M$52)</f>
+        <f>'ทีมขาย'!G7</f>
+        <v/>
+      </c>
+      <c r="O6" s="13">
+        <f>'ทีมขาย'!G8</f>
         <v/>
       </c>
     </row>
@@ -1218,19 +1313,19 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>SUMIF(C13:C52,"Q1",M13:M52)</f>
+        <f>SUMIF(C13:C52,"Q1",N13:N52)</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>SUMIF(C13:C52,"Q2",M13:M52)</f>
+        <f>SUMIF(C13:C52,"Q2",N13:N52)</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>SUMIF(C13:C52,"Q3",M13:M52)</f>
+        <f>SUMIF(C13:C52,"Q3",N13:N52)</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>SUMIF(C13:C52,"Q4",M13:M52)</f>
+        <f>SUMIF(C13:C52,"Q4",N13:N52)</f>
         <v/>
       </c>
       <c r="G7" s="16" t="inlineStr">
@@ -1240,22 +1335,22 @@
       </c>
       <c r="H7" s="70" t="n"/>
       <c r="I7" s="18" t="n"/>
-      <c r="K7" s="17" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>จ่ายแล้ว</t>
         </is>
       </c>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="19" t="inlineStr">
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="19" t="inlineStr">
         <is>
           <t>ค้างจ่าย</t>
         </is>
       </c>
-      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="18" t="n"/>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="14">
-        <f>SUM(M13:M52)</f>
+        <f>SUM(N13:N52)</f>
         <v/>
       </c>
       <c r="G8" s="13">
@@ -1264,17 +1359,19 @@
       </c>
       <c r="H8" s="70" t="n"/>
       <c r="I8" s="18" t="n"/>
-      <c r="K8" s="12">
-        <f>SUMIF(N13:N52,"จ่ายแล้ว",M13:M52)</f>
-        <v/>
-      </c>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="20">
-        <f>SUM(M13:M52)-SUMIF(N13:N52,"จ่ายแล้ว",M13:M52)</f>
-        <v/>
-      </c>
-      <c r="N8" s="18" t="n"/>
-    </row>
+      <c r="L8" s="12">
+        <f>SUMIF(O13:O52,"จ่ายแล้ว",N13:N52)</f>
+        <v/>
+      </c>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="20">
+        <f>SUM(N13:N52)-SUMIF(O13:O52,"จ่ายแล้ว",N13:N52)</f>
+        <v/>
+      </c>
+      <c r="O8" s="18" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -1306,14 +1403,15 @@
       </c>
       <c r="I11" s="71" t="n"/>
       <c r="J11" s="72" t="n"/>
-      <c r="K11" s="25" t="inlineStr">
+      <c r="K11" s="21" t="inlineStr">
         <is>
           <t>ค่าคอมมิชชั่น</t>
         </is>
       </c>
-      <c r="L11" s="71" t="n"/>
-      <c r="M11" s="72" t="n"/>
-      <c r="N11" s="21" t="inlineStr">
+      <c r="L11" s="86" t="n"/>
+      <c r="M11" s="86" t="n"/>
+      <c r="N11" s="87" t="n"/>
+      <c r="O11" s="21" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
@@ -1372,20 +1470,25 @@
       </c>
       <c r="K12" s="30" t="inlineStr">
         <is>
+          <t>จ่ายแบบ</t>
+        </is>
+      </c>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="M12" s="30" t="inlineStr">
         <is>
           <t>Rate %</t>
         </is>
       </c>
-      <c r="M12" s="30" t="inlineStr">
+      <c r="N12" s="30" t="inlineStr">
         <is>
           <t>ค่าคอม (THB)</t>
         </is>
       </c>
-      <c r="N12" s="26" t="inlineStr">
+      <c r="O12" s="26" t="inlineStr">
         <is>
           <t>สถานะจ่าย</t>
         </is>
@@ -1414,16 +1517,17 @@
         <f>IF(H13="","",H13*(1-IF(I13="",0,I13)))</f>
         <v/>
       </c>
-      <c r="K13" s="31" t="n"/>
-      <c r="L13" s="35">
-        <f>IF(G13="","",IF(K13="",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K13,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M13" s="36">
-        <f>IF(OR(J13="",L13=""),"",J13*L13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="31" t="n"/>
+      <c r="K13" s="88" t="n"/>
+      <c r="L13" s="31" t="n"/>
+      <c r="M13" s="35">
+        <f>IF(G13="","",IF(K13="ทีม",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IF(L13="",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N13" s="36">
+        <f>IF(OR(J13="",M13=""),"",J13*M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="31" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="37">
@@ -1448,16 +1552,17 @@
         <f>IF(H14="","",H14*(1-IF(I14="",0,I14)))</f>
         <v/>
       </c>
-      <c r="K14" s="37" t="n"/>
-      <c r="L14" s="41">
-        <f>IF(G14="","",IF(K14="",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K14,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M14" s="42">
-        <f>IF(OR(J14="",L14=""),"",J14*L14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="37" t="n"/>
+      <c r="K14" s="89" t="n"/>
+      <c r="L14" s="37" t="n"/>
+      <c r="M14" s="41">
+        <f>IF(G14="","",IF(K14="ทีม",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IF(L14="",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N14" s="42">
+        <f>IF(OR(J14="",M14=""),"",J14*M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="37" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="31">
@@ -1482,16 +1587,17 @@
         <f>IF(H15="","",H15*(1-IF(I15="",0,I15)))</f>
         <v/>
       </c>
-      <c r="K15" s="31" t="n"/>
-      <c r="L15" s="35">
-        <f>IF(G15="","",IF(K15="",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K15,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M15" s="36">
-        <f>IF(OR(J15="",L15=""),"",J15*L15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="31" t="n"/>
+      <c r="K15" s="88" t="n"/>
+      <c r="L15" s="31" t="n"/>
+      <c r="M15" s="35">
+        <f>IF(G15="","",IF(K15="ทีม",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IF(L15="",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N15" s="36">
+        <f>IF(OR(J15="",M15=""),"",J15*M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="31" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="37">
@@ -1516,16 +1622,17 @@
         <f>IF(H16="","",H16*(1-IF(I16="",0,I16)))</f>
         <v/>
       </c>
-      <c r="K16" s="37" t="n"/>
-      <c r="L16" s="41">
-        <f>IF(G16="","",IF(K16="",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K16,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M16" s="42">
-        <f>IF(OR(J16="",L16=""),"",J16*L16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="37" t="n"/>
+      <c r="K16" s="89" t="n"/>
+      <c r="L16" s="37" t="n"/>
+      <c r="M16" s="41">
+        <f>IF(G16="","",IF(K16="ทีม",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IF(L16="",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N16" s="42">
+        <f>IF(OR(J16="",M16=""),"",J16*M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="31">
@@ -1550,16 +1657,17 @@
         <f>IF(H17="","",H17*(1-IF(I17="",0,I17)))</f>
         <v/>
       </c>
-      <c r="K17" s="31" t="n"/>
-      <c r="L17" s="35">
-        <f>IF(G17="","",IF(K17="",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K17,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M17" s="36">
-        <f>IF(OR(J17="",L17=""),"",J17*L17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="31" t="n"/>
+      <c r="K17" s="88" t="n"/>
+      <c r="L17" s="31" t="n"/>
+      <c r="M17" s="35">
+        <f>IF(G17="","",IF(K17="ทีม",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IF(L17="",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N17" s="36">
+        <f>IF(OR(J17="",M17=""),"",J17*M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="31" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="37">
@@ -1584,16 +1692,17 @@
         <f>IF(H18="","",H18*(1-IF(I18="",0,I18)))</f>
         <v/>
       </c>
-      <c r="K18" s="37" t="n"/>
-      <c r="L18" s="41">
-        <f>IF(G18="","",IF(K18="",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K18,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M18" s="42">
-        <f>IF(OR(J18="",L18=""),"",J18*L18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="37" t="n"/>
+      <c r="K18" s="89" t="n"/>
+      <c r="L18" s="37" t="n"/>
+      <c r="M18" s="41">
+        <f>IF(G18="","",IF(K18="ทีม",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IF(L18="",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N18" s="42">
+        <f>IF(OR(J18="",M18=""),"",J18*M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="31">
@@ -1618,16 +1727,17 @@
         <f>IF(H19="","",H19*(1-IF(I19="",0,I19)))</f>
         <v/>
       </c>
-      <c r="K19" s="31" t="n"/>
-      <c r="L19" s="35">
-        <f>IF(G19="","",IF(K19="",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K19,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M19" s="36">
-        <f>IF(OR(J19="",L19=""),"",J19*L19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="31" t="n"/>
+      <c r="K19" s="88" t="n"/>
+      <c r="L19" s="31" t="n"/>
+      <c r="M19" s="35">
+        <f>IF(G19="","",IF(K19="ทีม",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IF(L19="",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N19" s="36">
+        <f>IF(OR(J19="",M19=""),"",J19*M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="31" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="37">
@@ -1652,16 +1762,17 @@
         <f>IF(H20="","",H20*(1-IF(I20="",0,I20)))</f>
         <v/>
       </c>
-      <c r="K20" s="37" t="n"/>
-      <c r="L20" s="41">
-        <f>IF(G20="","",IF(K20="",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K20,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M20" s="42">
-        <f>IF(OR(J20="",L20=""),"",J20*L20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="37" t="n"/>
+      <c r="K20" s="89" t="n"/>
+      <c r="L20" s="37" t="n"/>
+      <c r="M20" s="41">
+        <f>IF(G20="","",IF(K20="ทีม",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IF(L20="",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N20" s="42">
+        <f>IF(OR(J20="",M20=""),"",J20*M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="31">
@@ -1686,16 +1797,17 @@
         <f>IF(H21="","",H21*(1-IF(I21="",0,I21)))</f>
         <v/>
       </c>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="35">
-        <f>IF(G21="","",IF(K21="",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K21,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M21" s="36">
-        <f>IF(OR(J21="",L21=""),"",J21*L21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="31" t="n"/>
+      <c r="K21" s="88" t="n"/>
+      <c r="L21" s="31" t="n"/>
+      <c r="M21" s="35">
+        <f>IF(G21="","",IF(K21="ทีม",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IF(L21="",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N21" s="36">
+        <f>IF(OR(J21="",M21=""),"",J21*M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="31" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="37">
@@ -1720,16 +1832,17 @@
         <f>IF(H22="","",H22*(1-IF(I22="",0,I22)))</f>
         <v/>
       </c>
-      <c r="K22" s="37" t="n"/>
-      <c r="L22" s="41">
-        <f>IF(G22="","",IF(K22="",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K22,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M22" s="42">
-        <f>IF(OR(J22="",L22=""),"",J22*L22)</f>
-        <v/>
-      </c>
-      <c r="N22" s="37" t="n"/>
+      <c r="K22" s="89" t="n"/>
+      <c r="L22" s="37" t="n"/>
+      <c r="M22" s="41">
+        <f>IF(G22="","",IF(K22="ทีม",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IF(L22="",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N22" s="42">
+        <f>IF(OR(J22="",M22=""),"",J22*M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="37" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="31">
@@ -1754,16 +1867,17 @@
         <f>IF(H23="","",H23*(1-IF(I23="",0,I23)))</f>
         <v/>
       </c>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="35">
-        <f>IF(G23="","",IF(K23="",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K23,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M23" s="36">
-        <f>IF(OR(J23="",L23=""),"",J23*L23)</f>
-        <v/>
-      </c>
-      <c r="N23" s="31" t="n"/>
+      <c r="K23" s="88" t="n"/>
+      <c r="L23" s="31" t="n"/>
+      <c r="M23" s="35">
+        <f>IF(G23="","",IF(K23="ทีม",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IF(L23="",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="36">
+        <f>IF(OR(J23="",M23=""),"",J23*M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="31" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="37">
@@ -1788,16 +1902,17 @@
         <f>IF(H24="","",H24*(1-IF(I24="",0,I24)))</f>
         <v/>
       </c>
-      <c r="K24" s="37" t="n"/>
-      <c r="L24" s="41">
-        <f>IF(G24="","",IF(K24="",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K24,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M24" s="42">
-        <f>IF(OR(J24="",L24=""),"",J24*L24)</f>
-        <v/>
-      </c>
-      <c r="N24" s="37" t="n"/>
+      <c r="K24" s="89" t="n"/>
+      <c r="L24" s="37" t="n"/>
+      <c r="M24" s="41">
+        <f>IF(G24="","",IF(K24="ทีม",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IF(L24="",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="42">
+        <f>IF(OR(J24="",M24=""),"",J24*M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="31">
@@ -1822,16 +1937,17 @@
         <f>IF(H25="","",H25*(1-IF(I25="",0,I25)))</f>
         <v/>
       </c>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="35">
-        <f>IF(G25="","",IF(K25="",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K25,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M25" s="36">
-        <f>IF(OR(J25="",L25=""),"",J25*L25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="31" t="n"/>
+      <c r="K25" s="88" t="n"/>
+      <c r="L25" s="31" t="n"/>
+      <c r="M25" s="35">
+        <f>IF(G25="","",IF(K25="ทีม",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IF(L25="",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="36">
+        <f>IF(OR(J25="",M25=""),"",J25*M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="31" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="37">
@@ -1856,16 +1972,17 @@
         <f>IF(H26="","",H26*(1-IF(I26="",0,I26)))</f>
         <v/>
       </c>
-      <c r="K26" s="37" t="n"/>
-      <c r="L26" s="41">
-        <f>IF(G26="","",IF(K26="",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K26,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M26" s="42">
-        <f>IF(OR(J26="",L26=""),"",J26*L26)</f>
-        <v/>
-      </c>
-      <c r="N26" s="37" t="n"/>
+      <c r="K26" s="89" t="n"/>
+      <c r="L26" s="37" t="n"/>
+      <c r="M26" s="41">
+        <f>IF(G26="","",IF(K26="ทีม",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IF(L26="",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="42">
+        <f>IF(OR(J26="",M26=""),"",J26*M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="31">
@@ -1890,16 +2007,17 @@
         <f>IF(H27="","",H27*(1-IF(I27="",0,I27)))</f>
         <v/>
       </c>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="35">
-        <f>IF(G27="","",IF(K27="",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K27,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M27" s="36">
-        <f>IF(OR(J27="",L27=""),"",J27*L27)</f>
-        <v/>
-      </c>
-      <c r="N27" s="31" t="n"/>
+      <c r="K27" s="88" t="n"/>
+      <c r="L27" s="31" t="n"/>
+      <c r="M27" s="35">
+        <f>IF(G27="","",IF(K27="ทีม",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IF(L27="",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="36">
+        <f>IF(OR(J27="",M27=""),"",J27*M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="31" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="37">
@@ -1924,16 +2042,17 @@
         <f>IF(H28="","",H28*(1-IF(I28="",0,I28)))</f>
         <v/>
       </c>
-      <c r="K28" s="37" t="n"/>
-      <c r="L28" s="41">
-        <f>IF(G28="","",IF(K28="",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K28,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M28" s="42">
-        <f>IF(OR(J28="",L28=""),"",J28*L28)</f>
-        <v/>
-      </c>
-      <c r="N28" s="37" t="n"/>
+      <c r="K28" s="89" t="n"/>
+      <c r="L28" s="37" t="n"/>
+      <c r="M28" s="41">
+        <f>IF(G28="","",IF(K28="ทีม",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IF(L28="",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="42">
+        <f>IF(OR(J28="",M28=""),"",J28*M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="31">
@@ -1958,16 +2077,17 @@
         <f>IF(H29="","",H29*(1-IF(I29="",0,I29)))</f>
         <v/>
       </c>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="35">
-        <f>IF(G29="","",IF(K29="",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K29,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M29" s="36">
-        <f>IF(OR(J29="",L29=""),"",J29*L29)</f>
-        <v/>
-      </c>
-      <c r="N29" s="31" t="n"/>
+      <c r="K29" s="88" t="n"/>
+      <c r="L29" s="31" t="n"/>
+      <c r="M29" s="35">
+        <f>IF(G29="","",IF(K29="ทีม",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IF(L29="",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="36">
+        <f>IF(OR(J29="",M29=""),"",J29*M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="31" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="37">
@@ -1992,16 +2112,17 @@
         <f>IF(H30="","",H30*(1-IF(I30="",0,I30)))</f>
         <v/>
       </c>
-      <c r="K30" s="37" t="n"/>
-      <c r="L30" s="41">
-        <f>IF(G30="","",IF(K30="",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K30,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M30" s="42">
-        <f>IF(OR(J30="",L30=""),"",J30*L30)</f>
-        <v/>
-      </c>
-      <c r="N30" s="37" t="n"/>
+      <c r="K30" s="89" t="n"/>
+      <c r="L30" s="37" t="n"/>
+      <c r="M30" s="41">
+        <f>IF(G30="","",IF(K30="ทีม",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IF(L30="",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N30" s="42">
+        <f>IF(OR(J30="",M30=""),"",J30*M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="37" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="31">
@@ -2026,16 +2147,17 @@
         <f>IF(H31="","",H31*(1-IF(I31="",0,I31)))</f>
         <v/>
       </c>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="35">
-        <f>IF(G31="","",IF(K31="",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K31,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M31" s="36">
-        <f>IF(OR(J31="",L31=""),"",J31*L31)</f>
-        <v/>
-      </c>
-      <c r="N31" s="31" t="n"/>
+      <c r="K31" s="88" t="n"/>
+      <c r="L31" s="31" t="n"/>
+      <c r="M31" s="35">
+        <f>IF(G31="","",IF(K31="ทีม",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IF(L31="",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N31" s="36">
+        <f>IF(OR(J31="",M31=""),"",J31*M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="31" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="37">
@@ -2060,16 +2182,17 @@
         <f>IF(H32="","",H32*(1-IF(I32="",0,I32)))</f>
         <v/>
       </c>
-      <c r="K32" s="37" t="n"/>
-      <c r="L32" s="41">
-        <f>IF(G32="","",IF(K32="",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K32,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M32" s="42">
-        <f>IF(OR(J32="",L32=""),"",J32*L32)</f>
-        <v/>
-      </c>
-      <c r="N32" s="37" t="n"/>
+      <c r="K32" s="89" t="n"/>
+      <c r="L32" s="37" t="n"/>
+      <c r="M32" s="41">
+        <f>IF(G32="","",IF(K32="ทีม",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IF(L32="",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N32" s="42">
+        <f>IF(OR(J32="",M32=""),"",J32*M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="37" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="31">
@@ -2094,16 +2217,17 @@
         <f>IF(H33="","",H33*(1-IF(I33="",0,I33)))</f>
         <v/>
       </c>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="35">
-        <f>IF(G33="","",IF(K33="",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K33,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M33" s="36">
-        <f>IF(OR(J33="",L33=""),"",J33*L33)</f>
-        <v/>
-      </c>
-      <c r="N33" s="31" t="n"/>
+      <c r="K33" s="88" t="n"/>
+      <c r="L33" s="31" t="n"/>
+      <c r="M33" s="35">
+        <f>IF(G33="","",IF(K33="ทีม",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IF(L33="",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="36">
+        <f>IF(OR(J33="",M33=""),"",J33*M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="31" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="37">
@@ -2128,16 +2252,17 @@
         <f>IF(H34="","",H34*(1-IF(I34="",0,I34)))</f>
         <v/>
       </c>
-      <c r="K34" s="37" t="n"/>
-      <c r="L34" s="41">
-        <f>IF(G34="","",IF(K34="",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K34,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M34" s="42">
-        <f>IF(OR(J34="",L34=""),"",J34*L34)</f>
-        <v/>
-      </c>
-      <c r="N34" s="37" t="n"/>
+      <c r="K34" s="89" t="n"/>
+      <c r="L34" s="37" t="n"/>
+      <c r="M34" s="41">
+        <f>IF(G34="","",IF(K34="ทีม",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IF(L34="",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="42">
+        <f>IF(OR(J34="",M34=""),"",J34*M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="37" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="31">
@@ -2162,16 +2287,17 @@
         <f>IF(H35="","",H35*(1-IF(I35="",0,I35)))</f>
         <v/>
       </c>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="35">
-        <f>IF(G35="","",IF(K35="",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K35,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M35" s="36">
-        <f>IF(OR(J35="",L35=""),"",J35*L35)</f>
-        <v/>
-      </c>
-      <c r="N35" s="31" t="n"/>
+      <c r="K35" s="88" t="n"/>
+      <c r="L35" s="31" t="n"/>
+      <c r="M35" s="35">
+        <f>IF(G35="","",IF(K35="ทีม",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IF(L35="",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N35" s="36">
+        <f>IF(OR(J35="",M35=""),"",J35*M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="31" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="37">
@@ -2196,16 +2322,17 @@
         <f>IF(H36="","",H36*(1-IF(I36="",0,I36)))</f>
         <v/>
       </c>
-      <c r="K36" s="37" t="n"/>
-      <c r="L36" s="41">
-        <f>IF(G36="","",IF(K36="",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K36,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M36" s="42">
-        <f>IF(OR(J36="",L36=""),"",J36*L36)</f>
-        <v/>
-      </c>
-      <c r="N36" s="37" t="n"/>
+      <c r="K36" s="89" t="n"/>
+      <c r="L36" s="37" t="n"/>
+      <c r="M36" s="41">
+        <f>IF(G36="","",IF(K36="ทีม",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IF(L36="",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N36" s="42">
+        <f>IF(OR(J36="",M36=""),"",J36*M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="31">
@@ -2230,16 +2357,17 @@
         <f>IF(H37="","",H37*(1-IF(I37="",0,I37)))</f>
         <v/>
       </c>
-      <c r="K37" s="31" t="n"/>
-      <c r="L37" s="35">
-        <f>IF(G37="","",IF(K37="",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K37,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M37" s="36">
-        <f>IF(OR(J37="",L37=""),"",J37*L37)</f>
-        <v/>
-      </c>
-      <c r="N37" s="31" t="n"/>
+      <c r="K37" s="88" t="n"/>
+      <c r="L37" s="31" t="n"/>
+      <c r="M37" s="35">
+        <f>IF(G37="","",IF(K37="ทีม",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IF(L37="",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N37" s="36">
+        <f>IF(OR(J37="",M37=""),"",J37*M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="31" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="37">
@@ -2264,16 +2392,17 @@
         <f>IF(H38="","",H38*(1-IF(I38="",0,I38)))</f>
         <v/>
       </c>
-      <c r="K38" s="37" t="n"/>
-      <c r="L38" s="41">
-        <f>IF(G38="","",IF(K38="",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K38,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M38" s="42">
-        <f>IF(OR(J38="",L38=""),"",J38*L38)</f>
-        <v/>
-      </c>
-      <c r="N38" s="37" t="n"/>
+      <c r="K38" s="89" t="n"/>
+      <c r="L38" s="37" t="n"/>
+      <c r="M38" s="41">
+        <f>IF(G38="","",IF(K38="ทีม",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IF(L38="",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N38" s="42">
+        <f>IF(OR(J38="",M38=""),"",J38*M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="37" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="31">
@@ -2298,16 +2427,17 @@
         <f>IF(H39="","",H39*(1-IF(I39="",0,I39)))</f>
         <v/>
       </c>
-      <c r="K39" s="31" t="n"/>
-      <c r="L39" s="35">
-        <f>IF(G39="","",IF(K39="",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K39,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M39" s="36">
-        <f>IF(OR(J39="",L39=""),"",J39*L39)</f>
-        <v/>
-      </c>
-      <c r="N39" s="31" t="n"/>
+      <c r="K39" s="88" t="n"/>
+      <c r="L39" s="31" t="n"/>
+      <c r="M39" s="35">
+        <f>IF(G39="","",IF(K39="ทีม",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IF(L39="",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N39" s="36">
+        <f>IF(OR(J39="",M39=""),"",J39*M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="31" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="37">
@@ -2332,16 +2462,17 @@
         <f>IF(H40="","",H40*(1-IF(I40="",0,I40)))</f>
         <v/>
       </c>
-      <c r="K40" s="37" t="n"/>
-      <c r="L40" s="41">
-        <f>IF(G40="","",IF(K40="",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K40,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M40" s="42">
-        <f>IF(OR(J40="",L40=""),"",J40*L40)</f>
-        <v/>
-      </c>
-      <c r="N40" s="37" t="n"/>
+      <c r="K40" s="89" t="n"/>
+      <c r="L40" s="37" t="n"/>
+      <c r="M40" s="41">
+        <f>IF(G40="","",IF(K40="ทีม",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IF(L40="",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N40" s="42">
+        <f>IF(OR(J40="",M40=""),"",J40*M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="37" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="31">
@@ -2366,16 +2497,17 @@
         <f>IF(H41="","",H41*(1-IF(I41="",0,I41)))</f>
         <v/>
       </c>
-      <c r="K41" s="31" t="n"/>
-      <c r="L41" s="35">
-        <f>IF(G41="","",IF(K41="",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K41,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M41" s="36">
-        <f>IF(OR(J41="",L41=""),"",J41*L41)</f>
-        <v/>
-      </c>
-      <c r="N41" s="31" t="n"/>
+      <c r="K41" s="88" t="n"/>
+      <c r="L41" s="31" t="n"/>
+      <c r="M41" s="35">
+        <f>IF(G41="","",IF(K41="ทีม",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IF(L41="",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N41" s="36">
+        <f>IF(OR(J41="",M41=""),"",J41*M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="31" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="37">
@@ -2400,16 +2532,17 @@
         <f>IF(H42="","",H42*(1-IF(I42="",0,I42)))</f>
         <v/>
       </c>
-      <c r="K42" s="37" t="n"/>
-      <c r="L42" s="41">
-        <f>IF(G42="","",IF(K42="",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K42,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M42" s="42">
-        <f>IF(OR(J42="",L42=""),"",J42*L42)</f>
-        <v/>
-      </c>
-      <c r="N42" s="37" t="n"/>
+      <c r="K42" s="89" t="n"/>
+      <c r="L42" s="37" t="n"/>
+      <c r="M42" s="41">
+        <f>IF(G42="","",IF(K42="ทีม",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IF(L42="",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N42" s="42">
+        <f>IF(OR(J42="",M42=""),"",J42*M42)</f>
+        <v/>
+      </c>
+      <c r="O42" s="37" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="31">
@@ -2434,16 +2567,17 @@
         <f>IF(H43="","",H43*(1-IF(I43="",0,I43)))</f>
         <v/>
       </c>
-      <c r="K43" s="31" t="n"/>
-      <c r="L43" s="35">
-        <f>IF(G43="","",IF(K43="",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K43,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M43" s="36">
-        <f>IF(OR(J43="",L43=""),"",J43*L43)</f>
-        <v/>
-      </c>
-      <c r="N43" s="31" t="n"/>
+      <c r="K43" s="88" t="n"/>
+      <c r="L43" s="31" t="n"/>
+      <c r="M43" s="35">
+        <f>IF(G43="","",IF(K43="ทีม",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IF(L43="",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N43" s="36">
+        <f>IF(OR(J43="",M43=""),"",J43*M43)</f>
+        <v/>
+      </c>
+      <c r="O43" s="31" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="37">
@@ -2468,16 +2602,17 @@
         <f>IF(H44="","",H44*(1-IF(I44="",0,I44)))</f>
         <v/>
       </c>
-      <c r="K44" s="37" t="n"/>
-      <c r="L44" s="41">
-        <f>IF(G44="","",IF(K44="",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K44,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M44" s="42">
-        <f>IF(OR(J44="",L44=""),"",J44*L44)</f>
-        <v/>
-      </c>
-      <c r="N44" s="37" t="n"/>
+      <c r="K44" s="89" t="n"/>
+      <c r="L44" s="37" t="n"/>
+      <c r="M44" s="41">
+        <f>IF(G44="","",IF(K44="ทีม",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IF(L44="",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N44" s="42">
+        <f>IF(OR(J44="",M44=""),"",J44*M44)</f>
+        <v/>
+      </c>
+      <c r="O44" s="37" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="31">
@@ -2502,16 +2637,17 @@
         <f>IF(H45="","",H45*(1-IF(I45="",0,I45)))</f>
         <v/>
       </c>
-      <c r="K45" s="31" t="n"/>
-      <c r="L45" s="35">
-        <f>IF(G45="","",IF(K45="",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K45,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M45" s="36">
-        <f>IF(OR(J45="",L45=""),"",J45*L45)</f>
-        <v/>
-      </c>
-      <c r="N45" s="31" t="n"/>
+      <c r="K45" s="88" t="n"/>
+      <c r="L45" s="31" t="n"/>
+      <c r="M45" s="35">
+        <f>IF(G45="","",IF(K45="ทีม",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IF(L45="",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N45" s="36">
+        <f>IF(OR(J45="",M45=""),"",J45*M45)</f>
+        <v/>
+      </c>
+      <c r="O45" s="31" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="37">
@@ -2536,16 +2672,17 @@
         <f>IF(H46="","",H46*(1-IF(I46="",0,I46)))</f>
         <v/>
       </c>
-      <c r="K46" s="37" t="n"/>
-      <c r="L46" s="41">
-        <f>IF(G46="","",IF(K46="",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K46,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M46" s="42">
-        <f>IF(OR(J46="",L46=""),"",J46*L46)</f>
-        <v/>
-      </c>
-      <c r="N46" s="37" t="n"/>
+      <c r="K46" s="89" t="n"/>
+      <c r="L46" s="37" t="n"/>
+      <c r="M46" s="41">
+        <f>IF(G46="","",IF(K46="ทีม",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IF(L46="",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N46" s="42">
+        <f>IF(OR(J46="",M46=""),"",J46*M46)</f>
+        <v/>
+      </c>
+      <c r="O46" s="37" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="31">
@@ -2570,16 +2707,17 @@
         <f>IF(H47="","",H47*(1-IF(I47="",0,I47)))</f>
         <v/>
       </c>
-      <c r="K47" s="31" t="n"/>
-      <c r="L47" s="35">
-        <f>IF(G47="","",IF(K47="",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K47,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M47" s="36">
-        <f>IF(OR(J47="",L47=""),"",J47*L47)</f>
-        <v/>
-      </c>
-      <c r="N47" s="31" t="n"/>
+      <c r="K47" s="88" t="n"/>
+      <c r="L47" s="31" t="n"/>
+      <c r="M47" s="35">
+        <f>IF(G47="","",IF(K47="ทีม",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IF(L47="",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N47" s="36">
+        <f>IF(OR(J47="",M47=""),"",J47*M47)</f>
+        <v/>
+      </c>
+      <c r="O47" s="31" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="37">
@@ -2604,16 +2742,17 @@
         <f>IF(H48="","",H48*(1-IF(I48="",0,I48)))</f>
         <v/>
       </c>
-      <c r="K48" s="37" t="n"/>
-      <c r="L48" s="41">
-        <f>IF(G48="","",IF(K48="",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K48,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M48" s="42">
-        <f>IF(OR(J48="",L48=""),"",J48*L48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="37" t="n"/>
+      <c r="K48" s="89" t="n"/>
+      <c r="L48" s="37" t="n"/>
+      <c r="M48" s="41">
+        <f>IF(G48="","",IF(K48="ทีม",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IF(L48="",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N48" s="42">
+        <f>IF(OR(J48="",M48=""),"",J48*M48)</f>
+        <v/>
+      </c>
+      <c r="O48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="31">
@@ -2638,16 +2777,17 @@
         <f>IF(H49="","",H49*(1-IF(I49="",0,I49)))</f>
         <v/>
       </c>
-      <c r="K49" s="31" t="n"/>
-      <c r="L49" s="35">
-        <f>IF(G49="","",IF(K49="",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K49,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M49" s="36">
-        <f>IF(OR(J49="",L49=""),"",J49*L49)</f>
-        <v/>
-      </c>
-      <c r="N49" s="31" t="n"/>
+      <c r="K49" s="88" t="n"/>
+      <c r="L49" s="31" t="n"/>
+      <c r="M49" s="35">
+        <f>IF(G49="","",IF(K49="ทีม",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IF(L49="",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N49" s="36">
+        <f>IF(OR(J49="",M49=""),"",J49*M49)</f>
+        <v/>
+      </c>
+      <c r="O49" s="31" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="37">
@@ -2672,16 +2812,17 @@
         <f>IF(H50="","",H50*(1-IF(I50="",0,I50)))</f>
         <v/>
       </c>
-      <c r="K50" s="37" t="n"/>
-      <c r="L50" s="41">
-        <f>IF(G50="","",IF(K50="",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K50,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M50" s="42">
-        <f>IF(OR(J50="",L50=""),"",J50*L50)</f>
-        <v/>
-      </c>
-      <c r="N50" s="37" t="n"/>
+      <c r="K50" s="89" t="n"/>
+      <c r="L50" s="37" t="n"/>
+      <c r="M50" s="41">
+        <f>IF(G50="","",IF(K50="ทีม",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IF(L50="",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N50" s="42">
+        <f>IF(OR(J50="",M50=""),"",J50*M50)</f>
+        <v/>
+      </c>
+      <c r="O50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="31">
@@ -2706,16 +2847,17 @@
         <f>IF(H51="","",H51*(1-IF(I51="",0,I51)))</f>
         <v/>
       </c>
-      <c r="K51" s="31" t="n"/>
-      <c r="L51" s="35">
-        <f>IF(G51="","",IF(K51="",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K51,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M51" s="36">
-        <f>IF(OR(J51="",L51=""),"",J51*L51)</f>
-        <v/>
-      </c>
-      <c r="N51" s="31" t="n"/>
+      <c r="K51" s="88" t="n"/>
+      <c r="L51" s="31" t="n"/>
+      <c r="M51" s="35">
+        <f>IF(G51="","",IF(K51="ทีม",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IF(L51="",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N51" s="36">
+        <f>IF(OR(J51="",M51=""),"",J51*M51)</f>
+        <v/>
+      </c>
+      <c r="O51" s="31" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="37">
@@ -2740,16 +2882,17 @@
         <f>IF(H52="","",H52*(1-IF(I52="",0,I52)))</f>
         <v/>
       </c>
-      <c r="K52" s="37" t="n"/>
-      <c r="L52" s="41">
-        <f>IF(G52="","",IF(K52="",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(K52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(K52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(K52,'ทีมขาย'!$A$6:$C$20,3,FALSE),""))))</f>
-        <v/>
-      </c>
-      <c r="M52" s="42">
-        <f>IF(OR(J52="",L52=""),"",J52*L52)</f>
-        <v/>
-      </c>
-      <c r="N52" s="37" t="n"/>
+      <c r="K52" s="89" t="n"/>
+      <c r="L52" s="37" t="n"/>
+      <c r="M52" s="41">
+        <f>IF(G52="","",IF(K52="ทีม",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IF(L52="",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <v/>
+      </c>
+      <c r="N52" s="42">
+        <f>IF(OR(J52="",M52=""),"",J52*M52)</f>
+        <v/>
+      </c>
+      <c r="O52" s="37" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="43" t="n"/>
@@ -2772,39 +2915,39 @@
         <f>SUM(J13:J52)</f>
         <v/>
       </c>
-      <c r="K53" s="43" t="n"/>
       <c r="L53" s="43" t="n"/>
-      <c r="M53" s="83">
+      <c r="M53" s="43" t="n"/>
+      <c r="N53" s="83">
         <f>SUM(M13:M52)</f>
         <v/>
       </c>
-      <c r="N53" s="43" t="n"/>
+      <c r="O53" s="43" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="O11"/>
     <mergeCell ref="H11:J11"/>
-    <mergeCell ref="K4:N4"/>
     <mergeCell ref="C1:J1"/>
-    <mergeCell ref="N11"/>
+    <mergeCell ref="L2:O2"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G11"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="C2:J2"/>
+    <mergeCell ref="K11:N11"/>
     <mergeCell ref="D11"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K7:L7"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="L4:O4"/>
     <mergeCell ref="G8:I8"/>
-    <mergeCell ref="K2:N2"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="L1:O1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="E13:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ใหม่,ต่ออายุ"</formula1>
     </dataValidation>
@@ -2814,11 +2957,14 @@
     <dataValidation sqref="G13:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Starter,Plus,Premium,Enterprise"</formula1>
     </dataValidation>
-    <dataValidation sqref="N13:N52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"รายคน,ทีม"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L13:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'ทีมขาย'!$A$6:$A$20</formula1>
+    </dataValidation>
+    <dataValidation sqref="O13:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"รอจ่าย,จ่ายแล้ว"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'ทีมขาย'!$A$6:$A$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2831,16 +2977,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2852,432 +3000,532 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>TEAM &amp; COMMISSION RATE</t>
+          <t>TEAM &amp; COMMISSION SPLIT</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>ทีมขายและอัตราค่าคอมส่วนตัว · แก้รายชื่อ/เปอร์เซ็นต์ได้ที่นี่</t>
+          <t>ทีมขาย · ตั้งรายชื่อ + % ส่วนตัว (รายคน) + % แบ่งทีม</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="73" t="inlineStr">
-        <is>
-          <t>เพิ่ม/แก้รายชื่อได้เลย · ใส่ % ส่วนตัว (เช่น 12%) เพื่อใช้แทนเรตแพ็กเกจ · เว้นว่าง = คิดตามเรตแพ็กเกจ (แท็บ Rate) · ชื่อในนี้จะกลายเป็นดรอปดาวน์ Sales ในแท็บ Sales_Record อัตโนมัติ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A3" s="90" t="inlineStr">
+        <is>
+          <t>เพิ่ม/แก้รายชื่อได้เลย · 'รายคน' ใช้ %ส่วนตัว (เว้นว่าง=เรตแพ็กเกจ) · 'ทีม' หารพูลค่าคอมตาม %แบ่งทีม (ควรรวม=100%) · เลือกจ่ายแบบไหนต่อดีลในแท็บ Sales_Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="38" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>ชื่อ Sales</t>
         </is>
       </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>ตำแหน่ง / บทบาท</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
-        <is>
-          <t>% ค่าคอมส่วนตัว
-(เว้นว่าง = ตามแพ็กเกจ)</t>
-        </is>
-      </c>
-      <c r="D5" s="48" t="inlineStr">
-        <is>
-          <t>จำนวนดีล</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>ตำแหน่ง</t>
+        </is>
+      </c>
+      <c r="C5" s="91" t="inlineStr">
+        <is>
+          <t>% ส่วนตัว
+(รายคน)</t>
+        </is>
+      </c>
+      <c r="D5" s="91" t="inlineStr">
+        <is>
+          <t>% แบ่งทีม
+(รวม=100%)</t>
+        </is>
+      </c>
+      <c r="E5" s="91" t="inlineStr">
+        <is>
+          <t>ดีลปิดเอง</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>รายได้ (THB)</t>
+        </is>
+      </c>
+      <c r="G5" s="91" t="inlineStr">
         <is>
           <t>ค่าคอมรวม (THB)</t>
         </is>
       </c>
-      <c r="F5" s="48" t="inlineStr">
+      <c r="H5" s="91" t="inlineStr">
         <is>
           <t>จ่ายแล้ว (THB)</t>
         </is>
       </c>
-      <c r="G5" s="48" t="inlineStr">
+      <c r="I5" s="91" t="inlineStr">
         <is>
           <t>ค้างจ่าย (THB)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>MIZTEEN</t>
         </is>
       </c>
-      <c r="B6" s="75" t="inlineStr">
+      <c r="B6" s="93" t="inlineStr">
         <is>
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C6" s="76" t="n"/>
-      <c r="D6" s="77">
-        <f>IF($A6="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E6" s="78">
-        <f>IF($A6="","",SUMIF(Sales_Record!$K$13:$K$52,$A6,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F6" s="79">
-        <f>IF($A6="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G6" s="79">
-        <f>IF($A6="","",E6-F6)</f>
+      <c r="C6" s="94" t="n"/>
+      <c r="D6" s="95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="96">
+        <f>IF($A6="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F6" s="97">
+        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$J$13:$J$52)+$D6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G6" s="98">
+        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$N$13:$N$52)+$D6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H6" s="97">
+        <f>IF($A6="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A6,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D6*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I6" s="97">
+        <f>IF($A6="","",G6-H6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="74" t="inlineStr">
+      <c r="A7" s="92" t="inlineStr">
         <is>
           <t>OLIVE</t>
         </is>
       </c>
-      <c r="B7" s="75" t="inlineStr">
+      <c r="B7" s="93" t="inlineStr">
         <is>
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C7" s="76" t="n"/>
-      <c r="D7" s="77">
-        <f>IF($A7="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E7" s="78">
-        <f>IF($A7="","",SUMIF(Sales_Record!$K$13:$K$52,$A7,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F7" s="79">
-        <f>IF($A7="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="79">
-        <f>IF($A7="","",E7-F7)</f>
+      <c r="C7" s="94" t="n"/>
+      <c r="D7" s="95" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="96">
+        <f>IF($A7="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F7" s="97">
+        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$J$13:$J$52)+$D7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G7" s="98">
+        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$N$13:$N$52)+$D7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H7" s="97">
+        <f>IF($A7="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A7,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D7*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I7" s="97">
+        <f>IF($A7="","",G7-H7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="74" t="inlineStr">
+      <c r="A8" s="92" t="inlineStr">
         <is>
           <t>SUPPORT</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
+      <c r="B8" s="93" t="inlineStr">
         <is>
           <t>Support / Sales</t>
         </is>
       </c>
-      <c r="C8" s="76" t="n"/>
-      <c r="D8" s="77">
-        <f>IF($A8="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E8" s="78">
-        <f>IF($A8="","",SUMIF(Sales_Record!$K$13:$K$52,$A8,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F8" s="79">
-        <f>IF($A8="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A8,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G8" s="79">
-        <f>IF($A8="","",E8-F8)</f>
+      <c r="C8" s="94" t="n"/>
+      <c r="D8" s="95" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="96">
+        <f>IF($A8="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F8" s="97">
+        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$J$13:$J$52)+$D8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G8" s="98">
+        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$N$13:$N$52)+$D8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H8" s="97">
+        <f>IF($A8="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A8,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D8*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I8" s="97">
+        <f>IF($A8="","",G8-H8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="74" t="inlineStr"/>
-      <c r="B9" s="75" t="inlineStr"/>
-      <c r="C9" s="76" t="n"/>
-      <c r="D9" s="77">
-        <f>IF($A9="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E9" s="78">
-        <f>IF($A9="","",SUMIF(Sales_Record!$K$13:$K$52,$A9,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F9" s="79">
-        <f>IF($A9="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A9,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="79">
-        <f>IF($A9="","",E9-F9)</f>
+      <c r="A9" s="92" t="inlineStr"/>
+      <c r="B9" s="93" t="inlineStr"/>
+      <c r="C9" s="94" t="n"/>
+      <c r="D9" s="95" t="n"/>
+      <c r="E9" s="96">
+        <f>IF($A9="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F9" s="97">
+        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$J$13:$J$52)+$D9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G9" s="98">
+        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$N$13:$N$52)+$D9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H9" s="97">
+        <f>IF($A9="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A9,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D9*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I9" s="97">
+        <f>IF($A9="","",G9-H9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="74" t="inlineStr"/>
-      <c r="B10" s="75" t="inlineStr"/>
-      <c r="C10" s="76" t="n"/>
-      <c r="D10" s="77">
-        <f>IF($A10="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E10" s="78">
-        <f>IF($A10="","",SUMIF(Sales_Record!$K$13:$K$52,$A10,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F10" s="79">
-        <f>IF($A10="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A10,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G10" s="79">
-        <f>IF($A10="","",E10-F10)</f>
+      <c r="A10" s="92" t="inlineStr"/>
+      <c r="B10" s="93" t="inlineStr"/>
+      <c r="C10" s="94" t="n"/>
+      <c r="D10" s="95" t="n"/>
+      <c r="E10" s="96">
+        <f>IF($A10="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F10" s="97">
+        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$J$13:$J$52)+$D10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G10" s="98">
+        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$N$13:$N$52)+$D10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H10" s="97">
+        <f>IF($A10="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A10,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D10*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="97">
+        <f>IF($A10="","",G10-H10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="74" t="inlineStr"/>
-      <c r="B11" s="75" t="inlineStr"/>
-      <c r="C11" s="76" t="n"/>
-      <c r="D11" s="77">
-        <f>IF($A11="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E11" s="78">
-        <f>IF($A11="","",SUMIF(Sales_Record!$K$13:$K$52,$A11,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F11" s="79">
-        <f>IF($A11="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A11,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G11" s="79">
-        <f>IF($A11="","",E11-F11)</f>
+      <c r="A11" s="92" t="inlineStr"/>
+      <c r="B11" s="93" t="inlineStr"/>
+      <c r="C11" s="94" t="n"/>
+      <c r="D11" s="95" t="n"/>
+      <c r="E11" s="96">
+        <f>IF($A11="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F11" s="97">
+        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$J$13:$J$52)+$D11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G11" s="98">
+        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$N$13:$N$52)+$D11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H11" s="97">
+        <f>IF($A11="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A11,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D11*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="97">
+        <f>IF($A11="","",G11-H11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="74" t="inlineStr"/>
-      <c r="B12" s="75" t="inlineStr"/>
-      <c r="C12" s="76" t="n"/>
-      <c r="D12" s="77">
-        <f>IF($A12="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="78">
-        <f>IF($A12="","",SUMIF(Sales_Record!$K$13:$K$52,$A12,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F12" s="79">
-        <f>IF($A12="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A12,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G12" s="79">
-        <f>IF($A12="","",E12-F12)</f>
+      <c r="A12" s="92" t="inlineStr"/>
+      <c r="B12" s="93" t="inlineStr"/>
+      <c r="C12" s="94" t="n"/>
+      <c r="D12" s="95" t="n"/>
+      <c r="E12" s="96">
+        <f>IF($A12="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F12" s="97">
+        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$J$13:$J$52)+$D12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G12" s="98">
+        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$N$13:$N$52)+$D12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H12" s="97">
+        <f>IF($A12="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A12,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D12*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="97">
+        <f>IF($A12="","",G12-H12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="74" t="inlineStr"/>
-      <c r="B13" s="75" t="inlineStr"/>
-      <c r="C13" s="76" t="n"/>
-      <c r="D13" s="77">
-        <f>IF($A13="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E13" s="78">
-        <f>IF($A13="","",SUMIF(Sales_Record!$K$13:$K$52,$A13,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F13" s="79">
-        <f>IF($A13="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A13,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="79">
-        <f>IF($A13="","",E13-F13)</f>
+      <c r="A13" s="92" t="inlineStr"/>
+      <c r="B13" s="93" t="inlineStr"/>
+      <c r="C13" s="94" t="n"/>
+      <c r="D13" s="95" t="n"/>
+      <c r="E13" s="96">
+        <f>IF($A13="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F13" s="97">
+        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$J$13:$J$52)+$D13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G13" s="98">
+        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$N$13:$N$52)+$D13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H13" s="97">
+        <f>IF($A13="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A13,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D13*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I13" s="97">
+        <f>IF($A13="","",G13-H13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="74" t="inlineStr"/>
-      <c r="B14" s="75" t="inlineStr"/>
-      <c r="C14" s="76" t="n"/>
-      <c r="D14" s="77">
-        <f>IF($A14="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E14" s="78">
-        <f>IF($A14="","",SUMIF(Sales_Record!$K$13:$K$52,$A14,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F14" s="79">
-        <f>IF($A14="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A14,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G14" s="79">
-        <f>IF($A14="","",E14-F14)</f>
+      <c r="A14" s="92" t="inlineStr"/>
+      <c r="B14" s="93" t="inlineStr"/>
+      <c r="C14" s="94" t="n"/>
+      <c r="D14" s="95" t="n"/>
+      <c r="E14" s="96">
+        <f>IF($A14="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F14" s="97">
+        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$J$13:$J$52)+$D14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G14" s="98">
+        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$N$13:$N$52)+$D14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H14" s="97">
+        <f>IF($A14="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A14,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D14*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I14" s="97">
+        <f>IF($A14="","",G14-H14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="74" t="inlineStr"/>
-      <c r="B15" s="75" t="inlineStr"/>
-      <c r="C15" s="76" t="n"/>
-      <c r="D15" s="77">
-        <f>IF($A15="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E15" s="78">
-        <f>IF($A15="","",SUMIF(Sales_Record!$K$13:$K$52,$A15,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F15" s="79">
-        <f>IF($A15="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A15,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="79">
-        <f>IF($A15="","",E15-F15)</f>
+      <c r="A15" s="92" t="inlineStr"/>
+      <c r="B15" s="93" t="inlineStr"/>
+      <c r="C15" s="94" t="n"/>
+      <c r="D15" s="95" t="n"/>
+      <c r="E15" s="96">
+        <f>IF($A15="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F15" s="97">
+        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$J$13:$J$52)+$D15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G15" s="98">
+        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$N$13:$N$52)+$D15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H15" s="97">
+        <f>IF($A15="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A15,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D15*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I15" s="97">
+        <f>IF($A15="","",G15-H15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="74" t="inlineStr"/>
-      <c r="B16" s="75" t="inlineStr"/>
-      <c r="C16" s="76" t="n"/>
-      <c r="D16" s="77">
-        <f>IF($A16="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E16" s="78">
-        <f>IF($A16="","",SUMIF(Sales_Record!$K$13:$K$52,$A16,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F16" s="79">
-        <f>IF($A16="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A16,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="79">
-        <f>IF($A16="","",E16-F16)</f>
+      <c r="A16" s="92" t="inlineStr"/>
+      <c r="B16" s="93" t="inlineStr"/>
+      <c r="C16" s="94" t="n"/>
+      <c r="D16" s="95" t="n"/>
+      <c r="E16" s="96">
+        <f>IF($A16="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F16" s="97">
+        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$J$13:$J$52)+$D16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G16" s="98">
+        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$N$13:$N$52)+$D16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H16" s="97">
+        <f>IF($A16="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A16,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D16*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I16" s="97">
+        <f>IF($A16="","",G16-H16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="74" t="inlineStr"/>
-      <c r="B17" s="75" t="inlineStr"/>
-      <c r="C17" s="76" t="n"/>
-      <c r="D17" s="77">
-        <f>IF($A17="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E17" s="78">
-        <f>IF($A17="","",SUMIF(Sales_Record!$K$13:$K$52,$A17,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F17" s="79">
-        <f>IF($A17="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A17,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G17" s="79">
-        <f>IF($A17="","",E17-F17)</f>
+      <c r="A17" s="92" t="inlineStr"/>
+      <c r="B17" s="93" t="inlineStr"/>
+      <c r="C17" s="94" t="n"/>
+      <c r="D17" s="95" t="n"/>
+      <c r="E17" s="96">
+        <f>IF($A17="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F17" s="97">
+        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$J$13:$J$52)+$D17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G17" s="98">
+        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$N$13:$N$52)+$D17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H17" s="97">
+        <f>IF($A17="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A17,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D17*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I17" s="97">
+        <f>IF($A17="","",G17-H17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="74" t="inlineStr"/>
-      <c r="B18" s="75" t="inlineStr"/>
-      <c r="C18" s="76" t="n"/>
-      <c r="D18" s="77">
-        <f>IF($A18="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E18" s="78">
-        <f>IF($A18="","",SUMIF(Sales_Record!$K$13:$K$52,$A18,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F18" s="79">
-        <f>IF($A18="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A18,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G18" s="79">
-        <f>IF($A18="","",E18-F18)</f>
+      <c r="A18" s="92" t="inlineStr"/>
+      <c r="B18" s="93" t="inlineStr"/>
+      <c r="C18" s="94" t="n"/>
+      <c r="D18" s="95" t="n"/>
+      <c r="E18" s="96">
+        <f>IF($A18="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F18" s="97">
+        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$J$13:$J$52)+$D18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G18" s="98">
+        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$N$13:$N$52)+$D18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H18" s="97">
+        <f>IF($A18="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A18,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D18*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I18" s="97">
+        <f>IF($A18="","",G18-H18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="74" t="inlineStr"/>
-      <c r="B19" s="75" t="inlineStr"/>
-      <c r="C19" s="76" t="n"/>
-      <c r="D19" s="77">
-        <f>IF($A19="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E19" s="78">
-        <f>IF($A19="","",SUMIF(Sales_Record!$K$13:$K$52,$A19,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F19" s="79">
-        <f>IF($A19="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A19,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G19" s="79">
-        <f>IF($A19="","",E19-F19)</f>
+      <c r="A19" s="92" t="inlineStr"/>
+      <c r="B19" s="93" t="inlineStr"/>
+      <c r="C19" s="94" t="n"/>
+      <c r="D19" s="95" t="n"/>
+      <c r="E19" s="96">
+        <f>IF($A19="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F19" s="97">
+        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$J$13:$J$52)+$D19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G19" s="98">
+        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$N$13:$N$52)+$D19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H19" s="97">
+        <f>IF($A19="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A19,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D19*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I19" s="97">
+        <f>IF($A19="","",G19-H19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="74" t="inlineStr"/>
-      <c r="B20" s="75" t="inlineStr"/>
-      <c r="C20" s="76" t="n"/>
-      <c r="D20" s="77">
-        <f>IF($A20="","",COUNTIFS(Sales_Record!$K$13:$K$52,$A20,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E20" s="78">
-        <f>IF($A20="","",SUMIF(Sales_Record!$K$13:$K$52,$A20,Sales_Record!$M$13:$M$52))</f>
-        <v/>
-      </c>
-      <c r="F20" s="79">
-        <f>IF($A20="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$A20,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="G20" s="79">
-        <f>IF($A20="","",E20-F20)</f>
+      <c r="A20" s="92" t="inlineStr"/>
+      <c r="B20" s="93" t="inlineStr"/>
+      <c r="C20" s="94" t="n"/>
+      <c r="D20" s="95" t="n"/>
+      <c r="E20" s="96">
+        <f>IF($A20="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <v/>
+      </c>
+      <c r="F20" s="97">
+        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$J$13:$J$52)+$D20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="G20" s="98">
+        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$N$13:$N$52)+$D20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="H20" s="97">
+        <f>IF($A20="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A20,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D20*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="I20" s="97">
+        <f>IF($A20="","",G20-H20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="80" t="inlineStr">
+      <c r="A21" s="99" t="inlineStr">
         <is>
           <t>รวมทั้งทีม</t>
         </is>
       </c>
-      <c r="B21" s="84" t="n"/>
-      <c r="C21" s="85" t="n"/>
-      <c r="D21" s="82">
+      <c r="B21" s="81" t="n"/>
+      <c r="C21" s="81" t="n"/>
+      <c r="D21" s="100">
         <f>SUM(D6:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="83">
+      <c r="E21" s="101">
         <f>SUM(E6:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="83">
+      <c r="F21" s="102">
         <f>SUM(F6:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="83">
-        <f>E21-F21</f>
+      <c r="G21" s="102">
+        <f>SUM(G6:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="102">
+        <f>SUM(H6:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="102">
+        <f>SUM(I6:I20)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C1:I1"/>
     <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="C2:I2"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3555,23 +3803,23 @@
         <v/>
       </c>
       <c r="C5" s="62">
-        <f>IF($B5="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B5="","",'ทีมขาย'!E6)</f>
         <v/>
       </c>
       <c r="D5" s="63">
-        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B5="","",'ทีมขาย'!F6)</f>
         <v/>
       </c>
       <c r="E5" s="64">
-        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B5="","",'ทีมขาย'!G6)</f>
         <v/>
       </c>
       <c r="F5" s="63">
-        <f>IF($B5="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B5,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B5="","",'ทีมขาย'!H6)</f>
         <v/>
       </c>
       <c r="G5" s="63">
-        <f>IF($B5="","",E5-F5)</f>
+        <f>IF($B5="","",'ทีมขาย'!I6)</f>
         <v/>
       </c>
     </row>
@@ -3581,23 +3829,23 @@
         <v/>
       </c>
       <c r="C6" s="62">
-        <f>IF($B6="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B6="","",'ทีมขาย'!E7)</f>
         <v/>
       </c>
       <c r="D6" s="63">
-        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B6="","",'ทีมขาย'!F7)</f>
         <v/>
       </c>
       <c r="E6" s="64">
-        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B6="","",'ทีมขาย'!G7)</f>
         <v/>
       </c>
       <c r="F6" s="63">
-        <f>IF($B6="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B6="","",'ทีมขาย'!H7)</f>
         <v/>
       </c>
       <c r="G6" s="63">
-        <f>IF($B6="","",E6-F6)</f>
+        <f>IF($B6="","",'ทีมขาย'!I7)</f>
         <v/>
       </c>
     </row>
@@ -3607,23 +3855,23 @@
         <v/>
       </c>
       <c r="C7" s="62">
-        <f>IF($B7="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B7="","",'ทีมขาย'!E8)</f>
         <v/>
       </c>
       <c r="D7" s="63">
-        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B7="","",'ทีมขาย'!F8)</f>
         <v/>
       </c>
       <c r="E7" s="64">
-        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B7="","",'ทีมขาย'!G8)</f>
         <v/>
       </c>
       <c r="F7" s="63">
-        <f>IF($B7="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B7="","",'ทีมขาย'!H8)</f>
         <v/>
       </c>
       <c r="G7" s="63">
-        <f>IF($B7="","",E7-F7)</f>
+        <f>IF($B7="","",'ทีมขาย'!I8)</f>
         <v/>
       </c>
     </row>
@@ -3633,23 +3881,23 @@
         <v/>
       </c>
       <c r="C8" s="62">
-        <f>IF($B8="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B8="","",'ทีมขาย'!E9)</f>
         <v/>
       </c>
       <c r="D8" s="63">
-        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B8="","",'ทีมขาย'!F9)</f>
         <v/>
       </c>
       <c r="E8" s="64">
-        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B8="","",'ทีมขาย'!G9)</f>
         <v/>
       </c>
       <c r="F8" s="63">
-        <f>IF($B8="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B8,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B8="","",'ทีมขาย'!H9)</f>
         <v/>
       </c>
       <c r="G8" s="63">
-        <f>IF($B8="","",E8-F8)</f>
+        <f>IF($B8="","",'ทีมขาย'!I9)</f>
         <v/>
       </c>
     </row>
@@ -3659,23 +3907,23 @@
         <v/>
       </c>
       <c r="C9" s="62">
-        <f>IF($B9="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B9="","",'ทีมขาย'!E10)</f>
         <v/>
       </c>
       <c r="D9" s="63">
-        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B9="","",'ทีมขาย'!F10)</f>
         <v/>
       </c>
       <c r="E9" s="64">
-        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B9="","",'ทีมขาย'!G10)</f>
         <v/>
       </c>
       <c r="F9" s="63">
-        <f>IF($B9="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B9,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B9="","",'ทีมขาย'!H10)</f>
         <v/>
       </c>
       <c r="G9" s="63">
-        <f>IF($B9="","",E9-F9)</f>
+        <f>IF($B9="","",'ทีมขาย'!I10)</f>
         <v/>
       </c>
     </row>
@@ -3685,23 +3933,23 @@
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>IF($B10="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B10="","",'ทีมขาย'!E11)</f>
         <v/>
       </c>
       <c r="D10" s="63">
-        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B10="","",'ทีมขาย'!F11)</f>
         <v/>
       </c>
       <c r="E10" s="64">
-        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B10="","",'ทีมขาย'!G11)</f>
         <v/>
       </c>
       <c r="F10" s="63">
-        <f>IF($B10="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B10,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B10="","",'ทีมขาย'!H11)</f>
         <v/>
       </c>
       <c r="G10" s="63">
-        <f>IF($B10="","",E10-F10)</f>
+        <f>IF($B10="","",'ทีมขาย'!I11)</f>
         <v/>
       </c>
     </row>
@@ -3711,23 +3959,23 @@
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>IF($B11="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B11="","",'ทีมขาย'!E12)</f>
         <v/>
       </c>
       <c r="D11" s="63">
-        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B11="","",'ทีมขาย'!F12)</f>
         <v/>
       </c>
       <c r="E11" s="64">
-        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B11="","",'ทีมขาย'!G12)</f>
         <v/>
       </c>
       <c r="F11" s="63">
-        <f>IF($B11="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B11,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B11="","",'ทีมขาย'!H12)</f>
         <v/>
       </c>
       <c r="G11" s="63">
-        <f>IF($B11="","",E11-F11)</f>
+        <f>IF($B11="","",'ทีมขาย'!I12)</f>
         <v/>
       </c>
     </row>
@@ -3737,23 +3985,23 @@
         <v/>
       </c>
       <c r="C12" s="62">
-        <f>IF($B12="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B12="","",'ทีมขาย'!E13)</f>
         <v/>
       </c>
       <c r="D12" s="63">
-        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B12="","",'ทีมขาย'!F13)</f>
         <v/>
       </c>
       <c r="E12" s="64">
-        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B12="","",'ทีมขาย'!G13)</f>
         <v/>
       </c>
       <c r="F12" s="63">
-        <f>IF($B12="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B12,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B12="","",'ทีมขาย'!H13)</f>
         <v/>
       </c>
       <c r="G12" s="63">
-        <f>IF($B12="","",E12-F12)</f>
+        <f>IF($B12="","",'ทีมขาย'!I13)</f>
         <v/>
       </c>
     </row>
@@ -3763,23 +4011,23 @@
         <v/>
       </c>
       <c r="C13" s="62">
-        <f>IF($B13="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B13="","",'ทีมขาย'!E14)</f>
         <v/>
       </c>
       <c r="D13" s="63">
-        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B13="","",'ทีมขาย'!F14)</f>
         <v/>
       </c>
       <c r="E13" s="64">
-        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B13="","",'ทีมขาย'!G14)</f>
         <v/>
       </c>
       <c r="F13" s="63">
-        <f>IF($B13="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B13,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B13="","",'ทีมขาย'!H14)</f>
         <v/>
       </c>
       <c r="G13" s="63">
-        <f>IF($B13="","",E13-F13)</f>
+        <f>IF($B13="","",'ทีมขาย'!I14)</f>
         <v/>
       </c>
     </row>
@@ -3789,23 +4037,23 @@
         <v/>
       </c>
       <c r="C14" s="62">
-        <f>IF($B14="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B14="","",'ทีมขาย'!E15)</f>
         <v/>
       </c>
       <c r="D14" s="63">
-        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B14="","",'ทีมขาย'!F15)</f>
         <v/>
       </c>
       <c r="E14" s="64">
-        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B14="","",'ทีมขาย'!G15)</f>
         <v/>
       </c>
       <c r="F14" s="63">
-        <f>IF($B14="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B14,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B14="","",'ทีมขาย'!H15)</f>
         <v/>
       </c>
       <c r="G14" s="63">
-        <f>IF($B14="","",E14-F14)</f>
+        <f>IF($B14="","",'ทีมขาย'!I15)</f>
         <v/>
       </c>
     </row>
@@ -3815,23 +4063,23 @@
         <v/>
       </c>
       <c r="C15" s="62">
-        <f>IF($B15="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B15="","",'ทีมขาย'!E16)</f>
         <v/>
       </c>
       <c r="D15" s="63">
-        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B15="","",'ทีมขาย'!F16)</f>
         <v/>
       </c>
       <c r="E15" s="64">
-        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B15="","",'ทีมขาย'!G16)</f>
         <v/>
       </c>
       <c r="F15" s="63">
-        <f>IF($B15="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B15,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B15="","",'ทีมขาย'!H16)</f>
         <v/>
       </c>
       <c r="G15" s="63">
-        <f>IF($B15="","",E15-F15)</f>
+        <f>IF($B15="","",'ทีมขาย'!I16)</f>
         <v/>
       </c>
     </row>
@@ -3841,23 +4089,23 @@
         <v/>
       </c>
       <c r="C16" s="62">
-        <f>IF($B16="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B16="","",'ทีมขาย'!E17)</f>
         <v/>
       </c>
       <c r="D16" s="63">
-        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B16="","",'ทีมขาย'!F17)</f>
         <v/>
       </c>
       <c r="E16" s="64">
-        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B16="","",'ทีมขาย'!G17)</f>
         <v/>
       </c>
       <c r="F16" s="63">
-        <f>IF($B16="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B16,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B16="","",'ทีมขาย'!H17)</f>
         <v/>
       </c>
       <c r="G16" s="63">
-        <f>IF($B16="","",E16-F16)</f>
+        <f>IF($B16="","",'ทีมขาย'!I17)</f>
         <v/>
       </c>
     </row>
@@ -3867,23 +4115,23 @@
         <v/>
       </c>
       <c r="C17" s="62">
-        <f>IF($B17="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B17="","",'ทีมขาย'!E18)</f>
         <v/>
       </c>
       <c r="D17" s="63">
-        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B17="","",'ทีมขาย'!F18)</f>
         <v/>
       </c>
       <c r="E17" s="64">
-        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B17="","",'ทีมขาย'!G18)</f>
         <v/>
       </c>
       <c r="F17" s="63">
-        <f>IF($B17="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B17,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B17="","",'ทีมขาย'!H18)</f>
         <v/>
       </c>
       <c r="G17" s="63">
-        <f>IF($B17="","",E17-F17)</f>
+        <f>IF($B17="","",'ทีมขาย'!I18)</f>
         <v/>
       </c>
     </row>
@@ -3893,23 +4141,23 @@
         <v/>
       </c>
       <c r="C18" s="62">
-        <f>IF($B18="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B18="","",'ทีมขาย'!E19)</f>
         <v/>
       </c>
       <c r="D18" s="63">
-        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B18="","",'ทีมขาย'!F19)</f>
         <v/>
       </c>
       <c r="E18" s="64">
-        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B18="","",'ทีมขาย'!G19)</f>
         <v/>
       </c>
       <c r="F18" s="63">
-        <f>IF($B18="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B18,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B18="","",'ทีมขาย'!H19)</f>
         <v/>
       </c>
       <c r="G18" s="63">
-        <f>IF($B18="","",E18-F18)</f>
+        <f>IF($B18="","",'ทีมขาย'!I19)</f>
         <v/>
       </c>
     </row>
@@ -3919,50 +4167,50 @@
         <v/>
       </c>
       <c r="C19" s="62">
-        <f>IF($B19="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B19="","",'ทีมขาย'!E20)</f>
         <v/>
       </c>
       <c r="D19" s="63">
-        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B19="","",'ทีมขาย'!F20)</f>
         <v/>
       </c>
       <c r="E19" s="64">
-        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B19="","",'ทีมขาย'!G20)</f>
         <v/>
       </c>
       <c r="F19" s="63">
-        <f>IF($B19="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B19,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B19="","",'ทีมขาย'!H20)</f>
         <v/>
       </c>
       <c r="G19" s="63">
-        <f>IF($B19="","",E19-F19)</f>
+        <f>IF($B19="","",'ทีมขาย'!I20)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C20" s="69">
+      <c r="C20" s="62">
         <f>SUM(C5:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="83">
+      <c r="D20" s="63">
         <f>SUM(D5:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="83">
+      <c r="E20" s="64">
         <f>SUM(E5:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="83">
+      <c r="F20" s="63">
         <f>SUM(F5:F19)</f>
         <v/>
       </c>
-      <c r="G20" s="83">
-        <f>E20-F20</f>
+      <c r="G20" s="63">
+        <f>SUM(G5:G19)</f>
         <v/>
       </c>
     </row>
@@ -4045,23 +4293,23 @@
         <v/>
       </c>
       <c r="C5" s="62">
-        <f>IF($B5="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B5="","",'ทีมขาย'!E6)</f>
         <v/>
       </c>
       <c r="D5" s="63">
-        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B5="","",'ทีมขาย'!F6)</f>
         <v/>
       </c>
       <c r="E5" s="64">
-        <f>IF($B5="","",SUMIF(Sales_Record!$K$13:$K$52,$B5,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B5="","",'ทีมขาย'!G6)</f>
         <v/>
       </c>
       <c r="F5" s="63">
-        <f>IF($B5="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B5,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B5="","",'ทีมขาย'!H6)</f>
         <v/>
       </c>
       <c r="G5" s="63">
-        <f>IF($B5="","",E5-F5)</f>
+        <f>IF($B5="","",'ทีมขาย'!I6)</f>
         <v/>
       </c>
     </row>
@@ -4071,23 +4319,23 @@
         <v/>
       </c>
       <c r="C6" s="62">
-        <f>IF($B6="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B6="","",'ทีมขาย'!E7)</f>
         <v/>
       </c>
       <c r="D6" s="63">
-        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B6="","",'ทีมขาย'!F7)</f>
         <v/>
       </c>
       <c r="E6" s="64">
-        <f>IF($B6="","",SUMIF(Sales_Record!$K$13:$K$52,$B6,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B6="","",'ทีมขาย'!G7)</f>
         <v/>
       </c>
       <c r="F6" s="63">
-        <f>IF($B6="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B6,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B6="","",'ทีมขาย'!H7)</f>
         <v/>
       </c>
       <c r="G6" s="63">
-        <f>IF($B6="","",E6-F6)</f>
+        <f>IF($B6="","",'ทีมขาย'!I7)</f>
         <v/>
       </c>
     </row>
@@ -4097,23 +4345,23 @@
         <v/>
       </c>
       <c r="C7" s="62">
-        <f>IF($B7="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B7="","",'ทีมขาย'!E8)</f>
         <v/>
       </c>
       <c r="D7" s="63">
-        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B7="","",'ทีมขาย'!F8)</f>
         <v/>
       </c>
       <c r="E7" s="64">
-        <f>IF($B7="","",SUMIF(Sales_Record!$K$13:$K$52,$B7,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B7="","",'ทีมขาย'!G8)</f>
         <v/>
       </c>
       <c r="F7" s="63">
-        <f>IF($B7="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B7,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B7="","",'ทีมขาย'!H8)</f>
         <v/>
       </c>
       <c r="G7" s="63">
-        <f>IF($B7="","",E7-F7)</f>
+        <f>IF($B7="","",'ทีมขาย'!I8)</f>
         <v/>
       </c>
     </row>
@@ -4123,23 +4371,23 @@
         <v/>
       </c>
       <c r="C8" s="62">
-        <f>IF($B8="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B8="","",'ทีมขาย'!E9)</f>
         <v/>
       </c>
       <c r="D8" s="63">
-        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B8="","",'ทีมขาย'!F9)</f>
         <v/>
       </c>
       <c r="E8" s="64">
-        <f>IF($B8="","",SUMIF(Sales_Record!$K$13:$K$52,$B8,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B8="","",'ทีมขาย'!G9)</f>
         <v/>
       </c>
       <c r="F8" s="63">
-        <f>IF($B8="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B8,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B8="","",'ทีมขาย'!H9)</f>
         <v/>
       </c>
       <c r="G8" s="63">
-        <f>IF($B8="","",E8-F8)</f>
+        <f>IF($B8="","",'ทีมขาย'!I9)</f>
         <v/>
       </c>
     </row>
@@ -4149,23 +4397,23 @@
         <v/>
       </c>
       <c r="C9" s="62">
-        <f>IF($B9="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B9="","",'ทีมขาย'!E10)</f>
         <v/>
       </c>
       <c r="D9" s="63">
-        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B9="","",'ทีมขาย'!F10)</f>
         <v/>
       </c>
       <c r="E9" s="64">
-        <f>IF($B9="","",SUMIF(Sales_Record!$K$13:$K$52,$B9,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B9="","",'ทีมขาย'!G10)</f>
         <v/>
       </c>
       <c r="F9" s="63">
-        <f>IF($B9="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B9,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B9="","",'ทีมขาย'!H10)</f>
         <v/>
       </c>
       <c r="G9" s="63">
-        <f>IF($B9="","",E9-F9)</f>
+        <f>IF($B9="","",'ทีมขาย'!I10)</f>
         <v/>
       </c>
     </row>
@@ -4175,23 +4423,23 @@
         <v/>
       </c>
       <c r="C10" s="62">
-        <f>IF($B10="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B10="","",'ทีมขาย'!E11)</f>
         <v/>
       </c>
       <c r="D10" s="63">
-        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B10="","",'ทีมขาย'!F11)</f>
         <v/>
       </c>
       <c r="E10" s="64">
-        <f>IF($B10="","",SUMIF(Sales_Record!$K$13:$K$52,$B10,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B10="","",'ทีมขาย'!G11)</f>
         <v/>
       </c>
       <c r="F10" s="63">
-        <f>IF($B10="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B10,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B10="","",'ทีมขาย'!H11)</f>
         <v/>
       </c>
       <c r="G10" s="63">
-        <f>IF($B10="","",E10-F10)</f>
+        <f>IF($B10="","",'ทีมขาย'!I11)</f>
         <v/>
       </c>
     </row>
@@ -4201,23 +4449,23 @@
         <v/>
       </c>
       <c r="C11" s="62">
-        <f>IF($B11="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B11="","",'ทีมขาย'!E12)</f>
         <v/>
       </c>
       <c r="D11" s="63">
-        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B11="","",'ทีมขาย'!F12)</f>
         <v/>
       </c>
       <c r="E11" s="64">
-        <f>IF($B11="","",SUMIF(Sales_Record!$K$13:$K$52,$B11,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B11="","",'ทีมขาย'!G12)</f>
         <v/>
       </c>
       <c r="F11" s="63">
-        <f>IF($B11="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B11,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B11="","",'ทีมขาย'!H12)</f>
         <v/>
       </c>
       <c r="G11" s="63">
-        <f>IF($B11="","",E11-F11)</f>
+        <f>IF($B11="","",'ทีมขาย'!I12)</f>
         <v/>
       </c>
     </row>
@@ -4227,23 +4475,23 @@
         <v/>
       </c>
       <c r="C12" s="62">
-        <f>IF($B12="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B12="","",'ทีมขาย'!E13)</f>
         <v/>
       </c>
       <c r="D12" s="63">
-        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B12="","",'ทีมขาย'!F13)</f>
         <v/>
       </c>
       <c r="E12" s="64">
-        <f>IF($B12="","",SUMIF(Sales_Record!$K$13:$K$52,$B12,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B12="","",'ทีมขาย'!G13)</f>
         <v/>
       </c>
       <c r="F12" s="63">
-        <f>IF($B12="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B12,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B12="","",'ทีมขาย'!H13)</f>
         <v/>
       </c>
       <c r="G12" s="63">
-        <f>IF($B12="","",E12-F12)</f>
+        <f>IF($B12="","",'ทีมขาย'!I13)</f>
         <v/>
       </c>
     </row>
@@ -4253,23 +4501,23 @@
         <v/>
       </c>
       <c r="C13" s="62">
-        <f>IF($B13="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B13="","",'ทีมขาย'!E14)</f>
         <v/>
       </c>
       <c r="D13" s="63">
-        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B13="","",'ทีมขาย'!F14)</f>
         <v/>
       </c>
       <c r="E13" s="64">
-        <f>IF($B13="","",SUMIF(Sales_Record!$K$13:$K$52,$B13,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B13="","",'ทีมขาย'!G14)</f>
         <v/>
       </c>
       <c r="F13" s="63">
-        <f>IF($B13="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B13,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B13="","",'ทีมขาย'!H14)</f>
         <v/>
       </c>
       <c r="G13" s="63">
-        <f>IF($B13="","",E13-F13)</f>
+        <f>IF($B13="","",'ทีมขาย'!I14)</f>
         <v/>
       </c>
     </row>
@@ -4279,23 +4527,23 @@
         <v/>
       </c>
       <c r="C14" s="62">
-        <f>IF($B14="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B14="","",'ทีมขาย'!E15)</f>
         <v/>
       </c>
       <c r="D14" s="63">
-        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B14="","",'ทีมขาย'!F15)</f>
         <v/>
       </c>
       <c r="E14" s="64">
-        <f>IF($B14="","",SUMIF(Sales_Record!$K$13:$K$52,$B14,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B14="","",'ทีมขาย'!G15)</f>
         <v/>
       </c>
       <c r="F14" s="63">
-        <f>IF($B14="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B14,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B14="","",'ทีมขาย'!H15)</f>
         <v/>
       </c>
       <c r="G14" s="63">
-        <f>IF($B14="","",E14-F14)</f>
+        <f>IF($B14="","",'ทีมขาย'!I15)</f>
         <v/>
       </c>
     </row>
@@ -4305,23 +4553,23 @@
         <v/>
       </c>
       <c r="C15" s="62">
-        <f>IF($B15="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B15="","",'ทีมขาย'!E16)</f>
         <v/>
       </c>
       <c r="D15" s="63">
-        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B15="","",'ทีมขาย'!F16)</f>
         <v/>
       </c>
       <c r="E15" s="64">
-        <f>IF($B15="","",SUMIF(Sales_Record!$K$13:$K$52,$B15,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B15="","",'ทีมขาย'!G16)</f>
         <v/>
       </c>
       <c r="F15" s="63">
-        <f>IF($B15="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B15,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B15="","",'ทีมขาย'!H16)</f>
         <v/>
       </c>
       <c r="G15" s="63">
-        <f>IF($B15="","",E15-F15)</f>
+        <f>IF($B15="","",'ทีมขาย'!I16)</f>
         <v/>
       </c>
     </row>
@@ -4331,23 +4579,23 @@
         <v/>
       </c>
       <c r="C16" s="62">
-        <f>IF($B16="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B16="","",'ทีมขาย'!E17)</f>
         <v/>
       </c>
       <c r="D16" s="63">
-        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B16="","",'ทีมขาย'!F17)</f>
         <v/>
       </c>
       <c r="E16" s="64">
-        <f>IF($B16="","",SUMIF(Sales_Record!$K$13:$K$52,$B16,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B16="","",'ทีมขาย'!G17)</f>
         <v/>
       </c>
       <c r="F16" s="63">
-        <f>IF($B16="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B16,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B16="","",'ทีมขาย'!H17)</f>
         <v/>
       </c>
       <c r="G16" s="63">
-        <f>IF($B16="","",E16-F16)</f>
+        <f>IF($B16="","",'ทีมขาย'!I17)</f>
         <v/>
       </c>
     </row>
@@ -4357,23 +4605,23 @@
         <v/>
       </c>
       <c r="C17" s="62">
-        <f>IF($B17="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B17="","",'ทีมขาย'!E18)</f>
         <v/>
       </c>
       <c r="D17" s="63">
-        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B17="","",'ทีมขาย'!F18)</f>
         <v/>
       </c>
       <c r="E17" s="64">
-        <f>IF($B17="","",SUMIF(Sales_Record!$K$13:$K$52,$B17,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B17="","",'ทีมขาย'!G18)</f>
         <v/>
       </c>
       <c r="F17" s="63">
-        <f>IF($B17="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B17,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B17="","",'ทีมขาย'!H18)</f>
         <v/>
       </c>
       <c r="G17" s="63">
-        <f>IF($B17="","",E17-F17)</f>
+        <f>IF($B17="","",'ทีมขาย'!I18)</f>
         <v/>
       </c>
     </row>
@@ -4383,23 +4631,23 @@
         <v/>
       </c>
       <c r="C18" s="62">
-        <f>IF($B18="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B18="","",'ทีมขาย'!E19)</f>
         <v/>
       </c>
       <c r="D18" s="63">
-        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B18="","",'ทีมขาย'!F19)</f>
         <v/>
       </c>
       <c r="E18" s="64">
-        <f>IF($B18="","",SUMIF(Sales_Record!$K$13:$K$52,$B18,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B18="","",'ทีมขาย'!G19)</f>
         <v/>
       </c>
       <c r="F18" s="63">
-        <f>IF($B18="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B18,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B18="","",'ทีมขาย'!H19)</f>
         <v/>
       </c>
       <c r="G18" s="63">
-        <f>IF($B18="","",E18-F18)</f>
+        <f>IF($B18="","",'ทีมขาย'!I19)</f>
         <v/>
       </c>
     </row>
@@ -4409,50 +4657,50 @@
         <v/>
       </c>
       <c r="C19" s="62">
-        <f>IF($B19="","",COUNTIFS(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
+        <f>IF($B19="","",'ทีมขาย'!E20)</f>
         <v/>
       </c>
       <c r="D19" s="63">
-        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$J$13:$J$52))</f>
+        <f>IF($B19="","",'ทีมขาย'!F20)</f>
         <v/>
       </c>
       <c r="E19" s="64">
-        <f>IF($B19="","",SUMIF(Sales_Record!$K$13:$K$52,$B19,Sales_Record!$M$13:$M$52))</f>
+        <f>IF($B19="","",'ทีมขาย'!G20)</f>
         <v/>
       </c>
       <c r="F19" s="63">
-        <f>IF($B19="","",SUMIFS(Sales_Record!$M$13:$M$52,Sales_Record!$K$13:$K$52,$B19,Sales_Record!$N$13:$N$52,"จ่ายแล้ว"))</f>
+        <f>IF($B19="","",'ทีมขาย'!H20)</f>
         <v/>
       </c>
       <c r="G19" s="63">
-        <f>IF($B19="","",E19-F19)</f>
+        <f>IF($B19="","",'ทีมขาย'!I20)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>รวมทั้งทีม</t>
         </is>
       </c>
-      <c r="C20" s="69">
+      <c r="C20" s="62">
         <f>SUM(C5:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="83">
+      <c r="D20" s="63">
         <f>SUM(D5:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="83">
+      <c r="E20" s="64">
         <f>SUM(E5:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="83">
+      <c r="F20" s="63">
         <f>SUM(F5:F19)</f>
         <v/>
       </c>
-      <c r="G20" s="83">
-        <f>E20-F20</f>
+      <c r="G20" s="63">
+        <f>SUM(G5:G19)</f>
         <v/>
       </c>
     </row>

--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sales_Record" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ทีมขาย" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rate" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="REPORT (EN)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="รายได้" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="REPORT (TH)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;฿&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -179,8 +179,25 @@
       <color rgb="000E5E5D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F2A36"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A2433"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005A6673"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -277,8 +294,13 @@
         <fgColor rgb="00EAF1F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAEDF0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -480,11 +502,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+    </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="009AA7B2"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -763,6 +797,82 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="22" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1129,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1179,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="19" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1294,15 +1403,15 @@
         <v/>
       </c>
       <c r="M6" s="13">
-        <f>'ทีมขาย'!G6</f>
+        <f>'ทีมขาย'!F6</f>
         <v/>
       </c>
       <c r="N6" s="13">
-        <f>'ทีมขาย'!G7</f>
+        <f>'ทีมขาย'!F7</f>
         <v/>
       </c>
       <c r="O6" s="13">
-        <f>'ทีมขาย'!G8</f>
+        <f>'ทีมขาย'!F8</f>
         <v/>
       </c>
     </row>
@@ -1370,8 +1479,6 @@
       </c>
       <c r="O8" s="18" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="21" t="inlineStr">
         <is>
@@ -1408,9 +1515,9 @@
           <t>ค่าคอมมิชชั่น</t>
         </is>
       </c>
-      <c r="L11" s="86" t="n"/>
-      <c r="M11" s="86" t="n"/>
-      <c r="N11" s="87" t="n"/>
+      <c r="L11" s="71" t="n"/>
+      <c r="M11" s="71" t="n"/>
+      <c r="N11" s="72" t="n"/>
       <c r="O11" s="21" t="inlineStr">
         <is>
           <t>สถานะ</t>
@@ -1495,54 +1602,54 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31">
+      <c r="A13" s="106">
         <f>IF(B13="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="31">
+      <c r="B13" s="105" t="n"/>
+      <c r="C13" s="106">
         <f>IF(B13="","","Q"&amp;ROUNDUP(MONTH(B13)/3,0))</f>
         <v/>
       </c>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="31" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="34">
+      <c r="D13" s="107" t="n"/>
+      <c r="E13" s="106" t="n"/>
+      <c r="F13" s="106" t="n"/>
+      <c r="G13" s="106" t="n"/>
+      <c r="H13" s="108">
         <f>IF(G13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I13" s="35" t="n"/>
-      <c r="J13" s="34">
+      <c r="J13" s="108">
         <f>IF(H13="","",H13*(1-IF(I13="",0,I13)))</f>
         <v/>
       </c>
-      <c r="K13" s="88" t="n"/>
-      <c r="L13" s="31" t="n"/>
+      <c r="K13" s="106" t="n"/>
+      <c r="L13" s="106" t="n"/>
       <c r="M13" s="35">
-        <f>IF(G13="","",IF(K13="ทีม",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IF(L13="",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L13,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G13="","",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N13" s="36">
         <f>IF(OR(J13="",M13=""),"",J13*M13)</f>
         <v/>
       </c>
-      <c r="O13" s="31" t="n"/>
+      <c r="O13" s="106" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="37">
+      <c r="A14" s="89">
         <f>IF(B14="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B14" s="38" t="n"/>
-      <c r="C14" s="37">
+      <c r="C14" s="89">
         <f>IF(B14="","","Q"&amp;ROUNDUP(MONTH(B14)/3,0))</f>
         <v/>
       </c>
       <c r="D14" s="39" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="37" t="n"/>
+      <c r="E14" s="89" t="n"/>
+      <c r="F14" s="89" t="n"/>
+      <c r="G14" s="89" t="n"/>
       <c r="H14" s="40">
         <f>IF(G14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -1553,66 +1660,66 @@
         <v/>
       </c>
       <c r="K14" s="89" t="n"/>
-      <c r="L14" s="37" t="n"/>
+      <c r="L14" s="89" t="n"/>
       <c r="M14" s="41">
-        <f>IF(G14="","",IF(K14="ทีม",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IF(L14="",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L14,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G14="","",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N14" s="42">
         <f>IF(OR(J14="",M14=""),"",J14*M14)</f>
         <v/>
       </c>
-      <c r="O14" s="37" t="n"/>
+      <c r="O14" s="89" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="31">
+      <c r="A15" s="106">
         <f>IF(B15="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B15" s="32" t="n"/>
-      <c r="C15" s="31">
+      <c r="B15" s="105" t="n"/>
+      <c r="C15" s="106">
         <f>IF(B15="","","Q"&amp;ROUNDUP(MONTH(B15)/3,0))</f>
         <v/>
       </c>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="31" t="n"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="34">
+      <c r="D15" s="107" t="n"/>
+      <c r="E15" s="106" t="n"/>
+      <c r="F15" s="106" t="n"/>
+      <c r="G15" s="106" t="n"/>
+      <c r="H15" s="108">
         <f>IF(G15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I15" s="35" t="n"/>
-      <c r="J15" s="34">
+      <c r="J15" s="108">
         <f>IF(H15="","",H15*(1-IF(I15="",0,I15)))</f>
         <v/>
       </c>
-      <c r="K15" s="88" t="n"/>
-      <c r="L15" s="31" t="n"/>
+      <c r="K15" s="106" t="n"/>
+      <c r="L15" s="106" t="n"/>
       <c r="M15" s="35">
-        <f>IF(G15="","",IF(K15="ทีม",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IF(L15="",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L15,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G15="","",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N15" s="36">
         <f>IF(OR(J15="",M15=""),"",J15*M15)</f>
         <v/>
       </c>
-      <c r="O15" s="31" t="n"/>
+      <c r="O15" s="106" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="37">
+      <c r="A16" s="89">
         <f>IF(B16="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B16" s="38" t="n"/>
-      <c r="C16" s="37">
+      <c r="C16" s="89">
         <f>IF(B16="","","Q"&amp;ROUNDUP(MONTH(B16)/3,0))</f>
         <v/>
       </c>
       <c r="D16" s="39" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="37" t="n"/>
-      <c r="G16" s="37" t="n"/>
+      <c r="E16" s="89" t="n"/>
+      <c r="F16" s="89" t="n"/>
+      <c r="G16" s="89" t="n"/>
       <c r="H16" s="40">
         <f>IF(G16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -1623,66 +1730,66 @@
         <v/>
       </c>
       <c r="K16" s="89" t="n"/>
-      <c r="L16" s="37" t="n"/>
+      <c r="L16" s="89" t="n"/>
       <c r="M16" s="41">
-        <f>IF(G16="","",IF(K16="ทีม",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IF(L16="",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L16,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G16="","",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N16" s="42">
         <f>IF(OR(J16="",M16=""),"",J16*M16)</f>
         <v/>
       </c>
-      <c r="O16" s="37" t="n"/>
+      <c r="O16" s="89" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="31">
+      <c r="A17" s="106">
         <f>IF(B17="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="31">
+      <c r="B17" s="105" t="n"/>
+      <c r="C17" s="106">
         <f>IF(B17="","","Q"&amp;ROUNDUP(MONTH(B17)/3,0))</f>
         <v/>
       </c>
-      <c r="D17" s="33" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="31" t="n"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="34">
+      <c r="D17" s="107" t="n"/>
+      <c r="E17" s="106" t="n"/>
+      <c r="F17" s="106" t="n"/>
+      <c r="G17" s="106" t="n"/>
+      <c r="H17" s="108">
         <f>IF(G17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I17" s="35" t="n"/>
-      <c r="J17" s="34">
+      <c r="J17" s="108">
         <f>IF(H17="","",H17*(1-IF(I17="",0,I17)))</f>
         <v/>
       </c>
-      <c r="K17" s="88" t="n"/>
-      <c r="L17" s="31" t="n"/>
+      <c r="K17" s="106" t="n"/>
+      <c r="L17" s="106" t="n"/>
       <c r="M17" s="35">
-        <f>IF(G17="","",IF(K17="ทีม",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IF(L17="",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L17,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G17="","",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N17" s="36">
         <f>IF(OR(J17="",M17=""),"",J17*M17)</f>
         <v/>
       </c>
-      <c r="O17" s="31" t="n"/>
+      <c r="O17" s="106" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="37">
+      <c r="A18" s="89">
         <f>IF(B18="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B18" s="38" t="n"/>
-      <c r="C18" s="37">
+      <c r="C18" s="89">
         <f>IF(B18="","","Q"&amp;ROUNDUP(MONTH(B18)/3,0))</f>
         <v/>
       </c>
       <c r="D18" s="39" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="37" t="n"/>
-      <c r="G18" s="37" t="n"/>
+      <c r="E18" s="89" t="n"/>
+      <c r="F18" s="89" t="n"/>
+      <c r="G18" s="89" t="n"/>
       <c r="H18" s="40">
         <f>IF(G18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -1693,66 +1800,66 @@
         <v/>
       </c>
       <c r="K18" s="89" t="n"/>
-      <c r="L18" s="37" t="n"/>
+      <c r="L18" s="89" t="n"/>
       <c r="M18" s="41">
-        <f>IF(G18="","",IF(K18="ทีม",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IF(L18="",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L18,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G18="","",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N18" s="42">
         <f>IF(OR(J18="",M18=""),"",J18*M18)</f>
         <v/>
       </c>
-      <c r="O18" s="37" t="n"/>
+      <c r="O18" s="89" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="31">
+      <c r="A19" s="106">
         <f>IF(B19="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="31">
+      <c r="B19" s="105" t="n"/>
+      <c r="C19" s="106">
         <f>IF(B19="","","Q"&amp;ROUNDUP(MONTH(B19)/3,0))</f>
         <v/>
       </c>
-      <c r="D19" s="33" t="n"/>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="31" t="n"/>
-      <c r="H19" s="34">
+      <c r="D19" s="107" t="n"/>
+      <c r="E19" s="106" t="n"/>
+      <c r="F19" s="106" t="n"/>
+      <c r="G19" s="106" t="n"/>
+      <c r="H19" s="108">
         <f>IF(G19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I19" s="35" t="n"/>
-      <c r="J19" s="34">
+      <c r="J19" s="108">
         <f>IF(H19="","",H19*(1-IF(I19="",0,I19)))</f>
         <v/>
       </c>
-      <c r="K19" s="88" t="n"/>
-      <c r="L19" s="31" t="n"/>
+      <c r="K19" s="106" t="n"/>
+      <c r="L19" s="106" t="n"/>
       <c r="M19" s="35">
-        <f>IF(G19="","",IF(K19="ทีม",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IF(L19="",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L19,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G19="","",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N19" s="36">
         <f>IF(OR(J19="",M19=""),"",J19*M19)</f>
         <v/>
       </c>
-      <c r="O19" s="31" t="n"/>
+      <c r="O19" s="106" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="37">
+      <c r="A20" s="89">
         <f>IF(B20="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B20" s="38" t="n"/>
-      <c r="C20" s="37">
+      <c r="C20" s="89">
         <f>IF(B20="","","Q"&amp;ROUNDUP(MONTH(B20)/3,0))</f>
         <v/>
       </c>
       <c r="D20" s="39" t="n"/>
-      <c r="E20" s="37" t="n"/>
-      <c r="F20" s="37" t="n"/>
-      <c r="G20" s="37" t="n"/>
+      <c r="E20" s="89" t="n"/>
+      <c r="F20" s="89" t="n"/>
+      <c r="G20" s="89" t="n"/>
       <c r="H20" s="40">
         <f>IF(G20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -1763,66 +1870,66 @@
         <v/>
       </c>
       <c r="K20" s="89" t="n"/>
-      <c r="L20" s="37" t="n"/>
+      <c r="L20" s="89" t="n"/>
       <c r="M20" s="41">
-        <f>IF(G20="","",IF(K20="ทีม",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IF(L20="",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L20,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G20="","",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N20" s="42">
         <f>IF(OR(J20="",M20=""),"",J20*M20)</f>
         <v/>
       </c>
-      <c r="O20" s="37" t="n"/>
+      <c r="O20" s="89" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="31">
+      <c r="A21" s="106">
         <f>IF(B21="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="31">
+      <c r="B21" s="105" t="n"/>
+      <c r="C21" s="106">
         <f>IF(B21="","","Q"&amp;ROUNDUP(MONTH(B21)/3,0))</f>
         <v/>
       </c>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="31" t="n"/>
-      <c r="G21" s="31" t="n"/>
-      <c r="H21" s="34">
+      <c r="D21" s="107" t="n"/>
+      <c r="E21" s="106" t="n"/>
+      <c r="F21" s="106" t="n"/>
+      <c r="G21" s="106" t="n"/>
+      <c r="H21" s="108">
         <f>IF(G21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I21" s="35" t="n"/>
-      <c r="J21" s="34">
+      <c r="J21" s="108">
         <f>IF(H21="","",H21*(1-IF(I21="",0,I21)))</f>
         <v/>
       </c>
-      <c r="K21" s="88" t="n"/>
-      <c r="L21" s="31" t="n"/>
+      <c r="K21" s="106" t="n"/>
+      <c r="L21" s="106" t="n"/>
       <c r="M21" s="35">
-        <f>IF(G21="","",IF(K21="ทีม",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IF(L21="",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L21,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G21="","",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N21" s="36">
         <f>IF(OR(J21="",M21=""),"",J21*M21)</f>
         <v/>
       </c>
-      <c r="O21" s="31" t="n"/>
+      <c r="O21" s="106" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="37">
+      <c r="A22" s="89">
         <f>IF(B22="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B22" s="38" t="n"/>
-      <c r="C22" s="37">
+      <c r="C22" s="89">
         <f>IF(B22="","","Q"&amp;ROUNDUP(MONTH(B22)/3,0))</f>
         <v/>
       </c>
       <c r="D22" s="39" t="n"/>
-      <c r="E22" s="37" t="n"/>
-      <c r="F22" s="37" t="n"/>
-      <c r="G22" s="37" t="n"/>
+      <c r="E22" s="89" t="n"/>
+      <c r="F22" s="89" t="n"/>
+      <c r="G22" s="89" t="n"/>
       <c r="H22" s="40">
         <f>IF(G22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -1833,66 +1940,66 @@
         <v/>
       </c>
       <c r="K22" s="89" t="n"/>
-      <c r="L22" s="37" t="n"/>
+      <c r="L22" s="89" t="n"/>
       <c r="M22" s="41">
-        <f>IF(G22="","",IF(K22="ทีม",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IF(L22="",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L22,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G22="","",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N22" s="42">
         <f>IF(OR(J22="",M22=""),"",J22*M22)</f>
         <v/>
       </c>
-      <c r="O22" s="37" t="n"/>
+      <c r="O22" s="89" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="31">
+      <c r="A23" s="106">
         <f>IF(B23="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="31">
+      <c r="B23" s="105" t="n"/>
+      <c r="C23" s="106">
         <f>IF(B23="","","Q"&amp;ROUNDUP(MONTH(B23)/3,0))</f>
         <v/>
       </c>
-      <c r="D23" s="33" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="34">
+      <c r="D23" s="107" t="n"/>
+      <c r="E23" s="106" t="n"/>
+      <c r="F23" s="106" t="n"/>
+      <c r="G23" s="106" t="n"/>
+      <c r="H23" s="108">
         <f>IF(G23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I23" s="35" t="n"/>
-      <c r="J23" s="34">
+      <c r="J23" s="108">
         <f>IF(H23="","",H23*(1-IF(I23="",0,I23)))</f>
         <v/>
       </c>
-      <c r="K23" s="88" t="n"/>
-      <c r="L23" s="31" t="n"/>
+      <c r="K23" s="106" t="n"/>
+      <c r="L23" s="106" t="n"/>
       <c r="M23" s="35">
-        <f>IF(G23="","",IF(K23="ทีม",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IF(L23="",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L23,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G23="","",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N23" s="36">
         <f>IF(OR(J23="",M23=""),"",J23*M23)</f>
         <v/>
       </c>
-      <c r="O23" s="31" t="n"/>
+      <c r="O23" s="106" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="37">
+      <c r="A24" s="89">
         <f>IF(B24="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B24" s="38" t="n"/>
-      <c r="C24" s="37">
+      <c r="C24" s="89">
         <f>IF(B24="","","Q"&amp;ROUNDUP(MONTH(B24)/3,0))</f>
         <v/>
       </c>
       <c r="D24" s="39" t="n"/>
-      <c r="E24" s="37" t="n"/>
-      <c r="F24" s="37" t="n"/>
-      <c r="G24" s="37" t="n"/>
+      <c r="E24" s="89" t="n"/>
+      <c r="F24" s="89" t="n"/>
+      <c r="G24" s="89" t="n"/>
       <c r="H24" s="40">
         <f>IF(G24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -1903,66 +2010,66 @@
         <v/>
       </c>
       <c r="K24" s="89" t="n"/>
-      <c r="L24" s="37" t="n"/>
+      <c r="L24" s="89" t="n"/>
       <c r="M24" s="41">
-        <f>IF(G24="","",IF(K24="ทีม",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IF(L24="",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L24,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G24="","",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N24" s="42">
         <f>IF(OR(J24="",M24=""),"",J24*M24)</f>
         <v/>
       </c>
-      <c r="O24" s="37" t="n"/>
+      <c r="O24" s="89" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="31">
+      <c r="A25" s="106">
         <f>IF(B25="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="31">
+      <c r="B25" s="105" t="n"/>
+      <c r="C25" s="106">
         <f>IF(B25="","","Q"&amp;ROUNDUP(MONTH(B25)/3,0))</f>
         <v/>
       </c>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="34">
+      <c r="D25" s="107" t="n"/>
+      <c r="E25" s="106" t="n"/>
+      <c r="F25" s="106" t="n"/>
+      <c r="G25" s="106" t="n"/>
+      <c r="H25" s="108">
         <f>IF(G25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I25" s="35" t="n"/>
-      <c r="J25" s="34">
+      <c r="J25" s="108">
         <f>IF(H25="","",H25*(1-IF(I25="",0,I25)))</f>
         <v/>
       </c>
-      <c r="K25" s="88" t="n"/>
-      <c r="L25" s="31" t="n"/>
+      <c r="K25" s="106" t="n"/>
+      <c r="L25" s="106" t="n"/>
       <c r="M25" s="35">
-        <f>IF(G25="","",IF(K25="ทีม",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IF(L25="",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L25,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G25="","",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N25" s="36">
         <f>IF(OR(J25="",M25=""),"",J25*M25)</f>
         <v/>
       </c>
-      <c r="O25" s="31" t="n"/>
+      <c r="O25" s="106" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="37">
+      <c r="A26" s="89">
         <f>IF(B26="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B26" s="38" t="n"/>
-      <c r="C26" s="37">
+      <c r="C26" s="89">
         <f>IF(B26="","","Q"&amp;ROUNDUP(MONTH(B26)/3,0))</f>
         <v/>
       </c>
       <c r="D26" s="39" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="37" t="n"/>
-      <c r="G26" s="37" t="n"/>
+      <c r="E26" s="89" t="n"/>
+      <c r="F26" s="89" t="n"/>
+      <c r="G26" s="89" t="n"/>
       <c r="H26" s="40">
         <f>IF(G26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -1973,66 +2080,66 @@
         <v/>
       </c>
       <c r="K26" s="89" t="n"/>
-      <c r="L26" s="37" t="n"/>
+      <c r="L26" s="89" t="n"/>
       <c r="M26" s="41">
-        <f>IF(G26="","",IF(K26="ทีม",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IF(L26="",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L26,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G26="","",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N26" s="42">
         <f>IF(OR(J26="",M26=""),"",J26*M26)</f>
         <v/>
       </c>
-      <c r="O26" s="37" t="n"/>
+      <c r="O26" s="89" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="31">
+      <c r="A27" s="106">
         <f>IF(B27="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="31">
+      <c r="B27" s="105" t="n"/>
+      <c r="C27" s="106">
         <f>IF(B27="","","Q"&amp;ROUNDUP(MONTH(B27)/3,0))</f>
         <v/>
       </c>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="34">
+      <c r="D27" s="107" t="n"/>
+      <c r="E27" s="106" t="n"/>
+      <c r="F27" s="106" t="n"/>
+      <c r="G27" s="106" t="n"/>
+      <c r="H27" s="108">
         <f>IF(G27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I27" s="35" t="n"/>
-      <c r="J27" s="34">
+      <c r="J27" s="108">
         <f>IF(H27="","",H27*(1-IF(I27="",0,I27)))</f>
         <v/>
       </c>
-      <c r="K27" s="88" t="n"/>
-      <c r="L27" s="31" t="n"/>
+      <c r="K27" s="106" t="n"/>
+      <c r="L27" s="106" t="n"/>
       <c r="M27" s="35">
-        <f>IF(G27="","",IF(K27="ทีม",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IF(L27="",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L27,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G27="","",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N27" s="36">
         <f>IF(OR(J27="",M27=""),"",J27*M27)</f>
         <v/>
       </c>
-      <c r="O27" s="31" t="n"/>
+      <c r="O27" s="106" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="37">
+      <c r="A28" s="89">
         <f>IF(B28="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B28" s="38" t="n"/>
-      <c r="C28" s="37">
+      <c r="C28" s="89">
         <f>IF(B28="","","Q"&amp;ROUNDUP(MONTH(B28)/3,0))</f>
         <v/>
       </c>
       <c r="D28" s="39" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
-      <c r="G28" s="37" t="n"/>
+      <c r="E28" s="89" t="n"/>
+      <c r="F28" s="89" t="n"/>
+      <c r="G28" s="89" t="n"/>
       <c r="H28" s="40">
         <f>IF(G28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2043,66 +2150,66 @@
         <v/>
       </c>
       <c r="K28" s="89" t="n"/>
-      <c r="L28" s="37" t="n"/>
+      <c r="L28" s="89" t="n"/>
       <c r="M28" s="41">
-        <f>IF(G28="","",IF(K28="ทีม",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IF(L28="",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L28,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G28="","",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N28" s="42">
         <f>IF(OR(J28="",M28=""),"",J28*M28)</f>
         <v/>
       </c>
-      <c r="O28" s="37" t="n"/>
+      <c r="O28" s="89" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="31">
+      <c r="A29" s="106">
         <f>IF(B29="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="31">
+      <c r="B29" s="105" t="n"/>
+      <c r="C29" s="106">
         <f>IF(B29="","","Q"&amp;ROUNDUP(MONTH(B29)/3,0))</f>
         <v/>
       </c>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="34">
+      <c r="D29" s="107" t="n"/>
+      <c r="E29" s="106" t="n"/>
+      <c r="F29" s="106" t="n"/>
+      <c r="G29" s="106" t="n"/>
+      <c r="H29" s="108">
         <f>IF(G29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I29" s="35" t="n"/>
-      <c r="J29" s="34">
+      <c r="J29" s="108">
         <f>IF(H29="","",H29*(1-IF(I29="",0,I29)))</f>
         <v/>
       </c>
-      <c r="K29" s="88" t="n"/>
-      <c r="L29" s="31" t="n"/>
+      <c r="K29" s="106" t="n"/>
+      <c r="L29" s="106" t="n"/>
       <c r="M29" s="35">
-        <f>IF(G29="","",IF(K29="ทีม",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IF(L29="",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L29,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G29="","",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N29" s="36">
         <f>IF(OR(J29="",M29=""),"",J29*M29)</f>
         <v/>
       </c>
-      <c r="O29" s="31" t="n"/>
+      <c r="O29" s="106" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="37">
+      <c r="A30" s="89">
         <f>IF(B30="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B30" s="38" t="n"/>
-      <c r="C30" s="37">
+      <c r="C30" s="89">
         <f>IF(B30="","","Q"&amp;ROUNDUP(MONTH(B30)/3,0))</f>
         <v/>
       </c>
       <c r="D30" s="39" t="n"/>
-      <c r="E30" s="37" t="n"/>
-      <c r="F30" s="37" t="n"/>
-      <c r="G30" s="37" t="n"/>
+      <c r="E30" s="89" t="n"/>
+      <c r="F30" s="89" t="n"/>
+      <c r="G30" s="89" t="n"/>
       <c r="H30" s="40">
         <f>IF(G30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2113,66 +2220,66 @@
         <v/>
       </c>
       <c r="K30" s="89" t="n"/>
-      <c r="L30" s="37" t="n"/>
+      <c r="L30" s="89" t="n"/>
       <c r="M30" s="41">
-        <f>IF(G30="","",IF(K30="ทีม",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IF(L30="",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L30,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G30="","",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N30" s="42">
         <f>IF(OR(J30="",M30=""),"",J30*M30)</f>
         <v/>
       </c>
-      <c r="O30" s="37" t="n"/>
+      <c r="O30" s="89" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="31">
+      <c r="A31" s="106">
         <f>IF(B31="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="31">
+      <c r="B31" s="105" t="n"/>
+      <c r="C31" s="106">
         <f>IF(B31="","","Q"&amp;ROUNDUP(MONTH(B31)/3,0))</f>
         <v/>
       </c>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="34">
+      <c r="D31" s="107" t="n"/>
+      <c r="E31" s="106" t="n"/>
+      <c r="F31" s="106" t="n"/>
+      <c r="G31" s="106" t="n"/>
+      <c r="H31" s="108">
         <f>IF(G31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I31" s="35" t="n"/>
-      <c r="J31" s="34">
+      <c r="J31" s="108">
         <f>IF(H31="","",H31*(1-IF(I31="",0,I31)))</f>
         <v/>
       </c>
-      <c r="K31" s="88" t="n"/>
-      <c r="L31" s="31" t="n"/>
+      <c r="K31" s="106" t="n"/>
+      <c r="L31" s="106" t="n"/>
       <c r="M31" s="35">
-        <f>IF(G31="","",IF(K31="ทีม",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IF(L31="",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L31,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G31="","",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N31" s="36">
         <f>IF(OR(J31="",M31=""),"",J31*M31)</f>
         <v/>
       </c>
-      <c r="O31" s="31" t="n"/>
+      <c r="O31" s="106" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="37">
+      <c r="A32" s="89">
         <f>IF(B32="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B32" s="38" t="n"/>
-      <c r="C32" s="37">
+      <c r="C32" s="89">
         <f>IF(B32="","","Q"&amp;ROUNDUP(MONTH(B32)/3,0))</f>
         <v/>
       </c>
       <c r="D32" s="39" t="n"/>
-      <c r="E32" s="37" t="n"/>
-      <c r="F32" s="37" t="n"/>
-      <c r="G32" s="37" t="n"/>
+      <c r="E32" s="89" t="n"/>
+      <c r="F32" s="89" t="n"/>
+      <c r="G32" s="89" t="n"/>
       <c r="H32" s="40">
         <f>IF(G32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2183,66 +2290,66 @@
         <v/>
       </c>
       <c r="K32" s="89" t="n"/>
-      <c r="L32" s="37" t="n"/>
+      <c r="L32" s="89" t="n"/>
       <c r="M32" s="41">
-        <f>IF(G32="","",IF(K32="ทีม",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IF(L32="",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L32,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G32="","",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N32" s="42">
         <f>IF(OR(J32="",M32=""),"",J32*M32)</f>
         <v/>
       </c>
-      <c r="O32" s="37" t="n"/>
+      <c r="O32" s="89" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="31">
+      <c r="A33" s="106">
         <f>IF(B33="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B33" s="32" t="n"/>
-      <c r="C33" s="31">
+      <c r="B33" s="105" t="n"/>
+      <c r="C33" s="106">
         <f>IF(B33="","","Q"&amp;ROUNDUP(MONTH(B33)/3,0))</f>
         <v/>
       </c>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="34">
+      <c r="D33" s="107" t="n"/>
+      <c r="E33" s="106" t="n"/>
+      <c r="F33" s="106" t="n"/>
+      <c r="G33" s="106" t="n"/>
+      <c r="H33" s="108">
         <f>IF(G33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I33" s="35" t="n"/>
-      <c r="J33" s="34">
+      <c r="J33" s="108">
         <f>IF(H33="","",H33*(1-IF(I33="",0,I33)))</f>
         <v/>
       </c>
-      <c r="K33" s="88" t="n"/>
-      <c r="L33" s="31" t="n"/>
+      <c r="K33" s="106" t="n"/>
+      <c r="L33" s="106" t="n"/>
       <c r="M33" s="35">
-        <f>IF(G33="","",IF(K33="ทีม",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IF(L33="",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L33,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G33="","",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N33" s="36">
         <f>IF(OR(J33="",M33=""),"",J33*M33)</f>
         <v/>
       </c>
-      <c r="O33" s="31" t="n"/>
+      <c r="O33" s="106" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="37">
+      <c r="A34" s="89">
         <f>IF(B34="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B34" s="38" t="n"/>
-      <c r="C34" s="37">
+      <c r="C34" s="89">
         <f>IF(B34="","","Q"&amp;ROUNDUP(MONTH(B34)/3,0))</f>
         <v/>
       </c>
       <c r="D34" s="39" t="n"/>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="37" t="n"/>
-      <c r="G34" s="37" t="n"/>
+      <c r="E34" s="89" t="n"/>
+      <c r="F34" s="89" t="n"/>
+      <c r="G34" s="89" t="n"/>
       <c r="H34" s="40">
         <f>IF(G34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2253,66 +2360,66 @@
         <v/>
       </c>
       <c r="K34" s="89" t="n"/>
-      <c r="L34" s="37" t="n"/>
+      <c r="L34" s="89" t="n"/>
       <c r="M34" s="41">
-        <f>IF(G34="","",IF(K34="ทีม",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IF(L34="",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L34,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G34="","",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N34" s="42">
         <f>IF(OR(J34="",M34=""),"",J34*M34)</f>
         <v/>
       </c>
-      <c r="O34" s="37" t="n"/>
+      <c r="O34" s="89" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="31">
+      <c r="A35" s="106">
         <f>IF(B35="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B35" s="32" t="n"/>
-      <c r="C35" s="31">
+      <c r="B35" s="105" t="n"/>
+      <c r="C35" s="106">
         <f>IF(B35="","","Q"&amp;ROUNDUP(MONTH(B35)/3,0))</f>
         <v/>
       </c>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="34">
+      <c r="D35" s="107" t="n"/>
+      <c r="E35" s="106" t="n"/>
+      <c r="F35" s="106" t="n"/>
+      <c r="G35" s="106" t="n"/>
+      <c r="H35" s="108">
         <f>IF(G35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I35" s="35" t="n"/>
-      <c r="J35" s="34">
+      <c r="J35" s="108">
         <f>IF(H35="","",H35*(1-IF(I35="",0,I35)))</f>
         <v/>
       </c>
-      <c r="K35" s="88" t="n"/>
-      <c r="L35" s="31" t="n"/>
+      <c r="K35" s="106" t="n"/>
+      <c r="L35" s="106" t="n"/>
       <c r="M35" s="35">
-        <f>IF(G35="","",IF(K35="ทีม",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IF(L35="",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L35,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G35="","",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N35" s="36">
         <f>IF(OR(J35="",M35=""),"",J35*M35)</f>
         <v/>
       </c>
-      <c r="O35" s="31" t="n"/>
+      <c r="O35" s="106" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="37">
+      <c r="A36" s="89">
         <f>IF(B36="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B36" s="38" t="n"/>
-      <c r="C36" s="37">
+      <c r="C36" s="89">
         <f>IF(B36="","","Q"&amp;ROUNDUP(MONTH(B36)/3,0))</f>
         <v/>
       </c>
       <c r="D36" s="39" t="n"/>
-      <c r="E36" s="37" t="n"/>
-      <c r="F36" s="37" t="n"/>
-      <c r="G36" s="37" t="n"/>
+      <c r="E36" s="89" t="n"/>
+      <c r="F36" s="89" t="n"/>
+      <c r="G36" s="89" t="n"/>
       <c r="H36" s="40">
         <f>IF(G36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2323,66 +2430,66 @@
         <v/>
       </c>
       <c r="K36" s="89" t="n"/>
-      <c r="L36" s="37" t="n"/>
+      <c r="L36" s="89" t="n"/>
       <c r="M36" s="41">
-        <f>IF(G36="","",IF(K36="ทีม",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IF(L36="",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L36,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G36="","",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N36" s="42">
         <f>IF(OR(J36="",M36=""),"",J36*M36)</f>
         <v/>
       </c>
-      <c r="O36" s="37" t="n"/>
+      <c r="O36" s="89" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="31">
+      <c r="A37" s="106">
         <f>IF(B37="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B37" s="32" t="n"/>
-      <c r="C37" s="31">
+      <c r="B37" s="105" t="n"/>
+      <c r="C37" s="106">
         <f>IF(B37="","","Q"&amp;ROUNDUP(MONTH(B37)/3,0))</f>
         <v/>
       </c>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="31" t="n"/>
-      <c r="G37" s="31" t="n"/>
-      <c r="H37" s="34">
+      <c r="D37" s="107" t="n"/>
+      <c r="E37" s="106" t="n"/>
+      <c r="F37" s="106" t="n"/>
+      <c r="G37" s="106" t="n"/>
+      <c r="H37" s="108">
         <f>IF(G37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I37" s="35" t="n"/>
-      <c r="J37" s="34">
+      <c r="J37" s="108">
         <f>IF(H37="","",H37*(1-IF(I37="",0,I37)))</f>
         <v/>
       </c>
-      <c r="K37" s="88" t="n"/>
-      <c r="L37" s="31" t="n"/>
+      <c r="K37" s="106" t="n"/>
+      <c r="L37" s="106" t="n"/>
       <c r="M37" s="35">
-        <f>IF(G37="","",IF(K37="ทีม",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IF(L37="",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L37,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G37="","",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N37" s="36">
         <f>IF(OR(J37="",M37=""),"",J37*M37)</f>
         <v/>
       </c>
-      <c r="O37" s="31" t="n"/>
+      <c r="O37" s="106" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="37">
+      <c r="A38" s="89">
         <f>IF(B38="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B38" s="38" t="n"/>
-      <c r="C38" s="37">
+      <c r="C38" s="89">
         <f>IF(B38="","","Q"&amp;ROUNDUP(MONTH(B38)/3,0))</f>
         <v/>
       </c>
       <c r="D38" s="39" t="n"/>
-      <c r="E38" s="37" t="n"/>
-      <c r="F38" s="37" t="n"/>
-      <c r="G38" s="37" t="n"/>
+      <c r="E38" s="89" t="n"/>
+      <c r="F38" s="89" t="n"/>
+      <c r="G38" s="89" t="n"/>
       <c r="H38" s="40">
         <f>IF(G38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2393,66 +2500,66 @@
         <v/>
       </c>
       <c r="K38" s="89" t="n"/>
-      <c r="L38" s="37" t="n"/>
+      <c r="L38" s="89" t="n"/>
       <c r="M38" s="41">
-        <f>IF(G38="","",IF(K38="ทีม",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IF(L38="",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L38,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G38="","",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N38" s="42">
         <f>IF(OR(J38="",M38=""),"",J38*M38)</f>
         <v/>
       </c>
-      <c r="O38" s="37" t="n"/>
+      <c r="O38" s="89" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="31">
+      <c r="A39" s="106">
         <f>IF(B39="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="31">
+      <c r="B39" s="105" t="n"/>
+      <c r="C39" s="106">
         <f>IF(B39="","","Q"&amp;ROUNDUP(MONTH(B39)/3,0))</f>
         <v/>
       </c>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="31" t="n"/>
-      <c r="G39" s="31" t="n"/>
-      <c r="H39" s="34">
+      <c r="D39" s="107" t="n"/>
+      <c r="E39" s="106" t="n"/>
+      <c r="F39" s="106" t="n"/>
+      <c r="G39" s="106" t="n"/>
+      <c r="H39" s="108">
         <f>IF(G39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I39" s="35" t="n"/>
-      <c r="J39" s="34">
+      <c r="J39" s="108">
         <f>IF(H39="","",H39*(1-IF(I39="",0,I39)))</f>
         <v/>
       </c>
-      <c r="K39" s="88" t="n"/>
-      <c r="L39" s="31" t="n"/>
+      <c r="K39" s="106" t="n"/>
+      <c r="L39" s="106" t="n"/>
       <c r="M39" s="35">
-        <f>IF(G39="","",IF(K39="ทีม",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IF(L39="",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L39,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G39="","",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N39" s="36">
         <f>IF(OR(J39="",M39=""),"",J39*M39)</f>
         <v/>
       </c>
-      <c r="O39" s="31" t="n"/>
+      <c r="O39" s="106" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="37">
+      <c r="A40" s="89">
         <f>IF(B40="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B40" s="38" t="n"/>
-      <c r="C40" s="37">
+      <c r="C40" s="89">
         <f>IF(B40="","","Q"&amp;ROUNDUP(MONTH(B40)/3,0))</f>
         <v/>
       </c>
       <c r="D40" s="39" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
-      <c r="G40" s="37" t="n"/>
+      <c r="E40" s="89" t="n"/>
+      <c r="F40" s="89" t="n"/>
+      <c r="G40" s="89" t="n"/>
       <c r="H40" s="40">
         <f>IF(G40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2463,66 +2570,66 @@
         <v/>
       </c>
       <c r="K40" s="89" t="n"/>
-      <c r="L40" s="37" t="n"/>
+      <c r="L40" s="89" t="n"/>
       <c r="M40" s="41">
-        <f>IF(G40="","",IF(K40="ทีม",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IF(L40="",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L40,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G40="","",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N40" s="42">
         <f>IF(OR(J40="",M40=""),"",J40*M40)</f>
         <v/>
       </c>
-      <c r="O40" s="37" t="n"/>
+      <c r="O40" s="89" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="31">
+      <c r="A41" s="106">
         <f>IF(B41="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B41" s="32" t="n"/>
-      <c r="C41" s="31">
+      <c r="B41" s="105" t="n"/>
+      <c r="C41" s="106">
         <f>IF(B41="","","Q"&amp;ROUNDUP(MONTH(B41)/3,0))</f>
         <v/>
       </c>
-      <c r="D41" s="33" t="n"/>
-      <c r="E41" s="31" t="n"/>
-      <c r="F41" s="31" t="n"/>
-      <c r="G41" s="31" t="n"/>
-      <c r="H41" s="34">
+      <c r="D41" s="107" t="n"/>
+      <c r="E41" s="106" t="n"/>
+      <c r="F41" s="106" t="n"/>
+      <c r="G41" s="106" t="n"/>
+      <c r="H41" s="108">
         <f>IF(G41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I41" s="35" t="n"/>
-      <c r="J41" s="34">
+      <c r="J41" s="108">
         <f>IF(H41="","",H41*(1-IF(I41="",0,I41)))</f>
         <v/>
       </c>
-      <c r="K41" s="88" t="n"/>
-      <c r="L41" s="31" t="n"/>
+      <c r="K41" s="106" t="n"/>
+      <c r="L41" s="106" t="n"/>
       <c r="M41" s="35">
-        <f>IF(G41="","",IF(K41="ทีม",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IF(L41="",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L41,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G41="","",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N41" s="36">
         <f>IF(OR(J41="",M41=""),"",J41*M41)</f>
         <v/>
       </c>
-      <c r="O41" s="31" t="n"/>
+      <c r="O41" s="106" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="37">
+      <c r="A42" s="89">
         <f>IF(B42="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B42" s="38" t="n"/>
-      <c r="C42" s="37">
+      <c r="C42" s="89">
         <f>IF(B42="","","Q"&amp;ROUNDUP(MONTH(B42)/3,0))</f>
         <v/>
       </c>
       <c r="D42" s="39" t="n"/>
-      <c r="E42" s="37" t="n"/>
-      <c r="F42" s="37" t="n"/>
-      <c r="G42" s="37" t="n"/>
+      <c r="E42" s="89" t="n"/>
+      <c r="F42" s="89" t="n"/>
+      <c r="G42" s="89" t="n"/>
       <c r="H42" s="40">
         <f>IF(G42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2533,66 +2640,66 @@
         <v/>
       </c>
       <c r="K42" s="89" t="n"/>
-      <c r="L42" s="37" t="n"/>
+      <c r="L42" s="89" t="n"/>
       <c r="M42" s="41">
-        <f>IF(G42="","",IF(K42="ทีม",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IF(L42="",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L42,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G42="","",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N42" s="42">
         <f>IF(OR(J42="",M42=""),"",J42*M42)</f>
         <v/>
       </c>
-      <c r="O42" s="37" t="n"/>
+      <c r="O42" s="89" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="31">
+      <c r="A43" s="106">
         <f>IF(B43="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="31">
+      <c r="B43" s="105" t="n"/>
+      <c r="C43" s="106">
         <f>IF(B43="","","Q"&amp;ROUNDUP(MONTH(B43)/3,0))</f>
         <v/>
       </c>
-      <c r="D43" s="33" t="n"/>
-      <c r="E43" s="31" t="n"/>
-      <c r="F43" s="31" t="n"/>
-      <c r="G43" s="31" t="n"/>
-      <c r="H43" s="34">
+      <c r="D43" s="107" t="n"/>
+      <c r="E43" s="106" t="n"/>
+      <c r="F43" s="106" t="n"/>
+      <c r="G43" s="106" t="n"/>
+      <c r="H43" s="108">
         <f>IF(G43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I43" s="35" t="n"/>
-      <c r="J43" s="34">
+      <c r="J43" s="108">
         <f>IF(H43="","",H43*(1-IF(I43="",0,I43)))</f>
         <v/>
       </c>
-      <c r="K43" s="88" t="n"/>
-      <c r="L43" s="31" t="n"/>
+      <c r="K43" s="106" t="n"/>
+      <c r="L43" s="106" t="n"/>
       <c r="M43" s="35">
-        <f>IF(G43="","",IF(K43="ทีม",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IF(L43="",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L43,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G43="","",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N43" s="36">
         <f>IF(OR(J43="",M43=""),"",J43*M43)</f>
         <v/>
       </c>
-      <c r="O43" s="31" t="n"/>
+      <c r="O43" s="106" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="37">
+      <c r="A44" s="89">
         <f>IF(B44="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B44" s="38" t="n"/>
-      <c r="C44" s="37">
+      <c r="C44" s="89">
         <f>IF(B44="","","Q"&amp;ROUNDUP(MONTH(B44)/3,0))</f>
         <v/>
       </c>
       <c r="D44" s="39" t="n"/>
-      <c r="E44" s="37" t="n"/>
-      <c r="F44" s="37" t="n"/>
-      <c r="G44" s="37" t="n"/>
+      <c r="E44" s="89" t="n"/>
+      <c r="F44" s="89" t="n"/>
+      <c r="G44" s="89" t="n"/>
       <c r="H44" s="40">
         <f>IF(G44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2603,66 +2710,66 @@
         <v/>
       </c>
       <c r="K44" s="89" t="n"/>
-      <c r="L44" s="37" t="n"/>
+      <c r="L44" s="89" t="n"/>
       <c r="M44" s="41">
-        <f>IF(G44="","",IF(K44="ทีม",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IF(L44="",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L44,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G44="","",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N44" s="42">
         <f>IF(OR(J44="",M44=""),"",J44*M44)</f>
         <v/>
       </c>
-      <c r="O44" s="37" t="n"/>
+      <c r="O44" s="89" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="31">
+      <c r="A45" s="106">
         <f>IF(B45="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B45" s="32" t="n"/>
-      <c r="C45" s="31">
+      <c r="B45" s="105" t="n"/>
+      <c r="C45" s="106">
         <f>IF(B45="","","Q"&amp;ROUNDUP(MONTH(B45)/3,0))</f>
         <v/>
       </c>
-      <c r="D45" s="33" t="n"/>
-      <c r="E45" s="31" t="n"/>
-      <c r="F45" s="31" t="n"/>
-      <c r="G45" s="31" t="n"/>
-      <c r="H45" s="34">
+      <c r="D45" s="107" t="n"/>
+      <c r="E45" s="106" t="n"/>
+      <c r="F45" s="106" t="n"/>
+      <c r="G45" s="106" t="n"/>
+      <c r="H45" s="108">
         <f>IF(G45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I45" s="35" t="n"/>
-      <c r="J45" s="34">
+      <c r="J45" s="108">
         <f>IF(H45="","",H45*(1-IF(I45="",0,I45)))</f>
         <v/>
       </c>
-      <c r="K45" s="88" t="n"/>
-      <c r="L45" s="31" t="n"/>
+      <c r="K45" s="106" t="n"/>
+      <c r="L45" s="106" t="n"/>
       <c r="M45" s="35">
-        <f>IF(G45="","",IF(K45="ทีม",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IF(L45="",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L45,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G45="","",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N45" s="36">
         <f>IF(OR(J45="",M45=""),"",J45*M45)</f>
         <v/>
       </c>
-      <c r="O45" s="31" t="n"/>
+      <c r="O45" s="106" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="37">
+      <c r="A46" s="89">
         <f>IF(B46="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B46" s="38" t="n"/>
-      <c r="C46" s="37">
+      <c r="C46" s="89">
         <f>IF(B46="","","Q"&amp;ROUNDUP(MONTH(B46)/3,0))</f>
         <v/>
       </c>
       <c r="D46" s="39" t="n"/>
-      <c r="E46" s="37" t="n"/>
-      <c r="F46" s="37" t="n"/>
-      <c r="G46" s="37" t="n"/>
+      <c r="E46" s="89" t="n"/>
+      <c r="F46" s="89" t="n"/>
+      <c r="G46" s="89" t="n"/>
       <c r="H46" s="40">
         <f>IF(G46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2673,66 +2780,66 @@
         <v/>
       </c>
       <c r="K46" s="89" t="n"/>
-      <c r="L46" s="37" t="n"/>
+      <c r="L46" s="89" t="n"/>
       <c r="M46" s="41">
-        <f>IF(G46="","",IF(K46="ทีม",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IF(L46="",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L46,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G46="","",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N46" s="42">
         <f>IF(OR(J46="",M46=""),"",J46*M46)</f>
         <v/>
       </c>
-      <c r="O46" s="37" t="n"/>
+      <c r="O46" s="89" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="31">
+      <c r="A47" s="106">
         <f>IF(B47="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B47" s="32" t="n"/>
-      <c r="C47" s="31">
+      <c r="B47" s="105" t="n"/>
+      <c r="C47" s="106">
         <f>IF(B47="","","Q"&amp;ROUNDUP(MONTH(B47)/3,0))</f>
         <v/>
       </c>
-      <c r="D47" s="33" t="n"/>
-      <c r="E47" s="31" t="n"/>
-      <c r="F47" s="31" t="n"/>
-      <c r="G47" s="31" t="n"/>
-      <c r="H47" s="34">
+      <c r="D47" s="107" t="n"/>
+      <c r="E47" s="106" t="n"/>
+      <c r="F47" s="106" t="n"/>
+      <c r="G47" s="106" t="n"/>
+      <c r="H47" s="108">
         <f>IF(G47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I47" s="35" t="n"/>
-      <c r="J47" s="34">
+      <c r="J47" s="108">
         <f>IF(H47="","",H47*(1-IF(I47="",0,I47)))</f>
         <v/>
       </c>
-      <c r="K47" s="88" t="n"/>
-      <c r="L47" s="31" t="n"/>
+      <c r="K47" s="106" t="n"/>
+      <c r="L47" s="106" t="n"/>
       <c r="M47" s="35">
-        <f>IF(G47="","",IF(K47="ทีม",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IF(L47="",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L47,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G47="","",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N47" s="36">
         <f>IF(OR(J47="",M47=""),"",J47*M47)</f>
         <v/>
       </c>
-      <c r="O47" s="31" t="n"/>
+      <c r="O47" s="106" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="37">
+      <c r="A48" s="89">
         <f>IF(B48="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B48" s="38" t="n"/>
-      <c r="C48" s="37">
+      <c r="C48" s="89">
         <f>IF(B48="","","Q"&amp;ROUNDUP(MONTH(B48)/3,0))</f>
         <v/>
       </c>
       <c r="D48" s="39" t="n"/>
-      <c r="E48" s="37" t="n"/>
-      <c r="F48" s="37" t="n"/>
-      <c r="G48" s="37" t="n"/>
+      <c r="E48" s="89" t="n"/>
+      <c r="F48" s="89" t="n"/>
+      <c r="G48" s="89" t="n"/>
       <c r="H48" s="40">
         <f>IF(G48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2743,66 +2850,66 @@
         <v/>
       </c>
       <c r="K48" s="89" t="n"/>
-      <c r="L48" s="37" t="n"/>
+      <c r="L48" s="89" t="n"/>
       <c r="M48" s="41">
-        <f>IF(G48="","",IF(K48="ทีม",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IF(L48="",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L48,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G48="","",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N48" s="42">
         <f>IF(OR(J48="",M48=""),"",J48*M48)</f>
         <v/>
       </c>
-      <c r="O48" s="37" t="n"/>
+      <c r="O48" s="89" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="31">
+      <c r="A49" s="106">
         <f>IF(B49="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B49" s="32" t="n"/>
-      <c r="C49" s="31">
+      <c r="B49" s="105" t="n"/>
+      <c r="C49" s="106">
         <f>IF(B49="","","Q"&amp;ROUNDUP(MONTH(B49)/3,0))</f>
         <v/>
       </c>
-      <c r="D49" s="33" t="n"/>
-      <c r="E49" s="31" t="n"/>
-      <c r="F49" s="31" t="n"/>
-      <c r="G49" s="31" t="n"/>
-      <c r="H49" s="34">
+      <c r="D49" s="107" t="n"/>
+      <c r="E49" s="106" t="n"/>
+      <c r="F49" s="106" t="n"/>
+      <c r="G49" s="106" t="n"/>
+      <c r="H49" s="108">
         <f>IF(G49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I49" s="35" t="n"/>
-      <c r="J49" s="34">
+      <c r="J49" s="108">
         <f>IF(H49="","",H49*(1-IF(I49="",0,I49)))</f>
         <v/>
       </c>
-      <c r="K49" s="88" t="n"/>
-      <c r="L49" s="31" t="n"/>
+      <c r="K49" s="106" t="n"/>
+      <c r="L49" s="106" t="n"/>
       <c r="M49" s="35">
-        <f>IF(G49="","",IF(K49="ทีม",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IF(L49="",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L49,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G49="","",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N49" s="36">
         <f>IF(OR(J49="",M49=""),"",J49*M49)</f>
         <v/>
       </c>
-      <c r="O49" s="31" t="n"/>
+      <c r="O49" s="106" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="37">
+      <c r="A50" s="89">
         <f>IF(B50="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B50" s="38" t="n"/>
-      <c r="C50" s="37">
+      <c r="C50" s="89">
         <f>IF(B50="","","Q"&amp;ROUNDUP(MONTH(B50)/3,0))</f>
         <v/>
       </c>
       <c r="D50" s="39" t="n"/>
-      <c r="E50" s="37" t="n"/>
-      <c r="F50" s="37" t="n"/>
-      <c r="G50" s="37" t="n"/>
+      <c r="E50" s="89" t="n"/>
+      <c r="F50" s="89" t="n"/>
+      <c r="G50" s="89" t="n"/>
       <c r="H50" s="40">
         <f>IF(G50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2813,66 +2920,66 @@
         <v/>
       </c>
       <c r="K50" s="89" t="n"/>
-      <c r="L50" s="37" t="n"/>
+      <c r="L50" s="89" t="n"/>
       <c r="M50" s="41">
-        <f>IF(G50="","",IF(K50="ทีม",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IF(L50="",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L50,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G50="","",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N50" s="42">
         <f>IF(OR(J50="",M50=""),"",J50*M50)</f>
         <v/>
       </c>
-      <c r="O50" s="37" t="n"/>
+      <c r="O50" s="89" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="31">
+      <c r="A51" s="106">
         <f>IF(B51="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B51" s="32" t="n"/>
-      <c r="C51" s="31">
+      <c r="B51" s="105" t="n"/>
+      <c r="C51" s="106">
         <f>IF(B51="","","Q"&amp;ROUNDUP(MONTH(B51)/3,0))</f>
         <v/>
       </c>
-      <c r="D51" s="33" t="n"/>
-      <c r="E51" s="31" t="n"/>
-      <c r="F51" s="31" t="n"/>
-      <c r="G51" s="31" t="n"/>
-      <c r="H51" s="34">
+      <c r="D51" s="107" t="n"/>
+      <c r="E51" s="106" t="n"/>
+      <c r="F51" s="106" t="n"/>
+      <c r="G51" s="106" t="n"/>
+      <c r="H51" s="108">
         <f>IF(G51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I51" s="35" t="n"/>
-      <c r="J51" s="34">
+      <c r="J51" s="108">
         <f>IF(H51="","",H51*(1-IF(I51="",0,I51)))</f>
         <v/>
       </c>
-      <c r="K51" s="88" t="n"/>
-      <c r="L51" s="31" t="n"/>
+      <c r="K51" s="106" t="n"/>
+      <c r="L51" s="106" t="n"/>
       <c r="M51" s="35">
-        <f>IF(G51="","",IF(K51="ทีม",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IF(L51="",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L51,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G51="","",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N51" s="36">
         <f>IF(OR(J51="",M51=""),"",J51*M51)</f>
         <v/>
       </c>
-      <c r="O51" s="31" t="n"/>
+      <c r="O51" s="106" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="37">
+      <c r="A52" s="89">
         <f>IF(B52="","",ROW()-12)</f>
         <v/>
       </c>
       <c r="B52" s="38" t="n"/>
-      <c r="C52" s="37">
+      <c r="C52" s="89">
         <f>IF(B52="","","Q"&amp;ROUNDUP(MONTH(B52)/3,0))</f>
         <v/>
       </c>
       <c r="D52" s="39" t="n"/>
-      <c r="E52" s="37" t="n"/>
-      <c r="F52" s="37" t="n"/>
-      <c r="G52" s="37" t="n"/>
+      <c r="E52" s="89" t="n"/>
+      <c r="F52" s="89" t="n"/>
+      <c r="G52" s="89" t="n"/>
       <c r="H52" s="40">
         <f>IF(G52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
@@ -2883,16 +2990,16 @@
         <v/>
       </c>
       <c r="K52" s="89" t="n"/>
-      <c r="L52" s="37" t="n"/>
+      <c r="L52" s="89" t="n"/>
       <c r="M52" s="41">
-        <f>IF(G52="","",IF(K52="ทีม",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IF(L52="",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IF(OR(IFERROR(VLOOKUP(L52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")="",IFERROR(VLOOKUP(L52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")=0),IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""),IFERROR(VLOOKUP(L52,'ทีมขาย'!$A$6:$C$20,3,FALSE),"")))))</f>
+        <f>IF(G52="","",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
       <c r="N52" s="42">
         <f>IF(OR(J52="",M52=""),"",J52*M52)</f>
         <v/>
       </c>
-      <c r="O52" s="37" t="n"/>
+      <c r="O52" s="89" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="43" t="n"/>
@@ -2901,34 +3008,87 @@
       <c r="D53" s="43" t="n"/>
       <c r="E53" s="43" t="n"/>
       <c r="F53" s="43" t="n"/>
-      <c r="G53" s="80" t="inlineStr">
+      <c r="G53" s="121" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="H53" s="83">
+      <c r="H53" s="124">
         <f>SUM(H13:H52)</f>
         <v/>
       </c>
       <c r="I53" s="43" t="n"/>
-      <c r="J53" s="83">
+      <c r="J53" s="124">
         <f>SUM(J13:J52)</f>
         <v/>
       </c>
       <c r="L53" s="43" t="n"/>
       <c r="M53" s="43" t="n"/>
-      <c r="N53" s="83">
+      <c r="N53" s="124">
         <f>SUM(M13:M52)</f>
         <v/>
       </c>
       <c r="O53" s="43" t="n"/>
     </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="128" t="inlineStr">
+        <is>
+          <t>หมายเหตุ / วิธีใช้ — แท็บนี้คือที่กรอกดีลขายจริง</t>
+        </is>
+      </c>
+      <c r="B55" s="126" t="n"/>
+      <c r="C55" s="126" t="n"/>
+      <c r="D55" s="126" t="n"/>
+      <c r="E55" s="126" t="n"/>
+      <c r="F55" s="126" t="n"/>
+      <c r="G55" s="126" t="n"/>
+      <c r="H55" s="126" t="n"/>
+      <c r="I55" s="126" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="127" t="inlineStr">
+        <is>
+          <t>•  กรอกช่องขาว: วันที่ · ชื่อลูกค้า · ประเภท (ใหม่/ต่ออายุ) · การชำระเงิน · แพ็กเกจ · ส่วนลด% · จ่ายแบบ · Sales · สถานะจ่าย</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="127" t="inlineStr">
+        <is>
+          <t>•  ช่องที่เหลือคิดเองอัตโนมัติ: No · ไตรมาส · ราคาเต็ม · รายได้สุทธิ · Rate% · ค่าคอม</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="127" t="inlineStr">
+        <is>
+          <t>•  จ่ายแบบ 'รายคน' → ใส่ชื่อในช่อง Sales (คนนั้นได้ค่าคอมเต็มตามเรตแพ็กเกจ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="127" t="inlineStr">
+        <is>
+          <t>•  จ่ายแบบ 'ทีม' → เว้นช่อง Sales ว่าง (ค่าคอมหารทีมตาม %แบ่งทีม รวม 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="127" t="inlineStr">
+        <is>
+          <t>•  Enterprise: พิมพ์ราคาจริงทับช่อง 'ราคาเต็ม' ได้เลย</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="27">
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="O11"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="H11:J11"/>
+    <mergeCell ref="A57:I57"/>
     <mergeCell ref="C1:J1"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="G4:I4"/>
@@ -2939,9 +3099,12 @@
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="D11"/>
+    <mergeCell ref="A58:I58"/>
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A59:I59"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A60:I60"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="G7:I7"/>
@@ -2977,18 +3140,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3007,18 +3169,18 @@
     <row r="2" ht="18" customHeight="1">
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>ทีมขาย · ตั้งรายชื่อ + % ส่วนตัว (รายคน) + % แบ่งทีม</t>
+          <t>ทีมขาย · ตั้งรายชื่อ + % แบ่งทีม (ใช้เฉพาะดีลแบบทีม)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="90" t="inlineStr">
-        <is>
-          <t>เพิ่ม/แก้รายชื่อได้เลย · 'รายคน' ใช้ %ส่วนตัว (เว้นว่าง=เรตแพ็กเกจ) · 'ทีม' หารพูลค่าคอมตาม %แบ่งทีม (ควรรวม=100%) · เลือกจ่ายแบบไหนต่อดีลในแท็บ Sales_Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
+      <c r="A3" s="114" t="inlineStr">
+        <is>
+          <t>เพิ่ม/แก้รายชื่อได้เลย · 'รายคน' ได้ค่าคอมเต็มตามเรตแพ็กเกจ (แท็บ Rate) · 'ทีม' หารพูลค่าคอมตาม % แบ่งทีม (ควรรวม=100%) · เลือกจ่ายแบบไหนต่อดีลในแท็บ Sales_Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="91" t="inlineStr">
         <is>
           <t>ชื่อ Sales</t>
@@ -3030,503 +3192,526 @@
         </is>
       </c>
       <c r="C5" s="91" t="inlineStr">
-        <is>
-          <t>% ส่วนตัว
-(รายคน)</t>
-        </is>
-      </c>
-      <c r="D5" s="91" t="inlineStr">
         <is>
           <t>% แบ่งทีม
 (รวม=100%)</t>
         </is>
       </c>
+      <c r="D5" s="91" t="inlineStr">
+        <is>
+          <t>ดีลปิดเอง</t>
+        </is>
+      </c>
       <c r="E5" s="91" t="inlineStr">
         <is>
-          <t>ดีลปิดเอง</t>
+          <t>รายได้ (THB)</t>
         </is>
       </c>
       <c r="F5" s="91" t="inlineStr">
         <is>
-          <t>รายได้ (THB)</t>
+          <t>ค่าคอมรวม (THB)</t>
         </is>
       </c>
       <c r="G5" s="91" t="inlineStr">
         <is>
-          <t>ค่าคอมรวม (THB)</t>
+          <t>จ่ายแล้ว (THB)</t>
         </is>
       </c>
       <c r="H5" s="91" t="inlineStr">
         <is>
-          <t>จ่ายแล้ว (THB)</t>
-        </is>
-      </c>
-      <c r="I5" s="91" t="inlineStr">
-        <is>
           <t>ค้างจ่าย (THB)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="92" t="inlineStr">
+      <c r="A6" s="115" t="inlineStr">
         <is>
           <t>MIZTEEN</t>
         </is>
       </c>
-      <c r="B6" s="93" t="inlineStr">
+      <c r="B6" s="116" t="inlineStr">
         <is>
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C6" s="94" t="n"/>
-      <c r="D6" s="95" t="n">
+      <c r="C6" s="117" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="96">
+      <c r="D6" s="118">
         <f>IF($A6="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F6" s="97">
-        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$J$13:$J$52)+$D6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G6" s="98">
-        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$N$13:$N$52)+$D6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H6" s="97">
-        <f>IF($A6="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A6,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D6*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I6" s="97">
-        <f>IF($A6="","",G6-H6)</f>
+      <c r="E6" s="119">
+        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$J$13:$J$52)+$C6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F6" s="120">
+        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$N$13:$N$52)+$C6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G6" s="119">
+        <f>IF($A6="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A6,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C6*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="119">
+        <f>IF($A6="","",F6-G6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="92" t="inlineStr">
+      <c r="A7" s="115" t="inlineStr">
         <is>
           <t>OLIVE</t>
         </is>
       </c>
-      <c r="B7" s="93" t="inlineStr">
+      <c r="B7" s="116" t="inlineStr">
         <is>
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C7" s="94" t="n"/>
-      <c r="D7" s="95" t="n">
+      <c r="C7" s="117" t="n">
         <v>0.3</v>
       </c>
-      <c r="E7" s="96">
+      <c r="D7" s="118">
         <f>IF($A7="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F7" s="97">
-        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$J$13:$J$52)+$D7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G7" s="98">
-        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$N$13:$N$52)+$D7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H7" s="97">
-        <f>IF($A7="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A7,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D7*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I7" s="97">
-        <f>IF($A7="","",G7-H7)</f>
+      <c r="E7" s="119">
+        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$J$13:$J$52)+$C7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F7" s="120">
+        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$N$13:$N$52)+$C7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G7" s="119">
+        <f>IF($A7="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A7,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C7*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="119">
+        <f>IF($A7="","",F7-G7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="92" t="inlineStr">
+      <c r="A8" s="115" t="inlineStr">
         <is>
           <t>SUPPORT</t>
         </is>
       </c>
-      <c r="B8" s="93" t="inlineStr">
+      <c r="B8" s="116" t="inlineStr">
         <is>
           <t>Support / Sales</t>
         </is>
       </c>
-      <c r="C8" s="94" t="n"/>
-      <c r="D8" s="95" t="n">
+      <c r="C8" s="117" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="96">
+      <c r="D8" s="118">
         <f>IF($A8="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F8" s="97">
-        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$J$13:$J$52)+$D8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G8" s="98">
-        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$N$13:$N$52)+$D8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H8" s="97">
-        <f>IF($A8="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A8,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D8*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I8" s="97">
-        <f>IF($A8="","",G8-H8)</f>
+      <c r="E8" s="119">
+        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$J$13:$J$52)+$C8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F8" s="120">
+        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$N$13:$N$52)+$C8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G8" s="119">
+        <f>IF($A8="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A8,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C8*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="119">
+        <f>IF($A8="","",F8-G8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="92" t="inlineStr"/>
-      <c r="B9" s="93" t="inlineStr"/>
-      <c r="C9" s="94" t="n"/>
-      <c r="D9" s="95" t="n"/>
-      <c r="E9" s="96">
+      <c r="A9" s="115" t="inlineStr"/>
+      <c r="B9" s="116" t="inlineStr"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="118">
         <f>IF($A9="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F9" s="97">
-        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$J$13:$J$52)+$D9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G9" s="98">
-        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$N$13:$N$52)+$D9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H9" s="97">
-        <f>IF($A9="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A9,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D9*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I9" s="97">
-        <f>IF($A9="","",G9-H9)</f>
+      <c r="E9" s="119">
+        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$J$13:$J$52)+$C9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F9" s="120">
+        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$N$13:$N$52)+$C9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G9" s="119">
+        <f>IF($A9="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A9,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C9*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="119">
+        <f>IF($A9="","",F9-G9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="92" t="inlineStr"/>
-      <c r="B10" s="93" t="inlineStr"/>
-      <c r="C10" s="94" t="n"/>
-      <c r="D10" s="95" t="n"/>
-      <c r="E10" s="96">
+      <c r="A10" s="115" t="inlineStr"/>
+      <c r="B10" s="116" t="inlineStr"/>
+      <c r="C10" s="117" t="n"/>
+      <c r="D10" s="118">
         <f>IF($A10="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F10" s="97">
-        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$J$13:$J$52)+$D10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G10" s="98">
-        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$N$13:$N$52)+$D10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H10" s="97">
-        <f>IF($A10="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A10,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D10*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I10" s="97">
-        <f>IF($A10="","",G10-H10)</f>
+      <c r="E10" s="119">
+        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$J$13:$J$52)+$C10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F10" s="120">
+        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$N$13:$N$52)+$C10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G10" s="119">
+        <f>IF($A10="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A10,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C10*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="119">
+        <f>IF($A10="","",F10-G10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="92" t="inlineStr"/>
-      <c r="B11" s="93" t="inlineStr"/>
-      <c r="C11" s="94" t="n"/>
-      <c r="D11" s="95" t="n"/>
-      <c r="E11" s="96">
+      <c r="A11" s="115" t="inlineStr"/>
+      <c r="B11" s="116" t="inlineStr"/>
+      <c r="C11" s="117" t="n"/>
+      <c r="D11" s="118">
         <f>IF($A11="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F11" s="97">
-        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$J$13:$J$52)+$D11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G11" s="98">
-        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$N$13:$N$52)+$D11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H11" s="97">
-        <f>IF($A11="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A11,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D11*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I11" s="97">
-        <f>IF($A11="","",G11-H11)</f>
+      <c r="E11" s="119">
+        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$J$13:$J$52)+$C11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F11" s="120">
+        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$N$13:$N$52)+$C11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G11" s="119">
+        <f>IF($A11="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A11,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C11*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="119">
+        <f>IF($A11="","",F11-G11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="92" t="inlineStr"/>
-      <c r="B12" s="93" t="inlineStr"/>
-      <c r="C12" s="94" t="n"/>
-      <c r="D12" s="95" t="n"/>
-      <c r="E12" s="96">
+      <c r="A12" s="115" t="inlineStr"/>
+      <c r="B12" s="116" t="inlineStr"/>
+      <c r="C12" s="117" t="n"/>
+      <c r="D12" s="118">
         <f>IF($A12="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F12" s="97">
-        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$J$13:$J$52)+$D12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G12" s="98">
-        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$N$13:$N$52)+$D12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H12" s="97">
-        <f>IF($A12="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A12,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D12*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I12" s="97">
-        <f>IF($A12="","",G12-H12)</f>
+      <c r="E12" s="119">
+        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$J$13:$J$52)+$C12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F12" s="120">
+        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$N$13:$N$52)+$C12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G12" s="119">
+        <f>IF($A12="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A12,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C12*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="119">
+        <f>IF($A12="","",F12-G12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="92" t="inlineStr"/>
-      <c r="B13" s="93" t="inlineStr"/>
-      <c r="C13" s="94" t="n"/>
-      <c r="D13" s="95" t="n"/>
-      <c r="E13" s="96">
+      <c r="A13" s="115" t="inlineStr"/>
+      <c r="B13" s="116" t="inlineStr"/>
+      <c r="C13" s="117" t="n"/>
+      <c r="D13" s="118">
         <f>IF($A13="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F13" s="97">
-        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$J$13:$J$52)+$D13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G13" s="98">
-        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$N$13:$N$52)+$D13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H13" s="97">
-        <f>IF($A13="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A13,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D13*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I13" s="97">
-        <f>IF($A13="","",G13-H13)</f>
+      <c r="E13" s="119">
+        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$J$13:$J$52)+$C13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F13" s="120">
+        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$N$13:$N$52)+$C13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G13" s="119">
+        <f>IF($A13="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A13,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C13*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="119">
+        <f>IF($A13="","",F13-G13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="92" t="inlineStr"/>
-      <c r="B14" s="93" t="inlineStr"/>
-      <c r="C14" s="94" t="n"/>
-      <c r="D14" s="95" t="n"/>
-      <c r="E14" s="96">
+      <c r="A14" s="115" t="inlineStr"/>
+      <c r="B14" s="116" t="inlineStr"/>
+      <c r="C14" s="117" t="n"/>
+      <c r="D14" s="118">
         <f>IF($A14="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F14" s="97">
-        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$J$13:$J$52)+$D14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G14" s="98">
-        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$N$13:$N$52)+$D14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H14" s="97">
-        <f>IF($A14="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A14,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D14*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I14" s="97">
-        <f>IF($A14="","",G14-H14)</f>
+      <c r="E14" s="119">
+        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$J$13:$J$52)+$C14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F14" s="120">
+        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$N$13:$N$52)+$C14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G14" s="119">
+        <f>IF($A14="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A14,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C14*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="119">
+        <f>IF($A14="","",F14-G14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="92" t="inlineStr"/>
-      <c r="B15" s="93" t="inlineStr"/>
-      <c r="C15" s="94" t="n"/>
-      <c r="D15" s="95" t="n"/>
-      <c r="E15" s="96">
+      <c r="A15" s="115" t="inlineStr"/>
+      <c r="B15" s="116" t="inlineStr"/>
+      <c r="C15" s="117" t="n"/>
+      <c r="D15" s="118">
         <f>IF($A15="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F15" s="97">
-        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$J$13:$J$52)+$D15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G15" s="98">
-        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$N$13:$N$52)+$D15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H15" s="97">
-        <f>IF($A15="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A15,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D15*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I15" s="97">
-        <f>IF($A15="","",G15-H15)</f>
+      <c r="E15" s="119">
+        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$J$13:$J$52)+$C15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F15" s="120">
+        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$N$13:$N$52)+$C15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G15" s="119">
+        <f>IF($A15="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A15,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C15*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="119">
+        <f>IF($A15="","",F15-G15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="92" t="inlineStr"/>
-      <c r="B16" s="93" t="inlineStr"/>
-      <c r="C16" s="94" t="n"/>
-      <c r="D16" s="95" t="n"/>
-      <c r="E16" s="96">
+      <c r="A16" s="115" t="inlineStr"/>
+      <c r="B16" s="116" t="inlineStr"/>
+      <c r="C16" s="117" t="n"/>
+      <c r="D16" s="118">
         <f>IF($A16="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F16" s="97">
-        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$J$13:$J$52)+$D16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G16" s="98">
-        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$N$13:$N$52)+$D16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H16" s="97">
-        <f>IF($A16="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A16,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D16*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I16" s="97">
-        <f>IF($A16="","",G16-H16)</f>
+      <c r="E16" s="119">
+        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$J$13:$J$52)+$C16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F16" s="120">
+        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$N$13:$N$52)+$C16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G16" s="119">
+        <f>IF($A16="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A16,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C16*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="119">
+        <f>IF($A16="","",F16-G16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="92" t="inlineStr"/>
-      <c r="B17" s="93" t="inlineStr"/>
-      <c r="C17" s="94" t="n"/>
-      <c r="D17" s="95" t="n"/>
-      <c r="E17" s="96">
+      <c r="A17" s="115" t="inlineStr"/>
+      <c r="B17" s="116" t="inlineStr"/>
+      <c r="C17" s="117" t="n"/>
+      <c r="D17" s="118">
         <f>IF($A17="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F17" s="97">
-        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$J$13:$J$52)+$D17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G17" s="98">
-        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$N$13:$N$52)+$D17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H17" s="97">
-        <f>IF($A17="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A17,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D17*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I17" s="97">
-        <f>IF($A17="","",G17-H17)</f>
+      <c r="E17" s="119">
+        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$J$13:$J$52)+$C17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F17" s="120">
+        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$N$13:$N$52)+$C17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G17" s="119">
+        <f>IF($A17="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A17,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C17*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="119">
+        <f>IF($A17="","",F17-G17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="92" t="inlineStr"/>
-      <c r="B18" s="93" t="inlineStr"/>
-      <c r="C18" s="94" t="n"/>
-      <c r="D18" s="95" t="n"/>
-      <c r="E18" s="96">
+      <c r="A18" s="115" t="inlineStr"/>
+      <c r="B18" s="116" t="inlineStr"/>
+      <c r="C18" s="117" t="n"/>
+      <c r="D18" s="118">
         <f>IF($A18="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F18" s="97">
-        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$J$13:$J$52)+$D18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G18" s="98">
-        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$N$13:$N$52)+$D18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H18" s="97">
-        <f>IF($A18="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A18,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D18*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I18" s="97">
-        <f>IF($A18="","",G18-H18)</f>
+      <c r="E18" s="119">
+        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$J$13:$J$52)+$C18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F18" s="120">
+        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$N$13:$N$52)+$C18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G18" s="119">
+        <f>IF($A18="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A18,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C18*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="119">
+        <f>IF($A18="","",F18-G18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="92" t="inlineStr"/>
-      <c r="B19" s="93" t="inlineStr"/>
-      <c r="C19" s="94" t="n"/>
-      <c r="D19" s="95" t="n"/>
-      <c r="E19" s="96">
+      <c r="A19" s="115" t="inlineStr"/>
+      <c r="B19" s="116" t="inlineStr"/>
+      <c r="C19" s="117" t="n"/>
+      <c r="D19" s="118">
         <f>IF($A19="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F19" s="97">
-        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$J$13:$J$52)+$D19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G19" s="98">
-        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$N$13:$N$52)+$D19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H19" s="97">
-        <f>IF($A19="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A19,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D19*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I19" s="97">
-        <f>IF($A19="","",G19-H19)</f>
+      <c r="E19" s="119">
+        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$J$13:$J$52)+$C19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F19" s="120">
+        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$N$13:$N$52)+$C19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G19" s="119">
+        <f>IF($A19="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A19,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C19*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="119">
+        <f>IF($A19="","",F19-G19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="92" t="inlineStr"/>
-      <c r="B20" s="93" t="inlineStr"/>
-      <c r="C20" s="94" t="n"/>
-      <c r="D20" s="95" t="n"/>
-      <c r="E20" s="96">
+      <c r="A20" s="115" t="inlineStr"/>
+      <c r="B20" s="116" t="inlineStr"/>
+      <c r="C20" s="117" t="n"/>
+      <c r="D20" s="118">
         <f>IF($A20="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
       </c>
-      <c r="F20" s="97">
-        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$J$13:$J$52)+$D20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="G20" s="98">
-        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$N$13:$N$52)+$D20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="H20" s="97">
-        <f>IF($A20="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A20,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$D20*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="I20" s="97">
-        <f>IF($A20="","",G20-H20)</f>
+      <c r="E20" s="119">
+        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$J$13:$J$52)+$C20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F20" s="120">
+        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$N$13:$N$52)+$C20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G20" s="119">
+        <f>IF($A20="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A20,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C20*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="119">
+        <f>IF($A20="","",F20-G20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="99" t="inlineStr">
+      <c r="A21" s="121" t="inlineStr">
         <is>
           <t>รวมทั้งทีม</t>
         </is>
       </c>
-      <c r="B21" s="81" t="n"/>
-      <c r="C21" s="81" t="n"/>
-      <c r="D21" s="100">
+      <c r="B21" s="85" t="n"/>
+      <c r="C21" s="122">
+        <f>SUM(C6:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="123">
         <f>SUM(D6:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="101">
+      <c r="E21" s="124">
         <f>SUM(E6:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="102">
+      <c r="F21" s="124">
         <f>SUM(F6:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="102">
+      <c r="G21" s="124">
         <f>SUM(G6:G20)</f>
         <v/>
       </c>
-      <c r="H21" s="102">
+      <c r="H21" s="124">
         <f>SUM(H6:H20)</f>
         <v/>
       </c>
-      <c r="I21" s="102">
-        <f>SUM(I6:I20)</f>
-        <v/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="128" t="inlineStr">
+        <is>
+          <t>หมายเหตุ / วิธีใช้</t>
+        </is>
+      </c>
+      <c r="B24" s="126" t="n"/>
+      <c r="C24" s="126" t="n"/>
+      <c r="D24" s="126" t="n"/>
+      <c r="E24" s="126" t="n"/>
+      <c r="F24" s="126" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="127" t="inlineStr">
+        <is>
+          <t>•  กรอกเอง 3 ช่อง: ชื่อ Sales · ตำแหน่ง · %แบ่งทีม (รวมทุกคน = 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="127" t="inlineStr">
+        <is>
+          <t>•  ดีลปิดเอง · รายได้ · ค่าคอมรวม · จ่ายแล้ว · ค้างจ่าย → คิดเองจากแท็บ Sales_Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="127" t="inlineStr">
+        <is>
+          <t>•  %แบ่งทีม ใช้เฉพาะดีลที่เลือกจ่าย 'ทีม' · ดีลรายคนไม่ใช้</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="127" t="inlineStr">
+        <is>
+          <t>•  ชื่อในนี้ = ตัวเลือกดรอปดาวน์ Sales ในแท็บ Sales_Record</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="C2:I2"/>
+  <mergeCells count="10">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="C1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3538,7 +3723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3596,7 +3781,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="115" t="inlineStr">
         <is>
           <t>Starter</t>
         </is>
@@ -3644,7 +3829,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="74" t="inlineStr">
+      <c r="A6" s="115" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
@@ -3721,13 +3906,42 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="128" t="inlineStr">
+        <is>
+          <t>วิธีใช้</t>
+        </is>
+      </c>
+      <c r="B14" s="126" t="n"/>
+      <c r="C14" s="126" t="n"/>
+      <c r="D14" s="126" t="n"/>
+      <c r="E14" s="126" t="n"/>
+      <c r="F14" s="126" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="127" t="inlineStr">
+        <is>
+          <t>•  แก้ % ค่าคอมที่นี่ที่เดียว · แท็บ Sales_Record ดึงไปคิดอัตโนมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="127" t="inlineStr">
+        <is>
+          <t>•  ดีลใหม่ใช้ '% ค่าคอม (ใหม่)' · ต่ออายุใช้ '% ต่ออายุ'</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3739,7 +3953,1861 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G20"/>
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EASY
+CRM</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>REVENUE LEDGER 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>สรุปรายได้รายรายการ · EasyCRM (บริษัท อีซี่สลิป จำกัด)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="114" t="inlineStr">
+        <is>
+          <t>ดึงอัตโนมัติจากแท็บ Sales_Record · กรอกดีลในแท็บนั้น รายการตรงนี้ขึ้นเอง แล้วรวมยอดท้ายตาราง</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>วันที่</t>
+        </is>
+      </c>
+      <c r="C5" s="91" t="inlineStr">
+        <is>
+          <t>ไตรมาส</t>
+        </is>
+      </c>
+      <c r="D5" s="91" t="inlineStr">
+        <is>
+          <t>ชื่อลูกค้า</t>
+        </is>
+      </c>
+      <c r="E5" s="91" t="inlineStr">
+        <is>
+          <t>แพ็กเกจ</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>ประเภท</t>
+        </is>
+      </c>
+      <c r="G5" s="91" t="inlineStr">
+        <is>
+          <t>ราคาเต็ม (THB)</t>
+        </is>
+      </c>
+      <c r="H5" s="91" t="inlineStr">
+        <is>
+          <t>ส่วนลด %</t>
+        </is>
+      </c>
+      <c r="I5" s="91" t="inlineStr">
+        <is>
+          <t>รายได้สุทธิ (THB)</t>
+        </is>
+      </c>
+      <c r="J5" s="91" t="inlineStr">
+        <is>
+          <t>การชำระเงิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="104">
+        <f>IF($B6="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B6" s="105">
+        <f>IF(Sales_Record!B13="","",Sales_Record!B13)</f>
+        <v/>
+      </c>
+      <c r="C6" s="106">
+        <f>IF($B6="","",Sales_Record!C13)</f>
+        <v/>
+      </c>
+      <c r="D6" s="107">
+        <f>IF($B6="","",Sales_Record!D13)</f>
+        <v/>
+      </c>
+      <c r="E6" s="106">
+        <f>IF($B6="","",Sales_Record!G13)</f>
+        <v/>
+      </c>
+      <c r="F6" s="106">
+        <f>IF($B6="","",Sales_Record!E13)</f>
+        <v/>
+      </c>
+      <c r="G6" s="108">
+        <f>IF($B6="","",Sales_Record!H13)</f>
+        <v/>
+      </c>
+      <c r="H6" s="109">
+        <f>IF($B6="","",Sales_Record!I13)</f>
+        <v/>
+      </c>
+      <c r="I6" s="110">
+        <f>IF($B6="","",Sales_Record!J13)</f>
+        <v/>
+      </c>
+      <c r="J6" s="106">
+        <f>IF($B6="","",Sales_Record!F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="104">
+        <f>IF($B7="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B7" s="105">
+        <f>IF(Sales_Record!B14="","",Sales_Record!B14)</f>
+        <v/>
+      </c>
+      <c r="C7" s="106">
+        <f>IF($B7="","",Sales_Record!C14)</f>
+        <v/>
+      </c>
+      <c r="D7" s="107">
+        <f>IF($B7="","",Sales_Record!D14)</f>
+        <v/>
+      </c>
+      <c r="E7" s="106">
+        <f>IF($B7="","",Sales_Record!G14)</f>
+        <v/>
+      </c>
+      <c r="F7" s="106">
+        <f>IF($B7="","",Sales_Record!E14)</f>
+        <v/>
+      </c>
+      <c r="G7" s="108">
+        <f>IF($B7="","",Sales_Record!H14)</f>
+        <v/>
+      </c>
+      <c r="H7" s="109">
+        <f>IF($B7="","",Sales_Record!I14)</f>
+        <v/>
+      </c>
+      <c r="I7" s="110">
+        <f>IF($B7="","",Sales_Record!J14)</f>
+        <v/>
+      </c>
+      <c r="J7" s="106">
+        <f>IF($B7="","",Sales_Record!F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="104">
+        <f>IF($B8="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B8" s="105">
+        <f>IF(Sales_Record!B15="","",Sales_Record!B15)</f>
+        <v/>
+      </c>
+      <c r="C8" s="106">
+        <f>IF($B8="","",Sales_Record!C15)</f>
+        <v/>
+      </c>
+      <c r="D8" s="107">
+        <f>IF($B8="","",Sales_Record!D15)</f>
+        <v/>
+      </c>
+      <c r="E8" s="106">
+        <f>IF($B8="","",Sales_Record!G15)</f>
+        <v/>
+      </c>
+      <c r="F8" s="106">
+        <f>IF($B8="","",Sales_Record!E15)</f>
+        <v/>
+      </c>
+      <c r="G8" s="108">
+        <f>IF($B8="","",Sales_Record!H15)</f>
+        <v/>
+      </c>
+      <c r="H8" s="109">
+        <f>IF($B8="","",Sales_Record!I15)</f>
+        <v/>
+      </c>
+      <c r="I8" s="110">
+        <f>IF($B8="","",Sales_Record!J15)</f>
+        <v/>
+      </c>
+      <c r="J8" s="106">
+        <f>IF($B8="","",Sales_Record!F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="104">
+        <f>IF($B9="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B9" s="105">
+        <f>IF(Sales_Record!B16="","",Sales_Record!B16)</f>
+        <v/>
+      </c>
+      <c r="C9" s="106">
+        <f>IF($B9="","",Sales_Record!C16)</f>
+        <v/>
+      </c>
+      <c r="D9" s="107">
+        <f>IF($B9="","",Sales_Record!D16)</f>
+        <v/>
+      </c>
+      <c r="E9" s="106">
+        <f>IF($B9="","",Sales_Record!G16)</f>
+        <v/>
+      </c>
+      <c r="F9" s="106">
+        <f>IF($B9="","",Sales_Record!E16)</f>
+        <v/>
+      </c>
+      <c r="G9" s="108">
+        <f>IF($B9="","",Sales_Record!H16)</f>
+        <v/>
+      </c>
+      <c r="H9" s="109">
+        <f>IF($B9="","",Sales_Record!I16)</f>
+        <v/>
+      </c>
+      <c r="I9" s="110">
+        <f>IF($B9="","",Sales_Record!J16)</f>
+        <v/>
+      </c>
+      <c r="J9" s="106">
+        <f>IF($B9="","",Sales_Record!F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="104">
+        <f>IF($B10="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B10" s="105">
+        <f>IF(Sales_Record!B17="","",Sales_Record!B17)</f>
+        <v/>
+      </c>
+      <c r="C10" s="106">
+        <f>IF($B10="","",Sales_Record!C17)</f>
+        <v/>
+      </c>
+      <c r="D10" s="107">
+        <f>IF($B10="","",Sales_Record!D17)</f>
+        <v/>
+      </c>
+      <c r="E10" s="106">
+        <f>IF($B10="","",Sales_Record!G17)</f>
+        <v/>
+      </c>
+      <c r="F10" s="106">
+        <f>IF($B10="","",Sales_Record!E17)</f>
+        <v/>
+      </c>
+      <c r="G10" s="108">
+        <f>IF($B10="","",Sales_Record!H17)</f>
+        <v/>
+      </c>
+      <c r="H10" s="109">
+        <f>IF($B10="","",Sales_Record!I17)</f>
+        <v/>
+      </c>
+      <c r="I10" s="110">
+        <f>IF($B10="","",Sales_Record!J17)</f>
+        <v/>
+      </c>
+      <c r="J10" s="106">
+        <f>IF($B10="","",Sales_Record!F17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="104">
+        <f>IF($B11="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B11" s="105">
+        <f>IF(Sales_Record!B18="","",Sales_Record!B18)</f>
+        <v/>
+      </c>
+      <c r="C11" s="106">
+        <f>IF($B11="","",Sales_Record!C18)</f>
+        <v/>
+      </c>
+      <c r="D11" s="107">
+        <f>IF($B11="","",Sales_Record!D18)</f>
+        <v/>
+      </c>
+      <c r="E11" s="106">
+        <f>IF($B11="","",Sales_Record!G18)</f>
+        <v/>
+      </c>
+      <c r="F11" s="106">
+        <f>IF($B11="","",Sales_Record!E18)</f>
+        <v/>
+      </c>
+      <c r="G11" s="108">
+        <f>IF($B11="","",Sales_Record!H18)</f>
+        <v/>
+      </c>
+      <c r="H11" s="109">
+        <f>IF($B11="","",Sales_Record!I18)</f>
+        <v/>
+      </c>
+      <c r="I11" s="110">
+        <f>IF($B11="","",Sales_Record!J18)</f>
+        <v/>
+      </c>
+      <c r="J11" s="106">
+        <f>IF($B11="","",Sales_Record!F18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="104">
+        <f>IF($B12="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B12" s="105">
+        <f>IF(Sales_Record!B19="","",Sales_Record!B19)</f>
+        <v/>
+      </c>
+      <c r="C12" s="106">
+        <f>IF($B12="","",Sales_Record!C19)</f>
+        <v/>
+      </c>
+      <c r="D12" s="107">
+        <f>IF($B12="","",Sales_Record!D19)</f>
+        <v/>
+      </c>
+      <c r="E12" s="106">
+        <f>IF($B12="","",Sales_Record!G19)</f>
+        <v/>
+      </c>
+      <c r="F12" s="106">
+        <f>IF($B12="","",Sales_Record!E19)</f>
+        <v/>
+      </c>
+      <c r="G12" s="108">
+        <f>IF($B12="","",Sales_Record!H19)</f>
+        <v/>
+      </c>
+      <c r="H12" s="109">
+        <f>IF($B12="","",Sales_Record!I19)</f>
+        <v/>
+      </c>
+      <c r="I12" s="110">
+        <f>IF($B12="","",Sales_Record!J19)</f>
+        <v/>
+      </c>
+      <c r="J12" s="106">
+        <f>IF($B12="","",Sales_Record!F19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="104">
+        <f>IF($B13="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B13" s="105">
+        <f>IF(Sales_Record!B20="","",Sales_Record!B20)</f>
+        <v/>
+      </c>
+      <c r="C13" s="106">
+        <f>IF($B13="","",Sales_Record!C20)</f>
+        <v/>
+      </c>
+      <c r="D13" s="107">
+        <f>IF($B13="","",Sales_Record!D20)</f>
+        <v/>
+      </c>
+      <c r="E13" s="106">
+        <f>IF($B13="","",Sales_Record!G20)</f>
+        <v/>
+      </c>
+      <c r="F13" s="106">
+        <f>IF($B13="","",Sales_Record!E20)</f>
+        <v/>
+      </c>
+      <c r="G13" s="108">
+        <f>IF($B13="","",Sales_Record!H20)</f>
+        <v/>
+      </c>
+      <c r="H13" s="109">
+        <f>IF($B13="","",Sales_Record!I20)</f>
+        <v/>
+      </c>
+      <c r="I13" s="110">
+        <f>IF($B13="","",Sales_Record!J20)</f>
+        <v/>
+      </c>
+      <c r="J13" s="106">
+        <f>IF($B13="","",Sales_Record!F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="104">
+        <f>IF($B14="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B14" s="105">
+        <f>IF(Sales_Record!B21="","",Sales_Record!B21)</f>
+        <v/>
+      </c>
+      <c r="C14" s="106">
+        <f>IF($B14="","",Sales_Record!C21)</f>
+        <v/>
+      </c>
+      <c r="D14" s="107">
+        <f>IF($B14="","",Sales_Record!D21)</f>
+        <v/>
+      </c>
+      <c r="E14" s="106">
+        <f>IF($B14="","",Sales_Record!G21)</f>
+        <v/>
+      </c>
+      <c r="F14" s="106">
+        <f>IF($B14="","",Sales_Record!E21)</f>
+        <v/>
+      </c>
+      <c r="G14" s="108">
+        <f>IF($B14="","",Sales_Record!H21)</f>
+        <v/>
+      </c>
+      <c r="H14" s="109">
+        <f>IF($B14="","",Sales_Record!I21)</f>
+        <v/>
+      </c>
+      <c r="I14" s="110">
+        <f>IF($B14="","",Sales_Record!J21)</f>
+        <v/>
+      </c>
+      <c r="J14" s="106">
+        <f>IF($B14="","",Sales_Record!F21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="104">
+        <f>IF($B15="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B15" s="105">
+        <f>IF(Sales_Record!B22="","",Sales_Record!B22)</f>
+        <v/>
+      </c>
+      <c r="C15" s="106">
+        <f>IF($B15="","",Sales_Record!C22)</f>
+        <v/>
+      </c>
+      <c r="D15" s="107">
+        <f>IF($B15="","",Sales_Record!D22)</f>
+        <v/>
+      </c>
+      <c r="E15" s="106">
+        <f>IF($B15="","",Sales_Record!G22)</f>
+        <v/>
+      </c>
+      <c r="F15" s="106">
+        <f>IF($B15="","",Sales_Record!E22)</f>
+        <v/>
+      </c>
+      <c r="G15" s="108">
+        <f>IF($B15="","",Sales_Record!H22)</f>
+        <v/>
+      </c>
+      <c r="H15" s="109">
+        <f>IF($B15="","",Sales_Record!I22)</f>
+        <v/>
+      </c>
+      <c r="I15" s="110">
+        <f>IF($B15="","",Sales_Record!J22)</f>
+        <v/>
+      </c>
+      <c r="J15" s="106">
+        <f>IF($B15="","",Sales_Record!F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="104">
+        <f>IF($B16="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B16" s="105">
+        <f>IF(Sales_Record!B23="","",Sales_Record!B23)</f>
+        <v/>
+      </c>
+      <c r="C16" s="106">
+        <f>IF($B16="","",Sales_Record!C23)</f>
+        <v/>
+      </c>
+      <c r="D16" s="107">
+        <f>IF($B16="","",Sales_Record!D23)</f>
+        <v/>
+      </c>
+      <c r="E16" s="106">
+        <f>IF($B16="","",Sales_Record!G23)</f>
+        <v/>
+      </c>
+      <c r="F16" s="106">
+        <f>IF($B16="","",Sales_Record!E23)</f>
+        <v/>
+      </c>
+      <c r="G16" s="108">
+        <f>IF($B16="","",Sales_Record!H23)</f>
+        <v/>
+      </c>
+      <c r="H16" s="109">
+        <f>IF($B16="","",Sales_Record!I23)</f>
+        <v/>
+      </c>
+      <c r="I16" s="110">
+        <f>IF($B16="","",Sales_Record!J23)</f>
+        <v/>
+      </c>
+      <c r="J16" s="106">
+        <f>IF($B16="","",Sales_Record!F23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="104">
+        <f>IF($B17="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B17" s="105">
+        <f>IF(Sales_Record!B24="","",Sales_Record!B24)</f>
+        <v/>
+      </c>
+      <c r="C17" s="106">
+        <f>IF($B17="","",Sales_Record!C24)</f>
+        <v/>
+      </c>
+      <c r="D17" s="107">
+        <f>IF($B17="","",Sales_Record!D24)</f>
+        <v/>
+      </c>
+      <c r="E17" s="106">
+        <f>IF($B17="","",Sales_Record!G24)</f>
+        <v/>
+      </c>
+      <c r="F17" s="106">
+        <f>IF($B17="","",Sales_Record!E24)</f>
+        <v/>
+      </c>
+      <c r="G17" s="108">
+        <f>IF($B17="","",Sales_Record!H24)</f>
+        <v/>
+      </c>
+      <c r="H17" s="109">
+        <f>IF($B17="","",Sales_Record!I24)</f>
+        <v/>
+      </c>
+      <c r="I17" s="110">
+        <f>IF($B17="","",Sales_Record!J24)</f>
+        <v/>
+      </c>
+      <c r="J17" s="106">
+        <f>IF($B17="","",Sales_Record!F24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="104">
+        <f>IF($B18="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B18" s="105">
+        <f>IF(Sales_Record!B25="","",Sales_Record!B25)</f>
+        <v/>
+      </c>
+      <c r="C18" s="106">
+        <f>IF($B18="","",Sales_Record!C25)</f>
+        <v/>
+      </c>
+      <c r="D18" s="107">
+        <f>IF($B18="","",Sales_Record!D25)</f>
+        <v/>
+      </c>
+      <c r="E18" s="106">
+        <f>IF($B18="","",Sales_Record!G25)</f>
+        <v/>
+      </c>
+      <c r="F18" s="106">
+        <f>IF($B18="","",Sales_Record!E25)</f>
+        <v/>
+      </c>
+      <c r="G18" s="108">
+        <f>IF($B18="","",Sales_Record!H25)</f>
+        <v/>
+      </c>
+      <c r="H18" s="109">
+        <f>IF($B18="","",Sales_Record!I25)</f>
+        <v/>
+      </c>
+      <c r="I18" s="110">
+        <f>IF($B18="","",Sales_Record!J25)</f>
+        <v/>
+      </c>
+      <c r="J18" s="106">
+        <f>IF($B18="","",Sales_Record!F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="104">
+        <f>IF($B19="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B19" s="105">
+        <f>IF(Sales_Record!B26="","",Sales_Record!B26)</f>
+        <v/>
+      </c>
+      <c r="C19" s="106">
+        <f>IF($B19="","",Sales_Record!C26)</f>
+        <v/>
+      </c>
+      <c r="D19" s="107">
+        <f>IF($B19="","",Sales_Record!D26)</f>
+        <v/>
+      </c>
+      <c r="E19" s="106">
+        <f>IF($B19="","",Sales_Record!G26)</f>
+        <v/>
+      </c>
+      <c r="F19" s="106">
+        <f>IF($B19="","",Sales_Record!E26)</f>
+        <v/>
+      </c>
+      <c r="G19" s="108">
+        <f>IF($B19="","",Sales_Record!H26)</f>
+        <v/>
+      </c>
+      <c r="H19" s="109">
+        <f>IF($B19="","",Sales_Record!I26)</f>
+        <v/>
+      </c>
+      <c r="I19" s="110">
+        <f>IF($B19="","",Sales_Record!J26)</f>
+        <v/>
+      </c>
+      <c r="J19" s="106">
+        <f>IF($B19="","",Sales_Record!F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="104">
+        <f>IF($B20="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B20" s="105">
+        <f>IF(Sales_Record!B27="","",Sales_Record!B27)</f>
+        <v/>
+      </c>
+      <c r="C20" s="106">
+        <f>IF($B20="","",Sales_Record!C27)</f>
+        <v/>
+      </c>
+      <c r="D20" s="107">
+        <f>IF($B20="","",Sales_Record!D27)</f>
+        <v/>
+      </c>
+      <c r="E20" s="106">
+        <f>IF($B20="","",Sales_Record!G27)</f>
+        <v/>
+      </c>
+      <c r="F20" s="106">
+        <f>IF($B20="","",Sales_Record!E27)</f>
+        <v/>
+      </c>
+      <c r="G20" s="108">
+        <f>IF($B20="","",Sales_Record!H27)</f>
+        <v/>
+      </c>
+      <c r="H20" s="109">
+        <f>IF($B20="","",Sales_Record!I27)</f>
+        <v/>
+      </c>
+      <c r="I20" s="110">
+        <f>IF($B20="","",Sales_Record!J27)</f>
+        <v/>
+      </c>
+      <c r="J20" s="106">
+        <f>IF($B20="","",Sales_Record!F27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="104">
+        <f>IF($B21="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B21" s="105">
+        <f>IF(Sales_Record!B28="","",Sales_Record!B28)</f>
+        <v/>
+      </c>
+      <c r="C21" s="106">
+        <f>IF($B21="","",Sales_Record!C28)</f>
+        <v/>
+      </c>
+      <c r="D21" s="107">
+        <f>IF($B21="","",Sales_Record!D28)</f>
+        <v/>
+      </c>
+      <c r="E21" s="106">
+        <f>IF($B21="","",Sales_Record!G28)</f>
+        <v/>
+      </c>
+      <c r="F21" s="106">
+        <f>IF($B21="","",Sales_Record!E28)</f>
+        <v/>
+      </c>
+      <c r="G21" s="108">
+        <f>IF($B21="","",Sales_Record!H28)</f>
+        <v/>
+      </c>
+      <c r="H21" s="109">
+        <f>IF($B21="","",Sales_Record!I28)</f>
+        <v/>
+      </c>
+      <c r="I21" s="110">
+        <f>IF($B21="","",Sales_Record!J28)</f>
+        <v/>
+      </c>
+      <c r="J21" s="106">
+        <f>IF($B21="","",Sales_Record!F28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="104">
+        <f>IF($B22="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B22" s="105">
+        <f>IF(Sales_Record!B29="","",Sales_Record!B29)</f>
+        <v/>
+      </c>
+      <c r="C22" s="106">
+        <f>IF($B22="","",Sales_Record!C29)</f>
+        <v/>
+      </c>
+      <c r="D22" s="107">
+        <f>IF($B22="","",Sales_Record!D29)</f>
+        <v/>
+      </c>
+      <c r="E22" s="106">
+        <f>IF($B22="","",Sales_Record!G29)</f>
+        <v/>
+      </c>
+      <c r="F22" s="106">
+        <f>IF($B22="","",Sales_Record!E29)</f>
+        <v/>
+      </c>
+      <c r="G22" s="108">
+        <f>IF($B22="","",Sales_Record!H29)</f>
+        <v/>
+      </c>
+      <c r="H22" s="109">
+        <f>IF($B22="","",Sales_Record!I29)</f>
+        <v/>
+      </c>
+      <c r="I22" s="110">
+        <f>IF($B22="","",Sales_Record!J29)</f>
+        <v/>
+      </c>
+      <c r="J22" s="106">
+        <f>IF($B22="","",Sales_Record!F29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="104">
+        <f>IF($B23="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B23" s="105">
+        <f>IF(Sales_Record!B30="","",Sales_Record!B30)</f>
+        <v/>
+      </c>
+      <c r="C23" s="106">
+        <f>IF($B23="","",Sales_Record!C30)</f>
+        <v/>
+      </c>
+      <c r="D23" s="107">
+        <f>IF($B23="","",Sales_Record!D30)</f>
+        <v/>
+      </c>
+      <c r="E23" s="106">
+        <f>IF($B23="","",Sales_Record!G30)</f>
+        <v/>
+      </c>
+      <c r="F23" s="106">
+        <f>IF($B23="","",Sales_Record!E30)</f>
+        <v/>
+      </c>
+      <c r="G23" s="108">
+        <f>IF($B23="","",Sales_Record!H30)</f>
+        <v/>
+      </c>
+      <c r="H23" s="109">
+        <f>IF($B23="","",Sales_Record!I30)</f>
+        <v/>
+      </c>
+      <c r="I23" s="110">
+        <f>IF($B23="","",Sales_Record!J30)</f>
+        <v/>
+      </c>
+      <c r="J23" s="106">
+        <f>IF($B23="","",Sales_Record!F30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="104">
+        <f>IF($B24="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B24" s="105">
+        <f>IF(Sales_Record!B31="","",Sales_Record!B31)</f>
+        <v/>
+      </c>
+      <c r="C24" s="106">
+        <f>IF($B24="","",Sales_Record!C31)</f>
+        <v/>
+      </c>
+      <c r="D24" s="107">
+        <f>IF($B24="","",Sales_Record!D31)</f>
+        <v/>
+      </c>
+      <c r="E24" s="106">
+        <f>IF($B24="","",Sales_Record!G31)</f>
+        <v/>
+      </c>
+      <c r="F24" s="106">
+        <f>IF($B24="","",Sales_Record!E31)</f>
+        <v/>
+      </c>
+      <c r="G24" s="108">
+        <f>IF($B24="","",Sales_Record!H31)</f>
+        <v/>
+      </c>
+      <c r="H24" s="109">
+        <f>IF($B24="","",Sales_Record!I31)</f>
+        <v/>
+      </c>
+      <c r="I24" s="110">
+        <f>IF($B24="","",Sales_Record!J31)</f>
+        <v/>
+      </c>
+      <c r="J24" s="106">
+        <f>IF($B24="","",Sales_Record!F31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="104">
+        <f>IF($B25="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B25" s="105">
+        <f>IF(Sales_Record!B32="","",Sales_Record!B32)</f>
+        <v/>
+      </c>
+      <c r="C25" s="106">
+        <f>IF($B25="","",Sales_Record!C32)</f>
+        <v/>
+      </c>
+      <c r="D25" s="107">
+        <f>IF($B25="","",Sales_Record!D32)</f>
+        <v/>
+      </c>
+      <c r="E25" s="106">
+        <f>IF($B25="","",Sales_Record!G32)</f>
+        <v/>
+      </c>
+      <c r="F25" s="106">
+        <f>IF($B25="","",Sales_Record!E32)</f>
+        <v/>
+      </c>
+      <c r="G25" s="108">
+        <f>IF($B25="","",Sales_Record!H32)</f>
+        <v/>
+      </c>
+      <c r="H25" s="109">
+        <f>IF($B25="","",Sales_Record!I32)</f>
+        <v/>
+      </c>
+      <c r="I25" s="110">
+        <f>IF($B25="","",Sales_Record!J32)</f>
+        <v/>
+      </c>
+      <c r="J25" s="106">
+        <f>IF($B25="","",Sales_Record!F32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="104">
+        <f>IF($B26="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B26" s="105">
+        <f>IF(Sales_Record!B33="","",Sales_Record!B33)</f>
+        <v/>
+      </c>
+      <c r="C26" s="106">
+        <f>IF($B26="","",Sales_Record!C33)</f>
+        <v/>
+      </c>
+      <c r="D26" s="107">
+        <f>IF($B26="","",Sales_Record!D33)</f>
+        <v/>
+      </c>
+      <c r="E26" s="106">
+        <f>IF($B26="","",Sales_Record!G33)</f>
+        <v/>
+      </c>
+      <c r="F26" s="106">
+        <f>IF($B26="","",Sales_Record!E33)</f>
+        <v/>
+      </c>
+      <c r="G26" s="108">
+        <f>IF($B26="","",Sales_Record!H33)</f>
+        <v/>
+      </c>
+      <c r="H26" s="109">
+        <f>IF($B26="","",Sales_Record!I33)</f>
+        <v/>
+      </c>
+      <c r="I26" s="110">
+        <f>IF($B26="","",Sales_Record!J33)</f>
+        <v/>
+      </c>
+      <c r="J26" s="106">
+        <f>IF($B26="","",Sales_Record!F33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="104">
+        <f>IF($B27="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B27" s="105">
+        <f>IF(Sales_Record!B34="","",Sales_Record!B34)</f>
+        <v/>
+      </c>
+      <c r="C27" s="106">
+        <f>IF($B27="","",Sales_Record!C34)</f>
+        <v/>
+      </c>
+      <c r="D27" s="107">
+        <f>IF($B27="","",Sales_Record!D34)</f>
+        <v/>
+      </c>
+      <c r="E27" s="106">
+        <f>IF($B27="","",Sales_Record!G34)</f>
+        <v/>
+      </c>
+      <c r="F27" s="106">
+        <f>IF($B27="","",Sales_Record!E34)</f>
+        <v/>
+      </c>
+      <c r="G27" s="108">
+        <f>IF($B27="","",Sales_Record!H34)</f>
+        <v/>
+      </c>
+      <c r="H27" s="109">
+        <f>IF($B27="","",Sales_Record!I34)</f>
+        <v/>
+      </c>
+      <c r="I27" s="110">
+        <f>IF($B27="","",Sales_Record!J34)</f>
+        <v/>
+      </c>
+      <c r="J27" s="106">
+        <f>IF($B27="","",Sales_Record!F34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="104">
+        <f>IF($B28="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B28" s="105">
+        <f>IF(Sales_Record!B35="","",Sales_Record!B35)</f>
+        <v/>
+      </c>
+      <c r="C28" s="106">
+        <f>IF($B28="","",Sales_Record!C35)</f>
+        <v/>
+      </c>
+      <c r="D28" s="107">
+        <f>IF($B28="","",Sales_Record!D35)</f>
+        <v/>
+      </c>
+      <c r="E28" s="106">
+        <f>IF($B28="","",Sales_Record!G35)</f>
+        <v/>
+      </c>
+      <c r="F28" s="106">
+        <f>IF($B28="","",Sales_Record!E35)</f>
+        <v/>
+      </c>
+      <c r="G28" s="108">
+        <f>IF($B28="","",Sales_Record!H35)</f>
+        <v/>
+      </c>
+      <c r="H28" s="109">
+        <f>IF($B28="","",Sales_Record!I35)</f>
+        <v/>
+      </c>
+      <c r="I28" s="110">
+        <f>IF($B28="","",Sales_Record!J35)</f>
+        <v/>
+      </c>
+      <c r="J28" s="106">
+        <f>IF($B28="","",Sales_Record!F35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="104">
+        <f>IF($B29="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B29" s="105">
+        <f>IF(Sales_Record!B36="","",Sales_Record!B36)</f>
+        <v/>
+      </c>
+      <c r="C29" s="106">
+        <f>IF($B29="","",Sales_Record!C36)</f>
+        <v/>
+      </c>
+      <c r="D29" s="107">
+        <f>IF($B29="","",Sales_Record!D36)</f>
+        <v/>
+      </c>
+      <c r="E29" s="106">
+        <f>IF($B29="","",Sales_Record!G36)</f>
+        <v/>
+      </c>
+      <c r="F29" s="106">
+        <f>IF($B29="","",Sales_Record!E36)</f>
+        <v/>
+      </c>
+      <c r="G29" s="108">
+        <f>IF($B29="","",Sales_Record!H36)</f>
+        <v/>
+      </c>
+      <c r="H29" s="109">
+        <f>IF($B29="","",Sales_Record!I36)</f>
+        <v/>
+      </c>
+      <c r="I29" s="110">
+        <f>IF($B29="","",Sales_Record!J36)</f>
+        <v/>
+      </c>
+      <c r="J29" s="106">
+        <f>IF($B29="","",Sales_Record!F36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="104">
+        <f>IF($B30="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B30" s="105">
+        <f>IF(Sales_Record!B37="","",Sales_Record!B37)</f>
+        <v/>
+      </c>
+      <c r="C30" s="106">
+        <f>IF($B30="","",Sales_Record!C37)</f>
+        <v/>
+      </c>
+      <c r="D30" s="107">
+        <f>IF($B30="","",Sales_Record!D37)</f>
+        <v/>
+      </c>
+      <c r="E30" s="106">
+        <f>IF($B30="","",Sales_Record!G37)</f>
+        <v/>
+      </c>
+      <c r="F30" s="106">
+        <f>IF($B30="","",Sales_Record!E37)</f>
+        <v/>
+      </c>
+      <c r="G30" s="108">
+        <f>IF($B30="","",Sales_Record!H37)</f>
+        <v/>
+      </c>
+      <c r="H30" s="109">
+        <f>IF($B30="","",Sales_Record!I37)</f>
+        <v/>
+      </c>
+      <c r="I30" s="110">
+        <f>IF($B30="","",Sales_Record!J37)</f>
+        <v/>
+      </c>
+      <c r="J30" s="106">
+        <f>IF($B30="","",Sales_Record!F37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="104">
+        <f>IF($B31="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B31" s="105">
+        <f>IF(Sales_Record!B38="","",Sales_Record!B38)</f>
+        <v/>
+      </c>
+      <c r="C31" s="106">
+        <f>IF($B31="","",Sales_Record!C38)</f>
+        <v/>
+      </c>
+      <c r="D31" s="107">
+        <f>IF($B31="","",Sales_Record!D38)</f>
+        <v/>
+      </c>
+      <c r="E31" s="106">
+        <f>IF($B31="","",Sales_Record!G38)</f>
+        <v/>
+      </c>
+      <c r="F31" s="106">
+        <f>IF($B31="","",Sales_Record!E38)</f>
+        <v/>
+      </c>
+      <c r="G31" s="108">
+        <f>IF($B31="","",Sales_Record!H38)</f>
+        <v/>
+      </c>
+      <c r="H31" s="109">
+        <f>IF($B31="","",Sales_Record!I38)</f>
+        <v/>
+      </c>
+      <c r="I31" s="110">
+        <f>IF($B31="","",Sales_Record!J38)</f>
+        <v/>
+      </c>
+      <c r="J31" s="106">
+        <f>IF($B31="","",Sales_Record!F38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="104">
+        <f>IF($B32="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B32" s="105">
+        <f>IF(Sales_Record!B39="","",Sales_Record!B39)</f>
+        <v/>
+      </c>
+      <c r="C32" s="106">
+        <f>IF($B32="","",Sales_Record!C39)</f>
+        <v/>
+      </c>
+      <c r="D32" s="107">
+        <f>IF($B32="","",Sales_Record!D39)</f>
+        <v/>
+      </c>
+      <c r="E32" s="106">
+        <f>IF($B32="","",Sales_Record!G39)</f>
+        <v/>
+      </c>
+      <c r="F32" s="106">
+        <f>IF($B32="","",Sales_Record!E39)</f>
+        <v/>
+      </c>
+      <c r="G32" s="108">
+        <f>IF($B32="","",Sales_Record!H39)</f>
+        <v/>
+      </c>
+      <c r="H32" s="109">
+        <f>IF($B32="","",Sales_Record!I39)</f>
+        <v/>
+      </c>
+      <c r="I32" s="110">
+        <f>IF($B32="","",Sales_Record!J39)</f>
+        <v/>
+      </c>
+      <c r="J32" s="106">
+        <f>IF($B32="","",Sales_Record!F39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="104">
+        <f>IF($B33="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B33" s="105">
+        <f>IF(Sales_Record!B40="","",Sales_Record!B40)</f>
+        <v/>
+      </c>
+      <c r="C33" s="106">
+        <f>IF($B33="","",Sales_Record!C40)</f>
+        <v/>
+      </c>
+      <c r="D33" s="107">
+        <f>IF($B33="","",Sales_Record!D40)</f>
+        <v/>
+      </c>
+      <c r="E33" s="106">
+        <f>IF($B33="","",Sales_Record!G40)</f>
+        <v/>
+      </c>
+      <c r="F33" s="106">
+        <f>IF($B33="","",Sales_Record!E40)</f>
+        <v/>
+      </c>
+      <c r="G33" s="108">
+        <f>IF($B33="","",Sales_Record!H40)</f>
+        <v/>
+      </c>
+      <c r="H33" s="109">
+        <f>IF($B33="","",Sales_Record!I40)</f>
+        <v/>
+      </c>
+      <c r="I33" s="110">
+        <f>IF($B33="","",Sales_Record!J40)</f>
+        <v/>
+      </c>
+      <c r="J33" s="106">
+        <f>IF($B33="","",Sales_Record!F40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="104">
+        <f>IF($B34="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B34" s="105">
+        <f>IF(Sales_Record!B41="","",Sales_Record!B41)</f>
+        <v/>
+      </c>
+      <c r="C34" s="106">
+        <f>IF($B34="","",Sales_Record!C41)</f>
+        <v/>
+      </c>
+      <c r="D34" s="107">
+        <f>IF($B34="","",Sales_Record!D41)</f>
+        <v/>
+      </c>
+      <c r="E34" s="106">
+        <f>IF($B34="","",Sales_Record!G41)</f>
+        <v/>
+      </c>
+      <c r="F34" s="106">
+        <f>IF($B34="","",Sales_Record!E41)</f>
+        <v/>
+      </c>
+      <c r="G34" s="108">
+        <f>IF($B34="","",Sales_Record!H41)</f>
+        <v/>
+      </c>
+      <c r="H34" s="109">
+        <f>IF($B34="","",Sales_Record!I41)</f>
+        <v/>
+      </c>
+      <c r="I34" s="110">
+        <f>IF($B34="","",Sales_Record!J41)</f>
+        <v/>
+      </c>
+      <c r="J34" s="106">
+        <f>IF($B34="","",Sales_Record!F41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="104">
+        <f>IF($B35="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B35" s="105">
+        <f>IF(Sales_Record!B42="","",Sales_Record!B42)</f>
+        <v/>
+      </c>
+      <c r="C35" s="106">
+        <f>IF($B35="","",Sales_Record!C42)</f>
+        <v/>
+      </c>
+      <c r="D35" s="107">
+        <f>IF($B35="","",Sales_Record!D42)</f>
+        <v/>
+      </c>
+      <c r="E35" s="106">
+        <f>IF($B35="","",Sales_Record!G42)</f>
+        <v/>
+      </c>
+      <c r="F35" s="106">
+        <f>IF($B35="","",Sales_Record!E42)</f>
+        <v/>
+      </c>
+      <c r="G35" s="108">
+        <f>IF($B35="","",Sales_Record!H42)</f>
+        <v/>
+      </c>
+      <c r="H35" s="109">
+        <f>IF($B35="","",Sales_Record!I42)</f>
+        <v/>
+      </c>
+      <c r="I35" s="110">
+        <f>IF($B35="","",Sales_Record!J42)</f>
+        <v/>
+      </c>
+      <c r="J35" s="106">
+        <f>IF($B35="","",Sales_Record!F42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="104">
+        <f>IF($B36="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B36" s="105">
+        <f>IF(Sales_Record!B43="","",Sales_Record!B43)</f>
+        <v/>
+      </c>
+      <c r="C36" s="106">
+        <f>IF($B36="","",Sales_Record!C43)</f>
+        <v/>
+      </c>
+      <c r="D36" s="107">
+        <f>IF($B36="","",Sales_Record!D43)</f>
+        <v/>
+      </c>
+      <c r="E36" s="106">
+        <f>IF($B36="","",Sales_Record!G43)</f>
+        <v/>
+      </c>
+      <c r="F36" s="106">
+        <f>IF($B36="","",Sales_Record!E43)</f>
+        <v/>
+      </c>
+      <c r="G36" s="108">
+        <f>IF($B36="","",Sales_Record!H43)</f>
+        <v/>
+      </c>
+      <c r="H36" s="109">
+        <f>IF($B36="","",Sales_Record!I43)</f>
+        <v/>
+      </c>
+      <c r="I36" s="110">
+        <f>IF($B36="","",Sales_Record!J43)</f>
+        <v/>
+      </c>
+      <c r="J36" s="106">
+        <f>IF($B36="","",Sales_Record!F43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="104">
+        <f>IF($B37="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B37" s="105">
+        <f>IF(Sales_Record!B44="","",Sales_Record!B44)</f>
+        <v/>
+      </c>
+      <c r="C37" s="106">
+        <f>IF($B37="","",Sales_Record!C44)</f>
+        <v/>
+      </c>
+      <c r="D37" s="107">
+        <f>IF($B37="","",Sales_Record!D44)</f>
+        <v/>
+      </c>
+      <c r="E37" s="106">
+        <f>IF($B37="","",Sales_Record!G44)</f>
+        <v/>
+      </c>
+      <c r="F37" s="106">
+        <f>IF($B37="","",Sales_Record!E44)</f>
+        <v/>
+      </c>
+      <c r="G37" s="108">
+        <f>IF($B37="","",Sales_Record!H44)</f>
+        <v/>
+      </c>
+      <c r="H37" s="109">
+        <f>IF($B37="","",Sales_Record!I44)</f>
+        <v/>
+      </c>
+      <c r="I37" s="110">
+        <f>IF($B37="","",Sales_Record!J44)</f>
+        <v/>
+      </c>
+      <c r="J37" s="106">
+        <f>IF($B37="","",Sales_Record!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="104">
+        <f>IF($B38="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B38" s="105">
+        <f>IF(Sales_Record!B45="","",Sales_Record!B45)</f>
+        <v/>
+      </c>
+      <c r="C38" s="106">
+        <f>IF($B38="","",Sales_Record!C45)</f>
+        <v/>
+      </c>
+      <c r="D38" s="107">
+        <f>IF($B38="","",Sales_Record!D45)</f>
+        <v/>
+      </c>
+      <c r="E38" s="106">
+        <f>IF($B38="","",Sales_Record!G45)</f>
+        <v/>
+      </c>
+      <c r="F38" s="106">
+        <f>IF($B38="","",Sales_Record!E45)</f>
+        <v/>
+      </c>
+      <c r="G38" s="108">
+        <f>IF($B38="","",Sales_Record!H45)</f>
+        <v/>
+      </c>
+      <c r="H38" s="109">
+        <f>IF($B38="","",Sales_Record!I45)</f>
+        <v/>
+      </c>
+      <c r="I38" s="110">
+        <f>IF($B38="","",Sales_Record!J45)</f>
+        <v/>
+      </c>
+      <c r="J38" s="106">
+        <f>IF($B38="","",Sales_Record!F45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="104">
+        <f>IF($B39="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B39" s="105">
+        <f>IF(Sales_Record!B46="","",Sales_Record!B46)</f>
+        <v/>
+      </c>
+      <c r="C39" s="106">
+        <f>IF($B39="","",Sales_Record!C46)</f>
+        <v/>
+      </c>
+      <c r="D39" s="107">
+        <f>IF($B39="","",Sales_Record!D46)</f>
+        <v/>
+      </c>
+      <c r="E39" s="106">
+        <f>IF($B39="","",Sales_Record!G46)</f>
+        <v/>
+      </c>
+      <c r="F39" s="106">
+        <f>IF($B39="","",Sales_Record!E46)</f>
+        <v/>
+      </c>
+      <c r="G39" s="108">
+        <f>IF($B39="","",Sales_Record!H46)</f>
+        <v/>
+      </c>
+      <c r="H39" s="109">
+        <f>IF($B39="","",Sales_Record!I46)</f>
+        <v/>
+      </c>
+      <c r="I39" s="110">
+        <f>IF($B39="","",Sales_Record!J46)</f>
+        <v/>
+      </c>
+      <c r="J39" s="106">
+        <f>IF($B39="","",Sales_Record!F46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="104">
+        <f>IF($B40="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B40" s="105">
+        <f>IF(Sales_Record!B47="","",Sales_Record!B47)</f>
+        <v/>
+      </c>
+      <c r="C40" s="106">
+        <f>IF($B40="","",Sales_Record!C47)</f>
+        <v/>
+      </c>
+      <c r="D40" s="107">
+        <f>IF($B40="","",Sales_Record!D47)</f>
+        <v/>
+      </c>
+      <c r="E40" s="106">
+        <f>IF($B40="","",Sales_Record!G47)</f>
+        <v/>
+      </c>
+      <c r="F40" s="106">
+        <f>IF($B40="","",Sales_Record!E47)</f>
+        <v/>
+      </c>
+      <c r="G40" s="108">
+        <f>IF($B40="","",Sales_Record!H47)</f>
+        <v/>
+      </c>
+      <c r="H40" s="109">
+        <f>IF($B40="","",Sales_Record!I47)</f>
+        <v/>
+      </c>
+      <c r="I40" s="110">
+        <f>IF($B40="","",Sales_Record!J47)</f>
+        <v/>
+      </c>
+      <c r="J40" s="106">
+        <f>IF($B40="","",Sales_Record!F47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="104">
+        <f>IF($B41="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B41" s="105">
+        <f>IF(Sales_Record!B48="","",Sales_Record!B48)</f>
+        <v/>
+      </c>
+      <c r="C41" s="106">
+        <f>IF($B41="","",Sales_Record!C48)</f>
+        <v/>
+      </c>
+      <c r="D41" s="107">
+        <f>IF($B41="","",Sales_Record!D48)</f>
+        <v/>
+      </c>
+      <c r="E41" s="106">
+        <f>IF($B41="","",Sales_Record!G48)</f>
+        <v/>
+      </c>
+      <c r="F41" s="106">
+        <f>IF($B41="","",Sales_Record!E48)</f>
+        <v/>
+      </c>
+      <c r="G41" s="108">
+        <f>IF($B41="","",Sales_Record!H48)</f>
+        <v/>
+      </c>
+      <c r="H41" s="109">
+        <f>IF($B41="","",Sales_Record!I48)</f>
+        <v/>
+      </c>
+      <c r="I41" s="110">
+        <f>IF($B41="","",Sales_Record!J48)</f>
+        <v/>
+      </c>
+      <c r="J41" s="106">
+        <f>IF($B41="","",Sales_Record!F48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="104">
+        <f>IF($B42="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B42" s="105">
+        <f>IF(Sales_Record!B49="","",Sales_Record!B49)</f>
+        <v/>
+      </c>
+      <c r="C42" s="106">
+        <f>IF($B42="","",Sales_Record!C49)</f>
+        <v/>
+      </c>
+      <c r="D42" s="107">
+        <f>IF($B42="","",Sales_Record!D49)</f>
+        <v/>
+      </c>
+      <c r="E42" s="106">
+        <f>IF($B42="","",Sales_Record!G49)</f>
+        <v/>
+      </c>
+      <c r="F42" s="106">
+        <f>IF($B42="","",Sales_Record!E49)</f>
+        <v/>
+      </c>
+      <c r="G42" s="108">
+        <f>IF($B42="","",Sales_Record!H49)</f>
+        <v/>
+      </c>
+      <c r="H42" s="109">
+        <f>IF($B42="","",Sales_Record!I49)</f>
+        <v/>
+      </c>
+      <c r="I42" s="110">
+        <f>IF($B42="","",Sales_Record!J49)</f>
+        <v/>
+      </c>
+      <c r="J42" s="106">
+        <f>IF($B42="","",Sales_Record!F49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="104">
+        <f>IF($B43="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B43" s="105">
+        <f>IF(Sales_Record!B50="","",Sales_Record!B50)</f>
+        <v/>
+      </c>
+      <c r="C43" s="106">
+        <f>IF($B43="","",Sales_Record!C50)</f>
+        <v/>
+      </c>
+      <c r="D43" s="107">
+        <f>IF($B43="","",Sales_Record!D50)</f>
+        <v/>
+      </c>
+      <c r="E43" s="106">
+        <f>IF($B43="","",Sales_Record!G50)</f>
+        <v/>
+      </c>
+      <c r="F43" s="106">
+        <f>IF($B43="","",Sales_Record!E50)</f>
+        <v/>
+      </c>
+      <c r="G43" s="108">
+        <f>IF($B43="","",Sales_Record!H50)</f>
+        <v/>
+      </c>
+      <c r="H43" s="109">
+        <f>IF($B43="","",Sales_Record!I50)</f>
+        <v/>
+      </c>
+      <c r="I43" s="110">
+        <f>IF($B43="","",Sales_Record!J50)</f>
+        <v/>
+      </c>
+      <c r="J43" s="106">
+        <f>IF($B43="","",Sales_Record!F50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="104">
+        <f>IF($B44="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B44" s="105">
+        <f>IF(Sales_Record!B51="","",Sales_Record!B51)</f>
+        <v/>
+      </c>
+      <c r="C44" s="106">
+        <f>IF($B44="","",Sales_Record!C51)</f>
+        <v/>
+      </c>
+      <c r="D44" s="107">
+        <f>IF($B44="","",Sales_Record!D51)</f>
+        <v/>
+      </c>
+      <c r="E44" s="106">
+        <f>IF($B44="","",Sales_Record!G51)</f>
+        <v/>
+      </c>
+      <c r="F44" s="106">
+        <f>IF($B44="","",Sales_Record!E51)</f>
+        <v/>
+      </c>
+      <c r="G44" s="108">
+        <f>IF($B44="","",Sales_Record!H51)</f>
+        <v/>
+      </c>
+      <c r="H44" s="109">
+        <f>IF($B44="","",Sales_Record!I51)</f>
+        <v/>
+      </c>
+      <c r="I44" s="110">
+        <f>IF($B44="","",Sales_Record!J51)</f>
+        <v/>
+      </c>
+      <c r="J44" s="106">
+        <f>IF($B44="","",Sales_Record!F51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="104">
+        <f>IF($B45="","",ROW()-5)</f>
+        <v/>
+      </c>
+      <c r="B45" s="105">
+        <f>IF(Sales_Record!B52="","",Sales_Record!B52)</f>
+        <v/>
+      </c>
+      <c r="C45" s="106">
+        <f>IF($B45="","",Sales_Record!C52)</f>
+        <v/>
+      </c>
+      <c r="D45" s="107">
+        <f>IF($B45="","",Sales_Record!D52)</f>
+        <v/>
+      </c>
+      <c r="E45" s="106">
+        <f>IF($B45="","",Sales_Record!G52)</f>
+        <v/>
+      </c>
+      <c r="F45" s="106">
+        <f>IF($B45="","",Sales_Record!E52)</f>
+        <v/>
+      </c>
+      <c r="G45" s="108">
+        <f>IF($B45="","",Sales_Record!H52)</f>
+        <v/>
+      </c>
+      <c r="H45" s="109">
+        <f>IF($B45="","",Sales_Record!I52)</f>
+        <v/>
+      </c>
+      <c r="I45" s="110">
+        <f>IF($B45="","",Sales_Record!J52)</f>
+        <v/>
+      </c>
+      <c r="J45" s="106">
+        <f>IF($B45="","",Sales_Record!F52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="121" t="inlineStr">
+        <is>
+          <t>รวมรายได้ทั้งหมด</t>
+        </is>
+      </c>
+      <c r="B46" s="84" t="n"/>
+      <c r="C46" s="84" t="n"/>
+      <c r="D46" s="84" t="n"/>
+      <c r="E46" s="84" t="n"/>
+      <c r="F46" s="85" t="n"/>
+      <c r="G46" s="124">
+        <f>SUM(G6:G45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="113">
+        <f>COUNT(A6:A45)</f>
+        <v/>
+      </c>
+      <c r="I46" s="124">
+        <f>SUM(I6:I45)</f>
+        <v/>
+      </c>
+      <c r="J46" s="121" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="128" t="inlineStr">
+        <is>
+          <t>หมายเหตุ / วิธีใช้</t>
+        </is>
+      </c>
+      <c r="B49" s="126" t="n"/>
+      <c r="C49" s="126" t="n"/>
+      <c r="D49" s="126" t="n"/>
+      <c r="E49" s="126" t="n"/>
+      <c r="F49" s="126" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="127" t="inlineStr">
+        <is>
+          <t>•  ดึงทุกดีลจากแท็บ Sales_Record อัตโนมัติ — ไม่ต้องกรอกที่นี่</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="127" t="inlineStr">
+        <is>
+          <t>•  รายได้สุทธิ = ราคาเต็ม × (1 − ส่วนลด%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="127" t="inlineStr">
+        <is>
+          <t>•  แถวล่างสุด = รวมราคาเต็ม · จำนวนดีล · รวมรายได้สุทธิ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A1:B2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3754,46 +5822,46 @@
     <row r="1">
       <c r="B1" s="58" t="inlineStr">
         <is>
-          <t>EASYCRM — COMMISSION REPORT 2026</t>
+          <t>EASYCRM — รายงานค่าคอมมิชชั่น 2026</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="59" t="inlineStr">
         <is>
-          <t>Per-salesperson summary · auto-calculated from Sales_Record</t>
+          <t>สรุปรายคน · คำนวณอัตโนมัติจากแท็บ Sales_Record</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="60" t="inlineStr">
-        <is>
-          <t>Salesperson</t>
-        </is>
-      </c>
-      <c r="C4" s="60" t="inlineStr">
-        <is>
-          <t>Deals</t>
-        </is>
-      </c>
-      <c r="D4" s="60" t="inlineStr">
-        <is>
-          <t>Revenue (THB)</t>
-        </is>
-      </c>
-      <c r="E4" s="60" t="inlineStr">
-        <is>
-          <t>Commission (THB)</t>
-        </is>
-      </c>
-      <c r="F4" s="60" t="inlineStr">
-        <is>
-          <t>Paid (THB)</t>
-        </is>
-      </c>
-      <c r="G4" s="60" t="inlineStr">
-        <is>
-          <t>Pending (THB)</t>
+      <c r="B4" s="48" t="inlineStr">
+        <is>
+          <t>พนักงานขาย</t>
+        </is>
+      </c>
+      <c r="C4" s="48" t="inlineStr">
+        <is>
+          <t>จำนวนดีล</t>
+        </is>
+      </c>
+      <c r="D4" s="48" t="inlineStr">
+        <is>
+          <t>รายได้ (บาท)</t>
+        </is>
+      </c>
+      <c r="E4" s="48" t="inlineStr">
+        <is>
+          <t>ค่าคอม (บาท)</t>
+        </is>
+      </c>
+      <c r="F4" s="48" t="inlineStr">
+        <is>
+          <t>จ่ายแล้ว (บาท)</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="inlineStr">
+        <is>
+          <t>ค้างจ่าย (บาท)</t>
         </is>
       </c>
     </row>
@@ -3803,23 +5871,23 @@
         <v/>
       </c>
       <c r="C5" s="62">
+        <f>IF($B5="","",'ทีมขาย'!D6)</f>
+        <v/>
+      </c>
+      <c r="D5" s="63">
         <f>IF($B5="","",'ทีมขาย'!E6)</f>
         <v/>
       </c>
-      <c r="D5" s="63">
+      <c r="E5" s="64">
         <f>IF($B5="","",'ทีมขาย'!F6)</f>
         <v/>
       </c>
-      <c r="E5" s="64">
+      <c r="F5" s="63">
         <f>IF($B5="","",'ทีมขาย'!G6)</f>
         <v/>
       </c>
-      <c r="F5" s="63">
+      <c r="G5" s="63">
         <f>IF($B5="","",'ทีมขาย'!H6)</f>
-        <v/>
-      </c>
-      <c r="G5" s="63">
-        <f>IF($B5="","",'ทีมขาย'!I6)</f>
         <v/>
       </c>
     </row>
@@ -3829,23 +5897,23 @@
         <v/>
       </c>
       <c r="C6" s="62">
+        <f>IF($B6="","",'ทีมขาย'!D7)</f>
+        <v/>
+      </c>
+      <c r="D6" s="63">
         <f>IF($B6="","",'ทีมขาย'!E7)</f>
         <v/>
       </c>
-      <c r="D6" s="63">
+      <c r="E6" s="64">
         <f>IF($B6="","",'ทีมขาย'!F7)</f>
         <v/>
       </c>
-      <c r="E6" s="64">
+      <c r="F6" s="63">
         <f>IF($B6="","",'ทีมขาย'!G7)</f>
         <v/>
       </c>
-      <c r="F6" s="63">
+      <c r="G6" s="63">
         <f>IF($B6="","",'ทีมขาย'!H7)</f>
-        <v/>
-      </c>
-      <c r="G6" s="63">
-        <f>IF($B6="","",'ทีมขาย'!I7)</f>
         <v/>
       </c>
     </row>
@@ -3855,23 +5923,23 @@
         <v/>
       </c>
       <c r="C7" s="62">
+        <f>IF($B7="","",'ทีมขาย'!D8)</f>
+        <v/>
+      </c>
+      <c r="D7" s="63">
         <f>IF($B7="","",'ทีมขาย'!E8)</f>
         <v/>
       </c>
-      <c r="D7" s="63">
+      <c r="E7" s="64">
         <f>IF($B7="","",'ทีมขาย'!F8)</f>
         <v/>
       </c>
-      <c r="E7" s="64">
+      <c r="F7" s="63">
         <f>IF($B7="","",'ทีมขาย'!G8)</f>
         <v/>
       </c>
-      <c r="F7" s="63">
+      <c r="G7" s="63">
         <f>IF($B7="","",'ทีมขาย'!H8)</f>
-        <v/>
-      </c>
-      <c r="G7" s="63">
-        <f>IF($B7="","",'ทีมขาย'!I8)</f>
         <v/>
       </c>
     </row>
@@ -3881,23 +5949,23 @@
         <v/>
       </c>
       <c r="C8" s="62">
+        <f>IF($B8="","",'ทีมขาย'!D9)</f>
+        <v/>
+      </c>
+      <c r="D8" s="63">
         <f>IF($B8="","",'ทีมขาย'!E9)</f>
         <v/>
       </c>
-      <c r="D8" s="63">
+      <c r="E8" s="64">
         <f>IF($B8="","",'ทีมขาย'!F9)</f>
         <v/>
       </c>
-      <c r="E8" s="64">
+      <c r="F8" s="63">
         <f>IF($B8="","",'ทีมขาย'!G9)</f>
         <v/>
       </c>
-      <c r="F8" s="63">
+      <c r="G8" s="63">
         <f>IF($B8="","",'ทีมขาย'!H9)</f>
-        <v/>
-      </c>
-      <c r="G8" s="63">
-        <f>IF($B8="","",'ทีมขาย'!I9)</f>
         <v/>
       </c>
     </row>
@@ -3907,23 +5975,23 @@
         <v/>
       </c>
       <c r="C9" s="62">
+        <f>IF($B9="","",'ทีมขาย'!D10)</f>
+        <v/>
+      </c>
+      <c r="D9" s="63">
         <f>IF($B9="","",'ทีมขาย'!E10)</f>
         <v/>
       </c>
-      <c r="D9" s="63">
+      <c r="E9" s="64">
         <f>IF($B9="","",'ทีมขาย'!F10)</f>
         <v/>
       </c>
-      <c r="E9" s="64">
+      <c r="F9" s="63">
         <f>IF($B9="","",'ทีมขาย'!G10)</f>
         <v/>
       </c>
-      <c r="F9" s="63">
+      <c r="G9" s="63">
         <f>IF($B9="","",'ทีมขาย'!H10)</f>
-        <v/>
-      </c>
-      <c r="G9" s="63">
-        <f>IF($B9="","",'ทีมขาย'!I10)</f>
         <v/>
       </c>
     </row>
@@ -3933,23 +6001,23 @@
         <v/>
       </c>
       <c r="C10" s="62">
+        <f>IF($B10="","",'ทีมขาย'!D11)</f>
+        <v/>
+      </c>
+      <c r="D10" s="63">
         <f>IF($B10="","",'ทีมขาย'!E11)</f>
         <v/>
       </c>
-      <c r="D10" s="63">
+      <c r="E10" s="64">
         <f>IF($B10="","",'ทีมขาย'!F11)</f>
         <v/>
       </c>
-      <c r="E10" s="64">
+      <c r="F10" s="63">
         <f>IF($B10="","",'ทีมขาย'!G11)</f>
         <v/>
       </c>
-      <c r="F10" s="63">
+      <c r="G10" s="63">
         <f>IF($B10="","",'ทีมขาย'!H11)</f>
-        <v/>
-      </c>
-      <c r="G10" s="63">
-        <f>IF($B10="","",'ทีมขาย'!I11)</f>
         <v/>
       </c>
     </row>
@@ -3959,23 +6027,23 @@
         <v/>
       </c>
       <c r="C11" s="62">
+        <f>IF($B11="","",'ทีมขาย'!D12)</f>
+        <v/>
+      </c>
+      <c r="D11" s="63">
         <f>IF($B11="","",'ทีมขาย'!E12)</f>
         <v/>
       </c>
-      <c r="D11" s="63">
+      <c r="E11" s="64">
         <f>IF($B11="","",'ทีมขาย'!F12)</f>
         <v/>
       </c>
-      <c r="E11" s="64">
+      <c r="F11" s="63">
         <f>IF($B11="","",'ทีมขาย'!G12)</f>
         <v/>
       </c>
-      <c r="F11" s="63">
+      <c r="G11" s="63">
         <f>IF($B11="","",'ทีมขาย'!H12)</f>
-        <v/>
-      </c>
-      <c r="G11" s="63">
-        <f>IF($B11="","",'ทีมขาย'!I12)</f>
         <v/>
       </c>
     </row>
@@ -3985,23 +6053,23 @@
         <v/>
       </c>
       <c r="C12" s="62">
+        <f>IF($B12="","",'ทีมขาย'!D13)</f>
+        <v/>
+      </c>
+      <c r="D12" s="63">
         <f>IF($B12="","",'ทีมขาย'!E13)</f>
         <v/>
       </c>
-      <c r="D12" s="63">
+      <c r="E12" s="64">
         <f>IF($B12="","",'ทีมขาย'!F13)</f>
         <v/>
       </c>
-      <c r="E12" s="64">
+      <c r="F12" s="63">
         <f>IF($B12="","",'ทีมขาย'!G13)</f>
         <v/>
       </c>
-      <c r="F12" s="63">
+      <c r="G12" s="63">
         <f>IF($B12="","",'ทีมขาย'!H13)</f>
-        <v/>
-      </c>
-      <c r="G12" s="63">
-        <f>IF($B12="","",'ทีมขาย'!I13)</f>
         <v/>
       </c>
     </row>
@@ -4011,23 +6079,23 @@
         <v/>
       </c>
       <c r="C13" s="62">
+        <f>IF($B13="","",'ทีมขาย'!D14)</f>
+        <v/>
+      </c>
+      <c r="D13" s="63">
         <f>IF($B13="","",'ทีมขาย'!E14)</f>
         <v/>
       </c>
-      <c r="D13" s="63">
+      <c r="E13" s="64">
         <f>IF($B13="","",'ทีมขาย'!F14)</f>
         <v/>
       </c>
-      <c r="E13" s="64">
+      <c r="F13" s="63">
         <f>IF($B13="","",'ทีมขาย'!G14)</f>
         <v/>
       </c>
-      <c r="F13" s="63">
+      <c r="G13" s="63">
         <f>IF($B13="","",'ทีมขาย'!H14)</f>
-        <v/>
-      </c>
-      <c r="G13" s="63">
-        <f>IF($B13="","",'ทีมขาย'!I14)</f>
         <v/>
       </c>
     </row>
@@ -4037,23 +6105,23 @@
         <v/>
       </c>
       <c r="C14" s="62">
+        <f>IF($B14="","",'ทีมขาย'!D15)</f>
+        <v/>
+      </c>
+      <c r="D14" s="63">
         <f>IF($B14="","",'ทีมขาย'!E15)</f>
         <v/>
       </c>
-      <c r="D14" s="63">
+      <c r="E14" s="64">
         <f>IF($B14="","",'ทีมขาย'!F15)</f>
         <v/>
       </c>
-      <c r="E14" s="64">
+      <c r="F14" s="63">
         <f>IF($B14="","",'ทีมขาย'!G15)</f>
         <v/>
       </c>
-      <c r="F14" s="63">
+      <c r="G14" s="63">
         <f>IF($B14="","",'ทีมขาย'!H15)</f>
-        <v/>
-      </c>
-      <c r="G14" s="63">
-        <f>IF($B14="","",'ทีมขาย'!I15)</f>
         <v/>
       </c>
     </row>
@@ -4063,23 +6131,23 @@
         <v/>
       </c>
       <c r="C15" s="62">
+        <f>IF($B15="","",'ทีมขาย'!D16)</f>
+        <v/>
+      </c>
+      <c r="D15" s="63">
         <f>IF($B15="","",'ทีมขาย'!E16)</f>
         <v/>
       </c>
-      <c r="D15" s="63">
+      <c r="E15" s="64">
         <f>IF($B15="","",'ทีมขาย'!F16)</f>
         <v/>
       </c>
-      <c r="E15" s="64">
+      <c r="F15" s="63">
         <f>IF($B15="","",'ทีมขาย'!G16)</f>
         <v/>
       </c>
-      <c r="F15" s="63">
+      <c r="G15" s="63">
         <f>IF($B15="","",'ทีมขาย'!H16)</f>
-        <v/>
-      </c>
-      <c r="G15" s="63">
-        <f>IF($B15="","",'ทีมขาย'!I16)</f>
         <v/>
       </c>
     </row>
@@ -4089,23 +6157,23 @@
         <v/>
       </c>
       <c r="C16" s="62">
+        <f>IF($B16="","",'ทีมขาย'!D17)</f>
+        <v/>
+      </c>
+      <c r="D16" s="63">
         <f>IF($B16="","",'ทีมขาย'!E17)</f>
         <v/>
       </c>
-      <c r="D16" s="63">
+      <c r="E16" s="64">
         <f>IF($B16="","",'ทีมขาย'!F17)</f>
         <v/>
       </c>
-      <c r="E16" s="64">
+      <c r="F16" s="63">
         <f>IF($B16="","",'ทีมขาย'!G17)</f>
         <v/>
       </c>
-      <c r="F16" s="63">
+      <c r="G16" s="63">
         <f>IF($B16="","",'ทีมขาย'!H17)</f>
-        <v/>
-      </c>
-      <c r="G16" s="63">
-        <f>IF($B16="","",'ทีมขาย'!I17)</f>
         <v/>
       </c>
     </row>
@@ -4115,23 +6183,23 @@
         <v/>
       </c>
       <c r="C17" s="62">
+        <f>IF($B17="","",'ทีมขาย'!D18)</f>
+        <v/>
+      </c>
+      <c r="D17" s="63">
         <f>IF($B17="","",'ทีมขาย'!E18)</f>
         <v/>
       </c>
-      <c r="D17" s="63">
+      <c r="E17" s="64">
         <f>IF($B17="","",'ทีมขาย'!F18)</f>
         <v/>
       </c>
-      <c r="E17" s="64">
+      <c r="F17" s="63">
         <f>IF($B17="","",'ทีมขาย'!G18)</f>
         <v/>
       </c>
-      <c r="F17" s="63">
+      <c r="G17" s="63">
         <f>IF($B17="","",'ทีมขาย'!H18)</f>
-        <v/>
-      </c>
-      <c r="G17" s="63">
-        <f>IF($B17="","",'ทีมขาย'!I18)</f>
         <v/>
       </c>
     </row>
@@ -4141,23 +6209,23 @@
         <v/>
       </c>
       <c r="C18" s="62">
+        <f>IF($B18="","",'ทีมขาย'!D19)</f>
+        <v/>
+      </c>
+      <c r="D18" s="63">
         <f>IF($B18="","",'ทีมขาย'!E19)</f>
         <v/>
       </c>
-      <c r="D18" s="63">
+      <c r="E18" s="64">
         <f>IF($B18="","",'ทีมขาย'!F19)</f>
         <v/>
       </c>
-      <c r="E18" s="64">
+      <c r="F18" s="63">
         <f>IF($B18="","",'ทีมขาย'!G19)</f>
         <v/>
       </c>
-      <c r="F18" s="63">
+      <c r="G18" s="63">
         <f>IF($B18="","",'ทีมขาย'!H19)</f>
-        <v/>
-      </c>
-      <c r="G18" s="63">
-        <f>IF($B18="","",'ทีมขาย'!I19)</f>
         <v/>
       </c>
     </row>
@@ -4167,30 +6235,30 @@
         <v/>
       </c>
       <c r="C19" s="62">
+        <f>IF($B19="","",'ทีมขาย'!D20)</f>
+        <v/>
+      </c>
+      <c r="D19" s="63">
         <f>IF($B19="","",'ทีมขาย'!E20)</f>
         <v/>
       </c>
-      <c r="D19" s="63">
+      <c r="E19" s="64">
         <f>IF($B19="","",'ทีมขาย'!F20)</f>
         <v/>
       </c>
-      <c r="E19" s="64">
+      <c r="F19" s="63">
         <f>IF($B19="","",'ทีมขาย'!G20)</f>
         <v/>
       </c>
-      <c r="F19" s="63">
+      <c r="G19" s="63">
         <f>IF($B19="","",'ทีมขาย'!H20)</f>
-        <v/>
-      </c>
-      <c r="G19" s="63">
-        <f>IF($B19="","",'ทีมขาย'!I20)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="61" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>รวมทั้งทีม</t>
         </is>
       </c>
       <c r="C20" s="62">
@@ -4214,500 +6282,47 @@
         <v/>
       </c>
     </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="128" t="inlineStr">
+        <is>
+          <t>หมายเหตุ / วิธีใช้</t>
+        </is>
+      </c>
+      <c r="C23" s="126" t="n"/>
+      <c r="D23" s="126" t="n"/>
+      <c r="E23" s="126" t="n"/>
+      <c r="F23" s="126" t="n"/>
+      <c r="G23" s="126" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="127" t="inlineStr">
+        <is>
+          <t>•  สรุปค่าคอมรายคน คิดเองจาก Sales_Record + ทีมขาย — ไม่ต้องกรอก</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="127" t="inlineStr">
+        <is>
+          <t>•  ค่าคอม = งานที่ปิดเอง (รายคน) + ส่วนแบ่งจากดีลทีม</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="127" t="inlineStr">
+        <is>
+          <t>•  เพิ่มคนในแท็บทีมขาย รายงานนี้จะขึ้นตามเอง</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="B1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:G20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="58" t="inlineStr">
-        <is>
-          <t>EASYCRM — รายงานค่าคอมมิชชั่น 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="59" t="inlineStr">
-        <is>
-          <t>สรุปรายคน · คำนวณอัตโนมัติจากแท็บ Sales_Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="48" t="inlineStr">
-        <is>
-          <t>พนักงานขาย</t>
-        </is>
-      </c>
-      <c r="C4" s="48" t="inlineStr">
-        <is>
-          <t>จำนวนดีล</t>
-        </is>
-      </c>
-      <c r="D4" s="48" t="inlineStr">
-        <is>
-          <t>รายได้ (บาท)</t>
-        </is>
-      </c>
-      <c r="E4" s="48" t="inlineStr">
-        <is>
-          <t>ค่าคอม (บาท)</t>
-        </is>
-      </c>
-      <c r="F4" s="48" t="inlineStr">
-        <is>
-          <t>จ่ายแล้ว (บาท)</t>
-        </is>
-      </c>
-      <c r="G4" s="48" t="inlineStr">
-        <is>
-          <t>ค้างจ่าย (บาท)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="61">
-        <f>IF('ทีมขาย'!A6="","",'ทีมขาย'!A6)</f>
-        <v/>
-      </c>
-      <c r="C5" s="62">
-        <f>IF($B5="","",'ทีมขาย'!E6)</f>
-        <v/>
-      </c>
-      <c r="D5" s="63">
-        <f>IF($B5="","",'ทีมขาย'!F6)</f>
-        <v/>
-      </c>
-      <c r="E5" s="64">
-        <f>IF($B5="","",'ทีมขาย'!G6)</f>
-        <v/>
-      </c>
-      <c r="F5" s="63">
-        <f>IF($B5="","",'ทีมขาย'!H6)</f>
-        <v/>
-      </c>
-      <c r="G5" s="63">
-        <f>IF($B5="","",'ทีมขาย'!I6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="61">
-        <f>IF('ทีมขาย'!A7="","",'ทีมขาย'!A7)</f>
-        <v/>
-      </c>
-      <c r="C6" s="62">
-        <f>IF($B6="","",'ทีมขาย'!E7)</f>
-        <v/>
-      </c>
-      <c r="D6" s="63">
-        <f>IF($B6="","",'ทีมขาย'!F7)</f>
-        <v/>
-      </c>
-      <c r="E6" s="64">
-        <f>IF($B6="","",'ทีมขาย'!G7)</f>
-        <v/>
-      </c>
-      <c r="F6" s="63">
-        <f>IF($B6="","",'ทีมขาย'!H7)</f>
-        <v/>
-      </c>
-      <c r="G6" s="63">
-        <f>IF($B6="","",'ทีมขาย'!I7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="61">
-        <f>IF('ทีมขาย'!A8="","",'ทีมขาย'!A8)</f>
-        <v/>
-      </c>
-      <c r="C7" s="62">
-        <f>IF($B7="","",'ทีมขาย'!E8)</f>
-        <v/>
-      </c>
-      <c r="D7" s="63">
-        <f>IF($B7="","",'ทีมขาย'!F8)</f>
-        <v/>
-      </c>
-      <c r="E7" s="64">
-        <f>IF($B7="","",'ทีมขาย'!G8)</f>
-        <v/>
-      </c>
-      <c r="F7" s="63">
-        <f>IF($B7="","",'ทีมขาย'!H8)</f>
-        <v/>
-      </c>
-      <c r="G7" s="63">
-        <f>IF($B7="","",'ทีมขาย'!I8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="61">
-        <f>IF('ทีมขาย'!A9="","",'ทีมขาย'!A9)</f>
-        <v/>
-      </c>
-      <c r="C8" s="62">
-        <f>IF($B8="","",'ทีมขาย'!E9)</f>
-        <v/>
-      </c>
-      <c r="D8" s="63">
-        <f>IF($B8="","",'ทีมขาย'!F9)</f>
-        <v/>
-      </c>
-      <c r="E8" s="64">
-        <f>IF($B8="","",'ทีมขาย'!G9)</f>
-        <v/>
-      </c>
-      <c r="F8" s="63">
-        <f>IF($B8="","",'ทีมขาย'!H9)</f>
-        <v/>
-      </c>
-      <c r="G8" s="63">
-        <f>IF($B8="","",'ทีมขาย'!I9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="61">
-        <f>IF('ทีมขาย'!A10="","",'ทีมขาย'!A10)</f>
-        <v/>
-      </c>
-      <c r="C9" s="62">
-        <f>IF($B9="","",'ทีมขาย'!E10)</f>
-        <v/>
-      </c>
-      <c r="D9" s="63">
-        <f>IF($B9="","",'ทีมขาย'!F10)</f>
-        <v/>
-      </c>
-      <c r="E9" s="64">
-        <f>IF($B9="","",'ทีมขาย'!G10)</f>
-        <v/>
-      </c>
-      <c r="F9" s="63">
-        <f>IF($B9="","",'ทีมขาย'!H10)</f>
-        <v/>
-      </c>
-      <c r="G9" s="63">
-        <f>IF($B9="","",'ทีมขาย'!I10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="61">
-        <f>IF('ทีมขาย'!A11="","",'ทีมขาย'!A11)</f>
-        <v/>
-      </c>
-      <c r="C10" s="62">
-        <f>IF($B10="","",'ทีมขาย'!E11)</f>
-        <v/>
-      </c>
-      <c r="D10" s="63">
-        <f>IF($B10="","",'ทีมขาย'!F11)</f>
-        <v/>
-      </c>
-      <c r="E10" s="64">
-        <f>IF($B10="","",'ทีมขาย'!G11)</f>
-        <v/>
-      </c>
-      <c r="F10" s="63">
-        <f>IF($B10="","",'ทีมขาย'!H11)</f>
-        <v/>
-      </c>
-      <c r="G10" s="63">
-        <f>IF($B10="","",'ทีมขาย'!I11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="61">
-        <f>IF('ทีมขาย'!A12="","",'ทีมขาย'!A12)</f>
-        <v/>
-      </c>
-      <c r="C11" s="62">
-        <f>IF($B11="","",'ทีมขาย'!E12)</f>
-        <v/>
-      </c>
-      <c r="D11" s="63">
-        <f>IF($B11="","",'ทีมขาย'!F12)</f>
-        <v/>
-      </c>
-      <c r="E11" s="64">
-        <f>IF($B11="","",'ทีมขาย'!G12)</f>
-        <v/>
-      </c>
-      <c r="F11" s="63">
-        <f>IF($B11="","",'ทีมขาย'!H12)</f>
-        <v/>
-      </c>
-      <c r="G11" s="63">
-        <f>IF($B11="","",'ทีมขาย'!I12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="61">
-        <f>IF('ทีมขาย'!A13="","",'ทีมขาย'!A13)</f>
-        <v/>
-      </c>
-      <c r="C12" s="62">
-        <f>IF($B12="","",'ทีมขาย'!E13)</f>
-        <v/>
-      </c>
-      <c r="D12" s="63">
-        <f>IF($B12="","",'ทีมขาย'!F13)</f>
-        <v/>
-      </c>
-      <c r="E12" s="64">
-        <f>IF($B12="","",'ทีมขาย'!G13)</f>
-        <v/>
-      </c>
-      <c r="F12" s="63">
-        <f>IF($B12="","",'ทีมขาย'!H13)</f>
-        <v/>
-      </c>
-      <c r="G12" s="63">
-        <f>IF($B12="","",'ทีมขาย'!I13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="61">
-        <f>IF('ทีมขาย'!A14="","",'ทีมขาย'!A14)</f>
-        <v/>
-      </c>
-      <c r="C13" s="62">
-        <f>IF($B13="","",'ทีมขาย'!E14)</f>
-        <v/>
-      </c>
-      <c r="D13" s="63">
-        <f>IF($B13="","",'ทีมขาย'!F14)</f>
-        <v/>
-      </c>
-      <c r="E13" s="64">
-        <f>IF($B13="","",'ทีมขาย'!G14)</f>
-        <v/>
-      </c>
-      <c r="F13" s="63">
-        <f>IF($B13="","",'ทีมขาย'!H14)</f>
-        <v/>
-      </c>
-      <c r="G13" s="63">
-        <f>IF($B13="","",'ทีมขาย'!I14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="61">
-        <f>IF('ทีมขาย'!A15="","",'ทีมขาย'!A15)</f>
-        <v/>
-      </c>
-      <c r="C14" s="62">
-        <f>IF($B14="","",'ทีมขาย'!E15)</f>
-        <v/>
-      </c>
-      <c r="D14" s="63">
-        <f>IF($B14="","",'ทีมขาย'!F15)</f>
-        <v/>
-      </c>
-      <c r="E14" s="64">
-        <f>IF($B14="","",'ทีมขาย'!G15)</f>
-        <v/>
-      </c>
-      <c r="F14" s="63">
-        <f>IF($B14="","",'ทีมขาย'!H15)</f>
-        <v/>
-      </c>
-      <c r="G14" s="63">
-        <f>IF($B14="","",'ทีมขาย'!I15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="61">
-        <f>IF('ทีมขาย'!A16="","",'ทีมขาย'!A16)</f>
-        <v/>
-      </c>
-      <c r="C15" s="62">
-        <f>IF($B15="","",'ทีมขาย'!E16)</f>
-        <v/>
-      </c>
-      <c r="D15" s="63">
-        <f>IF($B15="","",'ทีมขาย'!F16)</f>
-        <v/>
-      </c>
-      <c r="E15" s="64">
-        <f>IF($B15="","",'ทีมขาย'!G16)</f>
-        <v/>
-      </c>
-      <c r="F15" s="63">
-        <f>IF($B15="","",'ทีมขาย'!H16)</f>
-        <v/>
-      </c>
-      <c r="G15" s="63">
-        <f>IF($B15="","",'ทีมขาย'!I16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="61">
-        <f>IF('ทีมขาย'!A17="","",'ทีมขาย'!A17)</f>
-        <v/>
-      </c>
-      <c r="C16" s="62">
-        <f>IF($B16="","",'ทีมขาย'!E17)</f>
-        <v/>
-      </c>
-      <c r="D16" s="63">
-        <f>IF($B16="","",'ทีมขาย'!F17)</f>
-        <v/>
-      </c>
-      <c r="E16" s="64">
-        <f>IF($B16="","",'ทีมขาย'!G17)</f>
-        <v/>
-      </c>
-      <c r="F16" s="63">
-        <f>IF($B16="","",'ทีมขาย'!H17)</f>
-        <v/>
-      </c>
-      <c r="G16" s="63">
-        <f>IF($B16="","",'ทีมขาย'!I17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="61">
-        <f>IF('ทีมขาย'!A18="","",'ทีมขาย'!A18)</f>
-        <v/>
-      </c>
-      <c r="C17" s="62">
-        <f>IF($B17="","",'ทีมขาย'!E18)</f>
-        <v/>
-      </c>
-      <c r="D17" s="63">
-        <f>IF($B17="","",'ทีมขาย'!F18)</f>
-        <v/>
-      </c>
-      <c r="E17" s="64">
-        <f>IF($B17="","",'ทีมขาย'!G18)</f>
-        <v/>
-      </c>
-      <c r="F17" s="63">
-        <f>IF($B17="","",'ทีมขาย'!H18)</f>
-        <v/>
-      </c>
-      <c r="G17" s="63">
-        <f>IF($B17="","",'ทีมขาย'!I18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="61">
-        <f>IF('ทีมขาย'!A19="","",'ทีมขาย'!A19)</f>
-        <v/>
-      </c>
-      <c r="C18" s="62">
-        <f>IF($B18="","",'ทีมขาย'!E19)</f>
-        <v/>
-      </c>
-      <c r="D18" s="63">
-        <f>IF($B18="","",'ทีมขาย'!F19)</f>
-        <v/>
-      </c>
-      <c r="E18" s="64">
-        <f>IF($B18="","",'ทีมขาย'!G19)</f>
-        <v/>
-      </c>
-      <c r="F18" s="63">
-        <f>IF($B18="","",'ทีมขาย'!H19)</f>
-        <v/>
-      </c>
-      <c r="G18" s="63">
-        <f>IF($B18="","",'ทีมขาย'!I19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="61">
-        <f>IF('ทีมขาย'!A20="","",'ทีมขาย'!A20)</f>
-        <v/>
-      </c>
-      <c r="C19" s="62">
-        <f>IF($B19="","",'ทีมขาย'!E20)</f>
-        <v/>
-      </c>
-      <c r="D19" s="63">
-        <f>IF($B19="","",'ทีมขาย'!F20)</f>
-        <v/>
-      </c>
-      <c r="E19" s="64">
-        <f>IF($B19="","",'ทีมขาย'!G20)</f>
-        <v/>
-      </c>
-      <c r="F19" s="63">
-        <f>IF($B19="","",'ทีมขาย'!H20)</f>
-        <v/>
-      </c>
-      <c r="G19" s="63">
-        <f>IF($B19="","",'ทีมขาย'!I20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="61" t="inlineStr">
-        <is>
-          <t>รวมทั้งทีม</t>
-        </is>
-      </c>
-      <c r="C20" s="62">
-        <f>SUM(C5:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="63">
-        <f>SUM(D5:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="64">
-        <f>SUM(E5:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="63">
-        <f>SUM(F5:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="63">
-        <f>SUM(G5:G19)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;฿&quot;"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -194,6 +194,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="005A6673"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B5791E"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -518,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -873,6 +878,81 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="19" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1239,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1606,26 +1686,26 @@
         <f>IF(B13="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B13" s="105" t="n"/>
+      <c r="B13" s="129" t="n"/>
       <c r="C13" s="106">
         <f>IF(B13="","","Q"&amp;ROUNDUP(MONTH(B13)/3,0))</f>
         <v/>
       </c>
-      <c r="D13" s="107" t="n"/>
-      <c r="E13" s="106" t="n"/>
-      <c r="F13" s="106" t="n"/>
-      <c r="G13" s="106" t="n"/>
-      <c r="H13" s="108">
+      <c r="D13" s="130" t="n"/>
+      <c r="E13" s="131" t="n"/>
+      <c r="F13" s="131" t="n"/>
+      <c r="G13" s="131" t="n"/>
+      <c r="H13" s="132">
         <f>IF(G13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I13" s="35" t="n"/>
+      <c r="I13" s="133" t="n"/>
       <c r="J13" s="108">
         <f>IF(H13="","",H13*(1-IF(I13="",0,I13)))</f>
         <v/>
       </c>
-      <c r="K13" s="106" t="n"/>
-      <c r="L13" s="106" t="n"/>
+      <c r="K13" s="131" t="n"/>
+      <c r="L13" s="131" t="n"/>
       <c r="M13" s="35">
         <f>IF(G13="","",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1634,33 +1714,33 @@
         <f>IF(OR(J13="",M13=""),"",J13*M13)</f>
         <v/>
       </c>
-      <c r="O13" s="106" t="n"/>
+      <c r="O13" s="131" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="89">
         <f>IF(B14="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B14" s="38" t="n"/>
+      <c r="B14" s="134" t="n"/>
       <c r="C14" s="89">
         <f>IF(B14="","","Q"&amp;ROUNDUP(MONTH(B14)/3,0))</f>
         <v/>
       </c>
-      <c r="D14" s="39" t="n"/>
-      <c r="E14" s="89" t="n"/>
-      <c r="F14" s="89" t="n"/>
-      <c r="G14" s="89" t="n"/>
-      <c r="H14" s="40">
+      <c r="D14" s="135" t="n"/>
+      <c r="E14" s="136" t="n"/>
+      <c r="F14" s="136" t="n"/>
+      <c r="G14" s="136" t="n"/>
+      <c r="H14" s="137">
         <f>IF(G14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I14" s="41" t="n"/>
+      <c r="I14" s="138" t="n"/>
       <c r="J14" s="40">
         <f>IF(H14="","",H14*(1-IF(I14="",0,I14)))</f>
         <v/>
       </c>
-      <c r="K14" s="89" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="K14" s="136" t="n"/>
+      <c r="L14" s="136" t="n"/>
       <c r="M14" s="41">
         <f>IF(G14="","",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1669,33 +1749,33 @@
         <f>IF(OR(J14="",M14=""),"",J14*M14)</f>
         <v/>
       </c>
-      <c r="O14" s="89" t="n"/>
+      <c r="O14" s="136" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="106">
         <f>IF(B15="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B15" s="105" t="n"/>
+      <c r="B15" s="129" t="n"/>
       <c r="C15" s="106">
         <f>IF(B15="","","Q"&amp;ROUNDUP(MONTH(B15)/3,0))</f>
         <v/>
       </c>
-      <c r="D15" s="107" t="n"/>
-      <c r="E15" s="106" t="n"/>
-      <c r="F15" s="106" t="n"/>
-      <c r="G15" s="106" t="n"/>
-      <c r="H15" s="108">
+      <c r="D15" s="130" t="n"/>
+      <c r="E15" s="131" t="n"/>
+      <c r="F15" s="131" t="n"/>
+      <c r="G15" s="131" t="n"/>
+      <c r="H15" s="132">
         <f>IF(G15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I15" s="35" t="n"/>
+      <c r="I15" s="133" t="n"/>
       <c r="J15" s="108">
         <f>IF(H15="","",H15*(1-IF(I15="",0,I15)))</f>
         <v/>
       </c>
-      <c r="K15" s="106" t="n"/>
-      <c r="L15" s="106" t="n"/>
+      <c r="K15" s="131" t="n"/>
+      <c r="L15" s="131" t="n"/>
       <c r="M15" s="35">
         <f>IF(G15="","",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1704,33 +1784,33 @@
         <f>IF(OR(J15="",M15=""),"",J15*M15)</f>
         <v/>
       </c>
-      <c r="O15" s="106" t="n"/>
+      <c r="O15" s="131" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="89">
         <f>IF(B16="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B16" s="38" t="n"/>
+      <c r="B16" s="134" t="n"/>
       <c r="C16" s="89">
         <f>IF(B16="","","Q"&amp;ROUNDUP(MONTH(B16)/3,0))</f>
         <v/>
       </c>
-      <c r="D16" s="39" t="n"/>
-      <c r="E16" s="89" t="n"/>
-      <c r="F16" s="89" t="n"/>
-      <c r="G16" s="89" t="n"/>
-      <c r="H16" s="40">
+      <c r="D16" s="135" t="n"/>
+      <c r="E16" s="136" t="n"/>
+      <c r="F16" s="136" t="n"/>
+      <c r="G16" s="136" t="n"/>
+      <c r="H16" s="137">
         <f>IF(G16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I16" s="41" t="n"/>
+      <c r="I16" s="138" t="n"/>
       <c r="J16" s="40">
         <f>IF(H16="","",H16*(1-IF(I16="",0,I16)))</f>
         <v/>
       </c>
-      <c r="K16" s="89" t="n"/>
-      <c r="L16" s="89" t="n"/>
+      <c r="K16" s="136" t="n"/>
+      <c r="L16" s="136" t="n"/>
       <c r="M16" s="41">
         <f>IF(G16="","",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1739,33 +1819,33 @@
         <f>IF(OR(J16="",M16=""),"",J16*M16)</f>
         <v/>
       </c>
-      <c r="O16" s="89" t="n"/>
+      <c r="O16" s="136" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="106">
         <f>IF(B17="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B17" s="105" t="n"/>
+      <c r="B17" s="129" t="n"/>
       <c r="C17" s="106">
         <f>IF(B17="","","Q"&amp;ROUNDUP(MONTH(B17)/3,0))</f>
         <v/>
       </c>
-      <c r="D17" s="107" t="n"/>
-      <c r="E17" s="106" t="n"/>
-      <c r="F17" s="106" t="n"/>
-      <c r="G17" s="106" t="n"/>
-      <c r="H17" s="108">
+      <c r="D17" s="130" t="n"/>
+      <c r="E17" s="131" t="n"/>
+      <c r="F17" s="131" t="n"/>
+      <c r="G17" s="131" t="n"/>
+      <c r="H17" s="132">
         <f>IF(G17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I17" s="35" t="n"/>
+      <c r="I17" s="133" t="n"/>
       <c r="J17" s="108">
         <f>IF(H17="","",H17*(1-IF(I17="",0,I17)))</f>
         <v/>
       </c>
-      <c r="K17" s="106" t="n"/>
-      <c r="L17" s="106" t="n"/>
+      <c r="K17" s="131" t="n"/>
+      <c r="L17" s="131" t="n"/>
       <c r="M17" s="35">
         <f>IF(G17="","",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1774,33 +1854,33 @@
         <f>IF(OR(J17="",M17=""),"",J17*M17)</f>
         <v/>
       </c>
-      <c r="O17" s="106" t="n"/>
+      <c r="O17" s="131" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="89">
         <f>IF(B18="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B18" s="38" t="n"/>
+      <c r="B18" s="134" t="n"/>
       <c r="C18" s="89">
         <f>IF(B18="","","Q"&amp;ROUNDUP(MONTH(B18)/3,0))</f>
         <v/>
       </c>
-      <c r="D18" s="39" t="n"/>
-      <c r="E18" s="89" t="n"/>
-      <c r="F18" s="89" t="n"/>
-      <c r="G18" s="89" t="n"/>
-      <c r="H18" s="40">
+      <c r="D18" s="135" t="n"/>
+      <c r="E18" s="136" t="n"/>
+      <c r="F18" s="136" t="n"/>
+      <c r="G18" s="136" t="n"/>
+      <c r="H18" s="137">
         <f>IF(G18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I18" s="41" t="n"/>
+      <c r="I18" s="138" t="n"/>
       <c r="J18" s="40">
         <f>IF(H18="","",H18*(1-IF(I18="",0,I18)))</f>
         <v/>
       </c>
-      <c r="K18" s="89" t="n"/>
-      <c r="L18" s="89" t="n"/>
+      <c r="K18" s="136" t="n"/>
+      <c r="L18" s="136" t="n"/>
       <c r="M18" s="41">
         <f>IF(G18="","",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1809,33 +1889,33 @@
         <f>IF(OR(J18="",M18=""),"",J18*M18)</f>
         <v/>
       </c>
-      <c r="O18" s="89" t="n"/>
+      <c r="O18" s="136" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="106">
         <f>IF(B19="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B19" s="105" t="n"/>
+      <c r="B19" s="129" t="n"/>
       <c r="C19" s="106">
         <f>IF(B19="","","Q"&amp;ROUNDUP(MONTH(B19)/3,0))</f>
         <v/>
       </c>
-      <c r="D19" s="107" t="n"/>
-      <c r="E19" s="106" t="n"/>
-      <c r="F19" s="106" t="n"/>
-      <c r="G19" s="106" t="n"/>
-      <c r="H19" s="108">
+      <c r="D19" s="130" t="n"/>
+      <c r="E19" s="131" t="n"/>
+      <c r="F19" s="131" t="n"/>
+      <c r="G19" s="131" t="n"/>
+      <c r="H19" s="132">
         <f>IF(G19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I19" s="35" t="n"/>
+      <c r="I19" s="133" t="n"/>
       <c r="J19" s="108">
         <f>IF(H19="","",H19*(1-IF(I19="",0,I19)))</f>
         <v/>
       </c>
-      <c r="K19" s="106" t="n"/>
-      <c r="L19" s="106" t="n"/>
+      <c r="K19" s="131" t="n"/>
+      <c r="L19" s="131" t="n"/>
       <c r="M19" s="35">
         <f>IF(G19="","",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1844,33 +1924,33 @@
         <f>IF(OR(J19="",M19=""),"",J19*M19)</f>
         <v/>
       </c>
-      <c r="O19" s="106" t="n"/>
+      <c r="O19" s="131" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="89">
         <f>IF(B20="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B20" s="38" t="n"/>
+      <c r="B20" s="134" t="n"/>
       <c r="C20" s="89">
         <f>IF(B20="","","Q"&amp;ROUNDUP(MONTH(B20)/3,0))</f>
         <v/>
       </c>
-      <c r="D20" s="39" t="n"/>
-      <c r="E20" s="89" t="n"/>
-      <c r="F20" s="89" t="n"/>
-      <c r="G20" s="89" t="n"/>
-      <c r="H20" s="40">
+      <c r="D20" s="135" t="n"/>
+      <c r="E20" s="136" t="n"/>
+      <c r="F20" s="136" t="n"/>
+      <c r="G20" s="136" t="n"/>
+      <c r="H20" s="137">
         <f>IF(G20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I20" s="41" t="n"/>
+      <c r="I20" s="138" t="n"/>
       <c r="J20" s="40">
         <f>IF(H20="","",H20*(1-IF(I20="",0,I20)))</f>
         <v/>
       </c>
-      <c r="K20" s="89" t="n"/>
-      <c r="L20" s="89" t="n"/>
+      <c r="K20" s="136" t="n"/>
+      <c r="L20" s="136" t="n"/>
       <c r="M20" s="41">
         <f>IF(G20="","",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1879,33 +1959,33 @@
         <f>IF(OR(J20="",M20=""),"",J20*M20)</f>
         <v/>
       </c>
-      <c r="O20" s="89" t="n"/>
+      <c r="O20" s="136" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="106">
         <f>IF(B21="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B21" s="105" t="n"/>
+      <c r="B21" s="129" t="n"/>
       <c r="C21" s="106">
         <f>IF(B21="","","Q"&amp;ROUNDUP(MONTH(B21)/3,0))</f>
         <v/>
       </c>
-      <c r="D21" s="107" t="n"/>
-      <c r="E21" s="106" t="n"/>
-      <c r="F21" s="106" t="n"/>
-      <c r="G21" s="106" t="n"/>
-      <c r="H21" s="108">
+      <c r="D21" s="130" t="n"/>
+      <c r="E21" s="131" t="n"/>
+      <c r="F21" s="131" t="n"/>
+      <c r="G21" s="131" t="n"/>
+      <c r="H21" s="132">
         <f>IF(G21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I21" s="35" t="n"/>
+      <c r="I21" s="133" t="n"/>
       <c r="J21" s="108">
         <f>IF(H21="","",H21*(1-IF(I21="",0,I21)))</f>
         <v/>
       </c>
-      <c r="K21" s="106" t="n"/>
-      <c r="L21" s="106" t="n"/>
+      <c r="K21" s="131" t="n"/>
+      <c r="L21" s="131" t="n"/>
       <c r="M21" s="35">
         <f>IF(G21="","",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1914,33 +1994,33 @@
         <f>IF(OR(J21="",M21=""),"",J21*M21)</f>
         <v/>
       </c>
-      <c r="O21" s="106" t="n"/>
+      <c r="O21" s="131" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="89">
         <f>IF(B22="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B22" s="38" t="n"/>
+      <c r="B22" s="134" t="n"/>
       <c r="C22" s="89">
         <f>IF(B22="","","Q"&amp;ROUNDUP(MONTH(B22)/3,0))</f>
         <v/>
       </c>
-      <c r="D22" s="39" t="n"/>
-      <c r="E22" s="89" t="n"/>
-      <c r="F22" s="89" t="n"/>
-      <c r="G22" s="89" t="n"/>
-      <c r="H22" s="40">
+      <c r="D22" s="135" t="n"/>
+      <c r="E22" s="136" t="n"/>
+      <c r="F22" s="136" t="n"/>
+      <c r="G22" s="136" t="n"/>
+      <c r="H22" s="137">
         <f>IF(G22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I22" s="41" t="n"/>
+      <c r="I22" s="138" t="n"/>
       <c r="J22" s="40">
         <f>IF(H22="","",H22*(1-IF(I22="",0,I22)))</f>
         <v/>
       </c>
-      <c r="K22" s="89" t="n"/>
-      <c r="L22" s="89" t="n"/>
+      <c r="K22" s="136" t="n"/>
+      <c r="L22" s="136" t="n"/>
       <c r="M22" s="41">
         <f>IF(G22="","",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1949,33 +2029,33 @@
         <f>IF(OR(J22="",M22=""),"",J22*M22)</f>
         <v/>
       </c>
-      <c r="O22" s="89" t="n"/>
+      <c r="O22" s="136" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="106">
         <f>IF(B23="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B23" s="105" t="n"/>
+      <c r="B23" s="129" t="n"/>
       <c r="C23" s="106">
         <f>IF(B23="","","Q"&amp;ROUNDUP(MONTH(B23)/3,0))</f>
         <v/>
       </c>
-      <c r="D23" s="107" t="n"/>
-      <c r="E23" s="106" t="n"/>
-      <c r="F23" s="106" t="n"/>
-      <c r="G23" s="106" t="n"/>
-      <c r="H23" s="108">
+      <c r="D23" s="130" t="n"/>
+      <c r="E23" s="131" t="n"/>
+      <c r="F23" s="131" t="n"/>
+      <c r="G23" s="131" t="n"/>
+      <c r="H23" s="132">
         <f>IF(G23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I23" s="35" t="n"/>
+      <c r="I23" s="133" t="n"/>
       <c r="J23" s="108">
         <f>IF(H23="","",H23*(1-IF(I23="",0,I23)))</f>
         <v/>
       </c>
-      <c r="K23" s="106" t="n"/>
-      <c r="L23" s="106" t="n"/>
+      <c r="K23" s="131" t="n"/>
+      <c r="L23" s="131" t="n"/>
       <c r="M23" s="35">
         <f>IF(G23="","",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -1984,33 +2064,33 @@
         <f>IF(OR(J23="",M23=""),"",J23*M23)</f>
         <v/>
       </c>
-      <c r="O23" s="106" t="n"/>
+      <c r="O23" s="131" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="89">
         <f>IF(B24="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B24" s="38" t="n"/>
+      <c r="B24" s="134" t="n"/>
       <c r="C24" s="89">
         <f>IF(B24="","","Q"&amp;ROUNDUP(MONTH(B24)/3,0))</f>
         <v/>
       </c>
-      <c r="D24" s="39" t="n"/>
-      <c r="E24" s="89" t="n"/>
-      <c r="F24" s="89" t="n"/>
-      <c r="G24" s="89" t="n"/>
-      <c r="H24" s="40">
+      <c r="D24" s="135" t="n"/>
+      <c r="E24" s="136" t="n"/>
+      <c r="F24" s="136" t="n"/>
+      <c r="G24" s="136" t="n"/>
+      <c r="H24" s="137">
         <f>IF(G24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I24" s="41" t="n"/>
+      <c r="I24" s="138" t="n"/>
       <c r="J24" s="40">
         <f>IF(H24="","",H24*(1-IF(I24="",0,I24)))</f>
         <v/>
       </c>
-      <c r="K24" s="89" t="n"/>
-      <c r="L24" s="89" t="n"/>
+      <c r="K24" s="136" t="n"/>
+      <c r="L24" s="136" t="n"/>
       <c r="M24" s="41">
         <f>IF(G24="","",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2019,33 +2099,33 @@
         <f>IF(OR(J24="",M24=""),"",J24*M24)</f>
         <v/>
       </c>
-      <c r="O24" s="89" t="n"/>
+      <c r="O24" s="136" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="106">
         <f>IF(B25="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B25" s="105" t="n"/>
+      <c r="B25" s="129" t="n"/>
       <c r="C25" s="106">
         <f>IF(B25="","","Q"&amp;ROUNDUP(MONTH(B25)/3,0))</f>
         <v/>
       </c>
-      <c r="D25" s="107" t="n"/>
-      <c r="E25" s="106" t="n"/>
-      <c r="F25" s="106" t="n"/>
-      <c r="G25" s="106" t="n"/>
-      <c r="H25" s="108">
+      <c r="D25" s="130" t="n"/>
+      <c r="E25" s="131" t="n"/>
+      <c r="F25" s="131" t="n"/>
+      <c r="G25" s="131" t="n"/>
+      <c r="H25" s="132">
         <f>IF(G25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I25" s="35" t="n"/>
+      <c r="I25" s="133" t="n"/>
       <c r="J25" s="108">
         <f>IF(H25="","",H25*(1-IF(I25="",0,I25)))</f>
         <v/>
       </c>
-      <c r="K25" s="106" t="n"/>
-      <c r="L25" s="106" t="n"/>
+      <c r="K25" s="131" t="n"/>
+      <c r="L25" s="131" t="n"/>
       <c r="M25" s="35">
         <f>IF(G25="","",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2054,33 +2134,33 @@
         <f>IF(OR(J25="",M25=""),"",J25*M25)</f>
         <v/>
       </c>
-      <c r="O25" s="106" t="n"/>
+      <c r="O25" s="131" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="89">
         <f>IF(B26="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B26" s="38" t="n"/>
+      <c r="B26" s="134" t="n"/>
       <c r="C26" s="89">
         <f>IF(B26="","","Q"&amp;ROUNDUP(MONTH(B26)/3,0))</f>
         <v/>
       </c>
-      <c r="D26" s="39" t="n"/>
-      <c r="E26" s="89" t="n"/>
-      <c r="F26" s="89" t="n"/>
-      <c r="G26" s="89" t="n"/>
-      <c r="H26" s="40">
+      <c r="D26" s="135" t="n"/>
+      <c r="E26" s="136" t="n"/>
+      <c r="F26" s="136" t="n"/>
+      <c r="G26" s="136" t="n"/>
+      <c r="H26" s="137">
         <f>IF(G26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I26" s="41" t="n"/>
+      <c r="I26" s="138" t="n"/>
       <c r="J26" s="40">
         <f>IF(H26="","",H26*(1-IF(I26="",0,I26)))</f>
         <v/>
       </c>
-      <c r="K26" s="89" t="n"/>
-      <c r="L26" s="89" t="n"/>
+      <c r="K26" s="136" t="n"/>
+      <c r="L26" s="136" t="n"/>
       <c r="M26" s="41">
         <f>IF(G26="","",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2089,33 +2169,33 @@
         <f>IF(OR(J26="",M26=""),"",J26*M26)</f>
         <v/>
       </c>
-      <c r="O26" s="89" t="n"/>
+      <c r="O26" s="136" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="106">
         <f>IF(B27="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B27" s="105" t="n"/>
+      <c r="B27" s="129" t="n"/>
       <c r="C27" s="106">
         <f>IF(B27="","","Q"&amp;ROUNDUP(MONTH(B27)/3,0))</f>
         <v/>
       </c>
-      <c r="D27" s="107" t="n"/>
-      <c r="E27" s="106" t="n"/>
-      <c r="F27" s="106" t="n"/>
-      <c r="G27" s="106" t="n"/>
-      <c r="H27" s="108">
+      <c r="D27" s="130" t="n"/>
+      <c r="E27" s="131" t="n"/>
+      <c r="F27" s="131" t="n"/>
+      <c r="G27" s="131" t="n"/>
+      <c r="H27" s="132">
         <f>IF(G27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I27" s="35" t="n"/>
+      <c r="I27" s="133" t="n"/>
       <c r="J27" s="108">
         <f>IF(H27="","",H27*(1-IF(I27="",0,I27)))</f>
         <v/>
       </c>
-      <c r="K27" s="106" t="n"/>
-      <c r="L27" s="106" t="n"/>
+      <c r="K27" s="131" t="n"/>
+      <c r="L27" s="131" t="n"/>
       <c r="M27" s="35">
         <f>IF(G27="","",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2124,33 +2204,33 @@
         <f>IF(OR(J27="",M27=""),"",J27*M27)</f>
         <v/>
       </c>
-      <c r="O27" s="106" t="n"/>
+      <c r="O27" s="131" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="89">
         <f>IF(B28="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B28" s="38" t="n"/>
+      <c r="B28" s="134" t="n"/>
       <c r="C28" s="89">
         <f>IF(B28="","","Q"&amp;ROUNDUP(MONTH(B28)/3,0))</f>
         <v/>
       </c>
-      <c r="D28" s="39" t="n"/>
-      <c r="E28" s="89" t="n"/>
-      <c r="F28" s="89" t="n"/>
-      <c r="G28" s="89" t="n"/>
-      <c r="H28" s="40">
+      <c r="D28" s="135" t="n"/>
+      <c r="E28" s="136" t="n"/>
+      <c r="F28" s="136" t="n"/>
+      <c r="G28" s="136" t="n"/>
+      <c r="H28" s="137">
         <f>IF(G28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I28" s="41" t="n"/>
+      <c r="I28" s="138" t="n"/>
       <c r="J28" s="40">
         <f>IF(H28="","",H28*(1-IF(I28="",0,I28)))</f>
         <v/>
       </c>
-      <c r="K28" s="89" t="n"/>
-      <c r="L28" s="89" t="n"/>
+      <c r="K28" s="136" t="n"/>
+      <c r="L28" s="136" t="n"/>
       <c r="M28" s="41">
         <f>IF(G28="","",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2159,33 +2239,33 @@
         <f>IF(OR(J28="",M28=""),"",J28*M28)</f>
         <v/>
       </c>
-      <c r="O28" s="89" t="n"/>
+      <c r="O28" s="136" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="106">
         <f>IF(B29="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B29" s="105" t="n"/>
+      <c r="B29" s="129" t="n"/>
       <c r="C29" s="106">
         <f>IF(B29="","","Q"&amp;ROUNDUP(MONTH(B29)/3,0))</f>
         <v/>
       </c>
-      <c r="D29" s="107" t="n"/>
-      <c r="E29" s="106" t="n"/>
-      <c r="F29" s="106" t="n"/>
-      <c r="G29" s="106" t="n"/>
-      <c r="H29" s="108">
+      <c r="D29" s="130" t="n"/>
+      <c r="E29" s="131" t="n"/>
+      <c r="F29" s="131" t="n"/>
+      <c r="G29" s="131" t="n"/>
+      <c r="H29" s="132">
         <f>IF(G29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I29" s="35" t="n"/>
+      <c r="I29" s="133" t="n"/>
       <c r="J29" s="108">
         <f>IF(H29="","",H29*(1-IF(I29="",0,I29)))</f>
         <v/>
       </c>
-      <c r="K29" s="106" t="n"/>
-      <c r="L29" s="106" t="n"/>
+      <c r="K29" s="131" t="n"/>
+      <c r="L29" s="131" t="n"/>
       <c r="M29" s="35">
         <f>IF(G29="","",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2194,33 +2274,33 @@
         <f>IF(OR(J29="",M29=""),"",J29*M29)</f>
         <v/>
       </c>
-      <c r="O29" s="106" t="n"/>
+      <c r="O29" s="131" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="89">
         <f>IF(B30="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B30" s="38" t="n"/>
+      <c r="B30" s="134" t="n"/>
       <c r="C30" s="89">
         <f>IF(B30="","","Q"&amp;ROUNDUP(MONTH(B30)/3,0))</f>
         <v/>
       </c>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="89" t="n"/>
-      <c r="F30" s="89" t="n"/>
-      <c r="G30" s="89" t="n"/>
-      <c r="H30" s="40">
+      <c r="D30" s="135" t="n"/>
+      <c r="E30" s="136" t="n"/>
+      <c r="F30" s="136" t="n"/>
+      <c r="G30" s="136" t="n"/>
+      <c r="H30" s="137">
         <f>IF(G30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I30" s="41" t="n"/>
+      <c r="I30" s="138" t="n"/>
       <c r="J30" s="40">
         <f>IF(H30="","",H30*(1-IF(I30="",0,I30)))</f>
         <v/>
       </c>
-      <c r="K30" s="89" t="n"/>
-      <c r="L30" s="89" t="n"/>
+      <c r="K30" s="136" t="n"/>
+      <c r="L30" s="136" t="n"/>
       <c r="M30" s="41">
         <f>IF(G30="","",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2229,33 +2309,33 @@
         <f>IF(OR(J30="",M30=""),"",J30*M30)</f>
         <v/>
       </c>
-      <c r="O30" s="89" t="n"/>
+      <c r="O30" s="136" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="106">
         <f>IF(B31="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B31" s="105" t="n"/>
+      <c r="B31" s="129" t="n"/>
       <c r="C31" s="106">
         <f>IF(B31="","","Q"&amp;ROUNDUP(MONTH(B31)/3,0))</f>
         <v/>
       </c>
-      <c r="D31" s="107" t="n"/>
-      <c r="E31" s="106" t="n"/>
-      <c r="F31" s="106" t="n"/>
-      <c r="G31" s="106" t="n"/>
-      <c r="H31" s="108">
+      <c r="D31" s="130" t="n"/>
+      <c r="E31" s="131" t="n"/>
+      <c r="F31" s="131" t="n"/>
+      <c r="G31" s="131" t="n"/>
+      <c r="H31" s="132">
         <f>IF(G31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I31" s="35" t="n"/>
+      <c r="I31" s="133" t="n"/>
       <c r="J31" s="108">
         <f>IF(H31="","",H31*(1-IF(I31="",0,I31)))</f>
         <v/>
       </c>
-      <c r="K31" s="106" t="n"/>
-      <c r="L31" s="106" t="n"/>
+      <c r="K31" s="131" t="n"/>
+      <c r="L31" s="131" t="n"/>
       <c r="M31" s="35">
         <f>IF(G31="","",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2264,33 +2344,33 @@
         <f>IF(OR(J31="",M31=""),"",J31*M31)</f>
         <v/>
       </c>
-      <c r="O31" s="106" t="n"/>
+      <c r="O31" s="131" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="89">
         <f>IF(B32="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B32" s="38" t="n"/>
+      <c r="B32" s="134" t="n"/>
       <c r="C32" s="89">
         <f>IF(B32="","","Q"&amp;ROUNDUP(MONTH(B32)/3,0))</f>
         <v/>
       </c>
-      <c r="D32" s="39" t="n"/>
-      <c r="E32" s="89" t="n"/>
-      <c r="F32" s="89" t="n"/>
-      <c r="G32" s="89" t="n"/>
-      <c r="H32" s="40">
+      <c r="D32" s="135" t="n"/>
+      <c r="E32" s="136" t="n"/>
+      <c r="F32" s="136" t="n"/>
+      <c r="G32" s="136" t="n"/>
+      <c r="H32" s="137">
         <f>IF(G32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I32" s="41" t="n"/>
+      <c r="I32" s="138" t="n"/>
       <c r="J32" s="40">
         <f>IF(H32="","",H32*(1-IF(I32="",0,I32)))</f>
         <v/>
       </c>
-      <c r="K32" s="89" t="n"/>
-      <c r="L32" s="89" t="n"/>
+      <c r="K32" s="136" t="n"/>
+      <c r="L32" s="136" t="n"/>
       <c r="M32" s="41">
         <f>IF(G32="","",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2299,33 +2379,33 @@
         <f>IF(OR(J32="",M32=""),"",J32*M32)</f>
         <v/>
       </c>
-      <c r="O32" s="89" t="n"/>
+      <c r="O32" s="136" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="106">
         <f>IF(B33="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B33" s="105" t="n"/>
+      <c r="B33" s="129" t="n"/>
       <c r="C33" s="106">
         <f>IF(B33="","","Q"&amp;ROUNDUP(MONTH(B33)/3,0))</f>
         <v/>
       </c>
-      <c r="D33" s="107" t="n"/>
-      <c r="E33" s="106" t="n"/>
-      <c r="F33" s="106" t="n"/>
-      <c r="G33" s="106" t="n"/>
-      <c r="H33" s="108">
+      <c r="D33" s="130" t="n"/>
+      <c r="E33" s="131" t="n"/>
+      <c r="F33" s="131" t="n"/>
+      <c r="G33" s="131" t="n"/>
+      <c r="H33" s="132">
         <f>IF(G33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I33" s="35" t="n"/>
+      <c r="I33" s="133" t="n"/>
       <c r="J33" s="108">
         <f>IF(H33="","",H33*(1-IF(I33="",0,I33)))</f>
         <v/>
       </c>
-      <c r="K33" s="106" t="n"/>
-      <c r="L33" s="106" t="n"/>
+      <c r="K33" s="131" t="n"/>
+      <c r="L33" s="131" t="n"/>
       <c r="M33" s="35">
         <f>IF(G33="","",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2334,33 +2414,33 @@
         <f>IF(OR(J33="",M33=""),"",J33*M33)</f>
         <v/>
       </c>
-      <c r="O33" s="106" t="n"/>
+      <c r="O33" s="131" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="89">
         <f>IF(B34="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B34" s="38" t="n"/>
+      <c r="B34" s="134" t="n"/>
       <c r="C34" s="89">
         <f>IF(B34="","","Q"&amp;ROUNDUP(MONTH(B34)/3,0))</f>
         <v/>
       </c>
-      <c r="D34" s="39" t="n"/>
-      <c r="E34" s="89" t="n"/>
-      <c r="F34" s="89" t="n"/>
-      <c r="G34" s="89" t="n"/>
-      <c r="H34" s="40">
+      <c r="D34" s="135" t="n"/>
+      <c r="E34" s="136" t="n"/>
+      <c r="F34" s="136" t="n"/>
+      <c r="G34" s="136" t="n"/>
+      <c r="H34" s="137">
         <f>IF(G34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I34" s="41" t="n"/>
+      <c r="I34" s="138" t="n"/>
       <c r="J34" s="40">
         <f>IF(H34="","",H34*(1-IF(I34="",0,I34)))</f>
         <v/>
       </c>
-      <c r="K34" s="89" t="n"/>
-      <c r="L34" s="89" t="n"/>
+      <c r="K34" s="136" t="n"/>
+      <c r="L34" s="136" t="n"/>
       <c r="M34" s="41">
         <f>IF(G34="","",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2369,33 +2449,33 @@
         <f>IF(OR(J34="",M34=""),"",J34*M34)</f>
         <v/>
       </c>
-      <c r="O34" s="89" t="n"/>
+      <c r="O34" s="136" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="106">
         <f>IF(B35="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B35" s="105" t="n"/>
+      <c r="B35" s="129" t="n"/>
       <c r="C35" s="106">
         <f>IF(B35="","","Q"&amp;ROUNDUP(MONTH(B35)/3,0))</f>
         <v/>
       </c>
-      <c r="D35" s="107" t="n"/>
-      <c r="E35" s="106" t="n"/>
-      <c r="F35" s="106" t="n"/>
-      <c r="G35" s="106" t="n"/>
-      <c r="H35" s="108">
+      <c r="D35" s="130" t="n"/>
+      <c r="E35" s="131" t="n"/>
+      <c r="F35" s="131" t="n"/>
+      <c r="G35" s="131" t="n"/>
+      <c r="H35" s="132">
         <f>IF(G35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I35" s="35" t="n"/>
+      <c r="I35" s="133" t="n"/>
       <c r="J35" s="108">
         <f>IF(H35="","",H35*(1-IF(I35="",0,I35)))</f>
         <v/>
       </c>
-      <c r="K35" s="106" t="n"/>
-      <c r="L35" s="106" t="n"/>
+      <c r="K35" s="131" t="n"/>
+      <c r="L35" s="131" t="n"/>
       <c r="M35" s="35">
         <f>IF(G35="","",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2404,33 +2484,33 @@
         <f>IF(OR(J35="",M35=""),"",J35*M35)</f>
         <v/>
       </c>
-      <c r="O35" s="106" t="n"/>
+      <c r="O35" s="131" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="89">
         <f>IF(B36="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B36" s="38" t="n"/>
+      <c r="B36" s="134" t="n"/>
       <c r="C36" s="89">
         <f>IF(B36="","","Q"&amp;ROUNDUP(MONTH(B36)/3,0))</f>
         <v/>
       </c>
-      <c r="D36" s="39" t="n"/>
-      <c r="E36" s="89" t="n"/>
-      <c r="F36" s="89" t="n"/>
-      <c r="G36" s="89" t="n"/>
-      <c r="H36" s="40">
+      <c r="D36" s="135" t="n"/>
+      <c r="E36" s="136" t="n"/>
+      <c r="F36" s="136" t="n"/>
+      <c r="G36" s="136" t="n"/>
+      <c r="H36" s="137">
         <f>IF(G36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I36" s="41" t="n"/>
+      <c r="I36" s="138" t="n"/>
       <c r="J36" s="40">
         <f>IF(H36="","",H36*(1-IF(I36="",0,I36)))</f>
         <v/>
       </c>
-      <c r="K36" s="89" t="n"/>
-      <c r="L36" s="89" t="n"/>
+      <c r="K36" s="136" t="n"/>
+      <c r="L36" s="136" t="n"/>
       <c r="M36" s="41">
         <f>IF(G36="","",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2439,33 +2519,33 @@
         <f>IF(OR(J36="",M36=""),"",J36*M36)</f>
         <v/>
       </c>
-      <c r="O36" s="89" t="n"/>
+      <c r="O36" s="136" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="106">
         <f>IF(B37="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B37" s="105" t="n"/>
+      <c r="B37" s="129" t="n"/>
       <c r="C37" s="106">
         <f>IF(B37="","","Q"&amp;ROUNDUP(MONTH(B37)/3,0))</f>
         <v/>
       </c>
-      <c r="D37" s="107" t="n"/>
-      <c r="E37" s="106" t="n"/>
-      <c r="F37" s="106" t="n"/>
-      <c r="G37" s="106" t="n"/>
-      <c r="H37" s="108">
+      <c r="D37" s="130" t="n"/>
+      <c r="E37" s="131" t="n"/>
+      <c r="F37" s="131" t="n"/>
+      <c r="G37" s="131" t="n"/>
+      <c r="H37" s="132">
         <f>IF(G37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I37" s="35" t="n"/>
+      <c r="I37" s="133" t="n"/>
       <c r="J37" s="108">
         <f>IF(H37="","",H37*(1-IF(I37="",0,I37)))</f>
         <v/>
       </c>
-      <c r="K37" s="106" t="n"/>
-      <c r="L37" s="106" t="n"/>
+      <c r="K37" s="131" t="n"/>
+      <c r="L37" s="131" t="n"/>
       <c r="M37" s="35">
         <f>IF(G37="","",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2474,33 +2554,33 @@
         <f>IF(OR(J37="",M37=""),"",J37*M37)</f>
         <v/>
       </c>
-      <c r="O37" s="106" t="n"/>
+      <c r="O37" s="131" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="89">
         <f>IF(B38="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B38" s="38" t="n"/>
+      <c r="B38" s="134" t="n"/>
       <c r="C38" s="89">
         <f>IF(B38="","","Q"&amp;ROUNDUP(MONTH(B38)/3,0))</f>
         <v/>
       </c>
-      <c r="D38" s="39" t="n"/>
-      <c r="E38" s="89" t="n"/>
-      <c r="F38" s="89" t="n"/>
-      <c r="G38" s="89" t="n"/>
-      <c r="H38" s="40">
+      <c r="D38" s="135" t="n"/>
+      <c r="E38" s="136" t="n"/>
+      <c r="F38" s="136" t="n"/>
+      <c r="G38" s="136" t="n"/>
+      <c r="H38" s="137">
         <f>IF(G38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I38" s="41" t="n"/>
+      <c r="I38" s="138" t="n"/>
       <c r="J38" s="40">
         <f>IF(H38="","",H38*(1-IF(I38="",0,I38)))</f>
         <v/>
       </c>
-      <c r="K38" s="89" t="n"/>
-      <c r="L38" s="89" t="n"/>
+      <c r="K38" s="136" t="n"/>
+      <c r="L38" s="136" t="n"/>
       <c r="M38" s="41">
         <f>IF(G38="","",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2509,33 +2589,33 @@
         <f>IF(OR(J38="",M38=""),"",J38*M38)</f>
         <v/>
       </c>
-      <c r="O38" s="89" t="n"/>
+      <c r="O38" s="136" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="106">
         <f>IF(B39="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B39" s="105" t="n"/>
+      <c r="B39" s="129" t="n"/>
       <c r="C39" s="106">
         <f>IF(B39="","","Q"&amp;ROUNDUP(MONTH(B39)/3,0))</f>
         <v/>
       </c>
-      <c r="D39" s="107" t="n"/>
-      <c r="E39" s="106" t="n"/>
-      <c r="F39" s="106" t="n"/>
-      <c r="G39" s="106" t="n"/>
-      <c r="H39" s="108">
+      <c r="D39" s="130" t="n"/>
+      <c r="E39" s="131" t="n"/>
+      <c r="F39" s="131" t="n"/>
+      <c r="G39" s="131" t="n"/>
+      <c r="H39" s="132">
         <f>IF(G39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I39" s="35" t="n"/>
+      <c r="I39" s="133" t="n"/>
       <c r="J39" s="108">
         <f>IF(H39="","",H39*(1-IF(I39="",0,I39)))</f>
         <v/>
       </c>
-      <c r="K39" s="106" t="n"/>
-      <c r="L39" s="106" t="n"/>
+      <c r="K39" s="131" t="n"/>
+      <c r="L39" s="131" t="n"/>
       <c r="M39" s="35">
         <f>IF(G39="","",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2544,33 +2624,33 @@
         <f>IF(OR(J39="",M39=""),"",J39*M39)</f>
         <v/>
       </c>
-      <c r="O39" s="106" t="n"/>
+      <c r="O39" s="131" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="89">
         <f>IF(B40="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B40" s="38" t="n"/>
+      <c r="B40" s="134" t="n"/>
       <c r="C40" s="89">
         <f>IF(B40="","","Q"&amp;ROUNDUP(MONTH(B40)/3,0))</f>
         <v/>
       </c>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="89" t="n"/>
-      <c r="F40" s="89" t="n"/>
-      <c r="G40" s="89" t="n"/>
-      <c r="H40" s="40">
+      <c r="D40" s="135" t="n"/>
+      <c r="E40" s="136" t="n"/>
+      <c r="F40" s="136" t="n"/>
+      <c r="G40" s="136" t="n"/>
+      <c r="H40" s="137">
         <f>IF(G40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I40" s="41" t="n"/>
+      <c r="I40" s="138" t="n"/>
       <c r="J40" s="40">
         <f>IF(H40="","",H40*(1-IF(I40="",0,I40)))</f>
         <v/>
       </c>
-      <c r="K40" s="89" t="n"/>
-      <c r="L40" s="89" t="n"/>
+      <c r="K40" s="136" t="n"/>
+      <c r="L40" s="136" t="n"/>
       <c r="M40" s="41">
         <f>IF(G40="","",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2579,33 +2659,33 @@
         <f>IF(OR(J40="",M40=""),"",J40*M40)</f>
         <v/>
       </c>
-      <c r="O40" s="89" t="n"/>
+      <c r="O40" s="136" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="106">
         <f>IF(B41="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B41" s="105" t="n"/>
+      <c r="B41" s="129" t="n"/>
       <c r="C41" s="106">
         <f>IF(B41="","","Q"&amp;ROUNDUP(MONTH(B41)/3,0))</f>
         <v/>
       </c>
-      <c r="D41" s="107" t="n"/>
-      <c r="E41" s="106" t="n"/>
-      <c r="F41" s="106" t="n"/>
-      <c r="G41" s="106" t="n"/>
-      <c r="H41" s="108">
+      <c r="D41" s="130" t="n"/>
+      <c r="E41" s="131" t="n"/>
+      <c r="F41" s="131" t="n"/>
+      <c r="G41" s="131" t="n"/>
+      <c r="H41" s="132">
         <f>IF(G41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I41" s="35" t="n"/>
+      <c r="I41" s="133" t="n"/>
       <c r="J41" s="108">
         <f>IF(H41="","",H41*(1-IF(I41="",0,I41)))</f>
         <v/>
       </c>
-      <c r="K41" s="106" t="n"/>
-      <c r="L41" s="106" t="n"/>
+      <c r="K41" s="131" t="n"/>
+      <c r="L41" s="131" t="n"/>
       <c r="M41" s="35">
         <f>IF(G41="","",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2614,33 +2694,33 @@
         <f>IF(OR(J41="",M41=""),"",J41*M41)</f>
         <v/>
       </c>
-      <c r="O41" s="106" t="n"/>
+      <c r="O41" s="131" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="89">
         <f>IF(B42="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B42" s="38" t="n"/>
+      <c r="B42" s="134" t="n"/>
       <c r="C42" s="89">
         <f>IF(B42="","","Q"&amp;ROUNDUP(MONTH(B42)/3,0))</f>
         <v/>
       </c>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="89" t="n"/>
-      <c r="F42" s="89" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="40">
+      <c r="D42" s="135" t="n"/>
+      <c r="E42" s="136" t="n"/>
+      <c r="F42" s="136" t="n"/>
+      <c r="G42" s="136" t="n"/>
+      <c r="H42" s="137">
         <f>IF(G42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I42" s="41" t="n"/>
+      <c r="I42" s="138" t="n"/>
       <c r="J42" s="40">
         <f>IF(H42="","",H42*(1-IF(I42="",0,I42)))</f>
         <v/>
       </c>
-      <c r="K42" s="89" t="n"/>
-      <c r="L42" s="89" t="n"/>
+      <c r="K42" s="136" t="n"/>
+      <c r="L42" s="136" t="n"/>
       <c r="M42" s="41">
         <f>IF(G42="","",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2649,33 +2729,33 @@
         <f>IF(OR(J42="",M42=""),"",J42*M42)</f>
         <v/>
       </c>
-      <c r="O42" s="89" t="n"/>
+      <c r="O42" s="136" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="106">
         <f>IF(B43="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B43" s="105" t="n"/>
+      <c r="B43" s="129" t="n"/>
       <c r="C43" s="106">
         <f>IF(B43="","","Q"&amp;ROUNDUP(MONTH(B43)/3,0))</f>
         <v/>
       </c>
-      <c r="D43" s="107" t="n"/>
-      <c r="E43" s="106" t="n"/>
-      <c r="F43" s="106" t="n"/>
-      <c r="G43" s="106" t="n"/>
-      <c r="H43" s="108">
+      <c r="D43" s="130" t="n"/>
+      <c r="E43" s="131" t="n"/>
+      <c r="F43" s="131" t="n"/>
+      <c r="G43" s="131" t="n"/>
+      <c r="H43" s="132">
         <f>IF(G43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I43" s="35" t="n"/>
+      <c r="I43" s="133" t="n"/>
       <c r="J43" s="108">
         <f>IF(H43="","",H43*(1-IF(I43="",0,I43)))</f>
         <v/>
       </c>
-      <c r="K43" s="106" t="n"/>
-      <c r="L43" s="106" t="n"/>
+      <c r="K43" s="131" t="n"/>
+      <c r="L43" s="131" t="n"/>
       <c r="M43" s="35">
         <f>IF(G43="","",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2684,33 +2764,33 @@
         <f>IF(OR(J43="",M43=""),"",J43*M43)</f>
         <v/>
       </c>
-      <c r="O43" s="106" t="n"/>
+      <c r="O43" s="131" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="89">
         <f>IF(B44="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B44" s="38" t="n"/>
+      <c r="B44" s="134" t="n"/>
       <c r="C44" s="89">
         <f>IF(B44="","","Q"&amp;ROUNDUP(MONTH(B44)/3,0))</f>
         <v/>
       </c>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="89" t="n"/>
-      <c r="F44" s="89" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="40">
+      <c r="D44" s="135" t="n"/>
+      <c r="E44" s="136" t="n"/>
+      <c r="F44" s="136" t="n"/>
+      <c r="G44" s="136" t="n"/>
+      <c r="H44" s="137">
         <f>IF(G44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I44" s="41" t="n"/>
+      <c r="I44" s="138" t="n"/>
       <c r="J44" s="40">
         <f>IF(H44="","",H44*(1-IF(I44="",0,I44)))</f>
         <v/>
       </c>
-      <c r="K44" s="89" t="n"/>
-      <c r="L44" s="89" t="n"/>
+      <c r="K44" s="136" t="n"/>
+      <c r="L44" s="136" t="n"/>
       <c r="M44" s="41">
         <f>IF(G44="","",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2719,33 +2799,33 @@
         <f>IF(OR(J44="",M44=""),"",J44*M44)</f>
         <v/>
       </c>
-      <c r="O44" s="89" t="n"/>
+      <c r="O44" s="136" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="106">
         <f>IF(B45="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B45" s="105" t="n"/>
+      <c r="B45" s="129" t="n"/>
       <c r="C45" s="106">
         <f>IF(B45="","","Q"&amp;ROUNDUP(MONTH(B45)/3,0))</f>
         <v/>
       </c>
-      <c r="D45" s="107" t="n"/>
-      <c r="E45" s="106" t="n"/>
-      <c r="F45" s="106" t="n"/>
-      <c r="G45" s="106" t="n"/>
-      <c r="H45" s="108">
+      <c r="D45" s="130" t="n"/>
+      <c r="E45" s="131" t="n"/>
+      <c r="F45" s="131" t="n"/>
+      <c r="G45" s="131" t="n"/>
+      <c r="H45" s="132">
         <f>IF(G45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I45" s="35" t="n"/>
+      <c r="I45" s="133" t="n"/>
       <c r="J45" s="108">
         <f>IF(H45="","",H45*(1-IF(I45="",0,I45)))</f>
         <v/>
       </c>
-      <c r="K45" s="106" t="n"/>
-      <c r="L45" s="106" t="n"/>
+      <c r="K45" s="131" t="n"/>
+      <c r="L45" s="131" t="n"/>
       <c r="M45" s="35">
         <f>IF(G45="","",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2754,33 +2834,33 @@
         <f>IF(OR(J45="",M45=""),"",J45*M45)</f>
         <v/>
       </c>
-      <c r="O45" s="106" t="n"/>
+      <c r="O45" s="131" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="89">
         <f>IF(B46="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B46" s="38" t="n"/>
+      <c r="B46" s="134" t="n"/>
       <c r="C46" s="89">
         <f>IF(B46="","","Q"&amp;ROUNDUP(MONTH(B46)/3,0))</f>
         <v/>
       </c>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="89" t="n"/>
-      <c r="F46" s="89" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="40">
+      <c r="D46" s="135" t="n"/>
+      <c r="E46" s="136" t="n"/>
+      <c r="F46" s="136" t="n"/>
+      <c r="G46" s="136" t="n"/>
+      <c r="H46" s="137">
         <f>IF(G46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I46" s="41" t="n"/>
+      <c r="I46" s="138" t="n"/>
       <c r="J46" s="40">
         <f>IF(H46="","",H46*(1-IF(I46="",0,I46)))</f>
         <v/>
       </c>
-      <c r="K46" s="89" t="n"/>
-      <c r="L46" s="89" t="n"/>
+      <c r="K46" s="136" t="n"/>
+      <c r="L46" s="136" t="n"/>
       <c r="M46" s="41">
         <f>IF(G46="","",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2789,33 +2869,33 @@
         <f>IF(OR(J46="",M46=""),"",J46*M46)</f>
         <v/>
       </c>
-      <c r="O46" s="89" t="n"/>
+      <c r="O46" s="136" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="106">
         <f>IF(B47="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B47" s="105" t="n"/>
+      <c r="B47" s="129" t="n"/>
       <c r="C47" s="106">
         <f>IF(B47="","","Q"&amp;ROUNDUP(MONTH(B47)/3,0))</f>
         <v/>
       </c>
-      <c r="D47" s="107" t="n"/>
-      <c r="E47" s="106" t="n"/>
-      <c r="F47" s="106" t="n"/>
-      <c r="G47" s="106" t="n"/>
-      <c r="H47" s="108">
+      <c r="D47" s="130" t="n"/>
+      <c r="E47" s="131" t="n"/>
+      <c r="F47" s="131" t="n"/>
+      <c r="G47" s="131" t="n"/>
+      <c r="H47" s="132">
         <f>IF(G47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I47" s="35" t="n"/>
+      <c r="I47" s="133" t="n"/>
       <c r="J47" s="108">
         <f>IF(H47="","",H47*(1-IF(I47="",0,I47)))</f>
         <v/>
       </c>
-      <c r="K47" s="106" t="n"/>
-      <c r="L47" s="106" t="n"/>
+      <c r="K47" s="131" t="n"/>
+      <c r="L47" s="131" t="n"/>
       <c r="M47" s="35">
         <f>IF(G47="","",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2824,33 +2904,33 @@
         <f>IF(OR(J47="",M47=""),"",J47*M47)</f>
         <v/>
       </c>
-      <c r="O47" s="106" t="n"/>
+      <c r="O47" s="131" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="89">
         <f>IF(B48="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B48" s="38" t="n"/>
+      <c r="B48" s="134" t="n"/>
       <c r="C48" s="89">
         <f>IF(B48="","","Q"&amp;ROUNDUP(MONTH(B48)/3,0))</f>
         <v/>
       </c>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="89" t="n"/>
-      <c r="F48" s="89" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="40">
+      <c r="D48" s="135" t="n"/>
+      <c r="E48" s="136" t="n"/>
+      <c r="F48" s="136" t="n"/>
+      <c r="G48" s="136" t="n"/>
+      <c r="H48" s="137">
         <f>IF(G48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I48" s="41" t="n"/>
+      <c r="I48" s="138" t="n"/>
       <c r="J48" s="40">
         <f>IF(H48="","",H48*(1-IF(I48="",0,I48)))</f>
         <v/>
       </c>
-      <c r="K48" s="89" t="n"/>
-      <c r="L48" s="89" t="n"/>
+      <c r="K48" s="136" t="n"/>
+      <c r="L48" s="136" t="n"/>
       <c r="M48" s="41">
         <f>IF(G48="","",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2859,33 +2939,33 @@
         <f>IF(OR(J48="",M48=""),"",J48*M48)</f>
         <v/>
       </c>
-      <c r="O48" s="89" t="n"/>
+      <c r="O48" s="136" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="106">
         <f>IF(B49="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B49" s="105" t="n"/>
+      <c r="B49" s="129" t="n"/>
       <c r="C49" s="106">
         <f>IF(B49="","","Q"&amp;ROUNDUP(MONTH(B49)/3,0))</f>
         <v/>
       </c>
-      <c r="D49" s="107" t="n"/>
-      <c r="E49" s="106" t="n"/>
-      <c r="F49" s="106" t="n"/>
-      <c r="G49" s="106" t="n"/>
-      <c r="H49" s="108">
+      <c r="D49" s="130" t="n"/>
+      <c r="E49" s="131" t="n"/>
+      <c r="F49" s="131" t="n"/>
+      <c r="G49" s="131" t="n"/>
+      <c r="H49" s="132">
         <f>IF(G49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I49" s="35" t="n"/>
+      <c r="I49" s="133" t="n"/>
       <c r="J49" s="108">
         <f>IF(H49="","",H49*(1-IF(I49="",0,I49)))</f>
         <v/>
       </c>
-      <c r="K49" s="106" t="n"/>
-      <c r="L49" s="106" t="n"/>
+      <c r="K49" s="131" t="n"/>
+      <c r="L49" s="131" t="n"/>
       <c r="M49" s="35">
         <f>IF(G49="","",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2894,33 +2974,33 @@
         <f>IF(OR(J49="",M49=""),"",J49*M49)</f>
         <v/>
       </c>
-      <c r="O49" s="106" t="n"/>
+      <c r="O49" s="131" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="89">
         <f>IF(B50="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B50" s="38" t="n"/>
+      <c r="B50" s="134" t="n"/>
       <c r="C50" s="89">
         <f>IF(B50="","","Q"&amp;ROUNDUP(MONTH(B50)/3,0))</f>
         <v/>
       </c>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="89" t="n"/>
-      <c r="F50" s="89" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="40">
+      <c r="D50" s="135" t="n"/>
+      <c r="E50" s="136" t="n"/>
+      <c r="F50" s="136" t="n"/>
+      <c r="G50" s="136" t="n"/>
+      <c r="H50" s="137">
         <f>IF(G50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I50" s="41" t="n"/>
+      <c r="I50" s="138" t="n"/>
       <c r="J50" s="40">
         <f>IF(H50="","",H50*(1-IF(I50="",0,I50)))</f>
         <v/>
       </c>
-      <c r="K50" s="89" t="n"/>
-      <c r="L50" s="89" t="n"/>
+      <c r="K50" s="136" t="n"/>
+      <c r="L50" s="136" t="n"/>
       <c r="M50" s="41">
         <f>IF(G50="","",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2929,33 +3009,33 @@
         <f>IF(OR(J50="",M50=""),"",J50*M50)</f>
         <v/>
       </c>
-      <c r="O50" s="89" t="n"/>
+      <c r="O50" s="136" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="106">
         <f>IF(B51="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B51" s="105" t="n"/>
+      <c r="B51" s="129" t="n"/>
       <c r="C51" s="106">
         <f>IF(B51="","","Q"&amp;ROUNDUP(MONTH(B51)/3,0))</f>
         <v/>
       </c>
-      <c r="D51" s="107" t="n"/>
-      <c r="E51" s="106" t="n"/>
-      <c r="F51" s="106" t="n"/>
-      <c r="G51" s="106" t="n"/>
-      <c r="H51" s="108">
+      <c r="D51" s="130" t="n"/>
+      <c r="E51" s="131" t="n"/>
+      <c r="F51" s="131" t="n"/>
+      <c r="G51" s="131" t="n"/>
+      <c r="H51" s="132">
         <f>IF(G51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I51" s="35" t="n"/>
+      <c r="I51" s="133" t="n"/>
       <c r="J51" s="108">
         <f>IF(H51="","",H51*(1-IF(I51="",0,I51)))</f>
         <v/>
       </c>
-      <c r="K51" s="106" t="n"/>
-      <c r="L51" s="106" t="n"/>
+      <c r="K51" s="131" t="n"/>
+      <c r="L51" s="131" t="n"/>
       <c r="M51" s="35">
         <f>IF(G51="","",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2964,33 +3044,33 @@
         <f>IF(OR(J51="",M51=""),"",J51*M51)</f>
         <v/>
       </c>
-      <c r="O51" s="106" t="n"/>
+      <c r="O51" s="131" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="89">
         <f>IF(B52="","",ROW()-12)</f>
         <v/>
       </c>
-      <c r="B52" s="38" t="n"/>
+      <c r="B52" s="134" t="n"/>
       <c r="C52" s="89">
         <f>IF(B52="","","Q"&amp;ROUNDUP(MONTH(B52)/3,0))</f>
         <v/>
       </c>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="89" t="n"/>
-      <c r="F52" s="89" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="40">
+      <c r="D52" s="135" t="n"/>
+      <c r="E52" s="136" t="n"/>
+      <c r="F52" s="136" t="n"/>
+      <c r="G52" s="136" t="n"/>
+      <c r="H52" s="137">
         <f>IF(G52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
-      <c r="I52" s="41" t="n"/>
+      <c r="I52" s="138" t="n"/>
       <c r="J52" s="40">
         <f>IF(H52="","",H52*(1-IF(I52="",0,I52)))</f>
         <v/>
       </c>
-      <c r="K52" s="89" t="n"/>
-      <c r="L52" s="89" t="n"/>
+      <c r="K52" s="136" t="n"/>
+      <c r="L52" s="136" t="n"/>
       <c r="M52" s="41">
         <f>IF(G52="","",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
@@ -2999,7 +3079,7 @@
         <f>IF(OR(J52="",M52=""),"",J52*M52)</f>
         <v/>
       </c>
-      <c r="O52" s="89" t="n"/>
+      <c r="O52" s="136" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="43" t="n"/>
@@ -3033,7 +3113,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="128" t="inlineStr">
         <is>
-          <t>หมายเหตุ / วิธีใช้ — แท็บนี้คือที่กรอกดีลขายจริง</t>
+          <t>หมายเหตุ / วิธีใช้ — แท็บนี้ใช้บันทึกดีลขายจริง</t>
         </is>
       </c>
       <c r="B55" s="126" t="n"/>
@@ -3048,40 +3128,48 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="127" t="inlineStr">
         <is>
-          <t>•  กรอกช่องขาว: วันที่ · ชื่อลูกค้า · ประเภท (ใหม่/ต่ออายุ) · การชำระเงิน · แพ็กเกจ · ส่วนลด% · จ่ายแบบ · Sales · สถานะจ่าย</t>
+          <t>• กรอกช่อง: วันที่ · ชื่อลูกค้า · ประเภท (ใหม่/ต่ออายุ) · การชำระเงิน · แพ็กเกจ · ส่วนลด% · จ่ายแบบ · Sales · สถานะจ่าย</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="127" t="inlineStr">
         <is>
-          <t>•  ช่องที่เหลือคิดเองอัตโนมัติ: No · ไตรมาส · ราคาเต็ม · รายได้สุทธิ · Rate% · ค่าคอม</t>
+          <t>• ช่องที่เหลือคำนวณอัตโนมัติ: No · ไตรมาส · ราคาเต็ม · รายได้สุทธิ · Rate% · ค่าคอม</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="127" t="inlineStr">
         <is>
-          <t>•  จ่ายแบบ 'รายคน' → ใส่ชื่อในช่อง Sales (คนนั้นได้ค่าคอมเต็มตามเรตแพ็กเกจ)</t>
+          <t>• จ่ายแบบ 'รายคน' → ใส่ชื่อในช่อง Sales (คนนั้นจะได้รับค่าคอมเต็มตามเรตแพ็กเกจ)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="127" t="inlineStr">
         <is>
-          <t>•  จ่ายแบบ 'ทีม' → เว้นช่อง Sales ว่าง (ค่าคอมหารทีมตาม %แบ่งทีม รวม 100%)</t>
+          <t>• จ่ายแบบ 'ทีม' → เว้นช่อง Sales ว่าง (ค่าคอมจะถูกแบ่งตาม %แบ่งทีม รวม 100%)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="127" t="inlineStr">
         <is>
-          <t>•  Enterprise: พิมพ์ราคาจริงทับช่อง 'ราคาเต็ม' ได้เลย</t>
+          <t>• Enterprise: พิมพ์ราคาจริงทับช่อง 'ราคาเต็ม' ได้เลย</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="139" t="inlineStr">
+        <is>
+          <t>• ช่องที่คำนวณถูกล็อกเพื่อป้องกันการแก้ไขผิดพลาด · ราคาเต็ม (Enterprise) สามารถพิมพ์ทับได้ · ปลดล็อก: Review ▸ Unprotect Sheet (ไม่มีรหัส)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="28">
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="O11"/>
@@ -3107,6 +3195,7 @@
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A61:I61"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="L1:O1"/>
   </mergeCells>
@@ -3140,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3176,7 +3265,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="114" t="inlineStr">
         <is>
-          <t>เพิ่ม/แก้รายชื่อได้เลย · 'รายคน' ได้ค่าคอมเต็มตามเรตแพ็กเกจ (แท็บ Rate) · 'ทีม' หารพูลค่าคอมตาม % แบ่งทีม (ควรรวม=100%) · เลือกจ่ายแบบไหนต่อดีลในแท็บ Sales_Record</t>
+          <t>เพิ่ม/แก้รายชื่อได้เลย · 'รายคน' จะได้รับค่าคอมเต็มตามเรตแพ็กเกจ (แท็บ Rate) · 'ทีม' จะหารค่าคอมตาม % แบ่งทีม (ควรรวม = 100%) · เลือกจ่ายแบบไหนต่อดีลในแท็บ Sales_Record</t>
         </is>
       </c>
     </row>
@@ -3224,17 +3313,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="115" t="inlineStr">
+      <c r="A6" s="140" t="inlineStr">
         <is>
           <t>MIZTEEN</t>
         </is>
       </c>
-      <c r="B6" s="116" t="inlineStr">
+      <c r="B6" s="141" t="inlineStr">
         <is>
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C6" s="117" t="n">
+      <c r="C6" s="142" t="n">
         <v>0.5</v>
       </c>
       <c r="D6" s="118">
@@ -3259,17 +3348,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="115" t="inlineStr">
+      <c r="A7" s="140" t="inlineStr">
         <is>
           <t>OLIVE</t>
         </is>
       </c>
-      <c r="B7" s="116" t="inlineStr">
+      <c r="B7" s="141" t="inlineStr">
         <is>
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C7" s="117" t="n">
+      <c r="C7" s="142" t="n">
         <v>0.3</v>
       </c>
       <c r="D7" s="118">
@@ -3294,17 +3383,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="115" t="inlineStr">
+      <c r="A8" s="140" t="inlineStr">
         <is>
           <t>SUPPORT</t>
         </is>
       </c>
-      <c r="B8" s="116" t="inlineStr">
+      <c r="B8" s="141" t="inlineStr">
         <is>
           <t>Support / Sales</t>
         </is>
       </c>
-      <c r="C8" s="117" t="n">
+      <c r="C8" s="142" t="n">
         <v>0.2</v>
       </c>
       <c r="D8" s="118">
@@ -3329,9 +3418,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="115" t="inlineStr"/>
-      <c r="B9" s="116" t="inlineStr"/>
-      <c r="C9" s="117" t="n"/>
+      <c r="A9" s="140" t="inlineStr"/>
+      <c r="B9" s="141" t="inlineStr"/>
+      <c r="C9" s="142" t="n"/>
       <c r="D9" s="118">
         <f>IF($A9="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3354,9 +3443,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="115" t="inlineStr"/>
-      <c r="B10" s="116" t="inlineStr"/>
-      <c r="C10" s="117" t="n"/>
+      <c r="A10" s="140" t="inlineStr"/>
+      <c r="B10" s="141" t="inlineStr"/>
+      <c r="C10" s="142" t="n"/>
       <c r="D10" s="118">
         <f>IF($A10="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3379,9 +3468,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="115" t="inlineStr"/>
-      <c r="B11" s="116" t="inlineStr"/>
-      <c r="C11" s="117" t="n"/>
+      <c r="A11" s="140" t="inlineStr"/>
+      <c r="B11" s="141" t="inlineStr"/>
+      <c r="C11" s="142" t="n"/>
       <c r="D11" s="118">
         <f>IF($A11="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3404,9 +3493,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="115" t="inlineStr"/>
-      <c r="B12" s="116" t="inlineStr"/>
-      <c r="C12" s="117" t="n"/>
+      <c r="A12" s="140" t="inlineStr"/>
+      <c r="B12" s="141" t="inlineStr"/>
+      <c r="C12" s="142" t="n"/>
       <c r="D12" s="118">
         <f>IF($A12="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3429,9 +3518,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="115" t="inlineStr"/>
-      <c r="B13" s="116" t="inlineStr"/>
-      <c r="C13" s="117" t="n"/>
+      <c r="A13" s="140" t="inlineStr"/>
+      <c r="B13" s="141" t="inlineStr"/>
+      <c r="C13" s="142" t="n"/>
       <c r="D13" s="118">
         <f>IF($A13="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3454,9 +3543,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="115" t="inlineStr"/>
-      <c r="B14" s="116" t="inlineStr"/>
-      <c r="C14" s="117" t="n"/>
+      <c r="A14" s="140" t="inlineStr"/>
+      <c r="B14" s="141" t="inlineStr"/>
+      <c r="C14" s="142" t="n"/>
       <c r="D14" s="118">
         <f>IF($A14="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3479,9 +3568,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="115" t="inlineStr"/>
-      <c r="B15" s="116" t="inlineStr"/>
-      <c r="C15" s="117" t="n"/>
+      <c r="A15" s="140" t="inlineStr"/>
+      <c r="B15" s="141" t="inlineStr"/>
+      <c r="C15" s="142" t="n"/>
       <c r="D15" s="118">
         <f>IF($A15="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3504,9 +3593,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="115" t="inlineStr"/>
-      <c r="B16" s="116" t="inlineStr"/>
-      <c r="C16" s="117" t="n"/>
+      <c r="A16" s="140" t="inlineStr"/>
+      <c r="B16" s="141" t="inlineStr"/>
+      <c r="C16" s="142" t="n"/>
       <c r="D16" s="118">
         <f>IF($A16="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3529,9 +3618,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="115" t="inlineStr"/>
-      <c r="B17" s="116" t="inlineStr"/>
-      <c r="C17" s="117" t="n"/>
+      <c r="A17" s="140" t="inlineStr"/>
+      <c r="B17" s="141" t="inlineStr"/>
+      <c r="C17" s="142" t="n"/>
       <c r="D17" s="118">
         <f>IF($A17="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3554,9 +3643,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="115" t="inlineStr"/>
-      <c r="B18" s="116" t="inlineStr"/>
-      <c r="C18" s="117" t="n"/>
+      <c r="A18" s="140" t="inlineStr"/>
+      <c r="B18" s="141" t="inlineStr"/>
+      <c r="C18" s="142" t="n"/>
       <c r="D18" s="118">
         <f>IF($A18="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3579,9 +3668,9 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="115" t="inlineStr"/>
-      <c r="B19" s="116" t="inlineStr"/>
-      <c r="C19" s="117" t="n"/>
+      <c r="A19" s="140" t="inlineStr"/>
+      <c r="B19" s="141" t="inlineStr"/>
+      <c r="C19" s="142" t="n"/>
       <c r="D19" s="118">
         <f>IF($A19="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3604,9 +3693,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="115" t="inlineStr"/>
-      <c r="B20" s="116" t="inlineStr"/>
-      <c r="C20" s="117" t="n"/>
+      <c r="A20" s="140" t="inlineStr"/>
+      <c r="B20" s="141" t="inlineStr"/>
+      <c r="C20" s="142" t="n"/>
       <c r="D20" s="118">
         <f>IF($A20="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
         <v/>
@@ -3675,33 +3764,41 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="127" t="inlineStr">
         <is>
-          <t>•  กรอกเอง 3 ช่อง: ชื่อ Sales · ตำแหน่ง · %แบ่งทีม (รวมทุกคน = 100%)</t>
+          <t>• กรอก 3 ช่อง: ชื่อ Sales · ตำแหน่ง · %แบ่งทีม (รวมทั้งหมด = 100%)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="127" t="inlineStr">
         <is>
-          <t>•  ดีลปิดเอง · รายได้ · ค่าคอมรวม · จ่ายแล้ว · ค้างจ่าย → คิดเองจากแท็บ Sales_Record</t>
+          <t>• ดีลที่ปิดเอง · รายได้ · ค่าคอมรวม · จ่ายแล้ว · ค้างจ่าย → คำนวณจากแท็บ Sales_Record</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="127" t="inlineStr">
         <is>
-          <t>•  %แบ่งทีม ใช้เฉพาะดีลที่เลือกจ่าย 'ทีม' · ดีลรายคนไม่ใช้</t>
+          <t>• %แบ่งทีม ใช้เฉพาะดีลที่เลือกจ่าย 'ทีม' · ไม่ใช้กับดีลรายคน</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="127" t="inlineStr">
         <is>
-          <t>•  ชื่อในนี้ = ตัวเลือกดรอปดาวน์ Sales ในแท็บ Sales_Record</t>
+          <t>• ชื่อในนี้คือตัวเลือกดรอปดาวน์ Sales ในแท็บ Sales_Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="139" t="inlineStr">
+        <is>
+          <t>• ช่องที่คำนวณถูกล็อก · กรอกได้เฉพาะ ชื่อ/ตำแหน่ง/%แบ่งทีม · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="11">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A3:H3"/>
@@ -3710,6 +3807,7 @@
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="C1:H1"/>
   </mergeCells>
@@ -3723,7 +3821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3744,7 +3842,7 @@
     <row r="2">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>ราคาก่อน VAT 7% · ต่ออายุ = ครึ่งของอัตราใหม่ · แก้ตัวเลขที่นี่ที่เดียว ตาราง Sales_Record ดึงไปคำนวณอัตโนมัติ</t>
+          <t>ราคาก่อน VAT 7% · ต่ออายุ = ครึ่งของอัตราใหม่ · แก้ตัวเลขที่นี่ที่เดียว ตาราง Sales_Record จะดึงไปคำนวณอัตโนมัติ</t>
         </is>
       </c>
     </row>
@@ -3786,17 +3884,17 @@
           <t>Starter</t>
         </is>
       </c>
-      <c r="B4" s="50" t="n">
+      <c r="B4" s="143" t="n">
         <v>15588</v>
       </c>
-      <c r="C4" s="51" t="n">
+      <c r="C4" s="144" t="n">
         <v>0.1</v>
       </c>
       <c r="D4" s="50">
         <f>B4*C4</f>
         <v/>
       </c>
-      <c r="E4" s="51" t="n">
+      <c r="E4" s="144" t="n">
         <v>0.05</v>
       </c>
       <c r="F4" s="50">
@@ -3810,17 +3908,17 @@
           <t>Plus</t>
         </is>
       </c>
-      <c r="B5" s="53" t="n">
+      <c r="B5" s="145" t="n">
         <v>23988</v>
       </c>
-      <c r="C5" s="54" t="n">
+      <c r="C5" s="146" t="n">
         <v>0.12</v>
       </c>
       <c r="D5" s="53">
         <f>B5*C5</f>
         <v/>
       </c>
-      <c r="E5" s="54" t="n">
+      <c r="E5" s="146" t="n">
         <v>0.06</v>
       </c>
       <c r="F5" s="53">
@@ -3834,17 +3932,17 @@
           <t>Premium</t>
         </is>
       </c>
-      <c r="B6" s="50" t="n">
+      <c r="B6" s="143" t="n">
         <v>35988</v>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="144" t="n">
         <v>0.15</v>
       </c>
       <c r="D6" s="50">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="144" t="n">
         <v>0.075</v>
       </c>
       <c r="F6" s="50">
@@ -3858,19 +3956,19 @@
           <t>Enterprise</t>
         </is>
       </c>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="147" t="inlineStr">
         <is>
           <t>ตามดีลจริง</t>
         </is>
       </c>
-      <c r="C7" s="54" t="n">
+      <c r="C7" s="146" t="n">
         <v>0.1</v>
       </c>
       <c r="D7" s="53">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="54" t="n">
+      <c r="E7" s="146" t="n">
         <v>0.05</v>
       </c>
       <c r="F7" s="53">
@@ -3921,25 +4019,34 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="127" t="inlineStr">
         <is>
-          <t>•  แก้ % ค่าคอมที่นี่ที่เดียว · แท็บ Sales_Record ดึงไปคิดอัตโนมัติ</t>
+          <t>• แก้ % ค่าคอมที่นี่ที่เดียว · แท็บ Sales_Record จะดึงไปคำนวณอัตโนมัติ</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="127" t="inlineStr">
         <is>
-          <t>•  ดีลใหม่ใช้ '% ค่าคอม (ใหม่)' · ต่ออายุใช้ '% ต่ออายุ'</t>
+          <t>• ดีลใหม่ใช้ '% ค่าคอม (ใหม่)' · ต่ออายุใช้ '% ต่ออายุ'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="139" t="inlineStr">
+        <is>
+          <t>• ช่องที่คำนวณ (ค่าคอม/ดีล) ถูกล็อก · แก้ได้เฉพาะราคา/% · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="9">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A15:F15"/>
   </mergeCells>
@@ -3953,7 +4060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3991,7 +4098,7 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="114" t="inlineStr">
         <is>
-          <t>ดึงอัตโนมัติจากแท็บ Sales_Record · กรอกดีลในแท็บนั้น รายการตรงนี้ขึ้นเอง แล้วรวมยอดท้ายตาราง</t>
+          <t>ดึงข้อมูลอัตโนมัติจากแท็บ Sales_Record · กรอกดีลในแท็บนั้น รายการตรงนี้จะขึ้นเอง และรวมยอดท้ายตาราง</t>
         </is>
       </c>
     </row>
@@ -5767,26 +5874,34 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="127" t="inlineStr">
         <is>
-          <t>•  ดึงทุกดีลจากแท็บ Sales_Record อัตโนมัติ — ไม่ต้องกรอกที่นี่</t>
+          <t>• ดึงข้อมูลทุกดีลจากแท็บ Sales_Record อัตโนมัติ — ไม่ต้องกรอกที่นี่</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="127" t="inlineStr">
         <is>
-          <t>•  รายได้สุทธิ = ราคาเต็ม × (1 − ส่วนลด%)</t>
+          <t>• รายได้สุทธิ = ราคาเต็ม × (1 − ส่วนลด%)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="127" t="inlineStr">
         <is>
-          <t>•  แถวล่างสุด = รวมราคาเต็ม · จำนวนดีล · รวมรายได้สุทธิ</t>
+          <t>• แถวล่างสุด = รวมราคาเต็ม · จำนวนดีล · รวมรายได้สุทธิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="139" t="inlineStr">
+        <is>
+          <t>• ทั้งแผ่นเป็นช่องคำนวณ ล็อกไว้ทั้งหมด (ไม่ต้องกรอก) · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="10">
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A51:F51"/>
@@ -5796,6 +5911,7 @@
     <mergeCell ref="C2:J2"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A53:F53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5807,7 +5923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G26"/>
+  <dimension ref="B1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6297,29 +6413,38 @@
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="127" t="inlineStr">
         <is>
-          <t>•  สรุปค่าคอมรายคน คิดเองจาก Sales_Record + ทีมขาย — ไม่ต้องกรอก</t>
+          <t>• สรุปค่าคอมรายคน คำนวณจาก Sales_Record + ทีมขาย — ไม่ต้องกรอก</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="127" t="inlineStr">
         <is>
-          <t>•  ค่าคอม = งานที่ปิดเอง (รายคน) + ส่วนแบ่งจากดีลทีม</t>
+          <t>• ค่าคอม = งานที่ปิดเอง (รายคน) + ส่วนแบ่งจากดีลทีม</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="B26" s="127" t="inlineStr">
         <is>
-          <t>•  เพิ่มคนในแท็บทีมขาย รายงานนี้จะขึ้นตามเอง</t>
+          <t>• เพิ่มคนในแท็บทีมขาย รายงานนี้จะแสดงตามเอง</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="139" t="inlineStr">
+        <is>
+          <t>• ทั้งแผ่นคำนวณอัตโนมัติ ล็อกไว้ทั้งหมด · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <mergeCells count="7">
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B25:G25"/>

--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;฿&quot;"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -201,8 +201,20 @@
       <color rgb="00B5791E"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005A6673"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002A3642"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -302,6 +314,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAEDF0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00666666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F4F4"/>
       </patternFill>
     </fill>
   </fills>
@@ -523,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -953,6 +985,103 @@
     <xf numFmtId="166" fontId="5" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="16" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="14" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="31" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1340,7 +1469,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>EASY
 CRM</t>
@@ -1369,100 +1498,101 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="149" t="inlineStr">
         <is>
           <t>รายได้ &amp; ค่าคอม รายไตรมาส (THB)</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="149" t="inlineStr">
         <is>
           <t>สรุปรายได้ (THB)</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="149" t="inlineStr">
         <is>
           <t>สรุปค่าคอมรายคน (THB)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="150" t="inlineStr">
         <is>
           <t>ทั้งปี</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="150" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="150" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="150" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="150" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="150" t="inlineStr">
         <is>
           <t>ยอดเต็ม</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="150" t="inlineStr">
         <is>
           <t>ส่วนลด</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="150" t="inlineStr">
         <is>
           <t>สุทธิ</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="150" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="150">
         <f>'ทีมขาย'!A6</f>
         <v/>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="150">
         <f>'ทีมขาย'!A7</f>
         <v/>
       </c>
-      <c r="O5" s="11">
+      <c r="O5" s="150">
         <f>'ทีมขาย'!A8</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="12">
+      <c r="A6" s="151">
         <f>SUM(J13:J52)</f>
         <v/>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="151">
         <f>SUMIF(C13:C52,"Q1",J13:J52)</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="151">
         <f>SUMIF(C13:C52,"Q2",J13:J52)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="151">
         <f>SUMIF(C13:C52,"Q3",J13:J52)</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="151">
         <f>SUMIF(C13:C52,"Q4",J13:J52)</f>
         <v/>
       </c>
@@ -1474,11 +1604,11 @@
         <f>SUM(H13:H52)-SUM(J13:J52)</f>
         <v/>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="151">
         <f>SUM(J13:J52)</f>
         <v/>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="151">
         <f>SUM(N13:N52)</f>
         <v/>
       </c>
@@ -1496,41 +1626,41 @@
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="152" t="inlineStr">
         <is>
           <t>ค่าคอม รวมทั้งปี</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="151">
         <f>SUMIF(C13:C52,"Q1",N13:N52)</f>
         <v/>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="151">
         <f>SUMIF(C13:C52,"Q2",N13:N52)</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="151">
         <f>SUMIF(C13:C52,"Q3",N13:N52)</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="151">
         <f>SUMIF(C13:C52,"Q4",N13:N52)</f>
         <v/>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G7" s="153" t="inlineStr">
         <is>
           <t>จำนวนดีลทั้งหมด</t>
         </is>
       </c>
       <c r="H7" s="70" t="n"/>
       <c r="I7" s="18" t="n"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="154" t="inlineStr">
         <is>
           <t>จ่ายแล้ว</t>
         </is>
       </c>
       <c r="M7" s="18" t="n"/>
-      <c r="N7" s="19" t="inlineStr">
+      <c r="N7" s="179" t="inlineStr">
         <is>
           <t>ค้างจ่าย</t>
         </is>
@@ -1538,7 +1668,7 @@
       <c r="O7" s="18" t="n"/>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="14">
+      <c r="A8" s="151">
         <f>SUM(N13:N52)</f>
         <v/>
       </c>
@@ -1548,49 +1678,51 @@
       </c>
       <c r="H8" s="70" t="n"/>
       <c r="I8" s="18" t="n"/>
-      <c r="L8" s="12">
+      <c r="L8" s="151">
         <f>SUMIF(O13:O52,"จ่ายแล้ว",N13:N52)</f>
         <v/>
       </c>
       <c r="M8" s="18" t="n"/>
-      <c r="N8" s="20">
+      <c r="N8" s="151">
         <f>SUM(N13:N52)-SUMIF(O13:O52,"จ่ายแล้ว",N13:N52)</f>
         <v/>
       </c>
       <c r="O8" s="18" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="156" t="inlineStr">
         <is>
           <t>บันทึก</t>
         </is>
       </c>
       <c r="B11" s="71" t="n"/>
       <c r="C11" s="72" t="n"/>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="156" t="inlineStr">
         <is>
           <t>ลูกค้า</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="156" t="inlineStr">
         <is>
           <t>ธุรกรรม</t>
         </is>
       </c>
       <c r="F11" s="72" t="n"/>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="156" t="inlineStr">
         <is>
           <t>บริการ</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H11" s="156" t="inlineStr">
         <is>
           <t>รายได้ (THB)</t>
         </is>
       </c>
       <c r="I11" s="71" t="n"/>
       <c r="J11" s="72" t="n"/>
-      <c r="K11" s="21" t="inlineStr">
+      <c r="K11" s="156" t="inlineStr">
         <is>
           <t>ค่าคอมมิชชั่น</t>
         </is>
@@ -1598,84 +1730,84 @@
       <c r="L11" s="71" t="n"/>
       <c r="M11" s="71" t="n"/>
       <c r="N11" s="72" t="n"/>
-      <c r="O11" s="21" t="inlineStr">
+      <c r="O11" s="156" t="inlineStr">
         <is>
           <t>สถานะ</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="157" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="157" t="inlineStr">
         <is>
           <t>วันที่</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="157" t="inlineStr">
         <is>
           <t>ไตรมาส</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D12" s="157" t="inlineStr">
         <is>
           <t>ชื่อลูกค้า</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr">
+      <c r="E12" s="157" t="inlineStr">
         <is>
           <t>ประเภท</t>
         </is>
       </c>
-      <c r="F12" s="28" t="inlineStr">
+      <c r="F12" s="157" t="inlineStr">
         <is>
           <t>การชำระเงิน</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="G12" s="157" t="inlineStr">
         <is>
           <t>แพ็กเกจ</t>
         </is>
       </c>
-      <c r="H12" s="29" t="inlineStr">
+      <c r="H12" s="157" t="inlineStr">
         <is>
           <t>ราคาเต็ม</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="157" t="inlineStr">
         <is>
           <t>ส่วนลด %</t>
         </is>
       </c>
-      <c r="J12" s="29" t="inlineStr">
+      <c r="J12" s="157" t="inlineStr">
         <is>
           <t>รายได้สุทธิ</t>
         </is>
       </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K12" s="157" t="inlineStr">
         <is>
           <t>จ่ายแบบ</t>
         </is>
       </c>
-      <c r="L12" s="30" t="inlineStr">
+      <c r="L12" s="157" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="M12" s="30" t="inlineStr">
+      <c r="M12" s="157" t="inlineStr">
         <is>
           <t>Rate %</t>
         </is>
       </c>
-      <c r="N12" s="30" t="inlineStr">
+      <c r="N12" s="157" t="inlineStr">
         <is>
           <t>ค่าคอม (THB)</t>
         </is>
       </c>
-      <c r="O12" s="26" t="inlineStr">
+      <c r="O12" s="157" t="inlineStr">
         <is>
           <t>สถานะจ่าย</t>
         </is>
@@ -1695,12 +1827,12 @@
       <c r="E13" s="131" t="n"/>
       <c r="F13" s="131" t="n"/>
       <c r="G13" s="131" t="n"/>
-      <c r="H13" s="132">
+      <c r="H13" s="158">
         <f>IF(G13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I13" s="133" t="n"/>
-      <c r="J13" s="108">
+      <c r="J13" s="159">
         <f>IF(H13="","",H13*(1-IF(I13="",0,I13)))</f>
         <v/>
       </c>
@@ -1710,7 +1842,7 @@
         <f>IF(G13="","",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N13" s="36">
+      <c r="N13" s="160">
         <f>IF(OR(J13="",M13=""),"",J13*M13)</f>
         <v/>
       </c>
@@ -1730,12 +1862,12 @@
       <c r="E14" s="136" t="n"/>
       <c r="F14" s="136" t="n"/>
       <c r="G14" s="136" t="n"/>
-      <c r="H14" s="137">
+      <c r="H14" s="161">
         <f>IF(G14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I14" s="138" t="n"/>
-      <c r="J14" s="40">
+      <c r="J14" s="162">
         <f>IF(H14="","",H14*(1-IF(I14="",0,I14)))</f>
         <v/>
       </c>
@@ -1745,7 +1877,7 @@
         <f>IF(G14="","",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N14" s="42">
+      <c r="N14" s="160">
         <f>IF(OR(J14="",M14=""),"",J14*M14)</f>
         <v/>
       </c>
@@ -1765,12 +1897,12 @@
       <c r="E15" s="131" t="n"/>
       <c r="F15" s="131" t="n"/>
       <c r="G15" s="131" t="n"/>
-      <c r="H15" s="132">
+      <c r="H15" s="158">
         <f>IF(G15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I15" s="133" t="n"/>
-      <c r="J15" s="108">
+      <c r="J15" s="159">
         <f>IF(H15="","",H15*(1-IF(I15="",0,I15)))</f>
         <v/>
       </c>
@@ -1780,7 +1912,7 @@
         <f>IF(G15="","",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N15" s="36">
+      <c r="N15" s="160">
         <f>IF(OR(J15="",M15=""),"",J15*M15)</f>
         <v/>
       </c>
@@ -1800,12 +1932,12 @@
       <c r="E16" s="136" t="n"/>
       <c r="F16" s="136" t="n"/>
       <c r="G16" s="136" t="n"/>
-      <c r="H16" s="137">
+      <c r="H16" s="161">
         <f>IF(G16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I16" s="138" t="n"/>
-      <c r="J16" s="40">
+      <c r="J16" s="162">
         <f>IF(H16="","",H16*(1-IF(I16="",0,I16)))</f>
         <v/>
       </c>
@@ -1815,7 +1947,7 @@
         <f>IF(G16="","",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N16" s="42">
+      <c r="N16" s="160">
         <f>IF(OR(J16="",M16=""),"",J16*M16)</f>
         <v/>
       </c>
@@ -1835,12 +1967,12 @@
       <c r="E17" s="131" t="n"/>
       <c r="F17" s="131" t="n"/>
       <c r="G17" s="131" t="n"/>
-      <c r="H17" s="132">
+      <c r="H17" s="158">
         <f>IF(G17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I17" s="133" t="n"/>
-      <c r="J17" s="108">
+      <c r="J17" s="159">
         <f>IF(H17="","",H17*(1-IF(I17="",0,I17)))</f>
         <v/>
       </c>
@@ -1850,7 +1982,7 @@
         <f>IF(G17="","",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N17" s="36">
+      <c r="N17" s="160">
         <f>IF(OR(J17="",M17=""),"",J17*M17)</f>
         <v/>
       </c>
@@ -1870,12 +2002,12 @@
       <c r="E18" s="136" t="n"/>
       <c r="F18" s="136" t="n"/>
       <c r="G18" s="136" t="n"/>
-      <c r="H18" s="137">
+      <c r="H18" s="161">
         <f>IF(G18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I18" s="138" t="n"/>
-      <c r="J18" s="40">
+      <c r="J18" s="162">
         <f>IF(H18="","",H18*(1-IF(I18="",0,I18)))</f>
         <v/>
       </c>
@@ -1885,7 +2017,7 @@
         <f>IF(G18="","",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N18" s="42">
+      <c r="N18" s="160">
         <f>IF(OR(J18="",M18=""),"",J18*M18)</f>
         <v/>
       </c>
@@ -1905,12 +2037,12 @@
       <c r="E19" s="131" t="n"/>
       <c r="F19" s="131" t="n"/>
       <c r="G19" s="131" t="n"/>
-      <c r="H19" s="132">
+      <c r="H19" s="158">
         <f>IF(G19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I19" s="133" t="n"/>
-      <c r="J19" s="108">
+      <c r="J19" s="159">
         <f>IF(H19="","",H19*(1-IF(I19="",0,I19)))</f>
         <v/>
       </c>
@@ -1920,7 +2052,7 @@
         <f>IF(G19="","",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N19" s="36">
+      <c r="N19" s="160">
         <f>IF(OR(J19="",M19=""),"",J19*M19)</f>
         <v/>
       </c>
@@ -1940,12 +2072,12 @@
       <c r="E20" s="136" t="n"/>
       <c r="F20" s="136" t="n"/>
       <c r="G20" s="136" t="n"/>
-      <c r="H20" s="137">
+      <c r="H20" s="161">
         <f>IF(G20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I20" s="138" t="n"/>
-      <c r="J20" s="40">
+      <c r="J20" s="162">
         <f>IF(H20="","",H20*(1-IF(I20="",0,I20)))</f>
         <v/>
       </c>
@@ -1955,7 +2087,7 @@
         <f>IF(G20="","",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N20" s="42">
+      <c r="N20" s="160">
         <f>IF(OR(J20="",M20=""),"",J20*M20)</f>
         <v/>
       </c>
@@ -1975,12 +2107,12 @@
       <c r="E21" s="131" t="n"/>
       <c r="F21" s="131" t="n"/>
       <c r="G21" s="131" t="n"/>
-      <c r="H21" s="132">
+      <c r="H21" s="158">
         <f>IF(G21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I21" s="133" t="n"/>
-      <c r="J21" s="108">
+      <c r="J21" s="159">
         <f>IF(H21="","",H21*(1-IF(I21="",0,I21)))</f>
         <v/>
       </c>
@@ -1990,7 +2122,7 @@
         <f>IF(G21="","",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="160">
         <f>IF(OR(J21="",M21=""),"",J21*M21)</f>
         <v/>
       </c>
@@ -2010,12 +2142,12 @@
       <c r="E22" s="136" t="n"/>
       <c r="F22" s="136" t="n"/>
       <c r="G22" s="136" t="n"/>
-      <c r="H22" s="137">
+      <c r="H22" s="161">
         <f>IF(G22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I22" s="138" t="n"/>
-      <c r="J22" s="40">
+      <c r="J22" s="162">
         <f>IF(H22="","",H22*(1-IF(I22="",0,I22)))</f>
         <v/>
       </c>
@@ -2025,7 +2157,7 @@
         <f>IF(G22="","",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N22" s="42">
+      <c r="N22" s="160">
         <f>IF(OR(J22="",M22=""),"",J22*M22)</f>
         <v/>
       </c>
@@ -2045,12 +2177,12 @@
       <c r="E23" s="131" t="n"/>
       <c r="F23" s="131" t="n"/>
       <c r="G23" s="131" t="n"/>
-      <c r="H23" s="132">
+      <c r="H23" s="158">
         <f>IF(G23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I23" s="133" t="n"/>
-      <c r="J23" s="108">
+      <c r="J23" s="159">
         <f>IF(H23="","",H23*(1-IF(I23="",0,I23)))</f>
         <v/>
       </c>
@@ -2060,7 +2192,7 @@
         <f>IF(G23="","",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N23" s="36">
+      <c r="N23" s="160">
         <f>IF(OR(J23="",M23=""),"",J23*M23)</f>
         <v/>
       </c>
@@ -2080,12 +2212,12 @@
       <c r="E24" s="136" t="n"/>
       <c r="F24" s="136" t="n"/>
       <c r="G24" s="136" t="n"/>
-      <c r="H24" s="137">
+      <c r="H24" s="161">
         <f>IF(G24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I24" s="138" t="n"/>
-      <c r="J24" s="40">
+      <c r="J24" s="162">
         <f>IF(H24="","",H24*(1-IF(I24="",0,I24)))</f>
         <v/>
       </c>
@@ -2095,7 +2227,7 @@
         <f>IF(G24="","",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N24" s="42">
+      <c r="N24" s="160">
         <f>IF(OR(J24="",M24=""),"",J24*M24)</f>
         <v/>
       </c>
@@ -2115,12 +2247,12 @@
       <c r="E25" s="131" t="n"/>
       <c r="F25" s="131" t="n"/>
       <c r="G25" s="131" t="n"/>
-      <c r="H25" s="132">
+      <c r="H25" s="158">
         <f>IF(G25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I25" s="133" t="n"/>
-      <c r="J25" s="108">
+      <c r="J25" s="159">
         <f>IF(H25="","",H25*(1-IF(I25="",0,I25)))</f>
         <v/>
       </c>
@@ -2130,7 +2262,7 @@
         <f>IF(G25="","",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N25" s="36">
+      <c r="N25" s="160">
         <f>IF(OR(J25="",M25=""),"",J25*M25)</f>
         <v/>
       </c>
@@ -2150,12 +2282,12 @@
       <c r="E26" s="136" t="n"/>
       <c r="F26" s="136" t="n"/>
       <c r="G26" s="136" t="n"/>
-      <c r="H26" s="137">
+      <c r="H26" s="161">
         <f>IF(G26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I26" s="138" t="n"/>
-      <c r="J26" s="40">
+      <c r="J26" s="162">
         <f>IF(H26="","",H26*(1-IF(I26="",0,I26)))</f>
         <v/>
       </c>
@@ -2165,7 +2297,7 @@
         <f>IF(G26="","",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N26" s="42">
+      <c r="N26" s="160">
         <f>IF(OR(J26="",M26=""),"",J26*M26)</f>
         <v/>
       </c>
@@ -2185,12 +2317,12 @@
       <c r="E27" s="131" t="n"/>
       <c r="F27" s="131" t="n"/>
       <c r="G27" s="131" t="n"/>
-      <c r="H27" s="132">
+      <c r="H27" s="158">
         <f>IF(G27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I27" s="133" t="n"/>
-      <c r="J27" s="108">
+      <c r="J27" s="159">
         <f>IF(H27="","",H27*(1-IF(I27="",0,I27)))</f>
         <v/>
       </c>
@@ -2200,7 +2332,7 @@
         <f>IF(G27="","",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N27" s="36">
+      <c r="N27" s="160">
         <f>IF(OR(J27="",M27=""),"",J27*M27)</f>
         <v/>
       </c>
@@ -2220,12 +2352,12 @@
       <c r="E28" s="136" t="n"/>
       <c r="F28" s="136" t="n"/>
       <c r="G28" s="136" t="n"/>
-      <c r="H28" s="137">
+      <c r="H28" s="161">
         <f>IF(G28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I28" s="138" t="n"/>
-      <c r="J28" s="40">
+      <c r="J28" s="162">
         <f>IF(H28="","",H28*(1-IF(I28="",0,I28)))</f>
         <v/>
       </c>
@@ -2235,7 +2367,7 @@
         <f>IF(G28="","",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N28" s="42">
+      <c r="N28" s="160">
         <f>IF(OR(J28="",M28=""),"",J28*M28)</f>
         <v/>
       </c>
@@ -2255,12 +2387,12 @@
       <c r="E29" s="131" t="n"/>
       <c r="F29" s="131" t="n"/>
       <c r="G29" s="131" t="n"/>
-      <c r="H29" s="132">
+      <c r="H29" s="158">
         <f>IF(G29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I29" s="133" t="n"/>
-      <c r="J29" s="108">
+      <c r="J29" s="159">
         <f>IF(H29="","",H29*(1-IF(I29="",0,I29)))</f>
         <v/>
       </c>
@@ -2270,7 +2402,7 @@
         <f>IF(G29="","",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N29" s="36">
+      <c r="N29" s="160">
         <f>IF(OR(J29="",M29=""),"",J29*M29)</f>
         <v/>
       </c>
@@ -2290,12 +2422,12 @@
       <c r="E30" s="136" t="n"/>
       <c r="F30" s="136" t="n"/>
       <c r="G30" s="136" t="n"/>
-      <c r="H30" s="137">
+      <c r="H30" s="161">
         <f>IF(G30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I30" s="138" t="n"/>
-      <c r="J30" s="40">
+      <c r="J30" s="162">
         <f>IF(H30="","",H30*(1-IF(I30="",0,I30)))</f>
         <v/>
       </c>
@@ -2305,7 +2437,7 @@
         <f>IF(G30="","",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N30" s="42">
+      <c r="N30" s="160">
         <f>IF(OR(J30="",M30=""),"",J30*M30)</f>
         <v/>
       </c>
@@ -2325,12 +2457,12 @@
       <c r="E31" s="131" t="n"/>
       <c r="F31" s="131" t="n"/>
       <c r="G31" s="131" t="n"/>
-      <c r="H31" s="132">
+      <c r="H31" s="158">
         <f>IF(G31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I31" s="133" t="n"/>
-      <c r="J31" s="108">
+      <c r="J31" s="159">
         <f>IF(H31="","",H31*(1-IF(I31="",0,I31)))</f>
         <v/>
       </c>
@@ -2340,7 +2472,7 @@
         <f>IF(G31="","",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="160">
         <f>IF(OR(J31="",M31=""),"",J31*M31)</f>
         <v/>
       </c>
@@ -2360,12 +2492,12 @@
       <c r="E32" s="136" t="n"/>
       <c r="F32" s="136" t="n"/>
       <c r="G32" s="136" t="n"/>
-      <c r="H32" s="137">
+      <c r="H32" s="161">
         <f>IF(G32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I32" s="138" t="n"/>
-      <c r="J32" s="40">
+      <c r="J32" s="162">
         <f>IF(H32="","",H32*(1-IF(I32="",0,I32)))</f>
         <v/>
       </c>
@@ -2375,7 +2507,7 @@
         <f>IF(G32="","",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N32" s="42">
+      <c r="N32" s="160">
         <f>IF(OR(J32="",M32=""),"",J32*M32)</f>
         <v/>
       </c>
@@ -2395,12 +2527,12 @@
       <c r="E33" s="131" t="n"/>
       <c r="F33" s="131" t="n"/>
       <c r="G33" s="131" t="n"/>
-      <c r="H33" s="132">
+      <c r="H33" s="158">
         <f>IF(G33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I33" s="133" t="n"/>
-      <c r="J33" s="108">
+      <c r="J33" s="159">
         <f>IF(H33="","",H33*(1-IF(I33="",0,I33)))</f>
         <v/>
       </c>
@@ -2410,7 +2542,7 @@
         <f>IF(G33="","",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="160">
         <f>IF(OR(J33="",M33=""),"",J33*M33)</f>
         <v/>
       </c>
@@ -2430,12 +2562,12 @@
       <c r="E34" s="136" t="n"/>
       <c r="F34" s="136" t="n"/>
       <c r="G34" s="136" t="n"/>
-      <c r="H34" s="137">
+      <c r="H34" s="161">
         <f>IF(G34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I34" s="138" t="n"/>
-      <c r="J34" s="40">
+      <c r="J34" s="162">
         <f>IF(H34="","",H34*(1-IF(I34="",0,I34)))</f>
         <v/>
       </c>
@@ -2445,7 +2577,7 @@
         <f>IF(G34="","",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N34" s="42">
+      <c r="N34" s="160">
         <f>IF(OR(J34="",M34=""),"",J34*M34)</f>
         <v/>
       </c>
@@ -2465,12 +2597,12 @@
       <c r="E35" s="131" t="n"/>
       <c r="F35" s="131" t="n"/>
       <c r="G35" s="131" t="n"/>
-      <c r="H35" s="132">
+      <c r="H35" s="158">
         <f>IF(G35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I35" s="133" t="n"/>
-      <c r="J35" s="108">
+      <c r="J35" s="159">
         <f>IF(H35="","",H35*(1-IF(I35="",0,I35)))</f>
         <v/>
       </c>
@@ -2480,7 +2612,7 @@
         <f>IF(G35="","",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="160">
         <f>IF(OR(J35="",M35=""),"",J35*M35)</f>
         <v/>
       </c>
@@ -2500,12 +2632,12 @@
       <c r="E36" s="136" t="n"/>
       <c r="F36" s="136" t="n"/>
       <c r="G36" s="136" t="n"/>
-      <c r="H36" s="137">
+      <c r="H36" s="161">
         <f>IF(G36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I36" s="138" t="n"/>
-      <c r="J36" s="40">
+      <c r="J36" s="162">
         <f>IF(H36="","",H36*(1-IF(I36="",0,I36)))</f>
         <v/>
       </c>
@@ -2515,7 +2647,7 @@
         <f>IF(G36="","",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N36" s="42">
+      <c r="N36" s="160">
         <f>IF(OR(J36="",M36=""),"",J36*M36)</f>
         <v/>
       </c>
@@ -2535,12 +2667,12 @@
       <c r="E37" s="131" t="n"/>
       <c r="F37" s="131" t="n"/>
       <c r="G37" s="131" t="n"/>
-      <c r="H37" s="132">
+      <c r="H37" s="158">
         <f>IF(G37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I37" s="133" t="n"/>
-      <c r="J37" s="108">
+      <c r="J37" s="159">
         <f>IF(H37="","",H37*(1-IF(I37="",0,I37)))</f>
         <v/>
       </c>
@@ -2550,7 +2682,7 @@
         <f>IF(G37="","",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N37" s="36">
+      <c r="N37" s="160">
         <f>IF(OR(J37="",M37=""),"",J37*M37)</f>
         <v/>
       </c>
@@ -2570,12 +2702,12 @@
       <c r="E38" s="136" t="n"/>
       <c r="F38" s="136" t="n"/>
       <c r="G38" s="136" t="n"/>
-      <c r="H38" s="137">
+      <c r="H38" s="161">
         <f>IF(G38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I38" s="138" t="n"/>
-      <c r="J38" s="40">
+      <c r="J38" s="162">
         <f>IF(H38="","",H38*(1-IF(I38="",0,I38)))</f>
         <v/>
       </c>
@@ -2585,7 +2717,7 @@
         <f>IF(G38="","",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N38" s="42">
+      <c r="N38" s="160">
         <f>IF(OR(J38="",M38=""),"",J38*M38)</f>
         <v/>
       </c>
@@ -2605,12 +2737,12 @@
       <c r="E39" s="131" t="n"/>
       <c r="F39" s="131" t="n"/>
       <c r="G39" s="131" t="n"/>
-      <c r="H39" s="132">
+      <c r="H39" s="158">
         <f>IF(G39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I39" s="133" t="n"/>
-      <c r="J39" s="108">
+      <c r="J39" s="159">
         <f>IF(H39="","",H39*(1-IF(I39="",0,I39)))</f>
         <v/>
       </c>
@@ -2620,7 +2752,7 @@
         <f>IF(G39="","",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N39" s="36">
+      <c r="N39" s="160">
         <f>IF(OR(J39="",M39=""),"",J39*M39)</f>
         <v/>
       </c>
@@ -2640,12 +2772,12 @@
       <c r="E40" s="136" t="n"/>
       <c r="F40" s="136" t="n"/>
       <c r="G40" s="136" t="n"/>
-      <c r="H40" s="137">
+      <c r="H40" s="161">
         <f>IF(G40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I40" s="138" t="n"/>
-      <c r="J40" s="40">
+      <c r="J40" s="162">
         <f>IF(H40="","",H40*(1-IF(I40="",0,I40)))</f>
         <v/>
       </c>
@@ -2655,7 +2787,7 @@
         <f>IF(G40="","",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N40" s="42">
+      <c r="N40" s="160">
         <f>IF(OR(J40="",M40=""),"",J40*M40)</f>
         <v/>
       </c>
@@ -2675,12 +2807,12 @@
       <c r="E41" s="131" t="n"/>
       <c r="F41" s="131" t="n"/>
       <c r="G41" s="131" t="n"/>
-      <c r="H41" s="132">
+      <c r="H41" s="158">
         <f>IF(G41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I41" s="133" t="n"/>
-      <c r="J41" s="108">
+      <c r="J41" s="159">
         <f>IF(H41="","",H41*(1-IF(I41="",0,I41)))</f>
         <v/>
       </c>
@@ -2690,7 +2822,7 @@
         <f>IF(G41="","",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N41" s="36">
+      <c r="N41" s="160">
         <f>IF(OR(J41="",M41=""),"",J41*M41)</f>
         <v/>
       </c>
@@ -2710,12 +2842,12 @@
       <c r="E42" s="136" t="n"/>
       <c r="F42" s="136" t="n"/>
       <c r="G42" s="136" t="n"/>
-      <c r="H42" s="137">
+      <c r="H42" s="161">
         <f>IF(G42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I42" s="138" t="n"/>
-      <c r="J42" s="40">
+      <c r="J42" s="162">
         <f>IF(H42="","",H42*(1-IF(I42="",0,I42)))</f>
         <v/>
       </c>
@@ -2725,7 +2857,7 @@
         <f>IF(G42="","",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N42" s="42">
+      <c r="N42" s="160">
         <f>IF(OR(J42="",M42=""),"",J42*M42)</f>
         <v/>
       </c>
@@ -2745,12 +2877,12 @@
       <c r="E43" s="131" t="n"/>
       <c r="F43" s="131" t="n"/>
       <c r="G43" s="131" t="n"/>
-      <c r="H43" s="132">
+      <c r="H43" s="158">
         <f>IF(G43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I43" s="133" t="n"/>
-      <c r="J43" s="108">
+      <c r="J43" s="159">
         <f>IF(H43="","",H43*(1-IF(I43="",0,I43)))</f>
         <v/>
       </c>
@@ -2760,7 +2892,7 @@
         <f>IF(G43="","",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N43" s="36">
+      <c r="N43" s="160">
         <f>IF(OR(J43="",M43=""),"",J43*M43)</f>
         <v/>
       </c>
@@ -2780,12 +2912,12 @@
       <c r="E44" s="136" t="n"/>
       <c r="F44" s="136" t="n"/>
       <c r="G44" s="136" t="n"/>
-      <c r="H44" s="137">
+      <c r="H44" s="161">
         <f>IF(G44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I44" s="138" t="n"/>
-      <c r="J44" s="40">
+      <c r="J44" s="162">
         <f>IF(H44="","",H44*(1-IF(I44="",0,I44)))</f>
         <v/>
       </c>
@@ -2795,7 +2927,7 @@
         <f>IF(G44="","",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N44" s="42">
+      <c r="N44" s="160">
         <f>IF(OR(J44="",M44=""),"",J44*M44)</f>
         <v/>
       </c>
@@ -2815,12 +2947,12 @@
       <c r="E45" s="131" t="n"/>
       <c r="F45" s="131" t="n"/>
       <c r="G45" s="131" t="n"/>
-      <c r="H45" s="132">
+      <c r="H45" s="158">
         <f>IF(G45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I45" s="133" t="n"/>
-      <c r="J45" s="108">
+      <c r="J45" s="159">
         <f>IF(H45="","",H45*(1-IF(I45="",0,I45)))</f>
         <v/>
       </c>
@@ -2830,7 +2962,7 @@
         <f>IF(G45="","",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N45" s="36">
+      <c r="N45" s="160">
         <f>IF(OR(J45="",M45=""),"",J45*M45)</f>
         <v/>
       </c>
@@ -2850,12 +2982,12 @@
       <c r="E46" s="136" t="n"/>
       <c r="F46" s="136" t="n"/>
       <c r="G46" s="136" t="n"/>
-      <c r="H46" s="137">
+      <c r="H46" s="161">
         <f>IF(G46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I46" s="138" t="n"/>
-      <c r="J46" s="40">
+      <c r="J46" s="162">
         <f>IF(H46="","",H46*(1-IF(I46="",0,I46)))</f>
         <v/>
       </c>
@@ -2865,7 +2997,7 @@
         <f>IF(G46="","",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N46" s="42">
+      <c r="N46" s="160">
         <f>IF(OR(J46="",M46=""),"",J46*M46)</f>
         <v/>
       </c>
@@ -2885,12 +3017,12 @@
       <c r="E47" s="131" t="n"/>
       <c r="F47" s="131" t="n"/>
       <c r="G47" s="131" t="n"/>
-      <c r="H47" s="132">
+      <c r="H47" s="158">
         <f>IF(G47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I47" s="133" t="n"/>
-      <c r="J47" s="108">
+      <c r="J47" s="159">
         <f>IF(H47="","",H47*(1-IF(I47="",0,I47)))</f>
         <v/>
       </c>
@@ -2900,7 +3032,7 @@
         <f>IF(G47="","",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N47" s="36">
+      <c r="N47" s="160">
         <f>IF(OR(J47="",M47=""),"",J47*M47)</f>
         <v/>
       </c>
@@ -2920,12 +3052,12 @@
       <c r="E48" s="136" t="n"/>
       <c r="F48" s="136" t="n"/>
       <c r="G48" s="136" t="n"/>
-      <c r="H48" s="137">
+      <c r="H48" s="161">
         <f>IF(G48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I48" s="138" t="n"/>
-      <c r="J48" s="40">
+      <c r="J48" s="162">
         <f>IF(H48="","",H48*(1-IF(I48="",0,I48)))</f>
         <v/>
       </c>
@@ -2935,7 +3067,7 @@
         <f>IF(G48="","",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N48" s="42">
+      <c r="N48" s="160">
         <f>IF(OR(J48="",M48=""),"",J48*M48)</f>
         <v/>
       </c>
@@ -2955,12 +3087,12 @@
       <c r="E49" s="131" t="n"/>
       <c r="F49" s="131" t="n"/>
       <c r="G49" s="131" t="n"/>
-      <c r="H49" s="132">
+      <c r="H49" s="158">
         <f>IF(G49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I49" s="133" t="n"/>
-      <c r="J49" s="108">
+      <c r="J49" s="159">
         <f>IF(H49="","",H49*(1-IF(I49="",0,I49)))</f>
         <v/>
       </c>
@@ -2970,7 +3102,7 @@
         <f>IF(G49="","",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N49" s="36">
+      <c r="N49" s="160">
         <f>IF(OR(J49="",M49=""),"",J49*M49)</f>
         <v/>
       </c>
@@ -2990,12 +3122,12 @@
       <c r="E50" s="136" t="n"/>
       <c r="F50" s="136" t="n"/>
       <c r="G50" s="136" t="n"/>
-      <c r="H50" s="137">
+      <c r="H50" s="161">
         <f>IF(G50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I50" s="138" t="n"/>
-      <c r="J50" s="40">
+      <c r="J50" s="162">
         <f>IF(H50="","",H50*(1-IF(I50="",0,I50)))</f>
         <v/>
       </c>
@@ -3005,7 +3137,7 @@
         <f>IF(G50="","",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N50" s="42">
+      <c r="N50" s="160">
         <f>IF(OR(J50="",M50=""),"",J50*M50)</f>
         <v/>
       </c>
@@ -3025,12 +3157,12 @@
       <c r="E51" s="131" t="n"/>
       <c r="F51" s="131" t="n"/>
       <c r="G51" s="131" t="n"/>
-      <c r="H51" s="132">
+      <c r="H51" s="158">
         <f>IF(G51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I51" s="133" t="n"/>
-      <c r="J51" s="108">
+      <c r="J51" s="159">
         <f>IF(H51="","",H51*(1-IF(I51="",0,I51)))</f>
         <v/>
       </c>
@@ -3040,7 +3172,7 @@
         <f>IF(G51="","",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N51" s="36">
+      <c r="N51" s="160">
         <f>IF(OR(J51="",M51=""),"",J51*M51)</f>
         <v/>
       </c>
@@ -3060,12 +3192,12 @@
       <c r="E52" s="136" t="n"/>
       <c r="F52" s="136" t="n"/>
       <c r="G52" s="136" t="n"/>
-      <c r="H52" s="137">
+      <c r="H52" s="161">
         <f>IF(G52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$B$7,2,FALSE),""))</f>
         <v/>
       </c>
       <c r="I52" s="138" t="n"/>
-      <c r="J52" s="40">
+      <c r="J52" s="162">
         <f>IF(H52="","",H52*(1-IF(I52="",0,I52)))</f>
         <v/>
       </c>
@@ -3075,43 +3207,44 @@
         <f>IF(G52="","",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""))</f>
         <v/>
       </c>
-      <c r="N52" s="42">
+      <c r="N52" s="160">
         <f>IF(OR(J52="",M52=""),"",J52*M52)</f>
         <v/>
       </c>
       <c r="O52" s="136" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="43" t="n"/>
-      <c r="B53" s="43" t="n"/>
-      <c r="C53" s="43" t="n"/>
-      <c r="D53" s="43" t="n"/>
-      <c r="E53" s="43" t="n"/>
-      <c r="F53" s="43" t="n"/>
-      <c r="G53" s="121" t="inlineStr">
+      <c r="A53" s="164" t="n"/>
+      <c r="B53" s="164" t="n"/>
+      <c r="C53" s="164" t="n"/>
+      <c r="D53" s="164" t="n"/>
+      <c r="E53" s="164" t="n"/>
+      <c r="F53" s="164" t="n"/>
+      <c r="G53" s="165" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="H53" s="124">
+      <c r="H53" s="166">
         <f>SUM(H13:H52)</f>
         <v/>
       </c>
-      <c r="I53" s="43" t="n"/>
-      <c r="J53" s="124">
+      <c r="I53" s="164" t="n"/>
+      <c r="J53" s="166">
         <f>SUM(J13:J52)</f>
         <v/>
       </c>
-      <c r="L53" s="43" t="n"/>
-      <c r="M53" s="43" t="n"/>
-      <c r="N53" s="124">
+      <c r="L53" s="164" t="n"/>
+      <c r="M53" s="164" t="n"/>
+      <c r="N53" s="166">
         <f>SUM(M13:M52)</f>
         <v/>
       </c>
-      <c r="O53" s="43" t="n"/>
-    </row>
+      <c r="O53" s="164" t="n"/>
+    </row>
+    <row r="54"/>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="128" t="inlineStr">
+      <c r="A55" s="167" t="inlineStr">
         <is>
           <t>หมายเหตุ / วิธีใช้ — แท็บนี้ใช้บันทึกดีลขายจริง</t>
         </is>
@@ -3161,7 +3294,7 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="139" t="inlineStr">
+      <c r="A61" s="127" t="inlineStr">
         <is>
           <t>• ช่องที่คำนวณถูกล็อกเพื่อป้องกันการแก้ไขผิดพลาด · ราคาเต็ม (Enterprise) สามารถพิมพ์ทับได้ · ปลดล็อก: Review ▸ Unprotect Sheet (ไม่มีรหัส)</t>
         </is>
@@ -3243,7 +3376,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>EASY
 CRM</t>
@@ -3269,44 +3402,45 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="168" t="inlineStr">
         <is>
           <t>ชื่อ Sales</t>
         </is>
       </c>
-      <c r="B5" s="91" t="inlineStr">
+      <c r="B5" s="168" t="inlineStr">
         <is>
           <t>ตำแหน่ง</t>
         </is>
       </c>
-      <c r="C5" s="91" t="inlineStr">
+      <c r="C5" s="168" t="inlineStr">
         <is>
           <t>% แบ่งทีม
 (รวม=100%)</t>
         </is>
       </c>
-      <c r="D5" s="91" t="inlineStr">
+      <c r="D5" s="168" t="inlineStr">
         <is>
           <t>ดีลปิดเอง</t>
         </is>
       </c>
-      <c r="E5" s="91" t="inlineStr">
+      <c r="E5" s="168" t="inlineStr">
         <is>
           <t>รายได้ (THB)</t>
         </is>
       </c>
-      <c r="F5" s="91" t="inlineStr">
+      <c r="F5" s="168" t="inlineStr">
         <is>
           <t>ค่าคอมรวม (THB)</t>
         </is>
       </c>
-      <c r="G5" s="91" t="inlineStr">
+      <c r="G5" s="168" t="inlineStr">
         <is>
           <t>จ่ายแล้ว (THB)</t>
         </is>
       </c>
-      <c r="H5" s="91" t="inlineStr">
+      <c r="H5" s="168" t="inlineStr">
         <is>
           <t>ค้างจ่าย (THB)</t>
         </is>
@@ -3323,26 +3457,26 @@
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C6" s="142" t="n">
+      <c r="C6" s="169" t="n">
         <v>0.5</v>
       </c>
-      <c r="D6" s="118">
-        <f>IF($A6="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E6" s="119">
-        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$J$13:$J$52)+$C6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F6" s="120">
-        <f>IF($A6="","",SUMIF(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$N$13:$N$52)+$C6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G6" s="119">
-        <f>IF($A6="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A6,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C6*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H6" s="119">
+      <c r="D6" s="170">
+        <f>IF($A6="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A6,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E6" s="171">
+        <f>IF($A6="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A6,Sales_Record!$K$13:$K$52,"รายคน")+$C6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F6" s="172">
+        <f>IF($A6="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A6,Sales_Record!$K$13:$K$52,"รายคน")+$C6*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G6" s="171">
+        <f>IF($A6="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A6,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C6*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="171">
         <f>IF($A6="","",F6-G6)</f>
         <v/>
       </c>
@@ -3358,26 +3492,26 @@
           <t>Sales Executive</t>
         </is>
       </c>
-      <c r="C7" s="142" t="n">
+      <c r="C7" s="169" t="n">
         <v>0.3</v>
       </c>
-      <c r="D7" s="118">
-        <f>IF($A7="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E7" s="119">
-        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$J$13:$J$52)+$C7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F7" s="120">
-        <f>IF($A7="","",SUMIF(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$N$13:$N$52)+$C7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G7" s="119">
-        <f>IF($A7="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A7,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C7*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H7" s="119">
+      <c r="D7" s="170">
+        <f>IF($A7="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A7,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E7" s="171">
+        <f>IF($A7="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A7,Sales_Record!$K$13:$K$52,"รายคน")+$C7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F7" s="172">
+        <f>IF($A7="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A7,Sales_Record!$K$13:$K$52,"รายคน")+$C7*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G7" s="171">
+        <f>IF($A7="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A7,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C7*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="171">
         <f>IF($A7="","",F7-G7)</f>
         <v/>
       </c>
@@ -3393,26 +3527,26 @@
           <t>Support / Sales</t>
         </is>
       </c>
-      <c r="C8" s="142" t="n">
+      <c r="C8" s="169" t="n">
         <v>0.2</v>
       </c>
-      <c r="D8" s="118">
-        <f>IF($A8="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E8" s="119">
-        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$J$13:$J$52)+$C8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F8" s="120">
-        <f>IF($A8="","",SUMIF(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$N$13:$N$52)+$C8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G8" s="119">
-        <f>IF($A8="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A8,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C8*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H8" s="119">
+      <c r="D8" s="170">
+        <f>IF($A8="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A8,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E8" s="171">
+        <f>IF($A8="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A8,Sales_Record!$K$13:$K$52,"รายคน")+$C8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F8" s="172">
+        <f>IF($A8="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A8,Sales_Record!$K$13:$K$52,"รายคน")+$C8*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G8" s="171">
+        <f>IF($A8="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A8,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C8*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="171">
         <f>IF($A8="","",F8-G8)</f>
         <v/>
       </c>
@@ -3420,24 +3554,24 @@
     <row r="9">
       <c r="A9" s="140" t="inlineStr"/>
       <c r="B9" s="141" t="inlineStr"/>
-      <c r="C9" s="142" t="n"/>
-      <c r="D9" s="118">
-        <f>IF($A9="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E9" s="119">
-        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$J$13:$J$52)+$C9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F9" s="120">
-        <f>IF($A9="","",SUMIF(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$N$13:$N$52)+$C9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G9" s="119">
-        <f>IF($A9="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A9,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C9*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H9" s="119">
+      <c r="C9" s="169" t="n"/>
+      <c r="D9" s="170">
+        <f>IF($A9="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A9,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E9" s="171">
+        <f>IF($A9="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A9,Sales_Record!$K$13:$K$52,"รายคน")+$C9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F9" s="172">
+        <f>IF($A9="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A9,Sales_Record!$K$13:$K$52,"รายคน")+$C9*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G9" s="171">
+        <f>IF($A9="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A9,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C9*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="171">
         <f>IF($A9="","",F9-G9)</f>
         <v/>
       </c>
@@ -3445,24 +3579,24 @@
     <row r="10">
       <c r="A10" s="140" t="inlineStr"/>
       <c r="B10" s="141" t="inlineStr"/>
-      <c r="C10" s="142" t="n"/>
-      <c r="D10" s="118">
-        <f>IF($A10="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E10" s="119">
-        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$J$13:$J$52)+$C10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F10" s="120">
-        <f>IF($A10="","",SUMIF(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$N$13:$N$52)+$C10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G10" s="119">
-        <f>IF($A10="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A10,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C10*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H10" s="119">
+      <c r="C10" s="169" t="n"/>
+      <c r="D10" s="170">
+        <f>IF($A10="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A10,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E10" s="171">
+        <f>IF($A10="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A10,Sales_Record!$K$13:$K$52,"รายคน")+$C10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F10" s="172">
+        <f>IF($A10="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A10,Sales_Record!$K$13:$K$52,"รายคน")+$C10*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G10" s="171">
+        <f>IF($A10="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A10,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C10*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="171">
         <f>IF($A10="","",F10-G10)</f>
         <v/>
       </c>
@@ -3470,24 +3604,24 @@
     <row r="11">
       <c r="A11" s="140" t="inlineStr"/>
       <c r="B11" s="141" t="inlineStr"/>
-      <c r="C11" s="142" t="n"/>
-      <c r="D11" s="118">
-        <f>IF($A11="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E11" s="119">
-        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$J$13:$J$52)+$C11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F11" s="120">
-        <f>IF($A11="","",SUMIF(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$N$13:$N$52)+$C11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G11" s="119">
-        <f>IF($A11="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A11,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C11*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H11" s="119">
+      <c r="C11" s="169" t="n"/>
+      <c r="D11" s="170">
+        <f>IF($A11="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A11,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E11" s="171">
+        <f>IF($A11="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A11,Sales_Record!$K$13:$K$52,"รายคน")+$C11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F11" s="172">
+        <f>IF($A11="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A11,Sales_Record!$K$13:$K$52,"รายคน")+$C11*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G11" s="171">
+        <f>IF($A11="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A11,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C11*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="171">
         <f>IF($A11="","",F11-G11)</f>
         <v/>
       </c>
@@ -3495,24 +3629,24 @@
     <row r="12">
       <c r="A12" s="140" t="inlineStr"/>
       <c r="B12" s="141" t="inlineStr"/>
-      <c r="C12" s="142" t="n"/>
-      <c r="D12" s="118">
-        <f>IF($A12="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="119">
-        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$J$13:$J$52)+$C12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F12" s="120">
-        <f>IF($A12="","",SUMIF(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$N$13:$N$52)+$C12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G12" s="119">
-        <f>IF($A12="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A12,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C12*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H12" s="119">
+      <c r="C12" s="169" t="n"/>
+      <c r="D12" s="170">
+        <f>IF($A12="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A12,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="171">
+        <f>IF($A12="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A12,Sales_Record!$K$13:$K$52,"รายคน")+$C12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F12" s="172">
+        <f>IF($A12="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A12,Sales_Record!$K$13:$K$52,"รายคน")+$C12*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G12" s="171">
+        <f>IF($A12="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A12,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C12*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="171">
         <f>IF($A12="","",F12-G12)</f>
         <v/>
       </c>
@@ -3520,24 +3654,24 @@
     <row r="13">
       <c r="A13" s="140" t="inlineStr"/>
       <c r="B13" s="141" t="inlineStr"/>
-      <c r="C13" s="142" t="n"/>
-      <c r="D13" s="118">
-        <f>IF($A13="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E13" s="119">
-        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$J$13:$J$52)+$C13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F13" s="120">
-        <f>IF($A13="","",SUMIF(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$N$13:$N$52)+$C13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G13" s="119">
-        <f>IF($A13="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A13,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C13*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="119">
+      <c r="C13" s="169" t="n"/>
+      <c r="D13" s="170">
+        <f>IF($A13="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A13,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="171">
+        <f>IF($A13="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A13,Sales_Record!$K$13:$K$52,"รายคน")+$C13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F13" s="172">
+        <f>IF($A13="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A13,Sales_Record!$K$13:$K$52,"รายคน")+$C13*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G13" s="171">
+        <f>IF($A13="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A13,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C13*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="171">
         <f>IF($A13="","",F13-G13)</f>
         <v/>
       </c>
@@ -3545,24 +3679,24 @@
     <row r="14">
       <c r="A14" s="140" t="inlineStr"/>
       <c r="B14" s="141" t="inlineStr"/>
-      <c r="C14" s="142" t="n"/>
-      <c r="D14" s="118">
-        <f>IF($A14="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E14" s="119">
-        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$J$13:$J$52)+$C14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F14" s="120">
-        <f>IF($A14="","",SUMIF(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$N$13:$N$52)+$C14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G14" s="119">
-        <f>IF($A14="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A14,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C14*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H14" s="119">
+      <c r="C14" s="169" t="n"/>
+      <c r="D14" s="170">
+        <f>IF($A14="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A14,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="171">
+        <f>IF($A14="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A14,Sales_Record!$K$13:$K$52,"รายคน")+$C14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F14" s="172">
+        <f>IF($A14="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A14,Sales_Record!$K$13:$K$52,"รายคน")+$C14*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G14" s="171">
+        <f>IF($A14="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A14,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C14*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="171">
         <f>IF($A14="","",F14-G14)</f>
         <v/>
       </c>
@@ -3570,24 +3704,24 @@
     <row r="15">
       <c r="A15" s="140" t="inlineStr"/>
       <c r="B15" s="141" t="inlineStr"/>
-      <c r="C15" s="142" t="n"/>
-      <c r="D15" s="118">
-        <f>IF($A15="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E15" s="119">
-        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$J$13:$J$52)+$C15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F15" s="120">
-        <f>IF($A15="","",SUMIF(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$N$13:$N$52)+$C15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G15" s="119">
-        <f>IF($A15="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A15,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C15*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H15" s="119">
+      <c r="C15" s="169" t="n"/>
+      <c r="D15" s="170">
+        <f>IF($A15="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A15,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="171">
+        <f>IF($A15="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A15,Sales_Record!$K$13:$K$52,"รายคน")+$C15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F15" s="172">
+        <f>IF($A15="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A15,Sales_Record!$K$13:$K$52,"รายคน")+$C15*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G15" s="171">
+        <f>IF($A15="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A15,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C15*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="171">
         <f>IF($A15="","",F15-G15)</f>
         <v/>
       </c>
@@ -3595,24 +3729,24 @@
     <row r="16">
       <c r="A16" s="140" t="inlineStr"/>
       <c r="B16" s="141" t="inlineStr"/>
-      <c r="C16" s="142" t="n"/>
-      <c r="D16" s="118">
-        <f>IF($A16="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E16" s="119">
-        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$J$13:$J$52)+$C16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F16" s="120">
-        <f>IF($A16="","",SUMIF(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$N$13:$N$52)+$C16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G16" s="119">
-        <f>IF($A16="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A16,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C16*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H16" s="119">
+      <c r="C16" s="169" t="n"/>
+      <c r="D16" s="170">
+        <f>IF($A16="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A16,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E16" s="171">
+        <f>IF($A16="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A16,Sales_Record!$K$13:$K$52,"รายคน")+$C16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F16" s="172">
+        <f>IF($A16="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A16,Sales_Record!$K$13:$K$52,"รายคน")+$C16*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G16" s="171">
+        <f>IF($A16="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A16,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C16*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="171">
         <f>IF($A16="","",F16-G16)</f>
         <v/>
       </c>
@@ -3620,24 +3754,24 @@
     <row r="17">
       <c r="A17" s="140" t="inlineStr"/>
       <c r="B17" s="141" t="inlineStr"/>
-      <c r="C17" s="142" t="n"/>
-      <c r="D17" s="118">
-        <f>IF($A17="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E17" s="119">
-        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$J$13:$J$52)+$C17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F17" s="120">
-        <f>IF($A17="","",SUMIF(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$N$13:$N$52)+$C17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G17" s="119">
-        <f>IF($A17="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A17,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C17*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H17" s="119">
+      <c r="C17" s="169" t="n"/>
+      <c r="D17" s="170">
+        <f>IF($A17="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A17,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E17" s="171">
+        <f>IF($A17="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A17,Sales_Record!$K$13:$K$52,"รายคน")+$C17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F17" s="172">
+        <f>IF($A17="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A17,Sales_Record!$K$13:$K$52,"รายคน")+$C17*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G17" s="171">
+        <f>IF($A17="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A17,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C17*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H17" s="171">
         <f>IF($A17="","",F17-G17)</f>
         <v/>
       </c>
@@ -3645,24 +3779,24 @@
     <row r="18">
       <c r="A18" s="140" t="inlineStr"/>
       <c r="B18" s="141" t="inlineStr"/>
-      <c r="C18" s="142" t="n"/>
-      <c r="D18" s="118">
-        <f>IF($A18="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E18" s="119">
-        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$J$13:$J$52)+$C18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F18" s="120">
-        <f>IF($A18="","",SUMIF(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$N$13:$N$52)+$C18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G18" s="119">
-        <f>IF($A18="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A18,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C18*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H18" s="119">
+      <c r="C18" s="169" t="n"/>
+      <c r="D18" s="170">
+        <f>IF($A18="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A18,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="171">
+        <f>IF($A18="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A18,Sales_Record!$K$13:$K$52,"รายคน")+$C18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F18" s="172">
+        <f>IF($A18="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A18,Sales_Record!$K$13:$K$52,"รายคน")+$C18*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G18" s="171">
+        <f>IF($A18="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A18,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C18*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H18" s="171">
         <f>IF($A18="","",F18-G18)</f>
         <v/>
       </c>
@@ -3670,24 +3804,24 @@
     <row r="19">
       <c r="A19" s="140" t="inlineStr"/>
       <c r="B19" s="141" t="inlineStr"/>
-      <c r="C19" s="142" t="n"/>
-      <c r="D19" s="118">
-        <f>IF($A19="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E19" s="119">
-        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$J$13:$J$52)+$C19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F19" s="120">
-        <f>IF($A19="","",SUMIF(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$N$13:$N$52)+$C19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G19" s="119">
-        <f>IF($A19="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A19,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C19*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H19" s="119">
+      <c r="C19" s="169" t="n"/>
+      <c r="D19" s="170">
+        <f>IF($A19="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A19,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="171">
+        <f>IF($A19="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A19,Sales_Record!$K$13:$K$52,"รายคน")+$C19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F19" s="172">
+        <f>IF($A19="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A19,Sales_Record!$K$13:$K$52,"รายคน")+$C19*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G19" s="171">
+        <f>IF($A19="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A19,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C19*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H19" s="171">
         <f>IF($A19="","",F19-G19)</f>
         <v/>
       </c>
@@ -3695,62 +3829,64 @@
     <row r="20">
       <c r="A20" s="140" t="inlineStr"/>
       <c r="B20" s="141" t="inlineStr"/>
-      <c r="C20" s="142" t="n"/>
-      <c r="D20" s="118">
-        <f>IF($A20="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$B$13:$B$52,"&lt;&gt;"))</f>
-        <v/>
-      </c>
-      <c r="E20" s="119">
-        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$J$13:$J$52)+$C20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
-        <v/>
-      </c>
-      <c r="F20" s="120">
-        <f>IF($A20="","",SUMIF(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$N$13:$N$52)+$C20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
-        <v/>
-      </c>
-      <c r="G20" s="119">
-        <f>IF($A20="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A20,Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C20*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
-        <v/>
-      </c>
-      <c r="H20" s="119">
+      <c r="C20" s="169" t="n"/>
+      <c r="D20" s="170">
+        <f>IF($A20="","",COUNTIFS(Sales_Record!$L$13:$L$52,$A20,Sales_Record!$K$13:$K$52,"รายคน"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="171">
+        <f>IF($A20="","",SUMIFS(Sales_Record!$J$13:$J$52,Sales_Record!$L$13:$L$52,$A20,Sales_Record!$K$13:$K$52,"รายคน")+$C20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$J$13:$J$52))</f>
+        <v/>
+      </c>
+      <c r="F20" s="172">
+        <f>IF($A20="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A20,Sales_Record!$K$13:$K$52,"รายคน")+$C20*SUMIF(Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$N$13:$N$52))</f>
+        <v/>
+      </c>
+      <c r="G20" s="171">
+        <f>IF($A20="","",SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$L$13:$L$52,$A20,Sales_Record!$K$13:$K$52,"รายคน",Sales_Record!$O$13:$O$52,"จ่ายแล้ว")+$C20*SUMIFS(Sales_Record!$N$13:$N$52,Sales_Record!$K$13:$K$52,"ทีม",Sales_Record!$O$13:$O$52,"จ่ายแล้ว"))</f>
+        <v/>
+      </c>
+      <c r="H20" s="171">
         <f>IF($A20="","",F20-G20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="121" t="inlineStr">
+      <c r="A21" s="165" t="inlineStr">
         <is>
           <t>รวมทั้งทีม</t>
         </is>
       </c>
       <c r="B21" s="85" t="n"/>
-      <c r="C21" s="122">
+      <c r="C21" s="173">
         <f>SUM(C6:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="123">
+      <c r="D21" s="174">
         <f>SUM(D6:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="124">
+      <c r="E21" s="166">
         <f>SUM(E6:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="124">
+      <c r="F21" s="166">
         <f>SUM(F6:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="124">
+      <c r="G21" s="166">
         <f>SUM(G6:G20)</f>
         <v/>
       </c>
-      <c r="H21" s="124">
+      <c r="H21" s="166">
         <f>SUM(H6:H20)</f>
         <v/>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="128" t="inlineStr">
+      <c r="A24" s="167" t="inlineStr">
         <is>
           <t>หมายเหตุ / วิธีใช้</t>
         </is>
@@ -3790,7 +3926,7 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="139" t="inlineStr">
+      <c r="A29" s="127" t="inlineStr">
         <is>
           <t>• ช่องที่คำนวณถูกล็อก · กรอกได้เฉพาะ ชื่อ/ตำแหน่ง/%แบ่งทีม · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>
@@ -3847,32 +3983,32 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="175" t="inlineStr">
         <is>
           <t>แพ็กเกจ</t>
         </is>
       </c>
-      <c r="B3" s="48" t="inlineStr">
+      <c r="B3" s="175" t="inlineStr">
         <is>
           <t>ราคาต่อปี (บาท)</t>
         </is>
       </c>
-      <c r="C3" s="48" t="inlineStr">
+      <c r="C3" s="175" t="inlineStr">
         <is>
           <t>% ค่าคอม (ใหม่)</t>
         </is>
       </c>
-      <c r="D3" s="48" t="inlineStr">
+      <c r="D3" s="175" t="inlineStr">
         <is>
           <t>ค่าคอม/ดีล ใหม่</t>
         </is>
       </c>
-      <c r="E3" s="48" t="inlineStr">
+      <c r="E3" s="175" t="inlineStr">
         <is>
           <t>% ต่ออายุ</t>
         </is>
       </c>
-      <c r="F3" s="48" t="inlineStr">
+      <c r="F3" s="175" t="inlineStr">
         <is>
           <t>ค่าคอม/ดีล ต่ออายุ</t>
         </is>
@@ -3976,6 +4112,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="56" t="inlineStr">
         <is>
@@ -4004,8 +4141,9 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="167" t="inlineStr">
         <is>
           <t>วิธีใช้</t>
         </is>
@@ -4031,7 +4169,7 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="139" t="inlineStr">
+      <c r="A17" s="127" t="inlineStr">
         <is>
           <t>• ช่องที่คำนวณ (ค่าคอม/ดีล) ถูกล็อก · แก้ได้เฉพาะราคา/% · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>
@@ -4076,7 +4214,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>EASY
 CRM</t>
@@ -4102,53 +4240,54 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="168" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B5" s="91" t="inlineStr">
+      <c r="B5" s="168" t="inlineStr">
         <is>
           <t>วันที่</t>
         </is>
       </c>
-      <c r="C5" s="91" t="inlineStr">
+      <c r="C5" s="168" t="inlineStr">
         <is>
           <t>ไตรมาส</t>
         </is>
       </c>
-      <c r="D5" s="91" t="inlineStr">
+      <c r="D5" s="168" t="inlineStr">
         <is>
           <t>ชื่อลูกค้า</t>
         </is>
       </c>
-      <c r="E5" s="91" t="inlineStr">
+      <c r="E5" s="168" t="inlineStr">
         <is>
           <t>แพ็กเกจ</t>
         </is>
       </c>
-      <c r="F5" s="91" t="inlineStr">
+      <c r="F5" s="168" t="inlineStr">
         <is>
           <t>ประเภท</t>
         </is>
       </c>
-      <c r="G5" s="91" t="inlineStr">
+      <c r="G5" s="168" t="inlineStr">
         <is>
           <t>ราคาเต็ม (THB)</t>
         </is>
       </c>
-      <c r="H5" s="91" t="inlineStr">
+      <c r="H5" s="168" t="inlineStr">
         <is>
           <t>ส่วนลด %</t>
         </is>
       </c>
-      <c r="I5" s="91" t="inlineStr">
+      <c r="I5" s="168" t="inlineStr">
         <is>
           <t>รายได้สุทธิ (THB)</t>
         </is>
       </c>
-      <c r="J5" s="91" t="inlineStr">
+      <c r="J5" s="168" t="inlineStr">
         <is>
           <t>การชำระเงิน</t>
         </is>
@@ -4179,15 +4318,15 @@
         <f>IF($B6="","",Sales_Record!E13)</f>
         <v/>
       </c>
-      <c r="G6" s="108">
+      <c r="G6" s="159">
         <f>IF($B6="","",Sales_Record!H13)</f>
         <v/>
       </c>
-      <c r="H6" s="109">
+      <c r="H6" s="35">
         <f>IF($B6="","",Sales_Record!I13)</f>
         <v/>
       </c>
-      <c r="I6" s="110">
+      <c r="I6" s="176">
         <f>IF($B6="","",Sales_Record!J13)</f>
         <v/>
       </c>
@@ -4221,15 +4360,15 @@
         <f>IF($B7="","",Sales_Record!E14)</f>
         <v/>
       </c>
-      <c r="G7" s="108">
+      <c r="G7" s="159">
         <f>IF($B7="","",Sales_Record!H14)</f>
         <v/>
       </c>
-      <c r="H7" s="109">
+      <c r="H7" s="35">
         <f>IF($B7="","",Sales_Record!I14)</f>
         <v/>
       </c>
-      <c r="I7" s="110">
+      <c r="I7" s="176">
         <f>IF($B7="","",Sales_Record!J14)</f>
         <v/>
       </c>
@@ -4263,15 +4402,15 @@
         <f>IF($B8="","",Sales_Record!E15)</f>
         <v/>
       </c>
-      <c r="G8" s="108">
+      <c r="G8" s="159">
         <f>IF($B8="","",Sales_Record!H15)</f>
         <v/>
       </c>
-      <c r="H8" s="109">
+      <c r="H8" s="35">
         <f>IF($B8="","",Sales_Record!I15)</f>
         <v/>
       </c>
-      <c r="I8" s="110">
+      <c r="I8" s="176">
         <f>IF($B8="","",Sales_Record!J15)</f>
         <v/>
       </c>
@@ -4305,15 +4444,15 @@
         <f>IF($B9="","",Sales_Record!E16)</f>
         <v/>
       </c>
-      <c r="G9" s="108">
+      <c r="G9" s="159">
         <f>IF($B9="","",Sales_Record!H16)</f>
         <v/>
       </c>
-      <c r="H9" s="109">
+      <c r="H9" s="35">
         <f>IF($B9="","",Sales_Record!I16)</f>
         <v/>
       </c>
-      <c r="I9" s="110">
+      <c r="I9" s="176">
         <f>IF($B9="","",Sales_Record!J16)</f>
         <v/>
       </c>
@@ -4347,15 +4486,15 @@
         <f>IF($B10="","",Sales_Record!E17)</f>
         <v/>
       </c>
-      <c r="G10" s="108">
+      <c r="G10" s="159">
         <f>IF($B10="","",Sales_Record!H17)</f>
         <v/>
       </c>
-      <c r="H10" s="109">
+      <c r="H10" s="35">
         <f>IF($B10="","",Sales_Record!I17)</f>
         <v/>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="176">
         <f>IF($B10="","",Sales_Record!J17)</f>
         <v/>
       </c>
@@ -4389,15 +4528,15 @@
         <f>IF($B11="","",Sales_Record!E18)</f>
         <v/>
       </c>
-      <c r="G11" s="108">
+      <c r="G11" s="159">
         <f>IF($B11="","",Sales_Record!H18)</f>
         <v/>
       </c>
-      <c r="H11" s="109">
+      <c r="H11" s="35">
         <f>IF($B11="","",Sales_Record!I18)</f>
         <v/>
       </c>
-      <c r="I11" s="110">
+      <c r="I11" s="176">
         <f>IF($B11="","",Sales_Record!J18)</f>
         <v/>
       </c>
@@ -4431,15 +4570,15 @@
         <f>IF($B12="","",Sales_Record!E19)</f>
         <v/>
       </c>
-      <c r="G12" s="108">
+      <c r="G12" s="159">
         <f>IF($B12="","",Sales_Record!H19)</f>
         <v/>
       </c>
-      <c r="H12" s="109">
+      <c r="H12" s="35">
         <f>IF($B12="","",Sales_Record!I19)</f>
         <v/>
       </c>
-      <c r="I12" s="110">
+      <c r="I12" s="176">
         <f>IF($B12="","",Sales_Record!J19)</f>
         <v/>
       </c>
@@ -4473,15 +4612,15 @@
         <f>IF($B13="","",Sales_Record!E20)</f>
         <v/>
       </c>
-      <c r="G13" s="108">
+      <c r="G13" s="159">
         <f>IF($B13="","",Sales_Record!H20)</f>
         <v/>
       </c>
-      <c r="H13" s="109">
+      <c r="H13" s="35">
         <f>IF($B13="","",Sales_Record!I20)</f>
         <v/>
       </c>
-      <c r="I13" s="110">
+      <c r="I13" s="176">
         <f>IF($B13="","",Sales_Record!J20)</f>
         <v/>
       </c>
@@ -4515,15 +4654,15 @@
         <f>IF($B14="","",Sales_Record!E21)</f>
         <v/>
       </c>
-      <c r="G14" s="108">
+      <c r="G14" s="159">
         <f>IF($B14="","",Sales_Record!H21)</f>
         <v/>
       </c>
-      <c r="H14" s="109">
+      <c r="H14" s="35">
         <f>IF($B14="","",Sales_Record!I21)</f>
         <v/>
       </c>
-      <c r="I14" s="110">
+      <c r="I14" s="176">
         <f>IF($B14="","",Sales_Record!J21)</f>
         <v/>
       </c>
@@ -4557,15 +4696,15 @@
         <f>IF($B15="","",Sales_Record!E22)</f>
         <v/>
       </c>
-      <c r="G15" s="108">
+      <c r="G15" s="159">
         <f>IF($B15="","",Sales_Record!H22)</f>
         <v/>
       </c>
-      <c r="H15" s="109">
+      <c r="H15" s="35">
         <f>IF($B15="","",Sales_Record!I22)</f>
         <v/>
       </c>
-      <c r="I15" s="110">
+      <c r="I15" s="176">
         <f>IF($B15="","",Sales_Record!J22)</f>
         <v/>
       </c>
@@ -4599,15 +4738,15 @@
         <f>IF($B16="","",Sales_Record!E23)</f>
         <v/>
       </c>
-      <c r="G16" s="108">
+      <c r="G16" s="159">
         <f>IF($B16="","",Sales_Record!H23)</f>
         <v/>
       </c>
-      <c r="H16" s="109">
+      <c r="H16" s="35">
         <f>IF($B16="","",Sales_Record!I23)</f>
         <v/>
       </c>
-      <c r="I16" s="110">
+      <c r="I16" s="176">
         <f>IF($B16="","",Sales_Record!J23)</f>
         <v/>
       </c>
@@ -4641,15 +4780,15 @@
         <f>IF($B17="","",Sales_Record!E24)</f>
         <v/>
       </c>
-      <c r="G17" s="108">
+      <c r="G17" s="159">
         <f>IF($B17="","",Sales_Record!H24)</f>
         <v/>
       </c>
-      <c r="H17" s="109">
+      <c r="H17" s="35">
         <f>IF($B17="","",Sales_Record!I24)</f>
         <v/>
       </c>
-      <c r="I17" s="110">
+      <c r="I17" s="176">
         <f>IF($B17="","",Sales_Record!J24)</f>
         <v/>
       </c>
@@ -4683,15 +4822,15 @@
         <f>IF($B18="","",Sales_Record!E25)</f>
         <v/>
       </c>
-      <c r="G18" s="108">
+      <c r="G18" s="159">
         <f>IF($B18="","",Sales_Record!H25)</f>
         <v/>
       </c>
-      <c r="H18" s="109">
+      <c r="H18" s="35">
         <f>IF($B18="","",Sales_Record!I25)</f>
         <v/>
       </c>
-      <c r="I18" s="110">
+      <c r="I18" s="176">
         <f>IF($B18="","",Sales_Record!J25)</f>
         <v/>
       </c>
@@ -4725,15 +4864,15 @@
         <f>IF($B19="","",Sales_Record!E26)</f>
         <v/>
       </c>
-      <c r="G19" s="108">
+      <c r="G19" s="159">
         <f>IF($B19="","",Sales_Record!H26)</f>
         <v/>
       </c>
-      <c r="H19" s="109">
+      <c r="H19" s="35">
         <f>IF($B19="","",Sales_Record!I26)</f>
         <v/>
       </c>
-      <c r="I19" s="110">
+      <c r="I19" s="176">
         <f>IF($B19="","",Sales_Record!J26)</f>
         <v/>
       </c>
@@ -4767,15 +4906,15 @@
         <f>IF($B20="","",Sales_Record!E27)</f>
         <v/>
       </c>
-      <c r="G20" s="108">
+      <c r="G20" s="159">
         <f>IF($B20="","",Sales_Record!H27)</f>
         <v/>
       </c>
-      <c r="H20" s="109">
+      <c r="H20" s="35">
         <f>IF($B20="","",Sales_Record!I27)</f>
         <v/>
       </c>
-      <c r="I20" s="110">
+      <c r="I20" s="176">
         <f>IF($B20="","",Sales_Record!J27)</f>
         <v/>
       </c>
@@ -4809,15 +4948,15 @@
         <f>IF($B21="","",Sales_Record!E28)</f>
         <v/>
       </c>
-      <c r="G21" s="108">
+      <c r="G21" s="159">
         <f>IF($B21="","",Sales_Record!H28)</f>
         <v/>
       </c>
-      <c r="H21" s="109">
+      <c r="H21" s="35">
         <f>IF($B21="","",Sales_Record!I28)</f>
         <v/>
       </c>
-      <c r="I21" s="110">
+      <c r="I21" s="176">
         <f>IF($B21="","",Sales_Record!J28)</f>
         <v/>
       </c>
@@ -4851,15 +4990,15 @@
         <f>IF($B22="","",Sales_Record!E29)</f>
         <v/>
       </c>
-      <c r="G22" s="108">
+      <c r="G22" s="159">
         <f>IF($B22="","",Sales_Record!H29)</f>
         <v/>
       </c>
-      <c r="H22" s="109">
+      <c r="H22" s="35">
         <f>IF($B22="","",Sales_Record!I29)</f>
         <v/>
       </c>
-      <c r="I22" s="110">
+      <c r="I22" s="176">
         <f>IF($B22="","",Sales_Record!J29)</f>
         <v/>
       </c>
@@ -4893,15 +5032,15 @@
         <f>IF($B23="","",Sales_Record!E30)</f>
         <v/>
       </c>
-      <c r="G23" s="108">
+      <c r="G23" s="159">
         <f>IF($B23="","",Sales_Record!H30)</f>
         <v/>
       </c>
-      <c r="H23" s="109">
+      <c r="H23" s="35">
         <f>IF($B23="","",Sales_Record!I30)</f>
         <v/>
       </c>
-      <c r="I23" s="110">
+      <c r="I23" s="176">
         <f>IF($B23="","",Sales_Record!J30)</f>
         <v/>
       </c>
@@ -4935,15 +5074,15 @@
         <f>IF($B24="","",Sales_Record!E31)</f>
         <v/>
       </c>
-      <c r="G24" s="108">
+      <c r="G24" s="159">
         <f>IF($B24="","",Sales_Record!H31)</f>
         <v/>
       </c>
-      <c r="H24" s="109">
+      <c r="H24" s="35">
         <f>IF($B24="","",Sales_Record!I31)</f>
         <v/>
       </c>
-      <c r="I24" s="110">
+      <c r="I24" s="176">
         <f>IF($B24="","",Sales_Record!J31)</f>
         <v/>
       </c>
@@ -4977,15 +5116,15 @@
         <f>IF($B25="","",Sales_Record!E32)</f>
         <v/>
       </c>
-      <c r="G25" s="108">
+      <c r="G25" s="159">
         <f>IF($B25="","",Sales_Record!H32)</f>
         <v/>
       </c>
-      <c r="H25" s="109">
+      <c r="H25" s="35">
         <f>IF($B25="","",Sales_Record!I32)</f>
         <v/>
       </c>
-      <c r="I25" s="110">
+      <c r="I25" s="176">
         <f>IF($B25="","",Sales_Record!J32)</f>
         <v/>
       </c>
@@ -5019,15 +5158,15 @@
         <f>IF($B26="","",Sales_Record!E33)</f>
         <v/>
       </c>
-      <c r="G26" s="108">
+      <c r="G26" s="159">
         <f>IF($B26="","",Sales_Record!H33)</f>
         <v/>
       </c>
-      <c r="H26" s="109">
+      <c r="H26" s="35">
         <f>IF($B26="","",Sales_Record!I33)</f>
         <v/>
       </c>
-      <c r="I26" s="110">
+      <c r="I26" s="176">
         <f>IF($B26="","",Sales_Record!J33)</f>
         <v/>
       </c>
@@ -5061,15 +5200,15 @@
         <f>IF($B27="","",Sales_Record!E34)</f>
         <v/>
       </c>
-      <c r="G27" s="108">
+      <c r="G27" s="159">
         <f>IF($B27="","",Sales_Record!H34)</f>
         <v/>
       </c>
-      <c r="H27" s="109">
+      <c r="H27" s="35">
         <f>IF($B27="","",Sales_Record!I34)</f>
         <v/>
       </c>
-      <c r="I27" s="110">
+      <c r="I27" s="176">
         <f>IF($B27="","",Sales_Record!J34)</f>
         <v/>
       </c>
@@ -5103,15 +5242,15 @@
         <f>IF($B28="","",Sales_Record!E35)</f>
         <v/>
       </c>
-      <c r="G28" s="108">
+      <c r="G28" s="159">
         <f>IF($B28="","",Sales_Record!H35)</f>
         <v/>
       </c>
-      <c r="H28" s="109">
+      <c r="H28" s="35">
         <f>IF($B28="","",Sales_Record!I35)</f>
         <v/>
       </c>
-      <c r="I28" s="110">
+      <c r="I28" s="176">
         <f>IF($B28="","",Sales_Record!J35)</f>
         <v/>
       </c>
@@ -5145,15 +5284,15 @@
         <f>IF($B29="","",Sales_Record!E36)</f>
         <v/>
       </c>
-      <c r="G29" s="108">
+      <c r="G29" s="159">
         <f>IF($B29="","",Sales_Record!H36)</f>
         <v/>
       </c>
-      <c r="H29" s="109">
+      <c r="H29" s="35">
         <f>IF($B29="","",Sales_Record!I36)</f>
         <v/>
       </c>
-      <c r="I29" s="110">
+      <c r="I29" s="176">
         <f>IF($B29="","",Sales_Record!J36)</f>
         <v/>
       </c>
@@ -5187,15 +5326,15 @@
         <f>IF($B30="","",Sales_Record!E37)</f>
         <v/>
       </c>
-      <c r="G30" s="108">
+      <c r="G30" s="159">
         <f>IF($B30="","",Sales_Record!H37)</f>
         <v/>
       </c>
-      <c r="H30" s="109">
+      <c r="H30" s="35">
         <f>IF($B30="","",Sales_Record!I37)</f>
         <v/>
       </c>
-      <c r="I30" s="110">
+      <c r="I30" s="176">
         <f>IF($B30="","",Sales_Record!J37)</f>
         <v/>
       </c>
@@ -5229,15 +5368,15 @@
         <f>IF($B31="","",Sales_Record!E38)</f>
         <v/>
       </c>
-      <c r="G31" s="108">
+      <c r="G31" s="159">
         <f>IF($B31="","",Sales_Record!H38)</f>
         <v/>
       </c>
-      <c r="H31" s="109">
+      <c r="H31" s="35">
         <f>IF($B31="","",Sales_Record!I38)</f>
         <v/>
       </c>
-      <c r="I31" s="110">
+      <c r="I31" s="176">
         <f>IF($B31="","",Sales_Record!J38)</f>
         <v/>
       </c>
@@ -5271,15 +5410,15 @@
         <f>IF($B32="","",Sales_Record!E39)</f>
         <v/>
       </c>
-      <c r="G32" s="108">
+      <c r="G32" s="159">
         <f>IF($B32="","",Sales_Record!H39)</f>
         <v/>
       </c>
-      <c r="H32" s="109">
+      <c r="H32" s="35">
         <f>IF($B32="","",Sales_Record!I39)</f>
         <v/>
       </c>
-      <c r="I32" s="110">
+      <c r="I32" s="176">
         <f>IF($B32="","",Sales_Record!J39)</f>
         <v/>
       </c>
@@ -5313,15 +5452,15 @@
         <f>IF($B33="","",Sales_Record!E40)</f>
         <v/>
       </c>
-      <c r="G33" s="108">
+      <c r="G33" s="159">
         <f>IF($B33="","",Sales_Record!H40)</f>
         <v/>
       </c>
-      <c r="H33" s="109">
+      <c r="H33" s="35">
         <f>IF($B33="","",Sales_Record!I40)</f>
         <v/>
       </c>
-      <c r="I33" s="110">
+      <c r="I33" s="176">
         <f>IF($B33="","",Sales_Record!J40)</f>
         <v/>
       </c>
@@ -5355,15 +5494,15 @@
         <f>IF($B34="","",Sales_Record!E41)</f>
         <v/>
       </c>
-      <c r="G34" s="108">
+      <c r="G34" s="159">
         <f>IF($B34="","",Sales_Record!H41)</f>
         <v/>
       </c>
-      <c r="H34" s="109">
+      <c r="H34" s="35">
         <f>IF($B34="","",Sales_Record!I41)</f>
         <v/>
       </c>
-      <c r="I34" s="110">
+      <c r="I34" s="176">
         <f>IF($B34="","",Sales_Record!J41)</f>
         <v/>
       </c>
@@ -5397,15 +5536,15 @@
         <f>IF($B35="","",Sales_Record!E42)</f>
         <v/>
       </c>
-      <c r="G35" s="108">
+      <c r="G35" s="159">
         <f>IF($B35="","",Sales_Record!H42)</f>
         <v/>
       </c>
-      <c r="H35" s="109">
+      <c r="H35" s="35">
         <f>IF($B35="","",Sales_Record!I42)</f>
         <v/>
       </c>
-      <c r="I35" s="110">
+      <c r="I35" s="176">
         <f>IF($B35="","",Sales_Record!J42)</f>
         <v/>
       </c>
@@ -5439,15 +5578,15 @@
         <f>IF($B36="","",Sales_Record!E43)</f>
         <v/>
       </c>
-      <c r="G36" s="108">
+      <c r="G36" s="159">
         <f>IF($B36="","",Sales_Record!H43)</f>
         <v/>
       </c>
-      <c r="H36" s="109">
+      <c r="H36" s="35">
         <f>IF($B36="","",Sales_Record!I43)</f>
         <v/>
       </c>
-      <c r="I36" s="110">
+      <c r="I36" s="176">
         <f>IF($B36="","",Sales_Record!J43)</f>
         <v/>
       </c>
@@ -5481,15 +5620,15 @@
         <f>IF($B37="","",Sales_Record!E44)</f>
         <v/>
       </c>
-      <c r="G37" s="108">
+      <c r="G37" s="159">
         <f>IF($B37="","",Sales_Record!H44)</f>
         <v/>
       </c>
-      <c r="H37" s="109">
+      <c r="H37" s="35">
         <f>IF($B37="","",Sales_Record!I44)</f>
         <v/>
       </c>
-      <c r="I37" s="110">
+      <c r="I37" s="176">
         <f>IF($B37="","",Sales_Record!J44)</f>
         <v/>
       </c>
@@ -5523,15 +5662,15 @@
         <f>IF($B38="","",Sales_Record!E45)</f>
         <v/>
       </c>
-      <c r="G38" s="108">
+      <c r="G38" s="159">
         <f>IF($B38="","",Sales_Record!H45)</f>
         <v/>
       </c>
-      <c r="H38" s="109">
+      <c r="H38" s="35">
         <f>IF($B38="","",Sales_Record!I45)</f>
         <v/>
       </c>
-      <c r="I38" s="110">
+      <c r="I38" s="176">
         <f>IF($B38="","",Sales_Record!J45)</f>
         <v/>
       </c>
@@ -5565,15 +5704,15 @@
         <f>IF($B39="","",Sales_Record!E46)</f>
         <v/>
       </c>
-      <c r="G39" s="108">
+      <c r="G39" s="159">
         <f>IF($B39="","",Sales_Record!H46)</f>
         <v/>
       </c>
-      <c r="H39" s="109">
+      <c r="H39" s="35">
         <f>IF($B39="","",Sales_Record!I46)</f>
         <v/>
       </c>
-      <c r="I39" s="110">
+      <c r="I39" s="176">
         <f>IF($B39="","",Sales_Record!J46)</f>
         <v/>
       </c>
@@ -5607,15 +5746,15 @@
         <f>IF($B40="","",Sales_Record!E47)</f>
         <v/>
       </c>
-      <c r="G40" s="108">
+      <c r="G40" s="159">
         <f>IF($B40="","",Sales_Record!H47)</f>
         <v/>
       </c>
-      <c r="H40" s="109">
+      <c r="H40" s="35">
         <f>IF($B40="","",Sales_Record!I47)</f>
         <v/>
       </c>
-      <c r="I40" s="110">
+      <c r="I40" s="176">
         <f>IF($B40="","",Sales_Record!J47)</f>
         <v/>
       </c>
@@ -5649,15 +5788,15 @@
         <f>IF($B41="","",Sales_Record!E48)</f>
         <v/>
       </c>
-      <c r="G41" s="108">
+      <c r="G41" s="159">
         <f>IF($B41="","",Sales_Record!H48)</f>
         <v/>
       </c>
-      <c r="H41" s="109">
+      <c r="H41" s="35">
         <f>IF($B41="","",Sales_Record!I48)</f>
         <v/>
       </c>
-      <c r="I41" s="110">
+      <c r="I41" s="176">
         <f>IF($B41="","",Sales_Record!J48)</f>
         <v/>
       </c>
@@ -5691,15 +5830,15 @@
         <f>IF($B42="","",Sales_Record!E49)</f>
         <v/>
       </c>
-      <c r="G42" s="108">
+      <c r="G42" s="159">
         <f>IF($B42="","",Sales_Record!H49)</f>
         <v/>
       </c>
-      <c r="H42" s="109">
+      <c r="H42" s="35">
         <f>IF($B42="","",Sales_Record!I49)</f>
         <v/>
       </c>
-      <c r="I42" s="110">
+      <c r="I42" s="176">
         <f>IF($B42="","",Sales_Record!J49)</f>
         <v/>
       </c>
@@ -5733,15 +5872,15 @@
         <f>IF($B43="","",Sales_Record!E50)</f>
         <v/>
       </c>
-      <c r="G43" s="108">
+      <c r="G43" s="159">
         <f>IF($B43="","",Sales_Record!H50)</f>
         <v/>
       </c>
-      <c r="H43" s="109">
+      <c r="H43" s="35">
         <f>IF($B43="","",Sales_Record!I50)</f>
         <v/>
       </c>
-      <c r="I43" s="110">
+      <c r="I43" s="176">
         <f>IF($B43="","",Sales_Record!J50)</f>
         <v/>
       </c>
@@ -5775,15 +5914,15 @@
         <f>IF($B44="","",Sales_Record!E51)</f>
         <v/>
       </c>
-      <c r="G44" s="108">
+      <c r="G44" s="159">
         <f>IF($B44="","",Sales_Record!H51)</f>
         <v/>
       </c>
-      <c r="H44" s="109">
+      <c r="H44" s="35">
         <f>IF($B44="","",Sales_Record!I51)</f>
         <v/>
       </c>
-      <c r="I44" s="110">
+      <c r="I44" s="176">
         <f>IF($B44="","",Sales_Record!J51)</f>
         <v/>
       </c>
@@ -5817,15 +5956,15 @@
         <f>IF($B45="","",Sales_Record!E52)</f>
         <v/>
       </c>
-      <c r="G45" s="108">
+      <c r="G45" s="159">
         <f>IF($B45="","",Sales_Record!H52)</f>
         <v/>
       </c>
-      <c r="H45" s="109">
+      <c r="H45" s="35">
         <f>IF($B45="","",Sales_Record!I52)</f>
         <v/>
       </c>
-      <c r="I45" s="110">
+      <c r="I45" s="176">
         <f>IF($B45="","",Sales_Record!J52)</f>
         <v/>
       </c>
@@ -5835,7 +5974,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="121" t="inlineStr">
+      <c r="A46" s="165" t="inlineStr">
         <is>
           <t>รวมรายได้ทั้งหมด</t>
         </is>
@@ -5845,22 +5984,24 @@
       <c r="D46" s="84" t="n"/>
       <c r="E46" s="84" t="n"/>
       <c r="F46" s="85" t="n"/>
-      <c r="G46" s="124">
+      <c r="G46" s="166">
         <f>SUM(G6:G45)</f>
         <v/>
       </c>
-      <c r="H46" s="113">
+      <c r="H46" s="177">
         <f>COUNT(A6:A45)</f>
         <v/>
       </c>
-      <c r="I46" s="124">
+      <c r="I46" s="166">
         <f>SUM(I6:I45)</f>
         <v/>
       </c>
-      <c r="J46" s="121" t="n"/>
-    </row>
+      <c r="J46" s="165" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48"/>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="128" t="inlineStr">
+      <c r="A49" s="167" t="inlineStr">
         <is>
           <t>หมายเหตุ / วิธีใช้</t>
         </is>
@@ -5893,7 +6034,7 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="139" t="inlineStr">
+      <c r="A53" s="127" t="inlineStr">
         <is>
           <t>• ทั้งแผ่นเป็นช่องคำนวณ ล็อกไว้ทั้งหมด (ไม่ต้องกรอก) · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>
@@ -5923,7 +6064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:G27"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5949,33 +6090,34 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="175" t="inlineStr">
         <is>
           <t>พนักงานขาย</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="175" t="inlineStr">
         <is>
           <t>จำนวนดีล</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="175" t="inlineStr">
         <is>
           <t>รายได้ (บาท)</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="175" t="inlineStr">
         <is>
           <t>ค่าคอม (บาท)</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="175" t="inlineStr">
         <is>
           <t>จ่ายแล้ว (บาท)</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="175" t="inlineStr">
         <is>
           <t>ค้างจ่าย (บาท)</t>
         </is>
@@ -5990,19 +6132,19 @@
         <f>IF($B5="","",'ทีมขาย'!D6)</f>
         <v/>
       </c>
-      <c r="D5" s="63">
+      <c r="D5" s="50">
         <f>IF($B5="","",'ทีมขาย'!E6)</f>
         <v/>
       </c>
-      <c r="E5" s="64">
+      <c r="E5" s="178">
         <f>IF($B5="","",'ทีมขาย'!F6)</f>
         <v/>
       </c>
-      <c r="F5" s="63">
+      <c r="F5" s="50">
         <f>IF($B5="","",'ทีมขาย'!G6)</f>
         <v/>
       </c>
-      <c r="G5" s="63">
+      <c r="G5" s="50">
         <f>IF($B5="","",'ทีมขาย'!H6)</f>
         <v/>
       </c>
@@ -6016,19 +6158,19 @@
         <f>IF($B6="","",'ทีมขาย'!D7)</f>
         <v/>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="50">
         <f>IF($B6="","",'ทีมขาย'!E7)</f>
         <v/>
       </c>
-      <c r="E6" s="64">
+      <c r="E6" s="178">
         <f>IF($B6="","",'ทีมขาย'!F7)</f>
         <v/>
       </c>
-      <c r="F6" s="63">
+      <c r="F6" s="50">
         <f>IF($B6="","",'ทีมขาย'!G7)</f>
         <v/>
       </c>
-      <c r="G6" s="63">
+      <c r="G6" s="50">
         <f>IF($B6="","",'ทีมขาย'!H7)</f>
         <v/>
       </c>
@@ -6042,19 +6184,19 @@
         <f>IF($B7="","",'ทีมขาย'!D8)</f>
         <v/>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="50">
         <f>IF($B7="","",'ทีมขาย'!E8)</f>
         <v/>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="178">
         <f>IF($B7="","",'ทีมขาย'!F8)</f>
         <v/>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="50">
         <f>IF($B7="","",'ทีมขาย'!G8)</f>
         <v/>
       </c>
-      <c r="G7" s="63">
+      <c r="G7" s="50">
         <f>IF($B7="","",'ทีมขาย'!H8)</f>
         <v/>
       </c>
@@ -6068,19 +6210,19 @@
         <f>IF($B8="","",'ทีมขาย'!D9)</f>
         <v/>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="50">
         <f>IF($B8="","",'ทีมขาย'!E9)</f>
         <v/>
       </c>
-      <c r="E8" s="64">
+      <c r="E8" s="178">
         <f>IF($B8="","",'ทีมขาย'!F9)</f>
         <v/>
       </c>
-      <c r="F8" s="63">
+      <c r="F8" s="50">
         <f>IF($B8="","",'ทีมขาย'!G9)</f>
         <v/>
       </c>
-      <c r="G8" s="63">
+      <c r="G8" s="50">
         <f>IF($B8="","",'ทีมขาย'!H9)</f>
         <v/>
       </c>
@@ -6094,19 +6236,19 @@
         <f>IF($B9="","",'ทีมขาย'!D10)</f>
         <v/>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="50">
         <f>IF($B9="","",'ทีมขาย'!E10)</f>
         <v/>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="178">
         <f>IF($B9="","",'ทีมขาย'!F10)</f>
         <v/>
       </c>
-      <c r="F9" s="63">
+      <c r="F9" s="50">
         <f>IF($B9="","",'ทีมขาย'!G10)</f>
         <v/>
       </c>
-      <c r="G9" s="63">
+      <c r="G9" s="50">
         <f>IF($B9="","",'ทีมขาย'!H10)</f>
         <v/>
       </c>
@@ -6120,19 +6262,19 @@
         <f>IF($B10="","",'ทีมขาย'!D11)</f>
         <v/>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="50">
         <f>IF($B10="","",'ทีมขาย'!E11)</f>
         <v/>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="178">
         <f>IF($B10="","",'ทีมขาย'!F11)</f>
         <v/>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="50">
         <f>IF($B10="","",'ทีมขาย'!G11)</f>
         <v/>
       </c>
-      <c r="G10" s="63">
+      <c r="G10" s="50">
         <f>IF($B10="","",'ทีมขาย'!H11)</f>
         <v/>
       </c>
@@ -6146,19 +6288,19 @@
         <f>IF($B11="","",'ทีมขาย'!D12)</f>
         <v/>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="50">
         <f>IF($B11="","",'ทีมขาย'!E12)</f>
         <v/>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="178">
         <f>IF($B11="","",'ทีมขาย'!F12)</f>
         <v/>
       </c>
-      <c r="F11" s="63">
+      <c r="F11" s="50">
         <f>IF($B11="","",'ทีมขาย'!G12)</f>
         <v/>
       </c>
-      <c r="G11" s="63">
+      <c r="G11" s="50">
         <f>IF($B11="","",'ทีมขาย'!H12)</f>
         <v/>
       </c>
@@ -6172,19 +6314,19 @@
         <f>IF($B12="","",'ทีมขาย'!D13)</f>
         <v/>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="50">
         <f>IF($B12="","",'ทีมขาย'!E13)</f>
         <v/>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="178">
         <f>IF($B12="","",'ทีมขาย'!F13)</f>
         <v/>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="50">
         <f>IF($B12="","",'ทีมขาย'!G13)</f>
         <v/>
       </c>
-      <c r="G12" s="63">
+      <c r="G12" s="50">
         <f>IF($B12="","",'ทีมขาย'!H13)</f>
         <v/>
       </c>
@@ -6198,19 +6340,19 @@
         <f>IF($B13="","",'ทีมขาย'!D14)</f>
         <v/>
       </c>
-      <c r="D13" s="63">
+      <c r="D13" s="50">
         <f>IF($B13="","",'ทีมขาย'!E14)</f>
         <v/>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="178">
         <f>IF($B13="","",'ทีมขาย'!F14)</f>
         <v/>
       </c>
-      <c r="F13" s="63">
+      <c r="F13" s="50">
         <f>IF($B13="","",'ทีมขาย'!G14)</f>
         <v/>
       </c>
-      <c r="G13" s="63">
+      <c r="G13" s="50">
         <f>IF($B13="","",'ทีมขาย'!H14)</f>
         <v/>
       </c>
@@ -6224,19 +6366,19 @@
         <f>IF($B14="","",'ทีมขาย'!D15)</f>
         <v/>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="50">
         <f>IF($B14="","",'ทีมขาย'!E15)</f>
         <v/>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="178">
         <f>IF($B14="","",'ทีมขาย'!F15)</f>
         <v/>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="50">
         <f>IF($B14="","",'ทีมขาย'!G15)</f>
         <v/>
       </c>
-      <c r="G14" s="63">
+      <c r="G14" s="50">
         <f>IF($B14="","",'ทีมขาย'!H15)</f>
         <v/>
       </c>
@@ -6250,19 +6392,19 @@
         <f>IF($B15="","",'ทีมขาย'!D16)</f>
         <v/>
       </c>
-      <c r="D15" s="63">
+      <c r="D15" s="50">
         <f>IF($B15="","",'ทีมขาย'!E16)</f>
         <v/>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="178">
         <f>IF($B15="","",'ทีมขาย'!F16)</f>
         <v/>
       </c>
-      <c r="F15" s="63">
+      <c r="F15" s="50">
         <f>IF($B15="","",'ทีมขาย'!G16)</f>
         <v/>
       </c>
-      <c r="G15" s="63">
+      <c r="G15" s="50">
         <f>IF($B15="","",'ทีมขาย'!H16)</f>
         <v/>
       </c>
@@ -6276,19 +6418,19 @@
         <f>IF($B16="","",'ทีมขาย'!D17)</f>
         <v/>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="50">
         <f>IF($B16="","",'ทีมขาย'!E17)</f>
         <v/>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="178">
         <f>IF($B16="","",'ทีมขาย'!F17)</f>
         <v/>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="50">
         <f>IF($B16="","",'ทีมขาย'!G17)</f>
         <v/>
       </c>
-      <c r="G16" s="63">
+      <c r="G16" s="50">
         <f>IF($B16="","",'ทีมขาย'!H17)</f>
         <v/>
       </c>
@@ -6302,19 +6444,19 @@
         <f>IF($B17="","",'ทีมขาย'!D18)</f>
         <v/>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="50">
         <f>IF($B17="","",'ทีมขาย'!E18)</f>
         <v/>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="178">
         <f>IF($B17="","",'ทีมขาย'!F18)</f>
         <v/>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="50">
         <f>IF($B17="","",'ทีมขาย'!G18)</f>
         <v/>
       </c>
-      <c r="G17" s="63">
+      <c r="G17" s="50">
         <f>IF($B17="","",'ทีมขาย'!H18)</f>
         <v/>
       </c>
@@ -6328,19 +6470,19 @@
         <f>IF($B18="","",'ทีมขาย'!D19)</f>
         <v/>
       </c>
-      <c r="D18" s="63">
+      <c r="D18" s="50">
         <f>IF($B18="","",'ทีมขาย'!E19)</f>
         <v/>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="178">
         <f>IF($B18="","",'ทีมขาย'!F19)</f>
         <v/>
       </c>
-      <c r="F18" s="63">
+      <c r="F18" s="50">
         <f>IF($B18="","",'ทีมขาย'!G19)</f>
         <v/>
       </c>
-      <c r="G18" s="63">
+      <c r="G18" s="50">
         <f>IF($B18="","",'ทีมขาย'!H19)</f>
         <v/>
       </c>
@@ -6354,19 +6496,19 @@
         <f>IF($B19="","",'ทีมขาย'!D20)</f>
         <v/>
       </c>
-      <c r="D19" s="63">
+      <c r="D19" s="50">
         <f>IF($B19="","",'ทีมขาย'!E20)</f>
         <v/>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="178">
         <f>IF($B19="","",'ทีมขาย'!F20)</f>
         <v/>
       </c>
-      <c r="F19" s="63">
+      <c r="F19" s="50">
         <f>IF($B19="","",'ทีมขาย'!G20)</f>
         <v/>
       </c>
-      <c r="G19" s="63">
+      <c r="G19" s="50">
         <f>IF($B19="","",'ทีมขาย'!H20)</f>
         <v/>
       </c>
@@ -6381,25 +6523,27 @@
         <f>SUM(C5:C19)</f>
         <v/>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="50">
         <f>SUM(D5:D19)</f>
         <v/>
       </c>
-      <c r="E20" s="64">
+      <c r="E20" s="178">
         <f>SUM(E5:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="63">
+      <c r="F20" s="50">
         <f>SUM(F5:F19)</f>
         <v/>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="50">
         <f>SUM(G5:G19)</f>
         <v/>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="128" t="inlineStr">
+      <c r="B23" s="167" t="inlineStr">
         <is>
           <t>หมายเหตุ / วิธีใช้</t>
         </is>
@@ -6432,7 +6576,7 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="139" t="inlineStr">
+      <c r="B27" s="127" t="inlineStr">
         <is>
           <t>• ทั้งแผ่นคำนวณอัตโนมัติ ล็อกไว้ทั้งหมด · ปลดล็อก: Review ▸ Unprotect Sheet</t>
         </is>

--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -1452,12 +1452,12 @@
         </is>
       </c>
       <c r="H13" s="35">
-        <f>IF(G13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I13" s="19" t="n"/>
       <c r="J13" s="36">
-        <f>IF(H13="","",H13*(1-IF(I13="",0,I13)))</f>
+        <f>IF(D13="","",H13*(1-N(I13)))</f>
         <v/>
       </c>
       <c r="K13" s="18" t="inlineStr">
@@ -1467,11 +1467,11 @@
       </c>
       <c r="L13" s="18" t="n"/>
       <c r="M13" s="5">
-        <f>IF(G13="","",IFERROR(IF(E13="ต่ออายุ",VLOOKUP(G13,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G13,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$E$7,IF(E13="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N13" s="37">
-        <f>IF(OR(J13="",M13=""),"",IF(P13="Y",0,IF(F13="จ่ายแล้ว",ROUND(J13*M13,2),0)))</f>
+        <f>IF(D13="","",ROUND(IFERROR(J13*M13,0)*(F13="จ่ายแล้ว")*(P13&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O13" s="18" t="inlineStr">
@@ -1495,22 +1495,22 @@
       <c r="F14" s="22" t="n"/>
       <c r="G14" s="22" t="n"/>
       <c r="H14" s="38">
-        <f>IF(G14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I14" s="23" t="n"/>
       <c r="J14" s="39">
-        <f>IF(H14="","",H14*(1-IF(I14="",0,I14)))</f>
+        <f>IF(D14="","",H14*(1-N(I14)))</f>
         <v/>
       </c>
       <c r="K14" s="22" t="n"/>
       <c r="L14" s="22" t="n"/>
       <c r="M14" s="7">
-        <f>IF(G14="","",IFERROR(IF(E14="ต่ออายุ",VLOOKUP(G14,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G14,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$E$7,IF(E14="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N14" s="37">
-        <f>IF(OR(J14="",M14=""),"",IF(P14="Y",0,IF(F14="จ่ายแล้ว",ROUND(J14*M14,2),0)))</f>
+        <f>IF(D14="","",ROUND(IFERROR(J14*M14,0)*(F14="จ่ายแล้ว")*(P14&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O14" s="22" t="n"/>
@@ -1530,22 +1530,22 @@
       <c r="F15" s="18" t="n"/>
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="35">
-        <f>IF(G15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I15" s="19" t="n"/>
       <c r="J15" s="36">
-        <f>IF(H15="","",H15*(1-IF(I15="",0,I15)))</f>
+        <f>IF(D15="","",H15*(1-N(I15)))</f>
         <v/>
       </c>
       <c r="K15" s="18" t="n"/>
       <c r="L15" s="18" t="n"/>
       <c r="M15" s="5">
-        <f>IF(G15="","",IFERROR(IF(E15="ต่ออายุ",VLOOKUP(G15,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G15,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$E$7,IF(E15="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N15" s="37">
-        <f>IF(OR(J15="",M15=""),"",IF(P15="Y",0,IF(F15="จ่ายแล้ว",ROUND(J15*M15,2),0)))</f>
+        <f>IF(D15="","",ROUND(IFERROR(J15*M15,0)*(F15="จ่ายแล้ว")*(P15&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O15" s="18" t="n"/>
@@ -1565,22 +1565,22 @@
       <c r="F16" s="22" t="n"/>
       <c r="G16" s="22" t="n"/>
       <c r="H16" s="38">
-        <f>IF(G16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I16" s="23" t="n"/>
       <c r="J16" s="39">
-        <f>IF(H16="","",H16*(1-IF(I16="",0,I16)))</f>
+        <f>IF(D16="","",H16*(1-N(I16)))</f>
         <v/>
       </c>
       <c r="K16" s="22" t="n"/>
       <c r="L16" s="22" t="n"/>
       <c r="M16" s="7">
-        <f>IF(G16="","",IFERROR(IF(E16="ต่ออายุ",VLOOKUP(G16,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G16,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$E$7,IF(E16="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N16" s="37">
-        <f>IF(OR(J16="",M16=""),"",IF(P16="Y",0,IF(F16="จ่ายแล้ว",ROUND(J16*M16,2),0)))</f>
+        <f>IF(D16="","",ROUND(IFERROR(J16*M16,0)*(F16="จ่ายแล้ว")*(P16&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O16" s="22" t="n"/>
@@ -1600,22 +1600,22 @@
       <c r="F17" s="18" t="n"/>
       <c r="G17" s="18" t="n"/>
       <c r="H17" s="35">
-        <f>IF(G17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I17" s="19" t="n"/>
       <c r="J17" s="36">
-        <f>IF(H17="","",H17*(1-IF(I17="",0,I17)))</f>
+        <f>IF(D17="","",H17*(1-N(I17)))</f>
         <v/>
       </c>
       <c r="K17" s="18" t="n"/>
       <c r="L17" s="18" t="n"/>
       <c r="M17" s="5">
-        <f>IF(G17="","",IFERROR(IF(E17="ต่ออายุ",VLOOKUP(G17,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G17,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$E$7,IF(E17="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N17" s="37">
-        <f>IF(OR(J17="",M17=""),"",IF(P17="Y",0,IF(F17="จ่ายแล้ว",ROUND(J17*M17,2),0)))</f>
+        <f>IF(D17="","",ROUND(IFERROR(J17*M17,0)*(F17="จ่ายแล้ว")*(P17&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O17" s="18" t="n"/>
@@ -1635,22 +1635,22 @@
       <c r="F18" s="22" t="n"/>
       <c r="G18" s="22" t="n"/>
       <c r="H18" s="38">
-        <f>IF(G18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I18" s="23" t="n"/>
       <c r="J18" s="39">
-        <f>IF(H18="","",H18*(1-IF(I18="",0,I18)))</f>
+        <f>IF(D18="","",H18*(1-N(I18)))</f>
         <v/>
       </c>
       <c r="K18" s="22" t="n"/>
       <c r="L18" s="22" t="n"/>
       <c r="M18" s="7">
-        <f>IF(G18="","",IFERROR(IF(E18="ต่ออายุ",VLOOKUP(G18,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G18,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$E$7,IF(E18="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N18" s="37">
-        <f>IF(OR(J18="",M18=""),"",IF(P18="Y",0,IF(F18="จ่ายแล้ว",ROUND(J18*M18,2),0)))</f>
+        <f>IF(D18="","",ROUND(IFERROR(J18*M18,0)*(F18="จ่ายแล้ว")*(P18&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O18" s="22" t="n"/>
@@ -1670,22 +1670,22 @@
       <c r="F19" s="18" t="n"/>
       <c r="G19" s="18" t="n"/>
       <c r="H19" s="35">
-        <f>IF(G19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I19" s="19" t="n"/>
       <c r="J19" s="36">
-        <f>IF(H19="","",H19*(1-IF(I19="",0,I19)))</f>
+        <f>IF(D19="","",H19*(1-N(I19)))</f>
         <v/>
       </c>
       <c r="K19" s="18" t="n"/>
       <c r="L19" s="18" t="n"/>
       <c r="M19" s="5">
-        <f>IF(G19="","",IFERROR(IF(E19="ต่ออายุ",VLOOKUP(G19,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G19,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$E$7,IF(E19="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N19" s="37">
-        <f>IF(OR(J19="",M19=""),"",IF(P19="Y",0,IF(F19="จ่ายแล้ว",ROUND(J19*M19,2),0)))</f>
+        <f>IF(D19="","",ROUND(IFERROR(J19*M19,0)*(F19="จ่ายแล้ว")*(P19&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O19" s="18" t="n"/>
@@ -1705,22 +1705,22 @@
       <c r="F20" s="22" t="n"/>
       <c r="G20" s="22" t="n"/>
       <c r="H20" s="38">
-        <f>IF(G20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I20" s="23" t="n"/>
       <c r="J20" s="39">
-        <f>IF(H20="","",H20*(1-IF(I20="",0,I20)))</f>
+        <f>IF(D20="","",H20*(1-N(I20)))</f>
         <v/>
       </c>
       <c r="K20" s="22" t="n"/>
       <c r="L20" s="22" t="n"/>
       <c r="M20" s="7">
-        <f>IF(G20="","",IFERROR(IF(E20="ต่ออายุ",VLOOKUP(G20,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G20,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$E$7,IF(E20="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N20" s="37">
-        <f>IF(OR(J20="",M20=""),"",IF(P20="Y",0,IF(F20="จ่ายแล้ว",ROUND(J20*M20,2),0)))</f>
+        <f>IF(D20="","",ROUND(IFERROR(J20*M20,0)*(F20="จ่ายแล้ว")*(P20&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O20" s="22" t="n"/>
@@ -1740,22 +1740,22 @@
       <c r="F21" s="18" t="n"/>
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="35">
-        <f>IF(G21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I21" s="19" t="n"/>
       <c r="J21" s="36">
-        <f>IF(H21="","",H21*(1-IF(I21="",0,I21)))</f>
+        <f>IF(D21="","",H21*(1-N(I21)))</f>
         <v/>
       </c>
       <c r="K21" s="18" t="n"/>
       <c r="L21" s="18" t="n"/>
       <c r="M21" s="5">
-        <f>IF(G21="","",IFERROR(IF(E21="ต่ออายุ",VLOOKUP(G21,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G21,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$E$7,IF(E21="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N21" s="37">
-        <f>IF(OR(J21="",M21=""),"",IF(P21="Y",0,IF(F21="จ่ายแล้ว",ROUND(J21*M21,2),0)))</f>
+        <f>IF(D21="","",ROUND(IFERROR(J21*M21,0)*(F21="จ่ายแล้ว")*(P21&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O21" s="18" t="n"/>
@@ -1775,22 +1775,22 @@
       <c r="F22" s="22" t="n"/>
       <c r="G22" s="22" t="n"/>
       <c r="H22" s="38">
-        <f>IF(G22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I22" s="23" t="n"/>
       <c r="J22" s="39">
-        <f>IF(H22="","",H22*(1-IF(I22="",0,I22)))</f>
+        <f>IF(D22="","",H22*(1-N(I22)))</f>
         <v/>
       </c>
       <c r="K22" s="22" t="n"/>
       <c r="L22" s="22" t="n"/>
       <c r="M22" s="7">
-        <f>IF(G22="","",IFERROR(IF(E22="ต่ออายุ",VLOOKUP(G22,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G22,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$E$7,IF(E22="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N22" s="37">
-        <f>IF(OR(J22="",M22=""),"",IF(P22="Y",0,IF(F22="จ่ายแล้ว",ROUND(J22*M22,2),0)))</f>
+        <f>IF(D22="","",ROUND(IFERROR(J22*M22,0)*(F22="จ่ายแล้ว")*(P22&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O22" s="22" t="n"/>
@@ -1810,22 +1810,22 @@
       <c r="F23" s="18" t="n"/>
       <c r="G23" s="18" t="n"/>
       <c r="H23" s="35">
-        <f>IF(G23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I23" s="19" t="n"/>
       <c r="J23" s="36">
-        <f>IF(H23="","",H23*(1-IF(I23="",0,I23)))</f>
+        <f>IF(D23="","",H23*(1-N(I23)))</f>
         <v/>
       </c>
       <c r="K23" s="18" t="n"/>
       <c r="L23" s="18" t="n"/>
       <c r="M23" s="5">
-        <f>IF(G23="","",IFERROR(IF(E23="ต่ออายุ",VLOOKUP(G23,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G23,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$E$7,IF(E23="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N23" s="37">
-        <f>IF(OR(J23="",M23=""),"",IF(P23="Y",0,IF(F23="จ่ายแล้ว",ROUND(J23*M23,2),0)))</f>
+        <f>IF(D23="","",ROUND(IFERROR(J23*M23,0)*(F23="จ่ายแล้ว")*(P23&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O23" s="18" t="n"/>
@@ -1845,22 +1845,22 @@
       <c r="F24" s="22" t="n"/>
       <c r="G24" s="22" t="n"/>
       <c r="H24" s="38">
-        <f>IF(G24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I24" s="23" t="n"/>
       <c r="J24" s="39">
-        <f>IF(H24="","",H24*(1-IF(I24="",0,I24)))</f>
+        <f>IF(D24="","",H24*(1-N(I24)))</f>
         <v/>
       </c>
       <c r="K24" s="22" t="n"/>
       <c r="L24" s="22" t="n"/>
       <c r="M24" s="7">
-        <f>IF(G24="","",IFERROR(IF(E24="ต่ออายุ",VLOOKUP(G24,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G24,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$E$7,IF(E24="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N24" s="37">
-        <f>IF(OR(J24="",M24=""),"",IF(P24="Y",0,IF(F24="จ่ายแล้ว",ROUND(J24*M24,2),0)))</f>
+        <f>IF(D24="","",ROUND(IFERROR(J24*M24,0)*(F24="จ่ายแล้ว")*(P24&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O24" s="22" t="n"/>
@@ -1880,22 +1880,22 @@
       <c r="F25" s="18" t="n"/>
       <c r="G25" s="18" t="n"/>
       <c r="H25" s="35">
-        <f>IF(G25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I25" s="19" t="n"/>
       <c r="J25" s="36">
-        <f>IF(H25="","",H25*(1-IF(I25="",0,I25)))</f>
+        <f>IF(D25="","",H25*(1-N(I25)))</f>
         <v/>
       </c>
       <c r="K25" s="18" t="n"/>
       <c r="L25" s="18" t="n"/>
       <c r="M25" s="5">
-        <f>IF(G25="","",IFERROR(IF(E25="ต่ออายุ",VLOOKUP(G25,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G25,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$E$7,IF(E25="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N25" s="37">
-        <f>IF(OR(J25="",M25=""),"",IF(P25="Y",0,IF(F25="จ่ายแล้ว",ROUND(J25*M25,2),0)))</f>
+        <f>IF(D25="","",ROUND(IFERROR(J25*M25,0)*(F25="จ่ายแล้ว")*(P25&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O25" s="18" t="n"/>
@@ -1915,22 +1915,22 @@
       <c r="F26" s="22" t="n"/>
       <c r="G26" s="22" t="n"/>
       <c r="H26" s="38">
-        <f>IF(G26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I26" s="23" t="n"/>
       <c r="J26" s="39">
-        <f>IF(H26="","",H26*(1-IF(I26="",0,I26)))</f>
+        <f>IF(D26="","",H26*(1-N(I26)))</f>
         <v/>
       </c>
       <c r="K26" s="22" t="n"/>
       <c r="L26" s="22" t="n"/>
       <c r="M26" s="7">
-        <f>IF(G26="","",IFERROR(IF(E26="ต่ออายุ",VLOOKUP(G26,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G26,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$E$7,IF(E26="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N26" s="37">
-        <f>IF(OR(J26="",M26=""),"",IF(P26="Y",0,IF(F26="จ่ายแล้ว",ROUND(J26*M26,2),0)))</f>
+        <f>IF(D26="","",ROUND(IFERROR(J26*M26,0)*(F26="จ่ายแล้ว")*(P26&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O26" s="22" t="n"/>
@@ -1950,22 +1950,22 @@
       <c r="F27" s="18" t="n"/>
       <c r="G27" s="18" t="n"/>
       <c r="H27" s="35">
-        <f>IF(G27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I27" s="19" t="n"/>
       <c r="J27" s="36">
-        <f>IF(H27="","",H27*(1-IF(I27="",0,I27)))</f>
+        <f>IF(D27="","",H27*(1-N(I27)))</f>
         <v/>
       </c>
       <c r="K27" s="18" t="n"/>
       <c r="L27" s="18" t="n"/>
       <c r="M27" s="5">
-        <f>IF(G27="","",IFERROR(IF(E27="ต่ออายุ",VLOOKUP(G27,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G27,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$E$7,IF(E27="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N27" s="37">
-        <f>IF(OR(J27="",M27=""),"",IF(P27="Y",0,IF(F27="จ่ายแล้ว",ROUND(J27*M27,2),0)))</f>
+        <f>IF(D27="","",ROUND(IFERROR(J27*M27,0)*(F27="จ่ายแล้ว")*(P27&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O27" s="18" t="n"/>
@@ -1985,22 +1985,22 @@
       <c r="F28" s="22" t="n"/>
       <c r="G28" s="22" t="n"/>
       <c r="H28" s="38">
-        <f>IF(G28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I28" s="23" t="n"/>
       <c r="J28" s="39">
-        <f>IF(H28="","",H28*(1-IF(I28="",0,I28)))</f>
+        <f>IF(D28="","",H28*(1-N(I28)))</f>
         <v/>
       </c>
       <c r="K28" s="22" t="n"/>
       <c r="L28" s="22" t="n"/>
       <c r="M28" s="7">
-        <f>IF(G28="","",IFERROR(IF(E28="ต่ออายุ",VLOOKUP(G28,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G28,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$E$7,IF(E28="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N28" s="37">
-        <f>IF(OR(J28="",M28=""),"",IF(P28="Y",0,IF(F28="จ่ายแล้ว",ROUND(J28*M28,2),0)))</f>
+        <f>IF(D28="","",ROUND(IFERROR(J28*M28,0)*(F28="จ่ายแล้ว")*(P28&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O28" s="22" t="n"/>
@@ -2020,22 +2020,22 @@
       <c r="F29" s="18" t="n"/>
       <c r="G29" s="18" t="n"/>
       <c r="H29" s="35">
-        <f>IF(G29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I29" s="19" t="n"/>
       <c r="J29" s="36">
-        <f>IF(H29="","",H29*(1-IF(I29="",0,I29)))</f>
+        <f>IF(D29="","",H29*(1-N(I29)))</f>
         <v/>
       </c>
       <c r="K29" s="18" t="n"/>
       <c r="L29" s="18" t="n"/>
       <c r="M29" s="5">
-        <f>IF(G29="","",IFERROR(IF(E29="ต่ออายุ",VLOOKUP(G29,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G29,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$E$7,IF(E29="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N29" s="37">
-        <f>IF(OR(J29="",M29=""),"",IF(P29="Y",0,IF(F29="จ่ายแล้ว",ROUND(J29*M29,2),0)))</f>
+        <f>IF(D29="","",ROUND(IFERROR(J29*M29,0)*(F29="จ่ายแล้ว")*(P29&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O29" s="18" t="n"/>
@@ -2055,22 +2055,22 @@
       <c r="F30" s="22" t="n"/>
       <c r="G30" s="22" t="n"/>
       <c r="H30" s="38">
-        <f>IF(G30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I30" s="23" t="n"/>
       <c r="J30" s="39">
-        <f>IF(H30="","",H30*(1-IF(I30="",0,I30)))</f>
+        <f>IF(D30="","",H30*(1-N(I30)))</f>
         <v/>
       </c>
       <c r="K30" s="22" t="n"/>
       <c r="L30" s="22" t="n"/>
       <c r="M30" s="7">
-        <f>IF(G30="","",IFERROR(IF(E30="ต่ออายุ",VLOOKUP(G30,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G30,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$E$7,IF(E30="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N30" s="37">
-        <f>IF(OR(J30="",M30=""),"",IF(P30="Y",0,IF(F30="จ่ายแล้ว",ROUND(J30*M30,2),0)))</f>
+        <f>IF(D30="","",ROUND(IFERROR(J30*M30,0)*(F30="จ่ายแล้ว")*(P30&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O30" s="22" t="n"/>
@@ -2090,22 +2090,22 @@
       <c r="F31" s="18" t="n"/>
       <c r="G31" s="18" t="n"/>
       <c r="H31" s="35">
-        <f>IF(G31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I31" s="19" t="n"/>
       <c r="J31" s="36">
-        <f>IF(H31="","",H31*(1-IF(I31="",0,I31)))</f>
+        <f>IF(D31="","",H31*(1-N(I31)))</f>
         <v/>
       </c>
       <c r="K31" s="18" t="n"/>
       <c r="L31" s="18" t="n"/>
       <c r="M31" s="5">
-        <f>IF(G31="","",IFERROR(IF(E31="ต่ออายุ",VLOOKUP(G31,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G31,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$E$7,IF(E31="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N31" s="37">
-        <f>IF(OR(J31="",M31=""),"",IF(P31="Y",0,IF(F31="จ่ายแล้ว",ROUND(J31*M31,2),0)))</f>
+        <f>IF(D31="","",ROUND(IFERROR(J31*M31,0)*(F31="จ่ายแล้ว")*(P31&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O31" s="18" t="n"/>
@@ -2125,22 +2125,22 @@
       <c r="F32" s="22" t="n"/>
       <c r="G32" s="22" t="n"/>
       <c r="H32" s="38">
-        <f>IF(G32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I32" s="23" t="n"/>
       <c r="J32" s="39">
-        <f>IF(H32="","",H32*(1-IF(I32="",0,I32)))</f>
+        <f>IF(D32="","",H32*(1-N(I32)))</f>
         <v/>
       </c>
       <c r="K32" s="22" t="n"/>
       <c r="L32" s="22" t="n"/>
       <c r="M32" s="7">
-        <f>IF(G32="","",IFERROR(IF(E32="ต่ออายุ",VLOOKUP(G32,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G32,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$E$7,IF(E32="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N32" s="37">
-        <f>IF(OR(J32="",M32=""),"",IF(P32="Y",0,IF(F32="จ่ายแล้ว",ROUND(J32*M32,2),0)))</f>
+        <f>IF(D32="","",ROUND(IFERROR(J32*M32,0)*(F32="จ่ายแล้ว")*(P32&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O32" s="22" t="n"/>
@@ -2160,22 +2160,22 @@
       <c r="F33" s="18" t="n"/>
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="35">
-        <f>IF(G33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I33" s="19" t="n"/>
       <c r="J33" s="36">
-        <f>IF(H33="","",H33*(1-IF(I33="",0,I33)))</f>
+        <f>IF(D33="","",H33*(1-N(I33)))</f>
         <v/>
       </c>
       <c r="K33" s="18" t="n"/>
       <c r="L33" s="18" t="n"/>
       <c r="M33" s="5">
-        <f>IF(G33="","",IFERROR(IF(E33="ต่ออายุ",VLOOKUP(G33,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G33,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$E$7,IF(E33="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N33" s="37">
-        <f>IF(OR(J33="",M33=""),"",IF(P33="Y",0,IF(F33="จ่ายแล้ว",ROUND(J33*M33,2),0)))</f>
+        <f>IF(D33="","",ROUND(IFERROR(J33*M33,0)*(F33="จ่ายแล้ว")*(P33&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O33" s="18" t="n"/>
@@ -2195,22 +2195,22 @@
       <c r="F34" s="22" t="n"/>
       <c r="G34" s="22" t="n"/>
       <c r="H34" s="38">
-        <f>IF(G34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I34" s="23" t="n"/>
       <c r="J34" s="39">
-        <f>IF(H34="","",H34*(1-IF(I34="",0,I34)))</f>
+        <f>IF(D34="","",H34*(1-N(I34)))</f>
         <v/>
       </c>
       <c r="K34" s="22" t="n"/>
       <c r="L34" s="22" t="n"/>
       <c r="M34" s="7">
-        <f>IF(G34="","",IFERROR(IF(E34="ต่ออายุ",VLOOKUP(G34,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G34,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$E$7,IF(E34="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N34" s="37">
-        <f>IF(OR(J34="",M34=""),"",IF(P34="Y",0,IF(F34="จ่ายแล้ว",ROUND(J34*M34,2),0)))</f>
+        <f>IF(D34="","",ROUND(IFERROR(J34*M34,0)*(F34="จ่ายแล้ว")*(P34&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O34" s="22" t="n"/>
@@ -2230,22 +2230,22 @@
       <c r="F35" s="18" t="n"/>
       <c r="G35" s="18" t="n"/>
       <c r="H35" s="35">
-        <f>IF(G35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I35" s="19" t="n"/>
       <c r="J35" s="36">
-        <f>IF(H35="","",H35*(1-IF(I35="",0,I35)))</f>
+        <f>IF(D35="","",H35*(1-N(I35)))</f>
         <v/>
       </c>
       <c r="K35" s="18" t="n"/>
       <c r="L35" s="18" t="n"/>
       <c r="M35" s="5">
-        <f>IF(G35="","",IFERROR(IF(E35="ต่ออายุ",VLOOKUP(G35,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G35,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$E$7,IF(E35="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N35" s="37">
-        <f>IF(OR(J35="",M35=""),"",IF(P35="Y",0,IF(F35="จ่ายแล้ว",ROUND(J35*M35,2),0)))</f>
+        <f>IF(D35="","",ROUND(IFERROR(J35*M35,0)*(F35="จ่ายแล้ว")*(P35&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O35" s="18" t="n"/>
@@ -2265,22 +2265,22 @@
       <c r="F36" s="22" t="n"/>
       <c r="G36" s="22" t="n"/>
       <c r="H36" s="38">
-        <f>IF(G36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I36" s="23" t="n"/>
       <c r="J36" s="39">
-        <f>IF(H36="","",H36*(1-IF(I36="",0,I36)))</f>
+        <f>IF(D36="","",H36*(1-N(I36)))</f>
         <v/>
       </c>
       <c r="K36" s="22" t="n"/>
       <c r="L36" s="22" t="n"/>
       <c r="M36" s="7">
-        <f>IF(G36="","",IFERROR(IF(E36="ต่ออายุ",VLOOKUP(G36,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G36,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$E$7,IF(E36="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N36" s="37">
-        <f>IF(OR(J36="",M36=""),"",IF(P36="Y",0,IF(F36="จ่ายแล้ว",ROUND(J36*M36,2),0)))</f>
+        <f>IF(D36="","",ROUND(IFERROR(J36*M36,0)*(F36="จ่ายแล้ว")*(P36&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O36" s="22" t="n"/>
@@ -2300,22 +2300,22 @@
       <c r="F37" s="18" t="n"/>
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="35">
-        <f>IF(G37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I37" s="19" t="n"/>
       <c r="J37" s="36">
-        <f>IF(H37="","",H37*(1-IF(I37="",0,I37)))</f>
+        <f>IF(D37="","",H37*(1-N(I37)))</f>
         <v/>
       </c>
       <c r="K37" s="18" t="n"/>
       <c r="L37" s="18" t="n"/>
       <c r="M37" s="5">
-        <f>IF(G37="","",IFERROR(IF(E37="ต่ออายุ",VLOOKUP(G37,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G37,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$E$7,IF(E37="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N37" s="37">
-        <f>IF(OR(J37="",M37=""),"",IF(P37="Y",0,IF(F37="จ่ายแล้ว",ROUND(J37*M37,2),0)))</f>
+        <f>IF(D37="","",ROUND(IFERROR(J37*M37,0)*(F37="จ่ายแล้ว")*(P37&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O37" s="18" t="n"/>
@@ -2335,22 +2335,22 @@
       <c r="F38" s="22" t="n"/>
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="38">
-        <f>IF(G38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I38" s="23" t="n"/>
       <c r="J38" s="39">
-        <f>IF(H38="","",H38*(1-IF(I38="",0,I38)))</f>
+        <f>IF(D38="","",H38*(1-N(I38)))</f>
         <v/>
       </c>
       <c r="K38" s="22" t="n"/>
       <c r="L38" s="22" t="n"/>
       <c r="M38" s="7">
-        <f>IF(G38="","",IFERROR(IF(E38="ต่ออายุ",VLOOKUP(G38,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G38,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$E$7,IF(E38="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N38" s="37">
-        <f>IF(OR(J38="",M38=""),"",IF(P38="Y",0,IF(F38="จ่ายแล้ว",ROUND(J38*M38,2),0)))</f>
+        <f>IF(D38="","",ROUND(IFERROR(J38*M38,0)*(F38="จ่ายแล้ว")*(P38&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O38" s="22" t="n"/>
@@ -2370,22 +2370,22 @@
       <c r="F39" s="18" t="n"/>
       <c r="G39" s="18" t="n"/>
       <c r="H39" s="35">
-        <f>IF(G39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I39" s="19" t="n"/>
       <c r="J39" s="36">
-        <f>IF(H39="","",H39*(1-IF(I39="",0,I39)))</f>
+        <f>IF(D39="","",H39*(1-N(I39)))</f>
         <v/>
       </c>
       <c r="K39" s="18" t="n"/>
       <c r="L39" s="18" t="n"/>
       <c r="M39" s="5">
-        <f>IF(G39="","",IFERROR(IF(E39="ต่ออายุ",VLOOKUP(G39,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G39,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$E$7,IF(E39="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N39" s="37">
-        <f>IF(OR(J39="",M39=""),"",IF(P39="Y",0,IF(F39="จ่ายแล้ว",ROUND(J39*M39,2),0)))</f>
+        <f>IF(D39="","",ROUND(IFERROR(J39*M39,0)*(F39="จ่ายแล้ว")*(P39&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O39" s="18" t="n"/>
@@ -2405,22 +2405,22 @@
       <c r="F40" s="22" t="n"/>
       <c r="G40" s="22" t="n"/>
       <c r="H40" s="38">
-        <f>IF(G40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I40" s="23" t="n"/>
       <c r="J40" s="39">
-        <f>IF(H40="","",H40*(1-IF(I40="",0,I40)))</f>
+        <f>IF(D40="","",H40*(1-N(I40)))</f>
         <v/>
       </c>
       <c r="K40" s="22" t="n"/>
       <c r="L40" s="22" t="n"/>
       <c r="M40" s="7">
-        <f>IF(G40="","",IFERROR(IF(E40="ต่ออายุ",VLOOKUP(G40,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G40,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$E$7,IF(E40="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N40" s="37">
-        <f>IF(OR(J40="",M40=""),"",IF(P40="Y",0,IF(F40="จ่ายแล้ว",ROUND(J40*M40,2),0)))</f>
+        <f>IF(D40="","",ROUND(IFERROR(J40*M40,0)*(F40="จ่ายแล้ว")*(P40&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O40" s="22" t="n"/>
@@ -2440,22 +2440,22 @@
       <c r="F41" s="18" t="n"/>
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="35">
-        <f>IF(G41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I41" s="19" t="n"/>
       <c r="J41" s="36">
-        <f>IF(H41="","",H41*(1-IF(I41="",0,I41)))</f>
+        <f>IF(D41="","",H41*(1-N(I41)))</f>
         <v/>
       </c>
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
       <c r="M41" s="5">
-        <f>IF(G41="","",IFERROR(IF(E41="ต่ออายุ",VLOOKUP(G41,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G41,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$E$7,IF(E41="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N41" s="37">
-        <f>IF(OR(J41="",M41=""),"",IF(P41="Y",0,IF(F41="จ่ายแล้ว",ROUND(J41*M41,2),0)))</f>
+        <f>IF(D41="","",ROUND(IFERROR(J41*M41,0)*(F41="จ่ายแล้ว")*(P41&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O41" s="18" t="n"/>
@@ -2475,22 +2475,22 @@
       <c r="F42" s="22" t="n"/>
       <c r="G42" s="22" t="n"/>
       <c r="H42" s="38">
-        <f>IF(G42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I42" s="23" t="n"/>
       <c r="J42" s="39">
-        <f>IF(H42="","",H42*(1-IF(I42="",0,I42)))</f>
+        <f>IF(D42="","",H42*(1-N(I42)))</f>
         <v/>
       </c>
       <c r="K42" s="22" t="n"/>
       <c r="L42" s="22" t="n"/>
       <c r="M42" s="7">
-        <f>IF(G42="","",IFERROR(IF(E42="ต่ออายุ",VLOOKUP(G42,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G42,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$E$7,IF(E42="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N42" s="37">
-        <f>IF(OR(J42="",M42=""),"",IF(P42="Y",0,IF(F42="จ่ายแล้ว",ROUND(J42*M42,2),0)))</f>
+        <f>IF(D42="","",ROUND(IFERROR(J42*M42,0)*(F42="จ่ายแล้ว")*(P42&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O42" s="22" t="n"/>
@@ -2510,22 +2510,22 @@
       <c r="F43" s="18" t="n"/>
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="35">
-        <f>IF(G43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I43" s="19" t="n"/>
       <c r="J43" s="36">
-        <f>IF(H43="","",H43*(1-IF(I43="",0,I43)))</f>
+        <f>IF(D43="","",H43*(1-N(I43)))</f>
         <v/>
       </c>
       <c r="K43" s="18" t="n"/>
       <c r="L43" s="18" t="n"/>
       <c r="M43" s="5">
-        <f>IF(G43="","",IFERROR(IF(E43="ต่ออายุ",VLOOKUP(G43,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G43,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$E$7,IF(E43="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N43" s="37">
-        <f>IF(OR(J43="",M43=""),"",IF(P43="Y",0,IF(F43="จ่ายแล้ว",ROUND(J43*M43,2),0)))</f>
+        <f>IF(D43="","",ROUND(IFERROR(J43*M43,0)*(F43="จ่ายแล้ว")*(P43&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O43" s="18" t="n"/>
@@ -2545,22 +2545,22 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="22" t="n"/>
       <c r="H44" s="38">
-        <f>IF(G44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I44" s="23" t="n"/>
       <c r="J44" s="39">
-        <f>IF(H44="","",H44*(1-IF(I44="",0,I44)))</f>
+        <f>IF(D44="","",H44*(1-N(I44)))</f>
         <v/>
       </c>
       <c r="K44" s="22" t="n"/>
       <c r="L44" s="22" t="n"/>
       <c r="M44" s="7">
-        <f>IF(G44="","",IFERROR(IF(E44="ต่ออายุ",VLOOKUP(G44,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G44,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$E$7,IF(E44="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N44" s="37">
-        <f>IF(OR(J44="",M44=""),"",IF(P44="Y",0,IF(F44="จ่ายแล้ว",ROUND(J44*M44,2),0)))</f>
+        <f>IF(D44="","",ROUND(IFERROR(J44*M44,0)*(F44="จ่ายแล้ว")*(P44&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O44" s="22" t="n"/>
@@ -2580,22 +2580,22 @@
       <c r="F45" s="18" t="n"/>
       <c r="G45" s="18" t="n"/>
       <c r="H45" s="35">
-        <f>IF(G45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I45" s="19" t="n"/>
       <c r="J45" s="36">
-        <f>IF(H45="","",H45*(1-IF(I45="",0,I45)))</f>
+        <f>IF(D45="","",H45*(1-N(I45)))</f>
         <v/>
       </c>
       <c r="K45" s="18" t="n"/>
       <c r="L45" s="18" t="n"/>
       <c r="M45" s="5">
-        <f>IF(G45="","",IFERROR(IF(E45="ต่ออายุ",VLOOKUP(G45,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G45,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$E$7,IF(E45="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N45" s="37">
-        <f>IF(OR(J45="",M45=""),"",IF(P45="Y",0,IF(F45="จ่ายแล้ว",ROUND(J45*M45,2),0)))</f>
+        <f>IF(D45="","",ROUND(IFERROR(J45*M45,0)*(F45="จ่ายแล้ว")*(P45&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O45" s="18" t="n"/>
@@ -2615,22 +2615,22 @@
       <c r="F46" s="22" t="n"/>
       <c r="G46" s="22" t="n"/>
       <c r="H46" s="38">
-        <f>IF(G46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I46" s="23" t="n"/>
       <c r="J46" s="39">
-        <f>IF(H46="","",H46*(1-IF(I46="",0,I46)))</f>
+        <f>IF(D46="","",H46*(1-N(I46)))</f>
         <v/>
       </c>
       <c r="K46" s="22" t="n"/>
       <c r="L46" s="22" t="n"/>
       <c r="M46" s="7">
-        <f>IF(G46="","",IFERROR(IF(E46="ต่ออายุ",VLOOKUP(G46,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G46,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$E$7,IF(E46="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N46" s="37">
-        <f>IF(OR(J46="",M46=""),"",IF(P46="Y",0,IF(F46="จ่ายแล้ว",ROUND(J46*M46,2),0)))</f>
+        <f>IF(D46="","",ROUND(IFERROR(J46*M46,0)*(F46="จ่ายแล้ว")*(P46&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O46" s="22" t="n"/>
@@ -2650,22 +2650,22 @@
       <c r="F47" s="18" t="n"/>
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="35">
-        <f>IF(G47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I47" s="19" t="n"/>
       <c r="J47" s="36">
-        <f>IF(H47="","",H47*(1-IF(I47="",0,I47)))</f>
+        <f>IF(D47="","",H47*(1-N(I47)))</f>
         <v/>
       </c>
       <c r="K47" s="18" t="n"/>
       <c r="L47" s="18" t="n"/>
       <c r="M47" s="5">
-        <f>IF(G47="","",IFERROR(IF(E47="ต่ออายุ",VLOOKUP(G47,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G47,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$E$7,IF(E47="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N47" s="37">
-        <f>IF(OR(J47="",M47=""),"",IF(P47="Y",0,IF(F47="จ่ายแล้ว",ROUND(J47*M47,2),0)))</f>
+        <f>IF(D47="","",ROUND(IFERROR(J47*M47,0)*(F47="จ่ายแล้ว")*(P47&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O47" s="18" t="n"/>
@@ -2685,22 +2685,22 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="22" t="n"/>
       <c r="H48" s="38">
-        <f>IF(G48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I48" s="23" t="n"/>
       <c r="J48" s="39">
-        <f>IF(H48="","",H48*(1-IF(I48="",0,I48)))</f>
+        <f>IF(D48="","",H48*(1-N(I48)))</f>
         <v/>
       </c>
       <c r="K48" s="22" t="n"/>
       <c r="L48" s="22" t="n"/>
       <c r="M48" s="7">
-        <f>IF(G48="","",IFERROR(IF(E48="ต่ออายุ",VLOOKUP(G48,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G48,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$E$7,IF(E48="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N48" s="37">
-        <f>IF(OR(J48="",M48=""),"",IF(P48="Y",0,IF(F48="จ่ายแล้ว",ROUND(J48*M48,2),0)))</f>
+        <f>IF(D48="","",ROUND(IFERROR(J48*M48,0)*(F48="จ่ายแล้ว")*(P48&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O48" s="22" t="n"/>
@@ -2720,22 +2720,22 @@
       <c r="F49" s="18" t="n"/>
       <c r="G49" s="18" t="n"/>
       <c r="H49" s="35">
-        <f>IF(G49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I49" s="19" t="n"/>
       <c r="J49" s="36">
-        <f>IF(H49="","",H49*(1-IF(I49="",0,I49)))</f>
+        <f>IF(D49="","",H49*(1-N(I49)))</f>
         <v/>
       </c>
       <c r="K49" s="18" t="n"/>
       <c r="L49" s="18" t="n"/>
       <c r="M49" s="5">
-        <f>IF(G49="","",IFERROR(IF(E49="ต่ออายุ",VLOOKUP(G49,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G49,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$E$7,IF(E49="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N49" s="37">
-        <f>IF(OR(J49="",M49=""),"",IF(P49="Y",0,IF(F49="จ่ายแล้ว",ROUND(J49*M49,2),0)))</f>
+        <f>IF(D49="","",ROUND(IFERROR(J49*M49,0)*(F49="จ่ายแล้ว")*(P49&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O49" s="18" t="n"/>
@@ -2755,22 +2755,22 @@
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="22" t="n"/>
       <c r="H50" s="38">
-        <f>IF(G50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I50" s="23" t="n"/>
       <c r="J50" s="39">
-        <f>IF(H50="","",H50*(1-IF(I50="",0,I50)))</f>
+        <f>IF(D50="","",H50*(1-N(I50)))</f>
         <v/>
       </c>
       <c r="K50" s="22" t="n"/>
       <c r="L50" s="22" t="n"/>
       <c r="M50" s="7">
-        <f>IF(G50="","",IFERROR(IF(E50="ต่ออายุ",VLOOKUP(G50,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G50,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$E$7,IF(E50="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N50" s="37">
-        <f>IF(OR(J50="",M50=""),"",IF(P50="Y",0,IF(F50="จ่ายแล้ว",ROUND(J50*M50,2),0)))</f>
+        <f>IF(D50="","",ROUND(IFERROR(J50*M50,0)*(F50="จ่ายแล้ว")*(P50&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O50" s="22" t="n"/>
@@ -2790,22 +2790,22 @@
       <c r="F51" s="18" t="n"/>
       <c r="G51" s="18" t="n"/>
       <c r="H51" s="35">
-        <f>IF(G51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I51" s="19" t="n"/>
       <c r="J51" s="36">
-        <f>IF(H51="","",H51*(1-IF(I51="",0,I51)))</f>
+        <f>IF(D51="","",H51*(1-N(I51)))</f>
         <v/>
       </c>
       <c r="K51" s="18" t="n"/>
       <c r="L51" s="18" t="n"/>
       <c r="M51" s="5">
-        <f>IF(G51="","",IFERROR(IF(E51="ต่ออายุ",VLOOKUP(G51,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G51,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$E$7,IF(E51="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N51" s="37">
-        <f>IF(OR(J51="",M51=""),"",IF(P51="Y",0,IF(F51="จ่ายแล้ว",ROUND(J51*M51,2),0)))</f>
+        <f>IF(D51="","",ROUND(IFERROR(J51*M51,0)*(F51="จ่ายแล้ว")*(P51&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O51" s="18" t="n"/>
@@ -2825,22 +2825,22 @@
       <c r="F52" s="22" t="n"/>
       <c r="G52" s="22" t="n"/>
       <c r="H52" s="38">
-        <f>IF(G52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$B$7,2,FALSE),""))</f>
+        <f>IF(D52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="I52" s="23" t="n"/>
       <c r="J52" s="39">
-        <f>IF(H52="","",H52*(1-IF(I52="",0,I52)))</f>
+        <f>IF(D52="","",H52*(1-N(I52)))</f>
         <v/>
       </c>
       <c r="K52" s="22" t="n"/>
       <c r="L52" s="22" t="n"/>
       <c r="M52" s="7">
-        <f>IF(G52="","",IFERROR(IF(E52="ต่ออายุ",VLOOKUP(G52,Rate!$A$4:$E$7,5,FALSE),VLOOKUP(G52,Rate!$A$4:$C$7,3,FALSE)),""))</f>
+        <f>IF(D52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$E$7,IF(E52="ต่ออายุ",5,3),FALSE),"NA"))</f>
         <v/>
       </c>
       <c r="N52" s="37">
-        <f>IF(OR(J52="",M52=""),"",IF(P52="Y",0,IF(F52="จ่ายแล้ว",ROUND(J52*M52,2),0)))</f>
+        <f>IF(D52="","",ROUND(IFERROR(J52*M52,0)*(F52="จ่ายแล้ว")*(P52&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O52" s="22" t="n"/>
@@ -2869,7 +2869,7 @@
       <c r="L53" s="40" t="n"/>
       <c r="M53" s="40" t="n"/>
       <c r="N53" s="42">
-        <f>ROUND(SUM(N13:N52),2)</f>
+        <f>SUM(N13:N52)</f>
         <v/>
       </c>
       <c r="O53" s="40" t="n"/>
@@ -2973,7 +2973,7 @@
       <formula>AND(F13="",D13&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="14">
+  <dataValidations count="9">
     <dataValidation sqref="E13:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ใหม่,ต่ออายุ"</formula1>
     </dataValidation>
@@ -2989,33 +2989,17 @@
     <dataValidation sqref="O13:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"รอจ่าย,จ่ายแล้ว"</formula1>
     </dataValidation>
-    <dataValidation sqref="B13:B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="วันที่ไม่ถูกต้อง" error="ต้องเป็นวันที่จริง (เช่น 2026-06-23)" promptTitle="วันที่" prompt="กรอกวันที่ดีล (จำเป็น)" type="date" errorStyle="stop" operator="between">
+    <dataValidation sqref="B13:B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="วันที่ไม่ถูกต้อง" error="ต้องเป็นวันที่ (เช่น 2026-06-23)" promptTitle="วันที่" prompt="จำเป็น — ถ้าว่าง ไตรมาส/รายได้จะ = 0" type="date" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>2020-01-01</formula1>
-      <formula2>2099-12-31</formula2>
     </dataValidation>
-    <dataValidation sqref="E13:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ประเภทไม่ถูกต้อง" error="เลือกได้แค่ &quot;ใหม่&quot; หรือ &quot;ต่ออายุ&quot;" type="list" errorStyle="stop">
-      <formula1>"ใหม่,ต่ออายุ"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F13:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="สถานะลูกค้าจ่าย" error="เลือกได้แค่ &quot;จ่ายแล้ว&quot; หรือ &quot;ค้างจ่าย&quot;" type="list" errorStyle="stop">
-      <formula1>"จ่ายแล้ว,ค้างจ่าย"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G13:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="แพ็กเกจไม่ถูกต้อง" error="เลือกแพ็กเกจจากตาราง Rate" type="list" errorStyle="stop">
-      <formula1>=Rate!$A$4:$A$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="I13:I52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ส่วนลด % ผิด" error="ส่วนลดต้องอยู่ระหว่าง 0–1 (เช่น 0.1 = 10%) ห้ามใส่ &quot;10&quot;" promptTitle="ส่วนลด %" prompt="ใส่เป็นทศนิยม: 0.1 = 10% (หรือพิมพ์ 10% แล้วเปลี่ยน format เป็น %)" type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="I13:I52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ส่วนลดผิด" error="ส่วนลดต้อง 0–1 เช่น 0.1 = 10%" promptTitle="ส่วนลด %" prompt="ทศนิยม: 0.1 = 10%" type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="จ่ายแบบ" error="เลือกได้แค่ &quot;ทีม&quot; หรือ &quot;รายคน&quot;" type="list" errorStyle="stop">
-      <formula1>"ทีม,รายคน"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L13:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Sales ไม่ถูกต้อง" error="เลือกชื่อจากแท็บ ทีมขาย" type="list" errorStyle="stop">
+    <dataValidation sqref="L13:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Sales" error="เลือกจากแท็บ ทีมขาย" type="list" errorStyle="stop">
       <formula1>=ทีมขาย!$A$6:$A$20</formula1>
     </dataValidation>
-    <dataValidation sqref="O13:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="สถานะค่าคอม" error="เลือกได้แค่ &quot;จ่ายแล้ว&quot; หรือ &quot;ค้างจ่าย&quot;" type="list" errorStyle="stop">
-      <formula1>"จ่ายแล้ว,ค้างจ่าย"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P13:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Refund" error="เลือก Y (refund) หรือ N (ปกติ)" promptTitle="Refund?" prompt="Y = ลูกค้าขอ refund ค่าคอมจะกลายเป็น 0 (clawback)" type="list" errorStyle="stop">
+    <dataValidation sqref="P13:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Refund" error="Y = refund / N = ปกติ" promptTitle="Refund?" prompt="Y → ค่าคอมเป็น 0 อัตโนมัติ" type="list" errorStyle="stop">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3142,7 +3126,7 @@
         <v/>
       </c>
       <c r="H6" s="46">
-        <f>IF($A6="","",ROUND(F6-G6,2))</f>
+        <f>IF($A6="","",F6-G6)</f>
         <v/>
       </c>
     </row>
@@ -3177,7 +3161,7 @@
         <v/>
       </c>
       <c r="H7" s="46">
-        <f>IF($A7="","",ROUND(F7-G7,2))</f>
+        <f>IF($A7="","",F7-G7)</f>
         <v/>
       </c>
     </row>
@@ -3212,7 +3196,7 @@
         <v/>
       </c>
       <c r="H8" s="46">
-        <f>IF($A8="","",ROUND(F8-G8,2))</f>
+        <f>IF($A8="","",F8-G8)</f>
         <v/>
       </c>
     </row>
@@ -3237,7 +3221,7 @@
         <v/>
       </c>
       <c r="H9" s="46">
-        <f>IF($A9="","",ROUND(F9-G9,2))</f>
+        <f>IF($A9="","",F9-G9)</f>
         <v/>
       </c>
     </row>
@@ -3262,7 +3246,7 @@
         <v/>
       </c>
       <c r="H10" s="46">
-        <f>IF($A10="","",ROUND(F10-G10,2))</f>
+        <f>IF($A10="","",F10-G10)</f>
         <v/>
       </c>
     </row>
@@ -3287,7 +3271,7 @@
         <v/>
       </c>
       <c r="H11" s="46">
-        <f>IF($A11="","",ROUND(F11-G11,2))</f>
+        <f>IF($A11="","",F11-G11)</f>
         <v/>
       </c>
     </row>
@@ -3312,7 +3296,7 @@
         <v/>
       </c>
       <c r="H12" s="46">
-        <f>IF($A12="","",ROUND(F12-G12,2))</f>
+        <f>IF($A12="","",F12-G12)</f>
         <v/>
       </c>
     </row>
@@ -3337,7 +3321,7 @@
         <v/>
       </c>
       <c r="H13" s="46">
-        <f>IF($A13="","",ROUND(F13-G13,2))</f>
+        <f>IF($A13="","",F13-G13)</f>
         <v/>
       </c>
     </row>
@@ -3362,7 +3346,7 @@
         <v/>
       </c>
       <c r="H14" s="46">
-        <f>IF($A14="","",ROUND(F14-G14,2))</f>
+        <f>IF($A14="","",F14-G14)</f>
         <v/>
       </c>
     </row>
@@ -3387,7 +3371,7 @@
         <v/>
       </c>
       <c r="H15" s="46">
-        <f>IF($A15="","",ROUND(F15-G15,2))</f>
+        <f>IF($A15="","",F15-G15)</f>
         <v/>
       </c>
     </row>
@@ -3412,7 +3396,7 @@
         <v/>
       </c>
       <c r="H16" s="46">
-        <f>IF($A16="","",ROUND(F16-G16,2))</f>
+        <f>IF($A16="","",F16-G16)</f>
         <v/>
       </c>
     </row>
@@ -3437,7 +3421,7 @@
         <v/>
       </c>
       <c r="H17" s="46">
-        <f>IF($A17="","",ROUND(F17-G17,2))</f>
+        <f>IF($A17="","",F17-G17)</f>
         <v/>
       </c>
     </row>
@@ -3462,7 +3446,7 @@
         <v/>
       </c>
       <c r="H18" s="46">
-        <f>IF($A18="","",ROUND(F18-G18,2))</f>
+        <f>IF($A18="","",F18-G18)</f>
         <v/>
       </c>
     </row>
@@ -3487,7 +3471,7 @@
         <v/>
       </c>
       <c r="H19" s="46">
-        <f>IF($A19="","",ROUND(F19-G19,2))</f>
+        <f>IF($A19="","",F19-G19)</f>
         <v/>
       </c>
     </row>
@@ -3512,7 +3496,7 @@
         <v/>
       </c>
       <c r="H20" s="46">
-        <f>IF($A20="","",ROUND(F20-G20,2))</f>
+        <f>IF($A20="","",F20-G20)</f>
         <v/>
       </c>
     </row>
@@ -5724,7 +5708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="B1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="59" min="1" max="1"/>
@@ -5746,7 +5730,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="59">
       <c r="B4" s="50" t="inlineStr">
         <is>
@@ -5781,391 +5764,391 @@
     </row>
     <row r="5">
       <c r="B5" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A6="","",ทีมขาย!A6),2),"")</f>
+        <f>IF(ทีมขาย!A6="","",ทีมขาย!A6)</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>IFERROR(ROUND(IF($B5="","",ทีมขาย!D6),2),"")</f>
+        <f>IF($B5="","",ทีมขาย!D6)</f>
         <v/>
       </c>
       <c r="D5" s="9">
-        <f>IFERROR(ROUND(IF($B5="","",ทีมขาย!E6),2),"")</f>
+        <f>IF($B5="","",ทีมขาย!E6)</f>
         <v/>
       </c>
       <c r="E5" s="53">
-        <f>IFERROR(ROUND(IF($B5="","",ทีมขาย!F6),2),"")</f>
+        <f>IF($B5="","",ทีมขาย!F6)</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>IFERROR(ROUND(IF($B5="","",ทีมขาย!G6),2),"")</f>
+        <f>IF($B5="","",ทีมขาย!G6)</f>
         <v/>
       </c>
       <c r="G5" s="9">
-        <f>IFERROR(ROUND(IF($B5="","",ทีมขาย!H6),2),"")</f>
+        <f>IF($B5="","",ทีมขาย!H6)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A7="","",ทีมขาย!A7),2),"")</f>
+        <f>IF(ทีมขาย!A7="","",ทีมขาย!A7)</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>IFERROR(ROUND(IF($B6="","",ทีมขาย!D7),2),"")</f>
+        <f>IF($B6="","",ทีมขาย!D7)</f>
         <v/>
       </c>
       <c r="D6" s="9">
-        <f>IFERROR(ROUND(IF($B6="","",ทีมขาย!E7),2),"")</f>
+        <f>IF($B6="","",ทีมขาย!E7)</f>
         <v/>
       </c>
       <c r="E6" s="53">
-        <f>IFERROR(ROUND(IF($B6="","",ทีมขาย!F7),2),"")</f>
+        <f>IF($B6="","",ทีมขาย!F7)</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>IFERROR(ROUND(IF($B6="","",ทีมขาย!G7),2),"")</f>
+        <f>IF($B6="","",ทีมขาย!G7)</f>
         <v/>
       </c>
       <c r="G6" s="9">
-        <f>IFERROR(ROUND(IF($B6="","",ทีมขาย!H7),2),"")</f>
+        <f>IF($B6="","",ทีมขาย!H7)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A8="","",ทีมขาย!A8),2),"")</f>
+        <f>IF(ทีมขาย!A8="","",ทีมขาย!A8)</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>IFERROR(ROUND(IF($B7="","",ทีมขาย!D8),2),"")</f>
+        <f>IF($B7="","",ทีมขาย!D8)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>IFERROR(ROUND(IF($B7="","",ทีมขาย!E8),2),"")</f>
+        <f>IF($B7="","",ทีมขาย!E8)</f>
         <v/>
       </c>
       <c r="E7" s="53">
-        <f>IFERROR(ROUND(IF($B7="","",ทีมขาย!F8),2),"")</f>
+        <f>IF($B7="","",ทีมขาย!F8)</f>
         <v/>
       </c>
       <c r="F7" s="9">
-        <f>IFERROR(ROUND(IF($B7="","",ทีมขาย!G8),2),"")</f>
+        <f>IF($B7="","",ทีมขาย!G8)</f>
         <v/>
       </c>
       <c r="G7" s="9">
-        <f>IFERROR(ROUND(IF($B7="","",ทีมขาย!H8),2),"")</f>
+        <f>IF($B7="","",ทีมขาย!H8)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A9="","",ทีมขาย!A9),2),"")</f>
+        <f>IF(ทีมขาย!A9="","",ทีมขาย!A9)</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>IFERROR(ROUND(IF($B8="","",ทีมขาย!D9),2),"")</f>
+        <f>IF($B8="","",ทีมขาย!D9)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>IFERROR(ROUND(IF($B8="","",ทีมขาย!E9),2),"")</f>
+        <f>IF($B8="","",ทีมขาย!E9)</f>
         <v/>
       </c>
       <c r="E8" s="53">
-        <f>IFERROR(ROUND(IF($B8="","",ทีมขาย!F9),2),"")</f>
+        <f>IF($B8="","",ทีมขาย!F9)</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>IFERROR(ROUND(IF($B8="","",ทีมขาย!G9),2),"")</f>
+        <f>IF($B8="","",ทีมขาย!G9)</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IFERROR(ROUND(IF($B8="","",ทีมขาย!H9),2),"")</f>
+        <f>IF($B8="","",ทีมขาย!H9)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A10="","",ทีมขาย!A10),2),"")</f>
+        <f>IF(ทีมขาย!A10="","",ทีมขาย!A10)</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>IFERROR(ROUND(IF($B9="","",ทีมขาย!D10),2),"")</f>
+        <f>IF($B9="","",ทีมขาย!D10)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>IFERROR(ROUND(IF($B9="","",ทีมขาย!E10),2),"")</f>
+        <f>IF($B9="","",ทีมขาย!E10)</f>
         <v/>
       </c>
       <c r="E9" s="53">
-        <f>IFERROR(ROUND(IF($B9="","",ทีมขาย!F10),2),"")</f>
+        <f>IF($B9="","",ทีมขาย!F10)</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>IFERROR(ROUND(IF($B9="","",ทีมขาย!G10),2),"")</f>
+        <f>IF($B9="","",ทีมขาย!G10)</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IFERROR(ROUND(IF($B9="","",ทีมขาย!H10),2),"")</f>
+        <f>IF($B9="","",ทีมขาย!H10)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A11="","",ทีมขาย!A11),2),"")</f>
+        <f>IF(ทีมขาย!A11="","",ทีมขาย!A11)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>IFERROR(ROUND(IF($B10="","",ทีมขาย!D11),2),"")</f>
+        <f>IF($B10="","",ทีมขาย!D11)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>IFERROR(ROUND(IF($B10="","",ทีมขาย!E11),2),"")</f>
+        <f>IF($B10="","",ทีมขาย!E11)</f>
         <v/>
       </c>
       <c r="E10" s="53">
-        <f>IFERROR(ROUND(IF($B10="","",ทีมขาย!F11),2),"")</f>
+        <f>IF($B10="","",ทีมขาย!F11)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IFERROR(ROUND(IF($B10="","",ทีมขาย!G11),2),"")</f>
+        <f>IF($B10="","",ทีมขาย!G11)</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IFERROR(ROUND(IF($B10="","",ทีมขาย!H11),2),"")</f>
+        <f>IF($B10="","",ทีมขาย!H11)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A12="","",ทีมขาย!A12),2),"")</f>
+        <f>IF(ทีมขาย!A12="","",ทีมขาย!A12)</f>
         <v/>
       </c>
       <c r="C11" s="14">
-        <f>IFERROR(ROUND(IF($B11="","",ทีมขาย!D12),2),"")</f>
+        <f>IF($B11="","",ทีมขาย!D12)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>IFERROR(ROUND(IF($B11="","",ทีมขาย!E12),2),"")</f>
+        <f>IF($B11="","",ทีมขาย!E12)</f>
         <v/>
       </c>
       <c r="E11" s="53">
-        <f>IFERROR(ROUND(IF($B11="","",ทีมขาย!F12),2),"")</f>
+        <f>IF($B11="","",ทีมขาย!F12)</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>IFERROR(ROUND(IF($B11="","",ทีมขาย!G12),2),"")</f>
+        <f>IF($B11="","",ทีมขาย!G12)</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IFERROR(ROUND(IF($B11="","",ทีมขาย!H12),2),"")</f>
+        <f>IF($B11="","",ทีมขาย!H12)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A13="","",ทีมขาย!A13),2),"")</f>
+        <f>IF(ทีมขาย!A13="","",ทีมขาย!A13)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>IFERROR(ROUND(IF($B12="","",ทีมขาย!D13),2),"")</f>
+        <f>IF($B12="","",ทีมขาย!D13)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>IFERROR(ROUND(IF($B12="","",ทีมขาย!E13),2),"")</f>
+        <f>IF($B12="","",ทีมขาย!E13)</f>
         <v/>
       </c>
       <c r="E12" s="53">
-        <f>IFERROR(ROUND(IF($B12="","",ทีมขาย!F13),2),"")</f>
+        <f>IF($B12="","",ทีมขาย!F13)</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>IFERROR(ROUND(IF($B12="","",ทีมขาย!G13),2),"")</f>
+        <f>IF($B12="","",ทีมขาย!G13)</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IFERROR(ROUND(IF($B12="","",ทีมขาย!H13),2),"")</f>
+        <f>IF($B12="","",ทีมขาย!H13)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A14="","",ทีมขาย!A14),2),"")</f>
+        <f>IF(ทีมขาย!A14="","",ทีมขาย!A14)</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>IFERROR(ROUND(IF($B13="","",ทีมขาย!D14),2),"")</f>
+        <f>IF($B13="","",ทีมขาย!D14)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>IFERROR(ROUND(IF($B13="","",ทีมขาย!E14),2),"")</f>
+        <f>IF($B13="","",ทีมขาย!E14)</f>
         <v/>
       </c>
       <c r="E13" s="53">
-        <f>IFERROR(ROUND(IF($B13="","",ทีมขาย!F14),2),"")</f>
+        <f>IF($B13="","",ทีมขาย!F14)</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>IFERROR(ROUND(IF($B13="","",ทีมขาย!G14),2),"")</f>
+        <f>IF($B13="","",ทีมขาย!G14)</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IFERROR(ROUND(IF($B13="","",ทีมขาย!H14),2),"")</f>
+        <f>IF($B13="","",ทีมขาย!H14)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A15="","",ทีมขาย!A15),2),"")</f>
+        <f>IF(ทีมขาย!A15="","",ทีมขาย!A15)</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>IFERROR(ROUND(IF($B14="","",ทีมขาย!D15),2),"")</f>
+        <f>IF($B14="","",ทีมขาย!D15)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>IFERROR(ROUND(IF($B14="","",ทีมขาย!E15),2),"")</f>
+        <f>IF($B14="","",ทีมขาย!E15)</f>
         <v/>
       </c>
       <c r="E14" s="53">
-        <f>IFERROR(ROUND(IF($B14="","",ทีมขาย!F15),2),"")</f>
+        <f>IF($B14="","",ทีมขาย!F15)</f>
         <v/>
       </c>
       <c r="F14" s="9">
-        <f>IFERROR(ROUND(IF($B14="","",ทีมขาย!G15),2),"")</f>
+        <f>IF($B14="","",ทีมขาย!G15)</f>
         <v/>
       </c>
       <c r="G14" s="9">
-        <f>IFERROR(ROUND(IF($B14="","",ทีมขาย!H15),2),"")</f>
+        <f>IF($B14="","",ทีมขาย!H15)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A16="","",ทีมขาย!A16),2),"")</f>
+        <f>IF(ทีมขาย!A16="","",ทีมขาย!A16)</f>
         <v/>
       </c>
       <c r="C15" s="14">
-        <f>IFERROR(ROUND(IF($B15="","",ทีมขาย!D16),2),"")</f>
+        <f>IF($B15="","",ทีมขาย!D16)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>IFERROR(ROUND(IF($B15="","",ทีมขาย!E16),2),"")</f>
+        <f>IF($B15="","",ทีมขาย!E16)</f>
         <v/>
       </c>
       <c r="E15" s="53">
-        <f>IFERROR(ROUND(IF($B15="","",ทีมขาย!F16),2),"")</f>
+        <f>IF($B15="","",ทีมขาย!F16)</f>
         <v/>
       </c>
       <c r="F15" s="9">
-        <f>IFERROR(ROUND(IF($B15="","",ทีมขาย!G16),2),"")</f>
+        <f>IF($B15="","",ทีมขาย!G16)</f>
         <v/>
       </c>
       <c r="G15" s="9">
-        <f>IFERROR(ROUND(IF($B15="","",ทีมขาย!H16),2),"")</f>
+        <f>IF($B15="","",ทีมขาย!H16)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A17="","",ทีมขาย!A17),2),"")</f>
+        <f>IF(ทีมขาย!A17="","",ทีมขาย!A17)</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>IFERROR(ROUND(IF($B16="","",ทีมขาย!D17),2),"")</f>
+        <f>IF($B16="","",ทีมขาย!D17)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>IFERROR(ROUND(IF($B16="","",ทีมขาย!E17),2),"")</f>
+        <f>IF($B16="","",ทีมขาย!E17)</f>
         <v/>
       </c>
       <c r="E16" s="53">
-        <f>IFERROR(ROUND(IF($B16="","",ทีมขาย!F17),2),"")</f>
+        <f>IF($B16="","",ทีมขาย!F17)</f>
         <v/>
       </c>
       <c r="F16" s="9">
-        <f>IFERROR(ROUND(IF($B16="","",ทีมขาย!G17),2),"")</f>
+        <f>IF($B16="","",ทีมขาย!G17)</f>
         <v/>
       </c>
       <c r="G16" s="9">
-        <f>IFERROR(ROUND(IF($B16="","",ทีมขาย!H17),2),"")</f>
+        <f>IF($B16="","",ทีมขาย!H17)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A18="","",ทีมขาย!A18),2),"")</f>
+        <f>IF(ทีมขาย!A18="","",ทีมขาย!A18)</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>IFERROR(ROUND(IF($B17="","",ทีมขาย!D18),2),"")</f>
+        <f>IF($B17="","",ทีมขาย!D18)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>IFERROR(ROUND(IF($B17="","",ทีมขาย!E18),2),"")</f>
+        <f>IF($B17="","",ทีมขาย!E18)</f>
         <v/>
       </c>
       <c r="E17" s="53">
-        <f>IFERROR(ROUND(IF($B17="","",ทีมขาย!F18),2),"")</f>
+        <f>IF($B17="","",ทีมขาย!F18)</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>IFERROR(ROUND(IF($B17="","",ทีมขาย!G18),2),"")</f>
+        <f>IF($B17="","",ทีมขาย!G18)</f>
         <v/>
       </c>
       <c r="G17" s="9">
-        <f>IFERROR(ROUND(IF($B17="","",ทีมขาย!H18),2),"")</f>
+        <f>IF($B17="","",ทีมขาย!H18)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A19="","",ทีมขาย!A19),2),"")</f>
+        <f>IF(ทีมขาย!A19="","",ทีมขาย!A19)</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>IFERROR(ROUND(IF($B18="","",ทีมขาย!D19),2),"")</f>
+        <f>IF($B18="","",ทีมขาย!D19)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>IFERROR(ROUND(IF($B18="","",ทีมขาย!E19),2),"")</f>
+        <f>IF($B18="","",ทีมขาย!E19)</f>
         <v/>
       </c>
       <c r="E18" s="53">
-        <f>IFERROR(ROUND(IF($B18="","",ทีมขาย!F19),2),"")</f>
+        <f>IF($B18="","",ทีมขาย!F19)</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>IFERROR(ROUND(IF($B18="","",ทีมขาย!G19),2),"")</f>
+        <f>IF($B18="","",ทีมขาย!G19)</f>
         <v/>
       </c>
       <c r="G18" s="9">
-        <f>IFERROR(ROUND(IF($B18="","",ทีมขาย!H19),2),"")</f>
+        <f>IF($B18="","",ทีมขาย!H19)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="13">
-        <f>IFERROR(ROUND(IF(ทีมขาย!A20="","",ทีมขาย!A20),2),"")</f>
+        <f>IF(ทีมขาย!A20="","",ทีมขาย!A20)</f>
         <v/>
       </c>
       <c r="C19" s="14">
-        <f>IFERROR(ROUND(IF($B19="","",ทีมขาย!D20),2),"")</f>
+        <f>IF($B19="","",ทีมขาย!D20)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>IFERROR(ROUND(IF($B19="","",ทีมขาย!E20),2),"")</f>
+        <f>IF($B19="","",ทีมขาย!E20)</f>
         <v/>
       </c>
       <c r="E19" s="53">
-        <f>IFERROR(ROUND(IF($B19="","",ทีมขาย!F20),2),"")</f>
+        <f>IF($B19="","",ทีมขาย!F20)</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>IFERROR(ROUND(IF($B19="","",ทีมขาย!G20),2),"")</f>
+        <f>IF($B19="","",ทีมขาย!G20)</f>
         <v/>
       </c>
       <c r="G19" s="9">
-        <f>IFERROR(ROUND(IF($B19="","",ทีมขาย!H20),2),"")</f>
+        <f>IF($B19="","",ทีมขาย!H20)</f>
         <v/>
       </c>
     </row>
@@ -6176,28 +6159,26 @@
         </is>
       </c>
       <c r="C20" s="14">
-        <f>IFERROR(ROUND(SUM(C5:C19),2),"")</f>
+        <f>SUM(C5:C19)</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>IFERROR(ROUND(SUM(D5:D19),2),"")</f>
+        <f>ROUND(SUM(D5:D19),2)</f>
         <v/>
       </c>
       <c r="E20" s="53">
-        <f>IFERROR(ROUND(SUM(E5:E19),2),"")</f>
+        <f>ROUND(SUM(E5:E19),2)</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>IFERROR(ROUND(SUM(F5:F19),2),"")</f>
+        <f>ROUND(SUM(F5:F19),2)</f>
         <v/>
       </c>
       <c r="G20" s="9">
-        <f>IFERROR(ROUND(SUM(G5:G19),2),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+        <f>ROUND(SUM(G5:G19),2)</f>
+        <v/>
+      </c>
+    </row>
     <row r="23" ht="18" customHeight="1" s="59">
       <c r="B23" s="60" t="inlineStr">
         <is>

--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -680,7 +680,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="1"/>
@@ -690,6 +690,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
           <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1431,54 +1439,30 @@
         <f>IF(B13="","","Q"&amp;ROUNDUP(MONTH(B13)/3,0))</f>
         <v/>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>วากิว</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>ใหม่</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>จ่ายแล้ว</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>Starter</t>
-        </is>
-      </c>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
       <c r="H13" s="35">
-        <f>IF(D13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I13" s="19" t="n"/>
       <c r="J13" s="36">
-        <f>IF(D13="","",H13*(1-N(I13)))</f>
-        <v/>
-      </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>ทีม</t>
-        </is>
-      </c>
+        <f>IF(B13="","",H13*(1-N(I13)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="18" t="n"/>
       <c r="L13" s="18" t="n"/>
       <c r="M13" s="5">
-        <f>IF(D13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$E$7,IF(E13="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B13="","",IFERROR(VLOOKUP(G13,Rate!$A$4:$E$7,IF(TRIM(E13)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N13" s="37">
-        <f>IF(D13="","",ROUND(IFERROR(J13*M13,0)*(F13="จ่ายแล้ว")*(P13&lt;&gt;"Y"),2))</f>
-        <v/>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
-        <is>
-          <t>จ่ายแล้ว</t>
-        </is>
-      </c>
+        <f>IF(B13="","",ROUND(J13*M13*(TRIM(F13)="จ่ายแล้ว")*(P13&lt;&gt;"Y"),2))</f>
+        <v/>
+      </c>
+      <c r="O13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6">
@@ -1495,22 +1479,22 @@
       <c r="F14" s="22" t="n"/>
       <c r="G14" s="22" t="n"/>
       <c r="H14" s="38">
-        <f>IF(D14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I14" s="23" t="n"/>
       <c r="J14" s="39">
-        <f>IF(D14="","",H14*(1-N(I14)))</f>
+        <f>IF(B14="","",H14*(1-N(I14)))</f>
         <v/>
       </c>
       <c r="K14" s="22" t="n"/>
       <c r="L14" s="22" t="n"/>
       <c r="M14" s="7">
-        <f>IF(D14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$E$7,IF(E14="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B14="","",IFERROR(VLOOKUP(G14,Rate!$A$4:$E$7,IF(TRIM(E14)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N14" s="37">
-        <f>IF(D14="","",ROUND(IFERROR(J14*M14,0)*(F14="จ่ายแล้ว")*(P14&lt;&gt;"Y"),2))</f>
+        <f>IF(B14="","",ROUND(J14*M14*(TRIM(F14)="จ่ายแล้ว")*(P14&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O14" s="22" t="n"/>
@@ -1530,22 +1514,22 @@
       <c r="F15" s="18" t="n"/>
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="35">
-        <f>IF(D15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I15" s="19" t="n"/>
       <c r="J15" s="36">
-        <f>IF(D15="","",H15*(1-N(I15)))</f>
+        <f>IF(B15="","",H15*(1-N(I15)))</f>
         <v/>
       </c>
       <c r="K15" s="18" t="n"/>
       <c r="L15" s="18" t="n"/>
       <c r="M15" s="5">
-        <f>IF(D15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$E$7,IF(E15="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B15="","",IFERROR(VLOOKUP(G15,Rate!$A$4:$E$7,IF(TRIM(E15)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N15" s="37">
-        <f>IF(D15="","",ROUND(IFERROR(J15*M15,0)*(F15="จ่ายแล้ว")*(P15&lt;&gt;"Y"),2))</f>
+        <f>IF(B15="","",ROUND(J15*M15*(TRIM(F15)="จ่ายแล้ว")*(P15&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O15" s="18" t="n"/>
@@ -1565,22 +1549,22 @@
       <c r="F16" s="22" t="n"/>
       <c r="G16" s="22" t="n"/>
       <c r="H16" s="38">
-        <f>IF(D16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I16" s="23" t="n"/>
       <c r="J16" s="39">
-        <f>IF(D16="","",H16*(1-N(I16)))</f>
+        <f>IF(B16="","",H16*(1-N(I16)))</f>
         <v/>
       </c>
       <c r="K16" s="22" t="n"/>
       <c r="L16" s="22" t="n"/>
       <c r="M16" s="7">
-        <f>IF(D16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$E$7,IF(E16="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B16="","",IFERROR(VLOOKUP(G16,Rate!$A$4:$E$7,IF(TRIM(E16)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N16" s="37">
-        <f>IF(D16="","",ROUND(IFERROR(J16*M16,0)*(F16="จ่ายแล้ว")*(P16&lt;&gt;"Y"),2))</f>
+        <f>IF(B16="","",ROUND(J16*M16*(TRIM(F16)="จ่ายแล้ว")*(P16&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O16" s="22" t="n"/>
@@ -1600,22 +1584,22 @@
       <c r="F17" s="18" t="n"/>
       <c r="G17" s="18" t="n"/>
       <c r="H17" s="35">
-        <f>IF(D17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I17" s="19" t="n"/>
       <c r="J17" s="36">
-        <f>IF(D17="","",H17*(1-N(I17)))</f>
+        <f>IF(B17="","",H17*(1-N(I17)))</f>
         <v/>
       </c>
       <c r="K17" s="18" t="n"/>
       <c r="L17" s="18" t="n"/>
       <c r="M17" s="5">
-        <f>IF(D17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$E$7,IF(E17="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B17="","",IFERROR(VLOOKUP(G17,Rate!$A$4:$E$7,IF(TRIM(E17)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N17" s="37">
-        <f>IF(D17="","",ROUND(IFERROR(J17*M17,0)*(F17="จ่ายแล้ว")*(P17&lt;&gt;"Y"),2))</f>
+        <f>IF(B17="","",ROUND(J17*M17*(TRIM(F17)="จ่ายแล้ว")*(P17&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O17" s="18" t="n"/>
@@ -1635,22 +1619,22 @@
       <c r="F18" s="22" t="n"/>
       <c r="G18" s="22" t="n"/>
       <c r="H18" s="38">
-        <f>IF(D18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I18" s="23" t="n"/>
       <c r="J18" s="39">
-        <f>IF(D18="","",H18*(1-N(I18)))</f>
+        <f>IF(B18="","",H18*(1-N(I18)))</f>
         <v/>
       </c>
       <c r="K18" s="22" t="n"/>
       <c r="L18" s="22" t="n"/>
       <c r="M18" s="7">
-        <f>IF(D18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$E$7,IF(E18="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B18="","",IFERROR(VLOOKUP(G18,Rate!$A$4:$E$7,IF(TRIM(E18)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N18" s="37">
-        <f>IF(D18="","",ROUND(IFERROR(J18*M18,0)*(F18="จ่ายแล้ว")*(P18&lt;&gt;"Y"),2))</f>
+        <f>IF(B18="","",ROUND(J18*M18*(TRIM(F18)="จ่ายแล้ว")*(P18&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O18" s="22" t="n"/>
@@ -1670,22 +1654,22 @@
       <c r="F19" s="18" t="n"/>
       <c r="G19" s="18" t="n"/>
       <c r="H19" s="35">
-        <f>IF(D19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I19" s="19" t="n"/>
       <c r="J19" s="36">
-        <f>IF(D19="","",H19*(1-N(I19)))</f>
+        <f>IF(B19="","",H19*(1-N(I19)))</f>
         <v/>
       </c>
       <c r="K19" s="18" t="n"/>
       <c r="L19" s="18" t="n"/>
       <c r="M19" s="5">
-        <f>IF(D19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$E$7,IF(E19="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B19="","",IFERROR(VLOOKUP(G19,Rate!$A$4:$E$7,IF(TRIM(E19)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N19" s="37">
-        <f>IF(D19="","",ROUND(IFERROR(J19*M19,0)*(F19="จ่ายแล้ว")*(P19&lt;&gt;"Y"),2))</f>
+        <f>IF(B19="","",ROUND(J19*M19*(TRIM(F19)="จ่ายแล้ว")*(P19&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O19" s="18" t="n"/>
@@ -1705,22 +1689,22 @@
       <c r="F20" s="22" t="n"/>
       <c r="G20" s="22" t="n"/>
       <c r="H20" s="38">
-        <f>IF(D20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I20" s="23" t="n"/>
       <c r="J20" s="39">
-        <f>IF(D20="","",H20*(1-N(I20)))</f>
+        <f>IF(B20="","",H20*(1-N(I20)))</f>
         <v/>
       </c>
       <c r="K20" s="22" t="n"/>
       <c r="L20" s="22" t="n"/>
       <c r="M20" s="7">
-        <f>IF(D20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$E$7,IF(E20="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B20="","",IFERROR(VLOOKUP(G20,Rate!$A$4:$E$7,IF(TRIM(E20)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N20" s="37">
-        <f>IF(D20="","",ROUND(IFERROR(J20*M20,0)*(F20="จ่ายแล้ว")*(P20&lt;&gt;"Y"),2))</f>
+        <f>IF(B20="","",ROUND(J20*M20*(TRIM(F20)="จ่ายแล้ว")*(P20&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O20" s="22" t="n"/>
@@ -1740,22 +1724,22 @@
       <c r="F21" s="18" t="n"/>
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="35">
-        <f>IF(D21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I21" s="19" t="n"/>
       <c r="J21" s="36">
-        <f>IF(D21="","",H21*(1-N(I21)))</f>
+        <f>IF(B21="","",H21*(1-N(I21)))</f>
         <v/>
       </c>
       <c r="K21" s="18" t="n"/>
       <c r="L21" s="18" t="n"/>
       <c r="M21" s="5">
-        <f>IF(D21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$E$7,IF(E21="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B21="","",IFERROR(VLOOKUP(G21,Rate!$A$4:$E$7,IF(TRIM(E21)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N21" s="37">
-        <f>IF(D21="","",ROUND(IFERROR(J21*M21,0)*(F21="จ่ายแล้ว")*(P21&lt;&gt;"Y"),2))</f>
+        <f>IF(B21="","",ROUND(J21*M21*(TRIM(F21)="จ่ายแล้ว")*(P21&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O21" s="18" t="n"/>
@@ -1775,22 +1759,22 @@
       <c r="F22" s="22" t="n"/>
       <c r="G22" s="22" t="n"/>
       <c r="H22" s="38">
-        <f>IF(D22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I22" s="23" t="n"/>
       <c r="J22" s="39">
-        <f>IF(D22="","",H22*(1-N(I22)))</f>
+        <f>IF(B22="","",H22*(1-N(I22)))</f>
         <v/>
       </c>
       <c r="K22" s="22" t="n"/>
       <c r="L22" s="22" t="n"/>
       <c r="M22" s="7">
-        <f>IF(D22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$E$7,IF(E22="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B22="","",IFERROR(VLOOKUP(G22,Rate!$A$4:$E$7,IF(TRIM(E22)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N22" s="37">
-        <f>IF(D22="","",ROUND(IFERROR(J22*M22,0)*(F22="จ่ายแล้ว")*(P22&lt;&gt;"Y"),2))</f>
+        <f>IF(B22="","",ROUND(J22*M22*(TRIM(F22)="จ่ายแล้ว")*(P22&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O22" s="22" t="n"/>
@@ -1810,22 +1794,22 @@
       <c r="F23" s="18" t="n"/>
       <c r="G23" s="18" t="n"/>
       <c r="H23" s="35">
-        <f>IF(D23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I23" s="19" t="n"/>
       <c r="J23" s="36">
-        <f>IF(D23="","",H23*(1-N(I23)))</f>
+        <f>IF(B23="","",H23*(1-N(I23)))</f>
         <v/>
       </c>
       <c r="K23" s="18" t="n"/>
       <c r="L23" s="18" t="n"/>
       <c r="M23" s="5">
-        <f>IF(D23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$E$7,IF(E23="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B23="","",IFERROR(VLOOKUP(G23,Rate!$A$4:$E$7,IF(TRIM(E23)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N23" s="37">
-        <f>IF(D23="","",ROUND(IFERROR(J23*M23,0)*(F23="จ่ายแล้ว")*(P23&lt;&gt;"Y"),2))</f>
+        <f>IF(B23="","",ROUND(J23*M23*(TRIM(F23)="จ่ายแล้ว")*(P23&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O23" s="18" t="n"/>
@@ -1845,22 +1829,22 @@
       <c r="F24" s="22" t="n"/>
       <c r="G24" s="22" t="n"/>
       <c r="H24" s="38">
-        <f>IF(D24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I24" s="23" t="n"/>
       <c r="J24" s="39">
-        <f>IF(D24="","",H24*(1-N(I24)))</f>
+        <f>IF(B24="","",H24*(1-N(I24)))</f>
         <v/>
       </c>
       <c r="K24" s="22" t="n"/>
       <c r="L24" s="22" t="n"/>
       <c r="M24" s="7">
-        <f>IF(D24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$E$7,IF(E24="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B24="","",IFERROR(VLOOKUP(G24,Rate!$A$4:$E$7,IF(TRIM(E24)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N24" s="37">
-        <f>IF(D24="","",ROUND(IFERROR(J24*M24,0)*(F24="จ่ายแล้ว")*(P24&lt;&gt;"Y"),2))</f>
+        <f>IF(B24="","",ROUND(J24*M24*(TRIM(F24)="จ่ายแล้ว")*(P24&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O24" s="22" t="n"/>
@@ -1880,22 +1864,22 @@
       <c r="F25" s="18" t="n"/>
       <c r="G25" s="18" t="n"/>
       <c r="H25" s="35">
-        <f>IF(D25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I25" s="19" t="n"/>
       <c r="J25" s="36">
-        <f>IF(D25="","",H25*(1-N(I25)))</f>
+        <f>IF(B25="","",H25*(1-N(I25)))</f>
         <v/>
       </c>
       <c r="K25" s="18" t="n"/>
       <c r="L25" s="18" t="n"/>
       <c r="M25" s="5">
-        <f>IF(D25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$E$7,IF(E25="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B25="","",IFERROR(VLOOKUP(G25,Rate!$A$4:$E$7,IF(TRIM(E25)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N25" s="37">
-        <f>IF(D25="","",ROUND(IFERROR(J25*M25,0)*(F25="จ่ายแล้ว")*(P25&lt;&gt;"Y"),2))</f>
+        <f>IF(B25="","",ROUND(J25*M25*(TRIM(F25)="จ่ายแล้ว")*(P25&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O25" s="18" t="n"/>
@@ -1915,22 +1899,22 @@
       <c r="F26" s="22" t="n"/>
       <c r="G26" s="22" t="n"/>
       <c r="H26" s="38">
-        <f>IF(D26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I26" s="23" t="n"/>
       <c r="J26" s="39">
-        <f>IF(D26="","",H26*(1-N(I26)))</f>
+        <f>IF(B26="","",H26*(1-N(I26)))</f>
         <v/>
       </c>
       <c r="K26" s="22" t="n"/>
       <c r="L26" s="22" t="n"/>
       <c r="M26" s="7">
-        <f>IF(D26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$E$7,IF(E26="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B26="","",IFERROR(VLOOKUP(G26,Rate!$A$4:$E$7,IF(TRIM(E26)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N26" s="37">
-        <f>IF(D26="","",ROUND(IFERROR(J26*M26,0)*(F26="จ่ายแล้ว")*(P26&lt;&gt;"Y"),2))</f>
+        <f>IF(B26="","",ROUND(J26*M26*(TRIM(F26)="จ่ายแล้ว")*(P26&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O26" s="22" t="n"/>
@@ -1950,22 +1934,22 @@
       <c r="F27" s="18" t="n"/>
       <c r="G27" s="18" t="n"/>
       <c r="H27" s="35">
-        <f>IF(D27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I27" s="19" t="n"/>
       <c r="J27" s="36">
-        <f>IF(D27="","",H27*(1-N(I27)))</f>
+        <f>IF(B27="","",H27*(1-N(I27)))</f>
         <v/>
       </c>
       <c r="K27" s="18" t="n"/>
       <c r="L27" s="18" t="n"/>
       <c r="M27" s="5">
-        <f>IF(D27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$E$7,IF(E27="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B27="","",IFERROR(VLOOKUP(G27,Rate!$A$4:$E$7,IF(TRIM(E27)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N27" s="37">
-        <f>IF(D27="","",ROUND(IFERROR(J27*M27,0)*(F27="จ่ายแล้ว")*(P27&lt;&gt;"Y"),2))</f>
+        <f>IF(B27="","",ROUND(J27*M27*(TRIM(F27)="จ่ายแล้ว")*(P27&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O27" s="18" t="n"/>
@@ -1985,22 +1969,22 @@
       <c r="F28" s="22" t="n"/>
       <c r="G28" s="22" t="n"/>
       <c r="H28" s="38">
-        <f>IF(D28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I28" s="23" t="n"/>
       <c r="J28" s="39">
-        <f>IF(D28="","",H28*(1-N(I28)))</f>
+        <f>IF(B28="","",H28*(1-N(I28)))</f>
         <v/>
       </c>
       <c r="K28" s="22" t="n"/>
       <c r="L28" s="22" t="n"/>
       <c r="M28" s="7">
-        <f>IF(D28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$E$7,IF(E28="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B28="","",IFERROR(VLOOKUP(G28,Rate!$A$4:$E$7,IF(TRIM(E28)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N28" s="37">
-        <f>IF(D28="","",ROUND(IFERROR(J28*M28,0)*(F28="จ่ายแล้ว")*(P28&lt;&gt;"Y"),2))</f>
+        <f>IF(B28="","",ROUND(J28*M28*(TRIM(F28)="จ่ายแล้ว")*(P28&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O28" s="22" t="n"/>
@@ -2020,22 +2004,22 @@
       <c r="F29" s="18" t="n"/>
       <c r="G29" s="18" t="n"/>
       <c r="H29" s="35">
-        <f>IF(D29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I29" s="19" t="n"/>
       <c r="J29" s="36">
-        <f>IF(D29="","",H29*(1-N(I29)))</f>
+        <f>IF(B29="","",H29*(1-N(I29)))</f>
         <v/>
       </c>
       <c r="K29" s="18" t="n"/>
       <c r="L29" s="18" t="n"/>
       <c r="M29" s="5">
-        <f>IF(D29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$E$7,IF(E29="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B29="","",IFERROR(VLOOKUP(G29,Rate!$A$4:$E$7,IF(TRIM(E29)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N29" s="37">
-        <f>IF(D29="","",ROUND(IFERROR(J29*M29,0)*(F29="จ่ายแล้ว")*(P29&lt;&gt;"Y"),2))</f>
+        <f>IF(B29="","",ROUND(J29*M29*(TRIM(F29)="จ่ายแล้ว")*(P29&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O29" s="18" t="n"/>
@@ -2055,22 +2039,22 @@
       <c r="F30" s="22" t="n"/>
       <c r="G30" s="22" t="n"/>
       <c r="H30" s="38">
-        <f>IF(D30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I30" s="23" t="n"/>
       <c r="J30" s="39">
-        <f>IF(D30="","",H30*(1-N(I30)))</f>
+        <f>IF(B30="","",H30*(1-N(I30)))</f>
         <v/>
       </c>
       <c r="K30" s="22" t="n"/>
       <c r="L30" s="22" t="n"/>
       <c r="M30" s="7">
-        <f>IF(D30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$E$7,IF(E30="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B30="","",IFERROR(VLOOKUP(G30,Rate!$A$4:$E$7,IF(TRIM(E30)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N30" s="37">
-        <f>IF(D30="","",ROUND(IFERROR(J30*M30,0)*(F30="จ่ายแล้ว")*(P30&lt;&gt;"Y"),2))</f>
+        <f>IF(B30="","",ROUND(J30*M30*(TRIM(F30)="จ่ายแล้ว")*(P30&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O30" s="22" t="n"/>
@@ -2090,22 +2074,22 @@
       <c r="F31" s="18" t="n"/>
       <c r="G31" s="18" t="n"/>
       <c r="H31" s="35">
-        <f>IF(D31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I31" s="19" t="n"/>
       <c r="J31" s="36">
-        <f>IF(D31="","",H31*(1-N(I31)))</f>
+        <f>IF(B31="","",H31*(1-N(I31)))</f>
         <v/>
       </c>
       <c r="K31" s="18" t="n"/>
       <c r="L31" s="18" t="n"/>
       <c r="M31" s="5">
-        <f>IF(D31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$E$7,IF(E31="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B31="","",IFERROR(VLOOKUP(G31,Rate!$A$4:$E$7,IF(TRIM(E31)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N31" s="37">
-        <f>IF(D31="","",ROUND(IFERROR(J31*M31,0)*(F31="จ่ายแล้ว")*(P31&lt;&gt;"Y"),2))</f>
+        <f>IF(B31="","",ROUND(J31*M31*(TRIM(F31)="จ่ายแล้ว")*(P31&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O31" s="18" t="n"/>
@@ -2125,22 +2109,22 @@
       <c r="F32" s="22" t="n"/>
       <c r="G32" s="22" t="n"/>
       <c r="H32" s="38">
-        <f>IF(D32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I32" s="23" t="n"/>
       <c r="J32" s="39">
-        <f>IF(D32="","",H32*(1-N(I32)))</f>
+        <f>IF(B32="","",H32*(1-N(I32)))</f>
         <v/>
       </c>
       <c r="K32" s="22" t="n"/>
       <c r="L32" s="22" t="n"/>
       <c r="M32" s="7">
-        <f>IF(D32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$E$7,IF(E32="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B32="","",IFERROR(VLOOKUP(G32,Rate!$A$4:$E$7,IF(TRIM(E32)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N32" s="37">
-        <f>IF(D32="","",ROUND(IFERROR(J32*M32,0)*(F32="จ่ายแล้ว")*(P32&lt;&gt;"Y"),2))</f>
+        <f>IF(B32="","",ROUND(J32*M32*(TRIM(F32)="จ่ายแล้ว")*(P32&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O32" s="22" t="n"/>
@@ -2160,22 +2144,22 @@
       <c r="F33" s="18" t="n"/>
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="35">
-        <f>IF(D33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I33" s="19" t="n"/>
       <c r="J33" s="36">
-        <f>IF(D33="","",H33*(1-N(I33)))</f>
+        <f>IF(B33="","",H33*(1-N(I33)))</f>
         <v/>
       </c>
       <c r="K33" s="18" t="n"/>
       <c r="L33" s="18" t="n"/>
       <c r="M33" s="5">
-        <f>IF(D33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$E$7,IF(E33="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B33="","",IFERROR(VLOOKUP(G33,Rate!$A$4:$E$7,IF(TRIM(E33)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N33" s="37">
-        <f>IF(D33="","",ROUND(IFERROR(J33*M33,0)*(F33="จ่ายแล้ว")*(P33&lt;&gt;"Y"),2))</f>
+        <f>IF(B33="","",ROUND(J33*M33*(TRIM(F33)="จ่ายแล้ว")*(P33&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O33" s="18" t="n"/>
@@ -2195,22 +2179,22 @@
       <c r="F34" s="22" t="n"/>
       <c r="G34" s="22" t="n"/>
       <c r="H34" s="38">
-        <f>IF(D34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I34" s="23" t="n"/>
       <c r="J34" s="39">
-        <f>IF(D34="","",H34*(1-N(I34)))</f>
+        <f>IF(B34="","",H34*(1-N(I34)))</f>
         <v/>
       </c>
       <c r="K34" s="22" t="n"/>
       <c r="L34" s="22" t="n"/>
       <c r="M34" s="7">
-        <f>IF(D34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$E$7,IF(E34="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B34="","",IFERROR(VLOOKUP(G34,Rate!$A$4:$E$7,IF(TRIM(E34)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N34" s="37">
-        <f>IF(D34="","",ROUND(IFERROR(J34*M34,0)*(F34="จ่ายแล้ว")*(P34&lt;&gt;"Y"),2))</f>
+        <f>IF(B34="","",ROUND(J34*M34*(TRIM(F34)="จ่ายแล้ว")*(P34&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O34" s="22" t="n"/>
@@ -2230,22 +2214,22 @@
       <c r="F35" s="18" t="n"/>
       <c r="G35" s="18" t="n"/>
       <c r="H35" s="35">
-        <f>IF(D35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I35" s="19" t="n"/>
       <c r="J35" s="36">
-        <f>IF(D35="","",H35*(1-N(I35)))</f>
+        <f>IF(B35="","",H35*(1-N(I35)))</f>
         <v/>
       </c>
       <c r="K35" s="18" t="n"/>
       <c r="L35" s="18" t="n"/>
       <c r="M35" s="5">
-        <f>IF(D35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$E$7,IF(E35="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B35="","",IFERROR(VLOOKUP(G35,Rate!$A$4:$E$7,IF(TRIM(E35)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N35" s="37">
-        <f>IF(D35="","",ROUND(IFERROR(J35*M35,0)*(F35="จ่ายแล้ว")*(P35&lt;&gt;"Y"),2))</f>
+        <f>IF(B35="","",ROUND(J35*M35*(TRIM(F35)="จ่ายแล้ว")*(P35&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O35" s="18" t="n"/>
@@ -2265,22 +2249,22 @@
       <c r="F36" s="22" t="n"/>
       <c r="G36" s="22" t="n"/>
       <c r="H36" s="38">
-        <f>IF(D36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I36" s="23" t="n"/>
       <c r="J36" s="39">
-        <f>IF(D36="","",H36*(1-N(I36)))</f>
+        <f>IF(B36="","",H36*(1-N(I36)))</f>
         <v/>
       </c>
       <c r="K36" s="22" t="n"/>
       <c r="L36" s="22" t="n"/>
       <c r="M36" s="7">
-        <f>IF(D36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$E$7,IF(E36="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B36="","",IFERROR(VLOOKUP(G36,Rate!$A$4:$E$7,IF(TRIM(E36)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N36" s="37">
-        <f>IF(D36="","",ROUND(IFERROR(J36*M36,0)*(F36="จ่ายแล้ว")*(P36&lt;&gt;"Y"),2))</f>
+        <f>IF(B36="","",ROUND(J36*M36*(TRIM(F36)="จ่ายแล้ว")*(P36&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O36" s="22" t="n"/>
@@ -2300,22 +2284,22 @@
       <c r="F37" s="18" t="n"/>
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="35">
-        <f>IF(D37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I37" s="19" t="n"/>
       <c r="J37" s="36">
-        <f>IF(D37="","",H37*(1-N(I37)))</f>
+        <f>IF(B37="","",H37*(1-N(I37)))</f>
         <v/>
       </c>
       <c r="K37" s="18" t="n"/>
       <c r="L37" s="18" t="n"/>
       <c r="M37" s="5">
-        <f>IF(D37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$E$7,IF(E37="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B37="","",IFERROR(VLOOKUP(G37,Rate!$A$4:$E$7,IF(TRIM(E37)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N37" s="37">
-        <f>IF(D37="","",ROUND(IFERROR(J37*M37,0)*(F37="จ่ายแล้ว")*(P37&lt;&gt;"Y"),2))</f>
+        <f>IF(B37="","",ROUND(J37*M37*(TRIM(F37)="จ่ายแล้ว")*(P37&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O37" s="18" t="n"/>
@@ -2335,22 +2319,22 @@
       <c r="F38" s="22" t="n"/>
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="38">
-        <f>IF(D38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I38" s="23" t="n"/>
       <c r="J38" s="39">
-        <f>IF(D38="","",H38*(1-N(I38)))</f>
+        <f>IF(B38="","",H38*(1-N(I38)))</f>
         <v/>
       </c>
       <c r="K38" s="22" t="n"/>
       <c r="L38" s="22" t="n"/>
       <c r="M38" s="7">
-        <f>IF(D38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$E$7,IF(E38="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B38="","",IFERROR(VLOOKUP(G38,Rate!$A$4:$E$7,IF(TRIM(E38)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N38" s="37">
-        <f>IF(D38="","",ROUND(IFERROR(J38*M38,0)*(F38="จ่ายแล้ว")*(P38&lt;&gt;"Y"),2))</f>
+        <f>IF(B38="","",ROUND(J38*M38*(TRIM(F38)="จ่ายแล้ว")*(P38&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O38" s="22" t="n"/>
@@ -2370,22 +2354,22 @@
       <c r="F39" s="18" t="n"/>
       <c r="G39" s="18" t="n"/>
       <c r="H39" s="35">
-        <f>IF(D39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I39" s="19" t="n"/>
       <c r="J39" s="36">
-        <f>IF(D39="","",H39*(1-N(I39)))</f>
+        <f>IF(B39="","",H39*(1-N(I39)))</f>
         <v/>
       </c>
       <c r="K39" s="18" t="n"/>
       <c r="L39" s="18" t="n"/>
       <c r="M39" s="5">
-        <f>IF(D39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$E$7,IF(E39="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B39="","",IFERROR(VLOOKUP(G39,Rate!$A$4:$E$7,IF(TRIM(E39)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N39" s="37">
-        <f>IF(D39="","",ROUND(IFERROR(J39*M39,0)*(F39="จ่ายแล้ว")*(P39&lt;&gt;"Y"),2))</f>
+        <f>IF(B39="","",ROUND(J39*M39*(TRIM(F39)="จ่ายแล้ว")*(P39&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O39" s="18" t="n"/>
@@ -2405,22 +2389,22 @@
       <c r="F40" s="22" t="n"/>
       <c r="G40" s="22" t="n"/>
       <c r="H40" s="38">
-        <f>IF(D40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I40" s="23" t="n"/>
       <c r="J40" s="39">
-        <f>IF(D40="","",H40*(1-N(I40)))</f>
+        <f>IF(B40="","",H40*(1-N(I40)))</f>
         <v/>
       </c>
       <c r="K40" s="22" t="n"/>
       <c r="L40" s="22" t="n"/>
       <c r="M40" s="7">
-        <f>IF(D40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$E$7,IF(E40="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B40="","",IFERROR(VLOOKUP(G40,Rate!$A$4:$E$7,IF(TRIM(E40)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N40" s="37">
-        <f>IF(D40="","",ROUND(IFERROR(J40*M40,0)*(F40="จ่ายแล้ว")*(P40&lt;&gt;"Y"),2))</f>
+        <f>IF(B40="","",ROUND(J40*M40*(TRIM(F40)="จ่ายแล้ว")*(P40&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O40" s="22" t="n"/>
@@ -2440,22 +2424,22 @@
       <c r="F41" s="18" t="n"/>
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="35">
-        <f>IF(D41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I41" s="19" t="n"/>
       <c r="J41" s="36">
-        <f>IF(D41="","",H41*(1-N(I41)))</f>
+        <f>IF(B41="","",H41*(1-N(I41)))</f>
         <v/>
       </c>
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
       <c r="M41" s="5">
-        <f>IF(D41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$E$7,IF(E41="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B41="","",IFERROR(VLOOKUP(G41,Rate!$A$4:$E$7,IF(TRIM(E41)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N41" s="37">
-        <f>IF(D41="","",ROUND(IFERROR(J41*M41,0)*(F41="จ่ายแล้ว")*(P41&lt;&gt;"Y"),2))</f>
+        <f>IF(B41="","",ROUND(J41*M41*(TRIM(F41)="จ่ายแล้ว")*(P41&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O41" s="18" t="n"/>
@@ -2475,22 +2459,22 @@
       <c r="F42" s="22" t="n"/>
       <c r="G42" s="22" t="n"/>
       <c r="H42" s="38">
-        <f>IF(D42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I42" s="23" t="n"/>
       <c r="J42" s="39">
-        <f>IF(D42="","",H42*(1-N(I42)))</f>
+        <f>IF(B42="","",H42*(1-N(I42)))</f>
         <v/>
       </c>
       <c r="K42" s="22" t="n"/>
       <c r="L42" s="22" t="n"/>
       <c r="M42" s="7">
-        <f>IF(D42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$E$7,IF(E42="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B42="","",IFERROR(VLOOKUP(G42,Rate!$A$4:$E$7,IF(TRIM(E42)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N42" s="37">
-        <f>IF(D42="","",ROUND(IFERROR(J42*M42,0)*(F42="จ่ายแล้ว")*(P42&lt;&gt;"Y"),2))</f>
+        <f>IF(B42="","",ROUND(J42*M42*(TRIM(F42)="จ่ายแล้ว")*(P42&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O42" s="22" t="n"/>
@@ -2510,22 +2494,22 @@
       <c r="F43" s="18" t="n"/>
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="35">
-        <f>IF(D43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I43" s="19" t="n"/>
       <c r="J43" s="36">
-        <f>IF(D43="","",H43*(1-N(I43)))</f>
+        <f>IF(B43="","",H43*(1-N(I43)))</f>
         <v/>
       </c>
       <c r="K43" s="18" t="n"/>
       <c r="L43" s="18" t="n"/>
       <c r="M43" s="5">
-        <f>IF(D43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$E$7,IF(E43="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B43="","",IFERROR(VLOOKUP(G43,Rate!$A$4:$E$7,IF(TRIM(E43)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N43" s="37">
-        <f>IF(D43="","",ROUND(IFERROR(J43*M43,0)*(F43="จ่ายแล้ว")*(P43&lt;&gt;"Y"),2))</f>
+        <f>IF(B43="","",ROUND(J43*M43*(TRIM(F43)="จ่ายแล้ว")*(P43&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O43" s="18" t="n"/>
@@ -2545,22 +2529,22 @@
       <c r="F44" s="22" t="n"/>
       <c r="G44" s="22" t="n"/>
       <c r="H44" s="38">
-        <f>IF(D44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I44" s="23" t="n"/>
       <c r="J44" s="39">
-        <f>IF(D44="","",H44*(1-N(I44)))</f>
+        <f>IF(B44="","",H44*(1-N(I44)))</f>
         <v/>
       </c>
       <c r="K44" s="22" t="n"/>
       <c r="L44" s="22" t="n"/>
       <c r="M44" s="7">
-        <f>IF(D44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$E$7,IF(E44="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B44="","",IFERROR(VLOOKUP(G44,Rate!$A$4:$E$7,IF(TRIM(E44)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N44" s="37">
-        <f>IF(D44="","",ROUND(IFERROR(J44*M44,0)*(F44="จ่ายแล้ว")*(P44&lt;&gt;"Y"),2))</f>
+        <f>IF(B44="","",ROUND(J44*M44*(TRIM(F44)="จ่ายแล้ว")*(P44&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O44" s="22" t="n"/>
@@ -2580,22 +2564,22 @@
       <c r="F45" s="18" t="n"/>
       <c r="G45" s="18" t="n"/>
       <c r="H45" s="35">
-        <f>IF(D45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I45" s="19" t="n"/>
       <c r="J45" s="36">
-        <f>IF(D45="","",H45*(1-N(I45)))</f>
+        <f>IF(B45="","",H45*(1-N(I45)))</f>
         <v/>
       </c>
       <c r="K45" s="18" t="n"/>
       <c r="L45" s="18" t="n"/>
       <c r="M45" s="5">
-        <f>IF(D45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$E$7,IF(E45="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B45="","",IFERROR(VLOOKUP(G45,Rate!$A$4:$E$7,IF(TRIM(E45)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N45" s="37">
-        <f>IF(D45="","",ROUND(IFERROR(J45*M45,0)*(F45="จ่ายแล้ว")*(P45&lt;&gt;"Y"),2))</f>
+        <f>IF(B45="","",ROUND(J45*M45*(TRIM(F45)="จ่ายแล้ว")*(P45&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O45" s="18" t="n"/>
@@ -2615,22 +2599,22 @@
       <c r="F46" s="22" t="n"/>
       <c r="G46" s="22" t="n"/>
       <c r="H46" s="38">
-        <f>IF(D46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I46" s="23" t="n"/>
       <c r="J46" s="39">
-        <f>IF(D46="","",H46*(1-N(I46)))</f>
+        <f>IF(B46="","",H46*(1-N(I46)))</f>
         <v/>
       </c>
       <c r="K46" s="22" t="n"/>
       <c r="L46" s="22" t="n"/>
       <c r="M46" s="7">
-        <f>IF(D46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$E$7,IF(E46="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B46="","",IFERROR(VLOOKUP(G46,Rate!$A$4:$E$7,IF(TRIM(E46)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N46" s="37">
-        <f>IF(D46="","",ROUND(IFERROR(J46*M46,0)*(F46="จ่ายแล้ว")*(P46&lt;&gt;"Y"),2))</f>
+        <f>IF(B46="","",ROUND(J46*M46*(TRIM(F46)="จ่ายแล้ว")*(P46&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O46" s="22" t="n"/>
@@ -2650,22 +2634,22 @@
       <c r="F47" s="18" t="n"/>
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="35">
-        <f>IF(D47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I47" s="19" t="n"/>
       <c r="J47" s="36">
-        <f>IF(D47="","",H47*(1-N(I47)))</f>
+        <f>IF(B47="","",H47*(1-N(I47)))</f>
         <v/>
       </c>
       <c r="K47" s="18" t="n"/>
       <c r="L47" s="18" t="n"/>
       <c r="M47" s="5">
-        <f>IF(D47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$E$7,IF(E47="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B47="","",IFERROR(VLOOKUP(G47,Rate!$A$4:$E$7,IF(TRIM(E47)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N47" s="37">
-        <f>IF(D47="","",ROUND(IFERROR(J47*M47,0)*(F47="จ่ายแล้ว")*(P47&lt;&gt;"Y"),2))</f>
+        <f>IF(B47="","",ROUND(J47*M47*(TRIM(F47)="จ่ายแล้ว")*(P47&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O47" s="18" t="n"/>
@@ -2685,22 +2669,22 @@
       <c r="F48" s="22" t="n"/>
       <c r="G48" s="22" t="n"/>
       <c r="H48" s="38">
-        <f>IF(D48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I48" s="23" t="n"/>
       <c r="J48" s="39">
-        <f>IF(D48="","",H48*(1-N(I48)))</f>
+        <f>IF(B48="","",H48*(1-N(I48)))</f>
         <v/>
       </c>
       <c r="K48" s="22" t="n"/>
       <c r="L48" s="22" t="n"/>
       <c r="M48" s="7">
-        <f>IF(D48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$E$7,IF(E48="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B48="","",IFERROR(VLOOKUP(G48,Rate!$A$4:$E$7,IF(TRIM(E48)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N48" s="37">
-        <f>IF(D48="","",ROUND(IFERROR(J48*M48,0)*(F48="จ่ายแล้ว")*(P48&lt;&gt;"Y"),2))</f>
+        <f>IF(B48="","",ROUND(J48*M48*(TRIM(F48)="จ่ายแล้ว")*(P48&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O48" s="22" t="n"/>
@@ -2720,22 +2704,22 @@
       <c r="F49" s="18" t="n"/>
       <c r="G49" s="18" t="n"/>
       <c r="H49" s="35">
-        <f>IF(D49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I49" s="19" t="n"/>
       <c r="J49" s="36">
-        <f>IF(D49="","",H49*(1-N(I49)))</f>
+        <f>IF(B49="","",H49*(1-N(I49)))</f>
         <v/>
       </c>
       <c r="K49" s="18" t="n"/>
       <c r="L49" s="18" t="n"/>
       <c r="M49" s="5">
-        <f>IF(D49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$E$7,IF(E49="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B49="","",IFERROR(VLOOKUP(G49,Rate!$A$4:$E$7,IF(TRIM(E49)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N49" s="37">
-        <f>IF(D49="","",ROUND(IFERROR(J49*M49,0)*(F49="จ่ายแล้ว")*(P49&lt;&gt;"Y"),2))</f>
+        <f>IF(B49="","",ROUND(J49*M49*(TRIM(F49)="จ่ายแล้ว")*(P49&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O49" s="18" t="n"/>
@@ -2755,22 +2739,22 @@
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="22" t="n"/>
       <c r="H50" s="38">
-        <f>IF(D50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I50" s="23" t="n"/>
       <c r="J50" s="39">
-        <f>IF(D50="","",H50*(1-N(I50)))</f>
+        <f>IF(B50="","",H50*(1-N(I50)))</f>
         <v/>
       </c>
       <c r="K50" s="22" t="n"/>
       <c r="L50" s="22" t="n"/>
       <c r="M50" s="7">
-        <f>IF(D50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$E$7,IF(E50="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B50="","",IFERROR(VLOOKUP(G50,Rate!$A$4:$E$7,IF(TRIM(E50)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N50" s="37">
-        <f>IF(D50="","",ROUND(IFERROR(J50*M50,0)*(F50="จ่ายแล้ว")*(P50&lt;&gt;"Y"),2))</f>
+        <f>IF(B50="","",ROUND(J50*M50*(TRIM(F50)="จ่ายแล้ว")*(P50&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O50" s="22" t="n"/>
@@ -2790,22 +2774,22 @@
       <c r="F51" s="18" t="n"/>
       <c r="G51" s="18" t="n"/>
       <c r="H51" s="35">
-        <f>IF(D51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I51" s="19" t="n"/>
       <c r="J51" s="36">
-        <f>IF(D51="","",H51*(1-N(I51)))</f>
+        <f>IF(B51="","",H51*(1-N(I51)))</f>
         <v/>
       </c>
       <c r="K51" s="18" t="n"/>
       <c r="L51" s="18" t="n"/>
       <c r="M51" s="5">
-        <f>IF(D51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$E$7,IF(E51="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B51="","",IFERROR(VLOOKUP(G51,Rate!$A$4:$E$7,IF(TRIM(E51)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N51" s="37">
-        <f>IF(D51="","",ROUND(IFERROR(J51*M51,0)*(F51="จ่ายแล้ว")*(P51&lt;&gt;"Y"),2))</f>
+        <f>IF(B51="","",ROUND(J51*M51*(TRIM(F51)="จ่ายแล้ว")*(P51&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O51" s="18" t="n"/>
@@ -2825,22 +2809,22 @@
       <c r="F52" s="22" t="n"/>
       <c r="G52" s="22" t="n"/>
       <c r="H52" s="38">
-        <f>IF(D52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$B$7,2,FALSE),"NA"))</f>
+        <f>IF(B52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$B$7,2,FALSE),0))</f>
         <v/>
       </c>
       <c r="I52" s="23" t="n"/>
       <c r="J52" s="39">
-        <f>IF(D52="","",H52*(1-N(I52)))</f>
+        <f>IF(B52="","",H52*(1-N(I52)))</f>
         <v/>
       </c>
       <c r="K52" s="22" t="n"/>
       <c r="L52" s="22" t="n"/>
       <c r="M52" s="7">
-        <f>IF(D52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$E$7,IF(E52="ต่ออายุ",5,3),FALSE),"NA"))</f>
+        <f>IF(B52="","",IFERROR(VLOOKUP(G52,Rate!$A$4:$E$7,IF(TRIM(E52)="ต่ออายุ",5,3),FALSE),0))</f>
         <v/>
       </c>
       <c r="N52" s="37">
-        <f>IF(D52="","",ROUND(IFERROR(J52*M52,0)*(F52="จ่ายแล้ว")*(P52&lt;&gt;"Y"),2))</f>
+        <f>IF(B52="","",ROUND(J52*M52*(TRIM(F52)="จ่ายแล้ว")*(P52&lt;&gt;"Y"),2))</f>
         <v/>
       </c>
       <c r="O52" s="22" t="n"/>
@@ -2968,38 +2952,57 @@
       <formula>AND(B13="",D13&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E13:E52">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>AND(E13="",B13&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F13:F52">
-    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
-      <formula>AND(F13="",D13&lt;&gt;"")</formula>
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="0">
+      <formula>AND(F13="",B13&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13:G52">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="0">
+      <formula>AND(G13="",B13&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1" stopIfTrue="0">
+      <formula>G13="Enterprise"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13:K52">
+    <cfRule type="expression" priority="5" dxfId="0" stopIfTrue="0">
+      <formula>AND(K13="",B13&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation sqref="E13:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B13:B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="วันที่" error="วันที่ปี 2026 เท่านั้น" promptTitle="วันที่" prompt="วันที่ปีงบ 2026 (จำเป็น)" type="date" errorStyle="warning" operator="between">
+      <formula1>2026-01-01</formula1>
+      <formula2>2026-12-31</formula2>
+    </dataValidation>
+    <dataValidation sqref="E13:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="ใหม่ หรือ ต่ออายุ" type="list" errorStyle="warning">
       <formula1>"ใหม่,ต่ออายุ"</formula1>
     </dataValidation>
-    <dataValidation sqref="F13:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F13:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
       <formula1>"จ่ายแล้ว,รอจ่าย,รอเงินลูกค้า,ยกเลิก"</formula1>
     </dataValidation>
-    <dataValidation sqref="G13:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Starter,Plus,Premium,Enterprise"</formula1>
+    <dataValidation sqref="G13:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
+      <formula1>=Rate!$A$4:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"รายคน,ทีม"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O13:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"รอจ่าย,จ่ายแล้ว"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B13:B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="วันที่ไม่ถูกต้อง" error="ต้องเป็นวันที่ (เช่น 2026-06-23)" promptTitle="วันที่" prompt="จำเป็น — ถ้าว่าง ไตรมาส/รายได้จะ = 0" type="date" errorStyle="stop" operator="greaterThanOrEqual">
-      <formula1>2020-01-01</formula1>
-    </dataValidation>
-    <dataValidation sqref="I13:I52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ส่วนลดผิด" error="ส่วนลดต้อง 0–1 เช่น 0.1 = 10%" promptTitle="ส่วนลด %" prompt="ทศนิยม: 0.1 = 10%" type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="I13:I52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ส่วนลด" error="0–1 เช่น 0.1 = 10%" promptTitle="ส่วนลด %" prompt="ทศนิยม: 0.1 = 10%" type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="L13:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Sales" error="เลือกจากแท็บ ทีมขาย" type="list" errorStyle="stop">
-      <formula1>=ทีมขาย!$A$6:$A$20</formula1>
+    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
+      <formula1>"รายคน,ทีม"</formula1>
     </dataValidation>
-    <dataValidation sqref="P13:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Refund" error="Y = refund / N = ปกติ" promptTitle="Refund?" prompt="Y → ค่าคอมเป็น 0 อัตโนมัติ" type="list" errorStyle="stop">
+    <dataValidation sqref="L13:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
+      <formula1>=ทีมขาย!$A$6:$A$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="O13:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
+      <formula1>"รอจ่าย,จ่ายแล้ว"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P13:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Refund?" prompt="Y → ค่าคอม = 0" type="list" errorStyle="warning">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3532,10 +3535,21 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ตรวจสอบยอด (ต้อง = 0)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>ROUND(Sales_Record!N53-F21,2)</f>
+        <v/>
+      </c>
+    </row>
     <row r="24" ht="18" customHeight="1" s="59">
       <c r="A24" s="60" t="inlineStr">
         <is>
-          <t>หมายเหตุ / วิธีใช้</t>
+          <t>หมายเหตุ: ≠ 0 = ดีลหลุดจากทีม (เช็คคอลัมน์ K, L)</t>
         </is>
       </c>
       <c r="B24" s="83" t="n"/>
@@ -3597,6 +3611,11 @@
   <conditionalFormatting sqref="C21">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0" stopIfTrue="0">
       <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="0" stopIfTrue="0">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3744,7 +3763,7 @@
         </is>
       </c>
       <c r="B7" s="30" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="C7" s="29" t="n">
         <v>0.1</v>

--- a/EasyCRM/EasyCRM-Commission-System-2026.xlsx
+++ b/EasyCRM/EasyCRM-Commission-System-2026.xlsx
@@ -2975,37 +2975,6 @@
       <formula>AND(K13="",B13&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
-    <dataValidation sqref="B13:B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="วันที่" error="วันที่ปี 2026 เท่านั้น" promptTitle="วันที่" prompt="วันที่ปีงบ 2026 (จำเป็น)" type="date" errorStyle="warning" operator="between">
-      <formula1>2026-01-01</formula1>
-      <formula2>2026-12-31</formula2>
-    </dataValidation>
-    <dataValidation sqref="E13:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="ใหม่ หรือ ต่ออายุ" type="list" errorStyle="warning">
-      <formula1>"ใหม่,ต่ออายุ"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F13:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>"จ่ายแล้ว,รอจ่าย,รอเงินลูกค้า,ยกเลิก"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G13:G52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>=Rate!$A$4:$A$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="I13:I52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ส่วนลด" error="0–1 เช่น 0.1 = 10%" promptTitle="ส่วนลด %" prompt="ทศนิยม: 0.1 = 10%" type="decimal" errorStyle="stop" operator="between">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation sqref="K13:K52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>"รายคน,ทีม"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L13:L52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>=ทีมขาย!$A$6:$A$8</formula1>
-    </dataValidation>
-    <dataValidation sqref="O13:O52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="warning">
-      <formula1>"รอจ่าย,จ่ายแล้ว"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P13:P52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Refund?" prompt="Y → ค่าคอม = 0" type="list" errorStyle="warning">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
